--- a/documentos/EVALUACIONES MNM 2025.xlsx
+++ b/documentos/EVALUACIONES MNM 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raúl\Dropbox (Personal)\2025\RESPALDO DE BASE DE DATOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\LandingPage\Landing_MNM\documentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D4E792-774C-4615-B169-02422A66A00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89F6C9E-C50A-4246-8EFB-D337CBC6AD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORTE" sheetId="5" r:id="rId1"/>
@@ -20,9 +20,9 @@
     <sheet name="EQUIPO" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11" hidden="1">NIVEL_1[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21" hidden="1">NIVEL_2[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31" hidden="1">NIVEL_3[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1" hidden="1">NIVEL_1[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2" hidden="1">NIVEL_2[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3" hidden="1">NIVEL_3[]</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">EQUIPO!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'NIVEL 1'!$F$129:$O$163</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'NIVEL 2'!$F$112:$O$133</definedName>
@@ -90,7 +90,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -99,7 +99,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_2">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -108,7 +108,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_3">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -11932,7 +11932,7 @@
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>480060</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>172</xdr:row>
       <xdr:rowOff>135255</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -12289,7 +12289,13 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O163" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63" tableBorderDxfId="62">
-  <autoFilter ref="A2:O163" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
+  <autoFilter ref="A2:O163" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Alanna Sofía Barreiro Garcés"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O163">
     <sortCondition ref="D3:D107"/>
     <sortCondition ref="A3:A107"/>
@@ -12689,14 +12695,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2031510B-662C-4B68-8770-DE372FF29377}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -12726,7 +12732,7 @@
       </c>
       <c r="J1" s="16"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
@@ -12763,7 +12769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>36</v>
       </c>
@@ -12800,7 +12806,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>37</v>
       </c>
@@ -12837,7 +12843,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>38</v>
       </c>
@@ -12874,7 +12880,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>39</v>
       </c>
@@ -12911,7 +12917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>40</v>
       </c>
@@ -12948,7 +12954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>41</v>
       </c>
@@ -12985,7 +12991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>42</v>
       </c>
@@ -13022,7 +13028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>43</v>
       </c>
@@ -13059,7 +13065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>44</v>
       </c>
@@ -13096,7 +13102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>45</v>
       </c>
@@ -13133,7 +13139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>46</v>
       </c>
@@ -13189,25 +13195,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O163"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" style="1" customWidth="1"/>
-    <col min="12" max="13" width="6.33203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="6.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" style="1" customWidth="1"/>
+    <col min="12" max="13" width="6.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="6.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E1" s="25" t="s">
         <v>48</v>
       </c>
@@ -13224,7 +13230,7 @@
       <c r="N1" s="33"/>
       <c r="O1" s="34"/>
     </row>
-    <row r="2" spans="1:15" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>62</v>
       </c>
@@ -13271,7 +13277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13323,7 +13329,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13375,7 +13381,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13427,7 +13433,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13479,7 +13485,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13531,7 +13537,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13583,7 +13589,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13635,7 +13641,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13687,7 +13693,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13739,7 +13745,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13791,7 +13797,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13843,7 +13849,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13895,7 +13901,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13947,7 +13953,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13999,7 +14005,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14051,7 +14057,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14103,7 +14109,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14155,7 +14161,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14207,7 +14213,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14259,7 +14265,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14311,7 +14317,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14363,7 +14369,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14415,7 +14421,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14467,7 +14473,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14519,7 +14525,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14571,7 +14577,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14623,7 +14629,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14675,7 +14681,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14727,7 +14733,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14779,7 +14785,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14831,7 +14837,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14883,7 +14889,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14935,7 +14941,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14987,7 +14993,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15039,7 +15045,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15091,7 +15097,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15143,7 +15149,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15195,7 +15201,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15247,7 +15253,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15299,7 +15305,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15351,7 +15357,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15403,7 +15409,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15455,7 +15461,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15507,7 +15513,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15559,7 +15565,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15611,7 +15617,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15663,7 +15669,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15715,7 +15721,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15767,7 +15773,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15819,7 +15825,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15871,7 +15877,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15923,7 +15929,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15975,7 +15981,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16027,7 +16033,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16079,7 +16085,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16131,7 +16137,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16183,7 +16189,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16235,7 +16241,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16287,7 +16293,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16339,7 +16345,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16391,7 +16397,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16443,7 +16449,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16495,7 +16501,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16547,7 +16553,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16599,7 +16605,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16651,7 +16657,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16703,7 +16709,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16755,7 +16761,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16807,7 +16813,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16859,7 +16865,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16911,7 +16917,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16963,7 +16969,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17015,7 +17021,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17067,7 +17073,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17119,7 +17125,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17171,7 +17177,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17223,7 +17229,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17275,7 +17281,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17327,7 +17333,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17379,7 +17385,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17431,7 +17437,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17483,7 +17489,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17535,7 +17541,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17587,7 +17593,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17639,7 +17645,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17691,7 +17697,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17743,7 +17749,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17795,7 +17801,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17847,7 +17853,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17899,7 +17905,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17951,7 +17957,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18003,7 +18009,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18055,7 +18061,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18107,7 +18113,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18159,7 +18165,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18211,7 +18217,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18263,7 +18269,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18315,7 +18321,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18367,7 +18373,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18419,7 +18425,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18471,7 +18477,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18523,7 +18529,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18575,7 +18581,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18627,7 +18633,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18679,7 +18685,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18731,7 +18737,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -18783,7 +18789,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -18835,7 +18841,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -18887,7 +18893,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -18939,7 +18945,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -18991,7 +18997,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19043,7 +19049,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19095,7 +19101,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19147,7 +19153,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19199,7 +19205,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19251,7 +19257,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19303,7 +19309,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19355,7 +19361,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19407,7 +19413,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19459,7 +19465,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19511,7 +19517,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19563,7 +19569,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19615,7 +19621,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19667,7 +19673,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19719,7 +19725,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19771,7 +19777,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19823,7 +19829,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -19875,7 +19881,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -19927,7 +19933,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -19979,7 +19985,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20031,7 +20037,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20083,7 +20089,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20135,7 +20141,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20187,7 +20193,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20239,7 +20245,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20291,7 +20297,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20343,7 +20349,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20395,7 +20401,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20447,7 +20453,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20499,7 +20505,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20551,7 +20557,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20603,7 +20609,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20655,7 +20661,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20707,7 +20713,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20759,7 +20765,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20811,7 +20817,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20863,7 +20869,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20915,7 +20921,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20967,7 +20973,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21019,7 +21025,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21071,7 +21077,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21123,7 +21129,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21175,7 +21181,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21227,7 +21233,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21279,7 +21285,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21331,7 +21337,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21383,7 +21389,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21435,7 +21441,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21487,7 +21493,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21539,7 +21545,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21591,7 +21597,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21639,7 +21645,7 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O163" s="18" t="str">
-        <f t="shared" ref="O163:O194" si="5">IF(N163=" "," ",IF(N163&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" ref="O163" si="5">IF(N163=" "," ",IF(N163&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -21668,28 +21674,28 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O133"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.44140625" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" customWidth="1"/>
-    <col min="5" max="5" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" customWidth="1"/>
-    <col min="12" max="12" width="6.33203125" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" customWidth="1"/>
-    <col min="14" max="14" width="7.109375" customWidth="1"/>
-    <col min="15" max="15" width="15.6640625" customWidth="1"/>
-    <col min="16" max="16" width="15.33203125" customWidth="1"/>
-    <col min="17" max="17" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" customWidth="1"/>
+    <col min="12" max="12" width="6.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C1" s="3"/>
       <c r="E1" s="25" t="s">
         <v>59</v>
@@ -21707,7 +21713,7 @@
       <c r="N1" s="35"/>
       <c r="O1" s="34"/>
     </row>
-    <row r="2" spans="1:15" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>62</v>
       </c>
@@ -21754,7 +21760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -21806,7 +21812,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -21858,7 +21864,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -21910,7 +21916,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -21962,7 +21968,7 @@
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22014,7 +22020,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22066,7 +22072,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22118,7 +22124,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22170,7 +22176,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22222,7 +22228,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22274,7 +22280,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22326,7 +22332,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22378,7 +22384,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22430,7 +22436,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22482,7 +22488,7 @@
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22534,7 +22540,7 @@
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22586,7 +22592,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22638,7 +22644,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22690,7 +22696,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22742,7 +22748,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22794,7 +22800,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -22846,7 +22852,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -22898,7 +22904,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -22950,7 +22956,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23002,7 +23008,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23054,7 +23060,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23106,7 +23112,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23158,7 +23164,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23210,7 +23216,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23262,7 +23268,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23314,7 +23320,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23366,7 +23372,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23418,7 +23424,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23470,7 +23476,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23522,7 +23528,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23574,7 +23580,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23626,7 +23632,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23678,7 +23684,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23730,7 +23736,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23782,7 +23788,7 @@
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23834,7 +23840,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23886,7 +23892,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23938,7 +23944,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23990,7 +23996,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -24042,7 +24048,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -24094,7 +24100,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -24146,7 +24152,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -24198,7 +24204,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -24250,7 +24256,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24302,7 +24308,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24354,7 +24360,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24406,7 +24412,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24458,7 +24464,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24510,7 +24516,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24562,7 +24568,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24614,7 +24620,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24666,7 +24672,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24718,7 +24724,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24770,7 +24776,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24822,7 +24828,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24874,7 +24880,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24926,7 +24932,7 @@
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24978,7 +24984,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25030,7 +25036,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25082,7 +25088,7 @@
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25134,7 +25140,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25186,7 +25192,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25238,7 +25244,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25290,7 +25296,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25342,7 +25348,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25394,7 +25400,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25446,7 +25452,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25498,7 +25504,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25550,7 +25556,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25602,7 +25608,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25654,7 +25660,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25706,7 +25712,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25758,7 +25764,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25810,7 +25816,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25862,7 +25868,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25914,7 +25920,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25966,7 +25972,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26018,7 +26024,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26070,7 +26076,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26122,7 +26128,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26174,7 +26180,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26226,7 +26232,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26278,7 +26284,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26330,7 +26336,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26382,7 +26388,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26434,7 +26440,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26486,7 +26492,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26538,7 +26544,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26590,7 +26596,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26642,7 +26648,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26694,7 +26700,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26746,7 +26752,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26798,7 +26804,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26850,7 +26856,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26902,7 +26908,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -26954,7 +26960,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27006,7 +27012,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27058,7 +27064,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27110,7 +27116,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27162,7 +27168,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27214,7 +27220,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27266,7 +27272,7 @@
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27318,7 +27324,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27370,7 +27376,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27422,7 +27428,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27474,7 +27480,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27526,7 +27532,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27578,7 +27584,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27630,7 +27636,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27682,7 +27688,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27734,7 +27740,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27786,7 +27792,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27838,7 +27844,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27890,7 +27896,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27942,7 +27948,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27994,7 +28000,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28046,7 +28052,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28098,7 +28104,7 @@
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28150,7 +28156,7 @@
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28202,7 +28208,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28254,7 +28260,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28306,7 +28312,7 @@
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28358,7 +28364,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28410,7 +28416,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28458,11 +28464,11 @@
         <v>4</v>
       </c>
       <c r="O131" s="18" t="str">
-        <f t="shared" ref="O131:O162" si="4">IF(N131=" "," ",IF(N131&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" ref="O131:O133" si="4">IF(N131=" "," ",IF(N131&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28514,7 +28520,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28591,31 +28597,31 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="2" customWidth="1"/>
-    <col min="7" max="7" width="7.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.33203125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="7.88671875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.33203125" style="2" customWidth="1"/>
-    <col min="16" max="17" width="5.5546875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="6.44140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="7.33203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="5.6640625" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.28515625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.85546875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.28515625" style="2" customWidth="1"/>
+    <col min="16" max="17" width="5.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="6.42578125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="7.28515625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="5.7109375" customWidth="1"/>
+    <col min="21" max="21" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="E1" s="28" t="s">
         <v>60</v>
       </c>
@@ -28636,7 +28642,7 @@
       <c r="R1" s="31"/>
       <c r="S1" s="31"/>
     </row>
-    <row r="2" spans="1:21" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>62</v>
       </c>
@@ -28701,7 +28707,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -28771,7 +28777,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -28841,7 +28847,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -28911,7 +28917,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -28981,7 +28987,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -29051,7 +29057,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -29121,7 +29127,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="29">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -29191,7 +29197,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -29261,7 +29267,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29331,7 +29337,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29401,7 +29407,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29471,7 +29477,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29541,7 +29547,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29611,7 +29617,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29681,7 +29687,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29751,7 +29757,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29821,7 +29827,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29891,7 +29897,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29961,7 +29967,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -30031,7 +30037,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -30101,7 +30107,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -30171,7 +30177,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -30241,7 +30247,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -30311,7 +30317,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -30381,7 +30387,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -30451,7 +30457,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -30521,7 +30527,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -30591,7 +30597,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -30661,7 +30667,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -30731,7 +30737,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -30801,7 +30807,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -30871,7 +30877,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -30941,7 +30947,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31011,7 +31017,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31081,7 +31087,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31168,15 +31174,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:D38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5546875" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
@@ -31190,7 +31196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="26">
         <v>2</v>
       </c>
@@ -31204,7 +31210,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>2</v>
       </c>
@@ -31218,7 +31224,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <v>2</v>
       </c>
@@ -31232,7 +31238,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="26">
         <v>2</v>
       </c>
@@ -31246,7 +31252,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
         <v>2</v>
       </c>
@@ -31260,7 +31266,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
         <v>2</v>
       </c>
@@ -31274,7 +31280,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
         <v>2</v>
       </c>
@@ -31288,7 +31294,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="26">
         <v>2</v>
       </c>
@@ -31302,7 +31308,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="26">
         <v>2</v>
       </c>
@@ -31316,7 +31322,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="26">
         <v>2</v>
       </c>
@@ -31330,7 +31336,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="26">
         <v>2</v>
       </c>
@@ -31344,7 +31350,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="26">
         <v>2</v>
       </c>
@@ -31358,7 +31364,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="26">
         <v>2</v>
       </c>
@@ -31372,7 +31378,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="26">
         <v>3</v>
       </c>
@@ -31386,7 +31392,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="26">
         <v>3</v>
       </c>
@@ -31400,7 +31406,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="26">
         <v>3</v>
       </c>
@@ -31414,7 +31420,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="26">
         <v>3</v>
       </c>
@@ -31428,7 +31434,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="26">
         <v>3</v>
       </c>
@@ -31442,7 +31448,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="26">
         <v>3</v>
       </c>
@@ -31456,7 +31462,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="26">
         <v>3</v>
       </c>
@@ -31470,7 +31476,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="26">
         <v>3</v>
       </c>
@@ -31484,7 +31490,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="26">
         <v>3</v>
       </c>
@@ -31498,7 +31504,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="26">
         <v>3</v>
       </c>
@@ -31512,7 +31518,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="26">
         <v>3</v>
       </c>
@@ -31526,7 +31532,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="26">
         <v>3</v>
       </c>
@@ -31540,7 +31546,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="26">
         <v>3</v>
       </c>
@@ -31554,7 +31560,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="26">
         <v>4</v>
       </c>
@@ -31568,7 +31574,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="26">
         <v>4</v>
       </c>
@@ -31582,7 +31588,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="26">
         <v>4</v>
       </c>
@@ -31596,7 +31602,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="26">
         <v>4</v>
       </c>
@@ -31610,7 +31616,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="26">
         <v>4</v>
       </c>
@@ -31624,7 +31630,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="26">
         <v>4</v>
       </c>
@@ -31638,7 +31644,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="26">
         <v>4</v>
       </c>
@@ -31652,7 +31658,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="26">
         <v>4</v>
       </c>
@@ -31666,7 +31672,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="26">
         <v>4</v>
       </c>
@@ -31680,7 +31686,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="26">
         <v>4</v>
       </c>

--- a/documentos/EVALUACIONES MNM 2025.xlsx
+++ b/documentos/EVALUACIONES MNM 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\LandingPage\Landing_MNM\documentos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raúl\Dropbox (Personal)\2025\RESPALDO DE BASE DE DATOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89F6C9E-C50A-4246-8EFB-D337CBC6AD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCE9CD2-CF0D-4168-87A5-22C08116E03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORTE" sheetId="5" r:id="rId1"/>
@@ -20,13 +20,13 @@
     <sheet name="EQUIPO" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1" hidden="1">NIVEL_1[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2" hidden="1">NIVEL_2[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3" hidden="1">NIVEL_3[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11" hidden="1">NIVEL_1[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21" hidden="1">NIVEL_2[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31" hidden="1">NIVEL_3[]</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">EQUIPO!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'NIVEL 1'!$F$129:$O$163</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'NIVEL 2'!$F$112:$O$133</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'NIVEL 3'!$F$34:$U$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'NIVEL 1'!$F$164:$O$187</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'NIVEL 2'!$F$134:$N$156</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'NIVEL 3'!$F$38:$U$41</definedName>
     <definedName name="SegmentaciónDeDatos_MES">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_NOMBRE_DEL_ALUMNO">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_NOMBRE_DEL_ALUMNO1">#N/A</definedName>
@@ -90,7 +90,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -99,7 +99,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_2">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -108,7 +108,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_3">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="219">
   <si>
     <t>NOMBRE DEL ALUMNO</t>
   </si>
@@ -861,6 +861,27 @@
   <si>
     <t>Tomas Sossa Ayala</t>
   </si>
+  <si>
+    <t>Isabel Sofia Negrete Viloria</t>
+  </si>
+  <si>
+    <t>Gabriel Perez</t>
+  </si>
+  <si>
+    <t>Sarath Milena Valencia Agudelo</t>
+  </si>
+  <si>
+    <t>Jesus David Mendoza</t>
+  </si>
+  <si>
+    <t>Yeison Daniel Zuluaga Marin</t>
+  </si>
+  <si>
+    <t>Luis Enrique Garces Carrascal</t>
+  </si>
+  <si>
+    <t>Jose Alejandro Peña Angulo</t>
+  </si>
 </sst>
 </file>
 
@@ -992,7 +1013,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1115,147 +1136,53 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="76">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2682,6 +2609,142 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -2970,7 +3033,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3219,7 +3282,7 @@
                   <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -3422,7 +3485,7 @@
                   <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -3625,7 +3688,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -4028,7 +4091,7 @@
                         <c:v>61</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>51</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -4196,7 +4259,7 @@
                         <c:v>3</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>9</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -4537,7 +4600,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -4726,7 +4789,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4975,7 +5038,7 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -5340,7 +5403,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -5521,7 +5584,7 @@
                         <c:v>61</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>51</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -5689,7 +5752,7 @@
                         <c:v>35</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>24</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -5862,7 +5925,7 @@
                         <c:v>22</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>23</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -6035,7 +6098,7 @@
                         <c:v>4</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>4</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -6456,7 +6519,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6710,7 +6773,7 @@
                   <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6896,7 +6959,7 @@
                         <c:v>35</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>24</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -7069,7 +7132,7 @@
                         <c:v>3</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>9</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -7242,7 +7305,7 @@
                         <c:v>22</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>23</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -7588,7 +7651,7 @@
                         <c:v>4</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>4</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -7761,7 +7824,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -8178,7 +8241,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11932,7 +11995,7 @@
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>480060</xdr:colOff>
-      <xdr:row>172</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>135255</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -12288,43 +12351,37 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O163" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63" tableBorderDxfId="62">
-  <autoFilter ref="A2:O163" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Alanna Sofía Barreiro Garcés"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O163">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O187" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57" tableBorderDxfId="56">
+  <autoFilter ref="A2:O187" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O187">
     <sortCondition ref="D3:D107"/>
     <sortCondition ref="A3:A107"/>
     <sortCondition ref="F3:F107"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="61">
+    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="55">
       <calculatedColumnFormula>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="60">
+    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="54">
       <calculatedColumnFormula>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="59">
+    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="53">
       <calculatedColumnFormula>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="56"/>
-    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="51"/>
-    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="50"/>
-    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="49"/>
-    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="48">
+    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="45"/>
+    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="44"/>
+    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="43"/>
+    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="42">
       <calculatedColumnFormula>AVERAGE('NIVEL 1'!G3:M3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="47">
+    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="41">
       <calculatedColumnFormula>IF(N3=" "," ",IF(N3&gt;=4.7,"CAMBIA A NIVEL 2"," "))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12333,36 +12390,36 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O133" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
-  <autoFilter ref="A2:O133" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O133">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O156" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
+  <autoFilter ref="A2:O156" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O156">
     <sortCondition ref="A3:A101"/>
     <sortCondition ref="F3:F101"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="44">
+    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="38">
       <calculatedColumnFormula>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="43">
+    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="37">
       <calculatedColumnFormula>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="42">
+    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="36">
       <calculatedColumnFormula>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="31">
+    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="27"/>
+    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="25">
       <calculatedColumnFormula>AVERAGE('NIVEL 2'!G3:M3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="30">
+    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="24">
       <calculatedColumnFormula>IF(N3=" "," ",IF(N3&gt;=4.7,"CAMBIA A NIVEL 3"," "))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12371,42 +12428,42 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U37" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" tableBorderDxfId="27">
-  <autoFilter ref="A2:U37" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U41" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
+  <autoFilter ref="A2:U41" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U41">
     <sortCondition ref="A3"/>
     <sortCondition ref="F3"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="26">
+    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="20">
       <calculatedColumnFormula>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="25">
+    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="19">
       <calculatedColumnFormula>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="24">
+    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="18">
       <calculatedColumnFormula>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="13"/>
-    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="11"/>
-    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="7">
+    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="1">
       <calculatedColumnFormula>AVERAGE('NIVEL 3'!G3:S3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="6">
+    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="0">
       <calculatedColumnFormula>IF(T3=" "," ",IF(T3&gt;=4.9,"CAMBIA A EQUIPO"," "))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12415,17 +12472,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D38" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D38" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
   <autoFilter ref="A2:D38" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D33">
     <sortCondition ref="A3"/>
     <sortCondition ref="D3"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="3"/>
-    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="62"/>
+    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="59"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12695,14 +12752,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2031510B-662C-4B68-8770-DE372FF29377}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -12732,7 +12789,7 @@
       </c>
       <c r="J1" s="16"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
@@ -12769,7 +12826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>36</v>
       </c>
@@ -12806,7 +12863,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>37</v>
       </c>
@@ -12843,7 +12900,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>38</v>
       </c>
@@ -12880,7 +12937,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>39</v>
       </c>
@@ -12917,7 +12974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>40</v>
       </c>
@@ -12954,7 +13011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>41</v>
       </c>
@@ -12991,25 +13048,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>42</v>
       </c>
       <c r="B9" s="17">
         <f>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="C9" s="17">
         <f>COUNTIF('NIVEL 1'!$C:$C,REPORTE!A9)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D9" s="17">
         <f>COUNTIFS('NIVEL 1'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$O:$O,"CAMBIA A NIVEL 2")</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E9" s="17">
         <f>COUNTIF('NIVEL 2'!$C:$C,REPORTE!A9)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F9" s="17">
         <f>COUNTIFS('NIVEL 2'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$O:$O,"CAMBIA A NIVEL 3")</f>
@@ -13017,18 +13074,18 @@
       </c>
       <c r="G9" s="17">
         <f>COUNTIF('NIVEL 3'!$C:$C,REPORTE!A9)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" s="17">
         <f>COUNTIFS('NIVEL 3'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$U:$U,"CAMBIA A EQUIPO")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="17">
         <f>COUNTIF(EQUIPO!$C:$C,REPORTE!A9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>43</v>
       </c>
@@ -13065,7 +13122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>44</v>
       </c>
@@ -13102,7 +13159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>45</v>
       </c>
@@ -13139,7 +13196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>46</v>
       </c>
@@ -13194,26 +13251,26 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O163"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O187"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="10" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.44140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.85546875" style="1" customWidth="1"/>
-    <col min="12" max="13" width="6.28515625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="6.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" style="1" customWidth="1"/>
+    <col min="12" max="13" width="6.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="6.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E1" s="25" t="s">
         <v>48</v>
       </c>
@@ -13230,7 +13287,7 @@
       <c r="N1" s="33"/>
       <c r="O1" s="34"/>
     </row>
-    <row r="2" spans="1:15" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>62</v>
       </c>
@@ -13277,7 +13334,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13325,11 +13382,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O3" s="18" t="str">
-        <f t="shared" ref="O3:O34" si="0">IF(N3=" "," ",IF(N3&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f>IF(N3=" "," ",IF(N3&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13377,11 +13434,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O4" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N4=" "," ",IF(N4&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13429,11 +13486,11 @@
         <v>2.7142857142857144</v>
       </c>
       <c r="O5" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N5=" "," ",IF(N5&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13481,11 +13538,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O6" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N6=" "," ",IF(N6&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13533,11 +13590,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O7" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N7=" "," ",IF(N7&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13585,11 +13642,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O8" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N8=" "," ",IF(N8&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13637,11 +13694,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O9" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N9=" "," ",IF(N9&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13689,11 +13746,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O10" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N10=" "," ",IF(N10&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13741,11 +13798,11 @@
         <v>5</v>
       </c>
       <c r="O11" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N11=" "," ",IF(N11&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13793,11 +13850,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O12" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N12=" "," ",IF(N12&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13845,11 +13902,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O13" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N13=" "," ",IF(N13&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13897,11 +13954,11 @@
         <v>5</v>
       </c>
       <c r="O14" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N14=" "," ",IF(N14&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13949,11 +14006,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O15" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N15=" "," ",IF(N15&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14001,11 +14058,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O16" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N16=" "," ",IF(N16&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14053,11 +14110,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O17" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N17=" "," ",IF(N17&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14105,11 +14162,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O18" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N18=" "," ",IF(N18&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14157,11 +14214,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O19" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N19=" "," ",IF(N19&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14209,11 +14266,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O20" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N20=" "," ",IF(N20&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14261,11 +14318,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O21" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N21=" "," ",IF(N21&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14313,11 +14370,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O22" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N22=" "," ",IF(N22&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14365,11 +14422,11 @@
         <v>2.7142857142857144</v>
       </c>
       <c r="O23" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N23=" "," ",IF(N23&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14417,11 +14474,11 @@
         <v>3</v>
       </c>
       <c r="O24" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N24=" "," ",IF(N24&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14469,11 +14526,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O25" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N25=" "," ",IF(N25&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14521,11 +14578,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O26" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N26=" "," ",IF(N26&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14573,11 +14630,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O27" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N27=" "," ",IF(N27&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14625,11 +14682,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O28" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N28=" "," ",IF(N28&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14677,11 +14734,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O29" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N29=" "," ",IF(N29&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14729,11 +14786,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O30" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N30=" "," ",IF(N30&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14781,11 +14838,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O31" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N31=" "," ",IF(N31&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14833,11 +14890,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O32" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N32=" "," ",IF(N32&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14885,11 +14942,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O33" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N33=" "," ",IF(N33&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14937,11 +14994,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O34" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N34=" "," ",IF(N34&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14989,11 +15046,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="O35" s="18" t="str">
-        <f t="shared" ref="O35:O66" si="1">IF(N35=" "," ",IF(N35&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f>IF(N35=" "," ",IF(N35&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15041,11 +15098,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O36" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N36=" "," ",IF(N36&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15093,11 +15150,11 @@
         <v>4</v>
       </c>
       <c r="O37" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N37=" "," ",IF(N37&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15145,11 +15202,11 @@
         <v>5</v>
       </c>
       <c r="O38" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N38=" "," ",IF(N38&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15197,11 +15254,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O39" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N39=" "," ",IF(N39&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15249,11 +15306,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O40" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N40=" "," ",IF(N40&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15301,11 +15358,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O41" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N41=" "," ",IF(N41&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15353,11 +15410,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O42" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N42=" "," ",IF(N42&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15405,11 +15462,11 @@
         <v>4</v>
       </c>
       <c r="O43" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N43=" "," ",IF(N43&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15457,11 +15514,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O44" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N44=" "," ",IF(N44&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15509,11 +15566,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O45" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N45=" "," ",IF(N45&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15561,11 +15618,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O46" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N46=" "," ",IF(N46&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15613,11 +15670,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O47" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N47=" "," ",IF(N47&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15665,11 +15722,11 @@
         <v>5</v>
       </c>
       <c r="O48" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N48=" "," ",IF(N48&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15717,11 +15774,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O49" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N49=" "," ",IF(N49&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15769,11 +15826,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O50" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N50=" "," ",IF(N50&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15821,11 +15878,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O51" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N51=" "," ",IF(N51&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15873,11 +15930,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O52" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N52=" "," ",IF(N52&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15925,11 +15982,11 @@
         <v>5</v>
       </c>
       <c r="O53" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N53=" "," ",IF(N53&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15977,11 +16034,11 @@
         <v>3</v>
       </c>
       <c r="O54" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N54=" "," ",IF(N54&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16029,11 +16086,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O55" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N55=" "," ",IF(N55&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16081,11 +16138,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O56" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N56=" "," ",IF(N56&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16133,11 +16190,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O57" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N57=" "," ",IF(N57&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16185,11 +16242,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O58" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N58=" "," ",IF(N58&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16237,11 +16294,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O59" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N59=" "," ",IF(N59&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16289,11 +16346,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O60" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N60=" "," ",IF(N60&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16341,11 +16398,11 @@
         <v>5</v>
       </c>
       <c r="O61" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N61=" "," ",IF(N61&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16393,11 +16450,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O62" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N62=" "," ",IF(N62&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16445,11 +16502,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O63" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N63=" "," ",IF(N63&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16497,11 +16554,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O64" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N64=" "," ",IF(N64&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16549,11 +16606,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O65" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N65=" "," ",IF(N65&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16601,11 +16658,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O66" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N66=" "," ",IF(N66&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16653,11 +16710,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O67" s="18" t="str">
-        <f t="shared" ref="O67:O98" si="2">IF(N67=" "," ",IF(N67&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f>IF(N67=" "," ",IF(N67&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16705,11 +16762,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O68" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N68=" "," ",IF(N68&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16757,11 +16814,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O69" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N69=" "," ",IF(N69&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16809,11 +16866,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O70" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N70=" "," ",IF(N70&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16861,11 +16918,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O71" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N71=" "," ",IF(N71&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16913,11 +16970,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O72" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N72=" "," ",IF(N72&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16965,11 +17022,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O73" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N73=" "," ",IF(N73&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17017,11 +17074,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O74" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N74=" "," ",IF(N74&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17069,11 +17126,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O75" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N75=" "," ",IF(N75&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17121,11 +17178,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O76" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N76=" "," ",IF(N76&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17173,11 +17230,11 @@
         <v>1.8571428571428572</v>
       </c>
       <c r="O77" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N77=" "," ",IF(N77&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17225,11 +17282,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O78" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N78=" "," ",IF(N78&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17277,11 +17334,11 @@
         <v>2.7142857142857144</v>
       </c>
       <c r="O79" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N79=" "," ",IF(N79&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17329,11 +17386,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O80" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N80=" "," ",IF(N80&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17381,11 +17438,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O81" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N81=" "," ",IF(N81&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17433,11 +17490,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O82" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N82=" "," ",IF(N82&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17485,11 +17542,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O83" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N83=" "," ",IF(N83&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17537,11 +17594,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O84" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N84=" "," ",IF(N84&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17589,11 +17646,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O85" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N85=" "," ",IF(N85&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17641,11 +17698,11 @@
         <v>4.2857142857142856</v>
       </c>
       <c r="O86" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N86=" "," ",IF(N86&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17693,11 +17750,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O87" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N87=" "," ",IF(N87&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17745,11 +17802,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O88" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N88=" "," ",IF(N88&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17797,11 +17854,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O89" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N89=" "," ",IF(N89&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17849,11 +17906,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O90" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N90=" "," ",IF(N90&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17901,11 +17958,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O91" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N91=" "," ",IF(N91&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17953,11 +18010,11 @@
         <v>3</v>
       </c>
       <c r="O92" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N92=" "," ",IF(N92&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18005,11 +18062,11 @@
         <v>5</v>
       </c>
       <c r="O93" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N93=" "," ",IF(N93&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18057,11 +18114,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O94" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N94=" "," ",IF(N94&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18109,11 +18166,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O95" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N95=" "," ",IF(N95&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18161,11 +18218,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O96" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N96=" "," ",IF(N96&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18213,11 +18270,11 @@
         <v>2.1428571428571428</v>
       </c>
       <c r="O97" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N97=" "," ",IF(N97&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18265,11 +18322,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O98" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N98=" "," ",IF(N98&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18317,11 +18374,11 @@
         <v>5</v>
       </c>
       <c r="O99" s="18" t="str">
-        <f t="shared" ref="O99:O130" si="3">IF(N99=" "," ",IF(N99&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f>IF(N99=" "," ",IF(N99&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18369,11 +18426,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O100" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N100=" "," ",IF(N100&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18421,11 +18478,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O101" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N101=" "," ",IF(N101&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18473,11 +18530,11 @@
         <v>4.8571428571428568</v>
       </c>
       <c r="O102" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N102=" "," ",IF(N102&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18525,11 +18582,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O103" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N103=" "," ",IF(N103&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18577,11 +18634,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O104" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N104=" "," ",IF(N104&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18629,11 +18686,11 @@
         <v>4</v>
       </c>
       <c r="O105" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N105=" "," ",IF(N105&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18681,11 +18738,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O106" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N106=" "," ",IF(N106&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18733,11 +18790,11 @@
         <v>2.7142857142857144</v>
       </c>
       <c r="O107" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N107=" "," ",IF(N107&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -18785,11 +18842,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O108" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N108=" "," ",IF(N108&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -18837,11 +18894,11 @@
         <v>5</v>
       </c>
       <c r="O109" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N109=" "," ",IF(N109&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -18889,11 +18946,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O110" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N110=" "," ",IF(N110&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -18941,11 +18998,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O111" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N111=" "," ",IF(N111&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -18993,11 +19050,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O112" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N112=" "," ",IF(N112&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19045,11 +19102,11 @@
         <v>5</v>
       </c>
       <c r="O113" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N113=" "," ",IF(N113&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19097,11 +19154,11 @@
         <v>5</v>
       </c>
       <c r="O114" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N114=" "," ",IF(N114&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19149,11 +19206,11 @@
         <v>5</v>
       </c>
       <c r="O115" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N115=" "," ",IF(N115&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19201,11 +19258,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O116" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N116=" "," ",IF(N116&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19253,11 +19310,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O117" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N117=" "," ",IF(N117&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19305,11 +19362,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O118" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N118=" "," ",IF(N118&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19357,11 +19414,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O119" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N119=" "," ",IF(N119&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19409,11 +19466,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O120" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N120=" "," ",IF(N120&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19461,11 +19518,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O121" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N121=" "," ",IF(N121&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19513,11 +19570,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O122" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N122=" "," ",IF(N122&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19565,11 +19622,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O123" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N123=" "," ",IF(N123&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19617,11 +19674,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="O124" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N124=" "," ",IF(N124&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19669,11 +19726,11 @@
         <v>3</v>
       </c>
       <c r="O125" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N125=" "," ",IF(N125&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19721,11 +19778,11 @@
         <v>2.7142857142857144</v>
       </c>
       <c r="O126" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N126=" "," ",IF(N126&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19773,11 +19830,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O127" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N127=" "," ",IF(N127&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19825,11 +19882,11 @@
         <v>2.2857142857142856</v>
       </c>
       <c r="O128" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N128=" "," ",IF(N128&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -19877,11 +19934,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O129" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N129=" "," ",IF(N129&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -19929,11 +19986,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O130" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N130=" "," ",IF(N130&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -19981,11 +20038,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O131" s="18" t="str">
-        <f t="shared" ref="O131:O162" si="4">IF(N131=" "," ",IF(N131&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f>IF(N131=" "," ",IF(N131&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20033,11 +20090,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O132" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N132=" "," ",IF(N132&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20085,11 +20142,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O133" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N133=" "," ",IF(N133&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20137,11 +20194,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O134" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N134=" "," ",IF(N134&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20189,11 +20246,11 @@
         <v>2.2857142857142856</v>
       </c>
       <c r="O135" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N135=" "," ",IF(N135&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20241,11 +20298,11 @@
         <v>4.2857142857142856</v>
       </c>
       <c r="O136" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N136=" "," ",IF(N136&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20293,11 +20350,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O137" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N137=" "," ",IF(N137&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20345,11 +20402,11 @@
         <v>2.1428571428571428</v>
       </c>
       <c r="O138" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N138=" "," ",IF(N138&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20397,11 +20454,11 @@
         <v>2</v>
       </c>
       <c r="O139" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N139=" "," ",IF(N139&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20449,11 +20506,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O140" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N140=" "," ",IF(N140&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20501,11 +20558,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O141" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N141=" "," ",IF(N141&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20553,11 +20610,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O142" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N142=" "," ",IF(N142&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20605,11 +20662,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O143" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N143=" "," ",IF(N143&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20657,11 +20714,11 @@
         <v>3</v>
       </c>
       <c r="O144" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N144=" "," ",IF(N144&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20709,11 +20766,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O145" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N145=" "," ",IF(N145&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20761,11 +20818,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O146" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N146=" "," ",IF(N146&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20813,11 +20870,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O147" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N147=" "," ",IF(N147&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20865,11 +20922,11 @@
         <v>5</v>
       </c>
       <c r="O148" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N148=" "," ",IF(N148&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20917,11 +20974,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O149" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N149=" "," ",IF(N149&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20969,11 +21026,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O150" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N150=" "," ",IF(N150&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21021,11 +21078,11 @@
         <v>1.2857142857142858</v>
       </c>
       <c r="O151" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N151=" "," ",IF(N151&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21073,11 +21130,11 @@
         <v>1.2857142857142858</v>
       </c>
       <c r="O152" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N152=" "," ",IF(N152&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21125,11 +21182,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O153" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N153=" "," ",IF(N153&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21177,11 +21234,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O154" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N154=" "," ",IF(N154&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21229,11 +21286,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O155" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N155=" "," ",IF(N155&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21281,11 +21338,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O156" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N156=" "," ",IF(N156&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21333,11 +21390,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O157" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N157=" "," ",IF(N157&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21385,11 +21442,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O158" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N158=" "," ",IF(N158&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21437,11 +21494,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O159" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N159=" "," ",IF(N159&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21489,11 +21546,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O160" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N160=" "," ",IF(N160&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21541,11 +21598,11 @@
         <v>5</v>
       </c>
       <c r="O161" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N161=" "," ",IF(N161&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21593,11 +21650,11 @@
         <v>2.1428571428571428</v>
       </c>
       <c r="O162" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N162=" "," ",IF(N162&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21645,8 +21702,1256 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O163" s="18" t="str">
-        <f t="shared" ref="O163" si="5">IF(N163=" "," ",IF(N163&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f>IF(N163=" "," ",IF(N163&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A164" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B164" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C164" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D164" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E164" s="46" t="s">
+        <v>216</v>
+      </c>
+      <c r="F164" s="47">
+        <v>1001452225</v>
+      </c>
+      <c r="G164" s="48">
+        <v>5</v>
+      </c>
+      <c r="H164" s="48">
+        <v>5</v>
+      </c>
+      <c r="I164" s="48">
+        <v>4</v>
+      </c>
+      <c r="J164" s="48">
+        <v>3</v>
+      </c>
+      <c r="K164" s="48">
+        <v>4</v>
+      </c>
+      <c r="L164" s="48">
+        <v>3</v>
+      </c>
+      <c r="M164" s="48">
+        <v>3</v>
+      </c>
+      <c r="N164" s="19">
+        <f>AVERAGE('NIVEL 1'!G164:M164)</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O164" s="44" t="str">
+        <f>IF(N164=" "," ",IF(N164&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A165" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B165" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C165" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D165" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E165" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="F165" s="47">
+        <v>1001481017</v>
+      </c>
+      <c r="G165" s="48">
+        <v>5</v>
+      </c>
+      <c r="H165" s="48">
+        <v>5</v>
+      </c>
+      <c r="I165" s="48">
+        <v>5</v>
+      </c>
+      <c r="J165" s="48">
+        <v>5</v>
+      </c>
+      <c r="K165" s="48">
+        <v>4</v>
+      </c>
+      <c r="L165" s="48">
+        <v>4</v>
+      </c>
+      <c r="M165" s="48">
+        <v>5</v>
+      </c>
+      <c r="N165" s="19">
+        <f>AVERAGE('NIVEL 1'!G165:M165)</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O165" s="44" t="str">
+        <f>IF(N165=" "," ",IF(N165&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A166" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B166" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C166" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D166" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E166" s="46" t="s">
+        <v>196</v>
+      </c>
+      <c r="F166" s="47">
+        <v>1003049821</v>
+      </c>
+      <c r="G166" s="48">
+        <v>5</v>
+      </c>
+      <c r="H166" s="48">
+        <v>5</v>
+      </c>
+      <c r="I166" s="48">
+        <v>5</v>
+      </c>
+      <c r="J166" s="48">
+        <v>5</v>
+      </c>
+      <c r="K166" s="48">
+        <v>5</v>
+      </c>
+      <c r="L166" s="48">
+        <v>4</v>
+      </c>
+      <c r="M166" s="48">
+        <v>5</v>
+      </c>
+      <c r="N166" s="19">
+        <f>AVERAGE('NIVEL 1'!G166:M166)</f>
+        <v>4.8571428571428568</v>
+      </c>
+      <c r="O166" s="44" t="str">
+        <f>IF(N166=" "," ",IF(N166&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A167" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B167" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C167" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D167" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E167" s="46" t="s">
+        <v>213</v>
+      </c>
+      <c r="F167" s="47">
+        <v>1034788626</v>
+      </c>
+      <c r="G167" s="48">
+        <v>5</v>
+      </c>
+      <c r="H167" s="48">
+        <v>5</v>
+      </c>
+      <c r="I167" s="48">
+        <v>5</v>
+      </c>
+      <c r="J167" s="48">
+        <v>5</v>
+      </c>
+      <c r="K167" s="48">
+        <v>5</v>
+      </c>
+      <c r="L167" s="48">
+        <v>4</v>
+      </c>
+      <c r="M167" s="48">
+        <v>5</v>
+      </c>
+      <c r="N167" s="19">
+        <f>AVERAGE('NIVEL 1'!G167:M167)</f>
+        <v>4.8571428571428568</v>
+      </c>
+      <c r="O167" s="44" t="str">
+        <f>IF(N167=" "," ",IF(N167&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A168" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B168" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C168" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D168" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E168" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="F168" s="47">
+        <v>1044227121</v>
+      </c>
+      <c r="G168" s="48">
+        <v>5</v>
+      </c>
+      <c r="H168" s="48">
+        <v>5</v>
+      </c>
+      <c r="I168" s="48">
+        <v>4</v>
+      </c>
+      <c r="J168" s="48">
+        <v>3</v>
+      </c>
+      <c r="K168" s="48">
+        <v>4</v>
+      </c>
+      <c r="L168" s="48">
+        <v>3</v>
+      </c>
+      <c r="M168" s="48">
+        <v>5</v>
+      </c>
+      <c r="N168" s="19">
+        <f>AVERAGE('NIVEL 1'!G168:M168)</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O168" s="44" t="str">
+        <f>IF(N168=" "," ",IF(N168&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A169" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B169" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C169" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D169" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E169" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="F169" s="47">
+        <v>1062529919</v>
+      </c>
+      <c r="G169" s="48">
+        <v>5</v>
+      </c>
+      <c r="H169" s="48">
+        <v>3</v>
+      </c>
+      <c r="I169" s="48">
+        <v>2</v>
+      </c>
+      <c r="J169" s="48">
+        <v>1</v>
+      </c>
+      <c r="K169" s="48">
+        <v>2</v>
+      </c>
+      <c r="L169" s="48">
+        <v>1</v>
+      </c>
+      <c r="M169" s="48">
+        <v>4</v>
+      </c>
+      <c r="N169" s="19">
+        <f>AVERAGE('NIVEL 1'!G169:M169)</f>
+        <v>2.5714285714285716</v>
+      </c>
+      <c r="O169" s="44" t="str">
+        <f>IF(N169=" "," ",IF(N169&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A170" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B170" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C170" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D170" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E170" s="46" t="s">
+        <v>212</v>
+      </c>
+      <c r="F170" s="47">
+        <v>1062531558</v>
+      </c>
+      <c r="G170" s="48">
+        <v>5</v>
+      </c>
+      <c r="H170" s="48">
+        <v>3</v>
+      </c>
+      <c r="I170" s="48">
+        <v>2</v>
+      </c>
+      <c r="J170" s="48">
+        <v>1</v>
+      </c>
+      <c r="K170" s="48">
+        <v>2</v>
+      </c>
+      <c r="L170" s="48">
+        <v>1</v>
+      </c>
+      <c r="M170" s="48">
+        <v>4</v>
+      </c>
+      <c r="N170" s="19">
+        <f>AVERAGE('NIVEL 1'!G170:M170)</f>
+        <v>2.5714285714285716</v>
+      </c>
+      <c r="O170" s="44" t="str">
+        <f>IF(N170=" "," ",IF(N170&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A171" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B171" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C171" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D171" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E171" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="F171" s="47">
+        <v>1062540642</v>
+      </c>
+      <c r="G171" s="48">
+        <v>5</v>
+      </c>
+      <c r="H171" s="48">
+        <v>3</v>
+      </c>
+      <c r="I171" s="48">
+        <v>2</v>
+      </c>
+      <c r="J171" s="48">
+        <v>1</v>
+      </c>
+      <c r="K171" s="48">
+        <v>2</v>
+      </c>
+      <c r="L171" s="48">
+        <v>1</v>
+      </c>
+      <c r="M171" s="48">
+        <v>4</v>
+      </c>
+      <c r="N171" s="19">
+        <f>AVERAGE('NIVEL 1'!G171:M171)</f>
+        <v>2.5714285714285716</v>
+      </c>
+      <c r="O171" s="44" t="str">
+        <f>IF(N171=" "," ",IF(N171&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A172" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B172" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C172" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D172" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E172" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="F172" s="47">
+        <v>1062544508</v>
+      </c>
+      <c r="G172" s="48">
+        <v>5</v>
+      </c>
+      <c r="H172" s="48">
+        <v>5</v>
+      </c>
+      <c r="I172" s="48">
+        <v>3</v>
+      </c>
+      <c r="J172" s="48">
+        <v>3</v>
+      </c>
+      <c r="K172" s="48">
+        <v>3</v>
+      </c>
+      <c r="L172" s="48">
+        <v>3</v>
+      </c>
+      <c r="M172" s="48">
+        <v>5</v>
+      </c>
+      <c r="N172" s="19">
+        <f>AVERAGE('NIVEL 1'!G172:M172)</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O172" s="44" t="str">
+        <f>IF(N172=" "," ",IF(N172&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A173" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B173" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C173" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D173" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E173" s="46" t="s">
+        <v>208</v>
+      </c>
+      <c r="F173" s="47">
+        <v>1066523010</v>
+      </c>
+      <c r="G173" s="48">
+        <v>5</v>
+      </c>
+      <c r="H173" s="48">
+        <v>5</v>
+      </c>
+      <c r="I173" s="48">
+        <v>5</v>
+      </c>
+      <c r="J173" s="48">
+        <v>4</v>
+      </c>
+      <c r="K173" s="48">
+        <v>5</v>
+      </c>
+      <c r="L173" s="48">
+        <v>4</v>
+      </c>
+      <c r="M173" s="48">
+        <v>5</v>
+      </c>
+      <c r="N173" s="19">
+        <f>AVERAGE('NIVEL 1'!G173:M173)</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O173" s="44" t="str">
+        <f>IF(N173=" "," ",IF(N173&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A174" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B174" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C174" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D174" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E174" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="F174" s="47">
+        <v>1067859838</v>
+      </c>
+      <c r="G174" s="48">
+        <v>5</v>
+      </c>
+      <c r="H174" s="48">
+        <v>3</v>
+      </c>
+      <c r="I174" s="48">
+        <v>2</v>
+      </c>
+      <c r="J174" s="48">
+        <v>2</v>
+      </c>
+      <c r="K174" s="48">
+        <v>1</v>
+      </c>
+      <c r="L174" s="48">
+        <v>1</v>
+      </c>
+      <c r="M174" s="48">
+        <v>2</v>
+      </c>
+      <c r="N174" s="19">
+        <f>AVERAGE('NIVEL 1'!G174:M174)</f>
+        <v>2.2857142857142856</v>
+      </c>
+      <c r="O174" s="44" t="str">
+        <f>IF(N174=" "," ",IF(N174&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A175" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B175" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C175" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D175" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E175" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="F175" s="47">
+        <v>1067872776</v>
+      </c>
+      <c r="G175" s="48">
+        <v>5</v>
+      </c>
+      <c r="H175" s="48">
+        <v>5</v>
+      </c>
+      <c r="I175" s="48">
+        <v>5</v>
+      </c>
+      <c r="J175" s="48">
+        <v>5</v>
+      </c>
+      <c r="K175" s="48">
+        <v>4</v>
+      </c>
+      <c r="L175" s="48">
+        <v>4</v>
+      </c>
+      <c r="M175" s="48">
+        <v>5</v>
+      </c>
+      <c r="N175" s="19">
+        <f>AVERAGE('NIVEL 1'!G175:M175)</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O175" s="44" t="str">
+        <f>IF(N175=" "," ",IF(N175&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A176" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B176" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C176" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D176" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E176" s="46" t="s">
+        <v>204</v>
+      </c>
+      <c r="F176" s="47">
+        <v>1067903477</v>
+      </c>
+      <c r="G176" s="48">
+        <v>5</v>
+      </c>
+      <c r="H176" s="48">
+        <v>5</v>
+      </c>
+      <c r="I176" s="48">
+        <v>5</v>
+      </c>
+      <c r="J176" s="48">
+        <v>5</v>
+      </c>
+      <c r="K176" s="48">
+        <v>4</v>
+      </c>
+      <c r="L176" s="48">
+        <v>4</v>
+      </c>
+      <c r="M176" s="48">
+        <v>5</v>
+      </c>
+      <c r="N176" s="19">
+        <f>AVERAGE('NIVEL 1'!G176:M176)</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O176" s="44" t="str">
+        <f>IF(N176=" "," ",IF(N176&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A177" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B177" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C177" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D177" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E177" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="F177" s="47">
+        <v>1068444523</v>
+      </c>
+      <c r="G177" s="48">
+        <v>5</v>
+      </c>
+      <c r="H177" s="48">
+        <v>4</v>
+      </c>
+      <c r="I177" s="48">
+        <v>3</v>
+      </c>
+      <c r="J177" s="48">
+        <v>1</v>
+      </c>
+      <c r="K177" s="48">
+        <v>3</v>
+      </c>
+      <c r="L177" s="48">
+        <v>1</v>
+      </c>
+      <c r="M177" s="48">
+        <v>5</v>
+      </c>
+      <c r="N177" s="19">
+        <f>AVERAGE('NIVEL 1'!G177:M177)</f>
+        <v>3.1428571428571428</v>
+      </c>
+      <c r="O177" s="44" t="str">
+        <f>IF(N177=" "," ",IF(N177&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A178" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B178" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C178" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D178" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E178" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="F178" s="47">
+        <v>1073817245</v>
+      </c>
+      <c r="G178" s="48">
+        <v>5</v>
+      </c>
+      <c r="H178" s="48">
+        <v>5</v>
+      </c>
+      <c r="I178" s="48">
+        <v>5</v>
+      </c>
+      <c r="J178" s="48">
+        <v>4</v>
+      </c>
+      <c r="K178" s="48">
+        <v>5</v>
+      </c>
+      <c r="L178" s="48">
+        <v>4</v>
+      </c>
+      <c r="M178" s="48">
+        <v>5</v>
+      </c>
+      <c r="N178" s="19">
+        <f>AVERAGE('NIVEL 1'!G178:M178)</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O178" s="44" t="str">
+        <f>IF(N178=" "," ",IF(N178&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A179" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B179" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C179" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D179" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E179" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="F179" s="47">
+        <v>1074002401</v>
+      </c>
+      <c r="G179" s="48">
+        <v>5</v>
+      </c>
+      <c r="H179" s="48">
+        <v>5</v>
+      </c>
+      <c r="I179" s="48">
+        <v>3</v>
+      </c>
+      <c r="J179" s="48">
+        <v>1</v>
+      </c>
+      <c r="K179" s="48">
+        <v>3</v>
+      </c>
+      <c r="L179" s="48">
+        <v>1</v>
+      </c>
+      <c r="M179" s="48">
+        <v>5</v>
+      </c>
+      <c r="N179" s="19">
+        <f>AVERAGE('NIVEL 1'!G179:M179)</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O179" s="44" t="str">
+        <f>IF(N179=" "," ",IF(N179&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A180" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B180" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C180" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D180" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E180" s="46" t="s">
+        <v>214</v>
+      </c>
+      <c r="F180" s="47">
+        <v>1126253349</v>
+      </c>
+      <c r="G180" s="48">
+        <v>5</v>
+      </c>
+      <c r="H180" s="48">
+        <v>1</v>
+      </c>
+      <c r="I180" s="48">
+        <v>1</v>
+      </c>
+      <c r="J180" s="48">
+        <v>1</v>
+      </c>
+      <c r="K180" s="48">
+        <v>1</v>
+      </c>
+      <c r="L180" s="48">
+        <v>1</v>
+      </c>
+      <c r="M180" s="48">
+        <v>1</v>
+      </c>
+      <c r="N180" s="19">
+        <f>AVERAGE('NIVEL 1'!G180:M180)</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O180" s="44" t="str">
+        <f>IF(N180=" "," ",IF(N180&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A181" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B181" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C181" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D181" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E181" s="46" t="s">
+        <v>215</v>
+      </c>
+      <c r="F181" s="47">
+        <v>1137975547</v>
+      </c>
+      <c r="G181" s="48">
+        <v>5</v>
+      </c>
+      <c r="H181" s="48">
+        <v>4</v>
+      </c>
+      <c r="I181" s="48">
+        <v>2</v>
+      </c>
+      <c r="J181" s="48">
+        <v>2</v>
+      </c>
+      <c r="K181" s="48">
+        <v>1</v>
+      </c>
+      <c r="L181" s="48">
+        <v>1</v>
+      </c>
+      <c r="M181" s="48">
+        <v>2</v>
+      </c>
+      <c r="N181" s="19">
+        <f>AVERAGE('NIVEL 1'!G181:M181)</f>
+        <v>2.4285714285714284</v>
+      </c>
+      <c r="O181" s="44" t="str">
+        <f>IF(N181=" "," ",IF(N181&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A182" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B182" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C182" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D182" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E182" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="F182" s="47">
+        <v>1138031947</v>
+      </c>
+      <c r="G182" s="48">
+        <v>5</v>
+      </c>
+      <c r="H182" s="48">
+        <v>5</v>
+      </c>
+      <c r="I182" s="48">
+        <v>3</v>
+      </c>
+      <c r="J182" s="48">
+        <v>2</v>
+      </c>
+      <c r="K182" s="48">
+        <v>3</v>
+      </c>
+      <c r="L182" s="48">
+        <v>2</v>
+      </c>
+      <c r="M182" s="48">
+        <v>5</v>
+      </c>
+      <c r="N182" s="19">
+        <f>AVERAGE('NIVEL 1'!G182:M182)</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="O182" s="44" t="str">
+        <f>IF(N182=" "," ",IF(N182&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A183" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B183" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C183" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D183" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E183" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="F183" s="47">
+        <v>1138032549</v>
+      </c>
+      <c r="G183" s="48">
+        <v>5</v>
+      </c>
+      <c r="H183" s="48">
+        <v>5</v>
+      </c>
+      <c r="I183" s="48">
+        <v>5</v>
+      </c>
+      <c r="J183" s="48">
+        <v>4</v>
+      </c>
+      <c r="K183" s="48">
+        <v>4</v>
+      </c>
+      <c r="L183" s="48">
+        <v>4</v>
+      </c>
+      <c r="M183" s="48">
+        <v>5</v>
+      </c>
+      <c r="N183" s="19">
+        <f>AVERAGE('NIVEL 1'!G183:M183)</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O183" s="44" t="str">
+        <f>IF(N183=" "," ",IF(N183&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A184" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B184" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C184" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D184" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E184" s="46" t="s">
+        <v>217</v>
+      </c>
+      <c r="F184" s="47">
+        <v>1138032702</v>
+      </c>
+      <c r="G184" s="48">
+        <v>5</v>
+      </c>
+      <c r="H184" s="48">
+        <v>3</v>
+      </c>
+      <c r="I184" s="48">
+        <v>2</v>
+      </c>
+      <c r="J184" s="48">
+        <v>2</v>
+      </c>
+      <c r="K184" s="48">
+        <v>2</v>
+      </c>
+      <c r="L184" s="48">
+        <v>2</v>
+      </c>
+      <c r="M184" s="48">
+        <v>2</v>
+      </c>
+      <c r="N184" s="19">
+        <f>AVERAGE('NIVEL 1'!G184:M184)</f>
+        <v>2.5714285714285716</v>
+      </c>
+      <c r="O184" s="44" t="str">
+        <f>IF(N184=" "," ",IF(N184&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A185" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B185" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C185" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D185" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E185" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="F185" s="47">
+        <v>1141358368</v>
+      </c>
+      <c r="G185" s="48">
+        <v>5</v>
+      </c>
+      <c r="H185" s="48">
+        <v>5</v>
+      </c>
+      <c r="I185" s="48">
+        <v>5</v>
+      </c>
+      <c r="J185" s="48">
+        <v>5</v>
+      </c>
+      <c r="K185" s="48">
+        <v>5</v>
+      </c>
+      <c r="L185" s="48">
+        <v>5</v>
+      </c>
+      <c r="M185" s="48">
+        <v>5</v>
+      </c>
+      <c r="N185" s="19">
+        <f>AVERAGE('NIVEL 1'!G185:M185)</f>
+        <v>5</v>
+      </c>
+      <c r="O185" s="44" t="str">
+        <f>IF(N185=" "," ",IF(N185&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A186" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B186" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C186" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D186" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E186" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="F186" s="47">
+        <v>1243758694</v>
+      </c>
+      <c r="G186" s="48">
+        <v>5</v>
+      </c>
+      <c r="H186" s="48">
+        <v>3</v>
+      </c>
+      <c r="I186" s="48">
+        <v>2</v>
+      </c>
+      <c r="J186" s="48">
+        <v>1</v>
+      </c>
+      <c r="K186" s="48">
+        <v>1</v>
+      </c>
+      <c r="L186" s="48">
+        <v>1</v>
+      </c>
+      <c r="M186" s="48">
+        <v>5</v>
+      </c>
+      <c r="N186" s="19">
+        <f>AVERAGE('NIVEL 1'!G186:M186)</f>
+        <v>2.5714285714285716</v>
+      </c>
+      <c r="O186" s="44" t="str">
+        <f>IF(N186=" "," ",IF(N186&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A187" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B187" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C187" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D187" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E187" s="46" t="s">
+        <v>201</v>
+      </c>
+      <c r="F187" s="47">
+        <v>3226990961</v>
+      </c>
+      <c r="G187" s="48">
+        <v>5</v>
+      </c>
+      <c r="H187" s="48">
+        <v>5</v>
+      </c>
+      <c r="I187" s="48">
+        <v>5</v>
+      </c>
+      <c r="J187" s="48">
+        <v>5</v>
+      </c>
+      <c r="K187" s="48">
+        <v>5</v>
+      </c>
+      <c r="L187" s="48">
+        <v>5</v>
+      </c>
+      <c r="M187" s="48">
+        <v>5</v>
+      </c>
+      <c r="N187" s="19">
+        <f>AVERAGE('NIVEL 1'!G187:M187)</f>
+        <v>5</v>
+      </c>
+      <c r="O187" s="44" t="str">
+        <f>IF(N187=" "," ",IF(N187&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
   </sheetData>
@@ -21673,29 +22978,29 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O133"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O156"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" customWidth="1"/>
+    <col min="5" max="5" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" customWidth="1"/>
-    <col min="11" max="11" width="7.85546875" customWidth="1"/>
-    <col min="12" max="12" width="6.28515625" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" customWidth="1"/>
-    <col min="14" max="14" width="7.140625" customWidth="1"/>
-    <col min="15" max="15" width="15.7109375" customWidth="1"/>
-    <col min="16" max="16" width="15.28515625" customWidth="1"/>
-    <col min="17" max="17" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" customWidth="1"/>
+    <col min="12" max="12" width="6.33203125" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" customWidth="1"/>
+    <col min="14" max="14" width="7.109375" customWidth="1"/>
+    <col min="15" max="15" width="15.6640625" customWidth="1"/>
+    <col min="16" max="16" width="15.33203125" customWidth="1"/>
+    <col min="17" max="17" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C1" s="3"/>
       <c r="E1" s="25" t="s">
         <v>59</v>
@@ -21713,7 +23018,7 @@
       <c r="N1" s="35"/>
       <c r="O1" s="34"/>
     </row>
-    <row r="2" spans="1:15" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>62</v>
       </c>
@@ -21760,7 +23065,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -21808,11 +23113,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O3" s="18" t="str">
-        <f t="shared" ref="O3:O34" si="0">IF(N3=" "," ",IF(N3&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f>IF(N3=" "," ",IF(N3&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -21860,11 +23165,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O4" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N4=" "," ",IF(N4&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -21912,11 +23217,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O5" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N5=" "," ",IF(N5&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -21964,11 +23269,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O6" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N6=" "," ",IF(N6&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22016,11 +23321,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O7" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N7=" "," ",IF(N7&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22068,11 +23373,11 @@
         <v>3</v>
       </c>
       <c r="O8" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N8=" "," ",IF(N8&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22120,11 +23425,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O9" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N9=" "," ",IF(N9&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22172,11 +23477,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O10" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N10=" "," ",IF(N10&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22224,11 +23529,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O11" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N11=" "," ",IF(N11&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22276,11 +23581,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O12" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N12=" "," ",IF(N12&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22328,11 +23633,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O13" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N13=" "," ",IF(N13&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22380,11 +23685,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O14" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N14=" "," ",IF(N14&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22432,11 +23737,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O15" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N15=" "," ",IF(N15&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22484,11 +23789,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O16" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N16=" "," ",IF(N16&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22536,11 +23841,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O17" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N17=" "," ",IF(N17&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22588,11 +23893,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O18" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N18=" "," ",IF(N18&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22640,11 +23945,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O19" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N19=" "," ",IF(N19&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22692,11 +23997,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O20" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N20=" "," ",IF(N20&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22744,11 +24049,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O21" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N21=" "," ",IF(N21&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22796,11 +24101,11 @@
         <v>3</v>
       </c>
       <c r="O22" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N22=" "," ",IF(N22&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -22848,11 +24153,11 @@
         <v>3</v>
       </c>
       <c r="O23" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N23=" "," ",IF(N23&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -22900,11 +24205,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O24" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N24=" "," ",IF(N24&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -22952,11 +24257,11 @@
         <v>4</v>
       </c>
       <c r="O25" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N25=" "," ",IF(N25&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23004,11 +24309,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O26" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N26=" "," ",IF(N26&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23056,11 +24361,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O27" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N27=" "," ",IF(N27&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23108,11 +24413,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O28" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N28=" "," ",IF(N28&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23160,11 +24465,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O29" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N29=" "," ",IF(N29&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23212,11 +24517,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O30" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N30=" "," ",IF(N30&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23264,11 +24569,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O31" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N31=" "," ",IF(N31&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23316,11 +24621,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O32" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N32=" "," ",IF(N32&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23368,11 +24673,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O33" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N33=" "," ",IF(N33&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23420,11 +24725,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O34" s="18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N34=" "," ",IF(N34&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23472,11 +24777,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O35" s="18" t="str">
-        <f t="shared" ref="O35:O66" si="1">IF(N35=" "," ",IF(N35&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f>IF(N35=" "," ",IF(N35&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23524,11 +24829,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O36" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N36=" "," ",IF(N36&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23576,11 +24881,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O37" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N37=" "," ",IF(N37&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23628,11 +24933,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O38" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N38=" "," ",IF(N38&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23680,11 +24985,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O39" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N39=" "," ",IF(N39&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23732,11 +25037,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O40" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N40=" "," ",IF(N40&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23784,11 +25089,11 @@
         <v>4.8571428571428568</v>
       </c>
       <c r="O41" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N41=" "," ",IF(N41&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23836,11 +25141,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O42" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N42=" "," ",IF(N42&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23888,11 +25193,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O43" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N43=" "," ",IF(N43&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23940,11 +25245,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O44" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N44=" "," ",IF(N44&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -23992,11 +25297,11 @@
         <v>2.7142857142857144</v>
       </c>
       <c r="O45" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N45=" "," ",IF(N45&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -24044,11 +25349,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O46" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N46=" "," ",IF(N46&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -24096,11 +25401,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O47" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N47=" "," ",IF(N47&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -24148,11 +25453,11 @@
         <v>3</v>
       </c>
       <c r="O48" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N48=" "," ",IF(N48&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -24200,11 +25505,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O49" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N49=" "," ",IF(N49&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -24252,11 +25557,11 @@
         <v>2.7142857142857144</v>
       </c>
       <c r="O50" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N50=" "," ",IF(N50&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24304,11 +25609,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O51" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N51=" "," ",IF(N51&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24356,11 +25661,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O52" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N52=" "," ",IF(N52&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24408,11 +25713,11 @@
         <v>4.2857142857142856</v>
       </c>
       <c r="O53" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N53=" "," ",IF(N53&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24460,11 +25765,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O54" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N54=" "," ",IF(N54&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24512,11 +25817,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O55" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N55=" "," ",IF(N55&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24564,11 +25869,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O56" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N56=" "," ",IF(N56&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24616,11 +25921,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O57" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N57=" "," ",IF(N57&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24668,11 +25973,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O58" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N58=" "," ",IF(N58&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24720,11 +26025,11 @@
         <v>3</v>
       </c>
       <c r="O59" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N59=" "," ",IF(N59&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24772,11 +26077,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O60" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N60=" "," ",IF(N60&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24824,11 +26129,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O61" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N61=" "," ",IF(N61&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24876,11 +26181,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O62" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N62=" "," ",IF(N62&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24928,11 +26233,11 @@
         <v>5</v>
       </c>
       <c r="O63" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N63=" "," ",IF(N63&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -24980,11 +26285,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O64" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N64=" "," ",IF(N64&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25032,11 +26337,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O65" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N65=" "," ",IF(N65&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25084,11 +26389,11 @@
         <v>5</v>
       </c>
       <c r="O66" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(N66=" "," ",IF(N66&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25136,11 +26441,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O67" s="18" t="str">
-        <f t="shared" ref="O67:O98" si="2">IF(N67=" "," ",IF(N67&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f>IF(N67=" "," ",IF(N67&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25188,11 +26493,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O68" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N68=" "," ",IF(N68&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25240,11 +26545,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O69" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N69=" "," ",IF(N69&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25292,11 +26597,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O70" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N70=" "," ",IF(N70&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25344,11 +26649,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O71" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N71=" "," ",IF(N71&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -25396,11 +26701,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O72" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N72=" "," ",IF(N72&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25448,11 +26753,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O73" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N73=" "," ",IF(N73&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25500,11 +26805,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O74" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N74=" "," ",IF(N74&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25552,11 +26857,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O75" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N75=" "," ",IF(N75&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25604,11 +26909,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O76" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N76=" "," ",IF(N76&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25656,11 +26961,11 @@
         <v>2</v>
       </c>
       <c r="O77" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N77=" "," ",IF(N77&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25708,11 +27013,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O78" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N78=" "," ",IF(N78&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25760,11 +27065,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O79" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N79=" "," ",IF(N79&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25812,11 +27117,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O80" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N80=" "," ",IF(N80&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25864,11 +27169,11 @@
         <v>3</v>
       </c>
       <c r="O81" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N81=" "," ",IF(N81&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25916,11 +27221,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O82" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N82=" "," ",IF(N82&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -25968,11 +27273,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O83" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N83=" "," ",IF(N83&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26020,11 +27325,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O84" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N84=" "," ",IF(N84&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26072,11 +27377,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O85" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N85=" "," ",IF(N85&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26124,11 +27429,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O86" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N86=" "," ",IF(N86&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26176,11 +27481,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O87" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N87=" "," ",IF(N87&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26228,11 +27533,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O88" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N88=" "," ",IF(N88&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26280,11 +27585,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O89" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N89=" "," ",IF(N89&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26332,11 +27637,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O90" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N90=" "," ",IF(N90&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26384,11 +27689,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O91" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N91=" "," ",IF(N91&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26436,11 +27741,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O92" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N92=" "," ",IF(N92&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26488,11 +27793,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O93" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N93=" "," ",IF(N93&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26540,11 +27845,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O94" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N94=" "," ",IF(N94&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26592,11 +27897,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O95" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N95=" "," ",IF(N95&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26644,11 +27949,11 @@
         <v>4</v>
       </c>
       <c r="O96" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N96=" "," ",IF(N96&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26696,11 +28001,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O97" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N97=" "," ",IF(N97&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26748,11 +28053,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O98" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(N98=" "," ",IF(N98&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26800,11 +28105,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O99" s="18" t="str">
-        <f t="shared" ref="O99:O130" si="3">IF(N99=" "," ",IF(N99&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f>IF(N99=" "," ",IF(N99&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26852,11 +28157,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O100" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N100=" "," ",IF(N100&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -26904,11 +28209,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O101" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N101=" "," ",IF(N101&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -26956,11 +28261,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O102" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N102=" "," ",IF(N102&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27008,11 +28313,11 @@
         <v>4</v>
       </c>
       <c r="O103" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N103=" "," ",IF(N103&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27060,11 +28365,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O104" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N104=" "," ",IF(N104&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27112,11 +28417,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O105" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N105=" "," ",IF(N105&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27164,11 +28469,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O106" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N106=" "," ",IF(N106&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27216,11 +28521,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O107" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N107=" "," ",IF(N107&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27268,11 +28573,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O108" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N108=" "," ",IF(N108&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27320,11 +28625,11 @@
         <v>4</v>
       </c>
       <c r="O109" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N109=" "," ",IF(N109&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27372,11 +28677,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O110" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N110=" "," ",IF(N110&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -27424,11 +28729,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O111" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N111=" "," ",IF(N111&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27476,11 +28781,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O112" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N112=" "," ",IF(N112&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27528,11 +28833,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O113" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N113=" "," ",IF(N113&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27580,11 +28885,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O114" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N114=" "," ",IF(N114&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27632,11 +28937,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O115" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N115=" "," ",IF(N115&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27684,11 +28989,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O116" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N116=" "," ",IF(N116&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27736,11 +29041,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O117" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N117=" "," ",IF(N117&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27788,11 +29093,11 @@
         <v>4.2857142857142856</v>
       </c>
       <c r="O118" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N118=" "," ",IF(N118&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27840,11 +29145,11 @@
         <v>4</v>
       </c>
       <c r="O119" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N119=" "," ",IF(N119&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27892,11 +29197,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O120" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N120=" "," ",IF(N120&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27944,11 +29249,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O121" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N121=" "," ",IF(N121&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -27996,11 +29301,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O122" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N122=" "," ",IF(N122&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28048,11 +29353,11 @@
         <v>4</v>
       </c>
       <c r="O123" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N123=" "," ",IF(N123&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28100,11 +29405,11 @@
         <v>5</v>
       </c>
       <c r="O124" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N124=" "," ",IF(N124&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28152,11 +29457,11 @@
         <v>5</v>
       </c>
       <c r="O125" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N125=" "," ",IF(N125&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28204,11 +29509,11 @@
         <v>4</v>
       </c>
       <c r="O126" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N126=" "," ",IF(N126&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28256,11 +29561,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O127" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N127=" "," ",IF(N127&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28308,11 +29613,11 @@
         <v>5</v>
       </c>
       <c r="O128" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N128=" "," ",IF(N128&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28360,11 +29665,11 @@
         <v>4</v>
       </c>
       <c r="O129" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N129=" "," ",IF(N129&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28412,11 +29717,11 @@
         <v>4</v>
       </c>
       <c r="O130" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(N130=" "," ",IF(N130&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28464,11 +29769,11 @@
         <v>4</v>
       </c>
       <c r="O131" s="18" t="str">
-        <f t="shared" ref="O131:O133" si="4">IF(N131=" "," ",IF(N131&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f>IF(N131=" "," ",IF(N131&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28516,11 +29821,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O132" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N132=" "," ",IF(N132&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -28568,7 +29873,1203 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O133" s="18" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N133=" "," ",IF(N133&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A134" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B134" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C134" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D134" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E134" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="F134" s="48">
+        <v>1018813</v>
+      </c>
+      <c r="G134" s="48">
+        <v>5</v>
+      </c>
+      <c r="H134" s="48">
+        <v>4</v>
+      </c>
+      <c r="I134" s="48">
+        <v>3</v>
+      </c>
+      <c r="J134" s="48">
+        <v>3</v>
+      </c>
+      <c r="K134" s="48">
+        <v>4</v>
+      </c>
+      <c r="L134" s="48">
+        <v>5</v>
+      </c>
+      <c r="M134" s="48">
+        <v>2</v>
+      </c>
+      <c r="N134" s="19">
+        <f>AVERAGE('NIVEL 2'!G134:M134)</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O134" s="44" t="str">
+        <f>IF(N134=" "," ",IF(N134&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A135" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B135" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C135" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D135" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E135" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="F135" s="48">
+        <v>1418308</v>
+      </c>
+      <c r="G135" s="48">
+        <v>5</v>
+      </c>
+      <c r="H135" s="48">
+        <v>5</v>
+      </c>
+      <c r="I135" s="48">
+        <v>4</v>
+      </c>
+      <c r="J135" s="48">
+        <v>5</v>
+      </c>
+      <c r="K135" s="48">
+        <v>5</v>
+      </c>
+      <c r="L135" s="48">
+        <v>5</v>
+      </c>
+      <c r="M135" s="48">
+        <v>3</v>
+      </c>
+      <c r="N135" s="19">
+        <f>AVERAGE('NIVEL 2'!G135:M135)</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O135" s="44" t="str">
+        <f>IF(N135=" "," ",IF(N135&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A136" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B136" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C136" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D136" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E136" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="F136" s="48">
+        <v>7384397</v>
+      </c>
+      <c r="G136" s="48">
+        <v>5</v>
+      </c>
+      <c r="H136" s="48">
+        <v>5</v>
+      </c>
+      <c r="I136" s="48">
+        <v>3</v>
+      </c>
+      <c r="J136" s="48">
+        <v>4</v>
+      </c>
+      <c r="K136" s="48">
+        <v>5</v>
+      </c>
+      <c r="L136" s="48">
+        <v>5</v>
+      </c>
+      <c r="M136" s="48">
+        <v>4</v>
+      </c>
+      <c r="N136" s="19">
+        <f>AVERAGE('NIVEL 2'!G136:M136)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O136" s="44" t="str">
+        <f>IF(N136=" "," ",IF(N136&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A137" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B137" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C137" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D137" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E137" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="F137" s="48">
+        <v>10966252</v>
+      </c>
+      <c r="G137" s="48">
+        <v>5</v>
+      </c>
+      <c r="H137" s="48">
+        <v>5</v>
+      </c>
+      <c r="I137" s="48">
+        <v>2</v>
+      </c>
+      <c r="J137" s="48">
+        <v>5</v>
+      </c>
+      <c r="K137" s="48">
+        <v>5</v>
+      </c>
+      <c r="L137" s="48">
+        <v>5</v>
+      </c>
+      <c r="M137" s="48">
+        <v>4</v>
+      </c>
+      <c r="N137" s="19">
+        <f>AVERAGE('NIVEL 2'!G137:M137)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O137" s="44" t="str">
+        <f>IF(N137=" "," ",IF(N137&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A138" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B138" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C138" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D138" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E138" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="F138" s="48">
+        <v>1007822238</v>
+      </c>
+      <c r="G138" s="48">
+        <v>5</v>
+      </c>
+      <c r="H138" s="48">
+        <v>5</v>
+      </c>
+      <c r="I138" s="48">
+        <v>3</v>
+      </c>
+      <c r="J138" s="48">
+        <v>5</v>
+      </c>
+      <c r="K138" s="48">
+        <v>5</v>
+      </c>
+      <c r="L138" s="48">
+        <v>5</v>
+      </c>
+      <c r="M138" s="48">
+        <v>3</v>
+      </c>
+      <c r="N138" s="19">
+        <f>AVERAGE('NIVEL 2'!G138:M138)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O138" s="44" t="str">
+        <f>IF(N138=" "," ",IF(N138&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A139" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B139" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C139" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D139" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E139" s="46" t="s">
+        <v>63</v>
+      </c>
+      <c r="F139" s="48">
+        <v>1027663882</v>
+      </c>
+      <c r="G139" s="48">
+        <v>4</v>
+      </c>
+      <c r="H139" s="48">
+        <v>3</v>
+      </c>
+      <c r="I139" s="48">
+        <v>4</v>
+      </c>
+      <c r="J139" s="48">
+        <v>4</v>
+      </c>
+      <c r="K139" s="48">
+        <v>3</v>
+      </c>
+      <c r="L139" s="48">
+        <v>5</v>
+      </c>
+      <c r="M139" s="48">
+        <v>3</v>
+      </c>
+      <c r="N139" s="19">
+        <f>AVERAGE('NIVEL 2'!G139:M139)</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O139" s="44" t="str">
+        <f>IF(N139=" "," ",IF(N139&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A140" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B140" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C140" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D140" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E140" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="F140" s="48">
+        <v>1029722943</v>
+      </c>
+      <c r="G140" s="48">
+        <v>5</v>
+      </c>
+      <c r="H140" s="48">
+        <v>4</v>
+      </c>
+      <c r="I140" s="48">
+        <v>4</v>
+      </c>
+      <c r="J140" s="48">
+        <v>4</v>
+      </c>
+      <c r="K140" s="48">
+        <v>5</v>
+      </c>
+      <c r="L140" s="48">
+        <v>5</v>
+      </c>
+      <c r="M140" s="48">
+        <v>3</v>
+      </c>
+      <c r="N140" s="19">
+        <f>AVERAGE('NIVEL 2'!G140:M140)</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O140" s="44" t="str">
+        <f>IF(N140=" "," ",IF(N140&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A141" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B141" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C141" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D141" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E141" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="F141" s="48">
+        <v>1031543523</v>
+      </c>
+      <c r="G141" s="48">
+        <v>5</v>
+      </c>
+      <c r="H141" s="48">
+        <v>5</v>
+      </c>
+      <c r="I141" s="48">
+        <v>4</v>
+      </c>
+      <c r="J141" s="48">
+        <v>4</v>
+      </c>
+      <c r="K141" s="48">
+        <v>5</v>
+      </c>
+      <c r="L141" s="48">
+        <v>5</v>
+      </c>
+      <c r="M141" s="48">
+        <v>3</v>
+      </c>
+      <c r="N141" s="19">
+        <f>AVERAGE('NIVEL 2'!G141:M141)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O141" s="44" t="str">
+        <f>IF(N141=" "," ",IF(N141&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A142" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B142" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C142" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D142" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E142" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="F142" s="48">
+        <v>1062432000</v>
+      </c>
+      <c r="G142" s="48">
+        <v>5</v>
+      </c>
+      <c r="H142" s="48">
+        <v>5</v>
+      </c>
+      <c r="I142" s="48">
+        <v>3</v>
+      </c>
+      <c r="J142" s="48">
+        <v>4</v>
+      </c>
+      <c r="K142" s="48">
+        <v>3</v>
+      </c>
+      <c r="L142" s="48">
+        <v>5</v>
+      </c>
+      <c r="M142" s="48">
+        <v>2</v>
+      </c>
+      <c r="N142" s="19">
+        <f>AVERAGE('NIVEL 2'!G142:M142)</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O142" s="44" t="str">
+        <f>IF(N142=" "," ",IF(N142&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A143" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B143" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C143" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D143" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E143" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="F143" s="48">
+        <v>1062539643</v>
+      </c>
+      <c r="G143" s="48">
+        <v>5</v>
+      </c>
+      <c r="H143" s="48">
+        <v>4</v>
+      </c>
+      <c r="I143" s="48">
+        <v>4</v>
+      </c>
+      <c r="J143" s="48">
+        <v>4</v>
+      </c>
+      <c r="K143" s="48">
+        <v>4</v>
+      </c>
+      <c r="L143" s="48">
+        <v>5</v>
+      </c>
+      <c r="M143" s="48">
+        <v>5</v>
+      </c>
+      <c r="N143" s="19">
+        <f>AVERAGE('NIVEL 2'!G143:M143)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O143" s="44" t="str">
+        <f>IF(N143=" "," ",IF(N143&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A144" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B144" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C144" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D144" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E144" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="F144" s="48">
+        <v>1062980565</v>
+      </c>
+      <c r="G144" s="48">
+        <v>4</v>
+      </c>
+      <c r="H144" s="48">
+        <v>4</v>
+      </c>
+      <c r="I144" s="48">
+        <v>3</v>
+      </c>
+      <c r="J144" s="48">
+        <v>4</v>
+      </c>
+      <c r="K144" s="48">
+        <v>4</v>
+      </c>
+      <c r="L144" s="48">
+        <v>5</v>
+      </c>
+      <c r="M144" s="48">
+        <v>4</v>
+      </c>
+      <c r="N144" s="19">
+        <f>AVERAGE('NIVEL 2'!G144:M144)</f>
+        <v>4</v>
+      </c>
+      <c r="O144" s="44" t="str">
+        <f>IF(N144=" "," ",IF(N144&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A145" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B145" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C145" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D145" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E145" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="F145" s="48">
+        <v>1062984834</v>
+      </c>
+      <c r="G145" s="48">
+        <v>5</v>
+      </c>
+      <c r="H145" s="48">
+        <v>4</v>
+      </c>
+      <c r="I145" s="48">
+        <v>3</v>
+      </c>
+      <c r="J145" s="48">
+        <v>4</v>
+      </c>
+      <c r="K145" s="48">
+        <v>5</v>
+      </c>
+      <c r="L145" s="48">
+        <v>5</v>
+      </c>
+      <c r="M145" s="48">
+        <v>3</v>
+      </c>
+      <c r="N145" s="19">
+        <f>AVERAGE('NIVEL 2'!G145:M145)</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O145" s="44" t="str">
+        <f>IF(N145=" "," ",IF(N145&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A146" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B146" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C146" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D146" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E146" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="F146" s="48">
+        <v>1062986616</v>
+      </c>
+      <c r="G146" s="48">
+        <v>5</v>
+      </c>
+      <c r="H146" s="48">
+        <v>4</v>
+      </c>
+      <c r="I146" s="48">
+        <v>3</v>
+      </c>
+      <c r="J146" s="48">
+        <v>3</v>
+      </c>
+      <c r="K146" s="48">
+        <v>3</v>
+      </c>
+      <c r="L146" s="48">
+        <v>4</v>
+      </c>
+      <c r="M146" s="48">
+        <v>2</v>
+      </c>
+      <c r="N146" s="19">
+        <f>AVERAGE('NIVEL 2'!G146:M146)</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O146" s="44" t="str">
+        <f>IF(N146=" "," ",IF(N146&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A147" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B147" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C147" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D147" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E147" s="46" t="s">
+        <v>218</v>
+      </c>
+      <c r="F147" s="48">
+        <v>1064990474</v>
+      </c>
+      <c r="G147" s="48">
+        <v>5</v>
+      </c>
+      <c r="H147" s="48">
+        <v>4</v>
+      </c>
+      <c r="I147" s="48">
+        <v>3</v>
+      </c>
+      <c r="J147" s="48">
+        <v>4</v>
+      </c>
+      <c r="K147" s="48">
+        <v>5</v>
+      </c>
+      <c r="L147" s="48">
+        <v>5</v>
+      </c>
+      <c r="M147" s="48">
+        <v>3</v>
+      </c>
+      <c r="N147" s="19">
+        <f>AVERAGE('NIVEL 2'!G147:M147)</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O147" s="44" t="str">
+        <f>IF(N147=" "," ",IF(N147&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A148" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B148" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C148" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D148" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E148" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F148" s="48">
+        <v>1066512697</v>
+      </c>
+      <c r="G148" s="48">
+        <v>4</v>
+      </c>
+      <c r="H148" s="48">
+        <v>3</v>
+      </c>
+      <c r="I148" s="48">
+        <v>2</v>
+      </c>
+      <c r="J148" s="48">
+        <v>3</v>
+      </c>
+      <c r="K148" s="48">
+        <v>2</v>
+      </c>
+      <c r="L148" s="48">
+        <v>4</v>
+      </c>
+      <c r="M148" s="48">
+        <v>2</v>
+      </c>
+      <c r="N148" s="19">
+        <f>AVERAGE('NIVEL 2'!G148:M148)</f>
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="O148" s="44" t="str">
+        <f>IF(N148=" "," ",IF(N148&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A149" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B149" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C149" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D149" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E149" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="F149" s="48">
+        <v>1066747786</v>
+      </c>
+      <c r="G149" s="48">
+        <v>5</v>
+      </c>
+      <c r="H149" s="48">
+        <v>5</v>
+      </c>
+      <c r="I149" s="48">
+        <v>3</v>
+      </c>
+      <c r="J149" s="48">
+        <v>4</v>
+      </c>
+      <c r="K149" s="48">
+        <v>5</v>
+      </c>
+      <c r="L149" s="48">
+        <v>5</v>
+      </c>
+      <c r="M149" s="48">
+        <v>3</v>
+      </c>
+      <c r="N149" s="19">
+        <f>AVERAGE('NIVEL 2'!G149:M149)</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O149" s="44" t="str">
+        <f>IF(N149=" "," ",IF(N149&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A150" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B150" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C150" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D150" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E150" s="46" t="s">
+        <v>67</v>
+      </c>
+      <c r="F150" s="48">
+        <v>1067849965</v>
+      </c>
+      <c r="G150" s="48">
+        <v>5</v>
+      </c>
+      <c r="H150" s="48">
+        <v>5</v>
+      </c>
+      <c r="I150" s="48">
+        <v>3</v>
+      </c>
+      <c r="J150" s="48">
+        <v>4</v>
+      </c>
+      <c r="K150" s="48">
+        <v>5</v>
+      </c>
+      <c r="L150" s="48">
+        <v>5</v>
+      </c>
+      <c r="M150" s="48">
+        <v>2</v>
+      </c>
+      <c r="N150" s="19">
+        <f>AVERAGE('NIVEL 2'!G150:M150)</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O150" s="44" t="str">
+        <f>IF(N150=" "," ",IF(N150&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A151" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B151" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C151" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D151" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E151" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="F151" s="48">
+        <v>1068439668</v>
+      </c>
+      <c r="G151" s="48">
+        <v>5</v>
+      </c>
+      <c r="H151" s="48">
+        <v>5</v>
+      </c>
+      <c r="I151" s="48">
+        <v>5</v>
+      </c>
+      <c r="J151" s="48">
+        <v>4</v>
+      </c>
+      <c r="K151" s="48">
+        <v>3</v>
+      </c>
+      <c r="L151" s="48">
+        <v>5</v>
+      </c>
+      <c r="M151" s="48">
+        <v>2</v>
+      </c>
+      <c r="N151" s="19">
+        <f>AVERAGE('NIVEL 2'!G151:M151)</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O151" s="44" t="str">
+        <f>IF(N151=" "," ",IF(N151&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A152" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B152" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C152" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D152" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E152" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="F152" s="48">
+        <v>1138031207</v>
+      </c>
+      <c r="G152" s="48">
+        <v>5</v>
+      </c>
+      <c r="H152" s="48">
+        <v>5</v>
+      </c>
+      <c r="I152" s="48">
+        <v>4</v>
+      </c>
+      <c r="J152" s="48">
+        <v>4</v>
+      </c>
+      <c r="K152" s="48">
+        <v>4</v>
+      </c>
+      <c r="L152" s="48">
+        <v>5</v>
+      </c>
+      <c r="M152" s="48">
+        <v>2</v>
+      </c>
+      <c r="N152" s="19">
+        <f>AVERAGE('NIVEL 2'!G152:M152)</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O152" s="44" t="str">
+        <f>IF(N152=" "," ",IF(N152&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A153" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B153" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C153" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D153" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E153" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="F153" s="48">
+        <v>1138032406</v>
+      </c>
+      <c r="G153" s="48">
+        <v>5</v>
+      </c>
+      <c r="H153" s="48">
+        <v>5</v>
+      </c>
+      <c r="I153" s="48">
+        <v>4</v>
+      </c>
+      <c r="J153" s="48">
+        <v>4</v>
+      </c>
+      <c r="K153" s="48">
+        <v>3</v>
+      </c>
+      <c r="L153" s="48">
+        <v>5</v>
+      </c>
+      <c r="M153" s="48">
+        <v>2</v>
+      </c>
+      <c r="N153" s="19">
+        <f>AVERAGE('NIVEL 2'!G153:M153)</f>
+        <v>4</v>
+      </c>
+      <c r="O153" s="44" t="str">
+        <f>IF(N153=" "," ",IF(N153&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A154" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B154" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C154" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D154" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E154" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="F154" s="48">
+        <v>1138032417</v>
+      </c>
+      <c r="G154" s="48">
+        <v>5</v>
+      </c>
+      <c r="H154" s="48">
+        <v>5</v>
+      </c>
+      <c r="I154" s="48">
+        <v>3</v>
+      </c>
+      <c r="J154" s="48">
+        <v>4</v>
+      </c>
+      <c r="K154" s="48">
+        <v>1</v>
+      </c>
+      <c r="L154" s="48">
+        <v>5</v>
+      </c>
+      <c r="M154" s="48">
+        <v>1</v>
+      </c>
+      <c r="N154" s="19">
+        <f>AVERAGE('NIVEL 2'!G154:M154)</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O154" s="44" t="str">
+        <f>IF(N154=" "," ",IF(N154&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A155" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B155" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C155" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D155" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E155" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="F155" s="48">
+        <v>1140444971</v>
+      </c>
+      <c r="G155" s="48">
+        <v>5</v>
+      </c>
+      <c r="H155" s="48">
+        <v>5</v>
+      </c>
+      <c r="I155" s="48">
+        <v>3</v>
+      </c>
+      <c r="J155" s="48">
+        <v>3</v>
+      </c>
+      <c r="K155" s="48">
+        <v>3</v>
+      </c>
+      <c r="L155" s="48">
+        <v>4</v>
+      </c>
+      <c r="M155" s="48">
+        <v>2</v>
+      </c>
+      <c r="N155" s="19">
+        <f>AVERAGE('NIVEL 2'!G155:M155)</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="O155" s="44" t="str">
+        <f>IF(N155=" "," ",IF(N155&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A156" s="48">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B156" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C156" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D156" s="45">
+        <v>45899</v>
+      </c>
+      <c r="E156" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="F156" s="48">
+        <v>1142930859</v>
+      </c>
+      <c r="G156" s="48">
+        <v>5</v>
+      </c>
+      <c r="H156" s="48">
+        <v>4</v>
+      </c>
+      <c r="I156" s="48">
+        <v>3</v>
+      </c>
+      <c r="J156" s="48">
+        <v>3</v>
+      </c>
+      <c r="K156" s="48">
+        <v>3</v>
+      </c>
+      <c r="L156" s="48">
+        <v>5</v>
+      </c>
+      <c r="M156" s="48">
+        <v>3</v>
+      </c>
+      <c r="N156" s="19">
+        <f>AVERAGE('NIVEL 2'!G156:M156)</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O156" s="44" t="str">
+        <f>IF(N156=" "," ",IF(N156&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -28596,32 +31097,32 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="2" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.85546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.28515625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="7.85546875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.28515625" style="2" customWidth="1"/>
-    <col min="16" max="17" width="5.5703125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="6.42578125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="7.28515625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" customWidth="1"/>
-    <col min="21" max="21" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.33203125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" style="2" customWidth="1"/>
+    <col min="16" max="17" width="5.5546875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="6.44140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="7.33203125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E1" s="28" t="s">
         <v>60</v>
       </c>
@@ -28642,7 +31143,7 @@
       <c r="R1" s="31"/>
       <c r="S1" s="31"/>
     </row>
-    <row r="2" spans="1:21" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>62</v>
       </c>
@@ -28707,7 +31208,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -28773,11 +31274,11 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U3" s="32" t="str">
-        <f t="shared" ref="U3:U37" si="0">IF(T3=" "," ",IF(T3&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f>IF(T3=" "," ",IF(T3&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -28843,11 +31344,11 @@
         <v>4.384615384615385</v>
       </c>
       <c r="U4" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T4=" "," ",IF(T4&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -28913,11 +31414,11 @@
         <v>4.4615384615384617</v>
       </c>
       <c r="U5" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T5=" "," ",IF(T5&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -28983,11 +31484,11 @@
         <v>4.5384615384615383</v>
       </c>
       <c r="U6" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T6=" "," ",IF(T6&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -29053,11 +31554,11 @@
         <v>4.6923076923076925</v>
       </c>
       <c r="U7" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T7=" "," ",IF(T7&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -29123,11 +31624,11 @@
         <v>4.615384615384615</v>
       </c>
       <c r="U8" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T8=" "," ",IF(T8&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="29">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -29193,11 +31694,11 @@
         <v>4.7692307692307692</v>
       </c>
       <c r="U9" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T9=" "," ",IF(T9&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -29263,11 +31764,11 @@
         <v>4.615384615384615</v>
       </c>
       <c r="U10" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T10=" "," ",IF(T10&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29333,11 +31834,11 @@
         <v>4.5384615384615383</v>
       </c>
       <c r="U11" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T11=" "," ",IF(T11&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29403,11 +31904,11 @@
         <v>4.3076923076923075</v>
       </c>
       <c r="U12" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T12=" "," ",IF(T12&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29473,11 +31974,11 @@
         <v>4.6923076923076925</v>
       </c>
       <c r="U13" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T13=" "," ",IF(T13&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29543,11 +32044,11 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U14" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T14=" "," ",IF(T14&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29613,11 +32114,11 @@
         <v>4.8461538461538458</v>
       </c>
       <c r="U15" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T15=" "," ",IF(T15&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29683,11 +32184,11 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U16" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T16=" "," ",IF(T16&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29753,11 +32254,11 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U17" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T17=" "," ",IF(T17&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29823,11 +32324,11 @@
         <v>4.7692307692307692</v>
       </c>
       <c r="U18" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T18=" "," ",IF(T18&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29893,11 +32394,11 @@
         <v>4.7692307692307692</v>
       </c>
       <c r="U19" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T19=" "," ",IF(T19&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -29963,11 +32464,11 @@
         <v>4.6923076923076925</v>
       </c>
       <c r="U20" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T20=" "," ",IF(T20&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -30033,11 +32534,11 @@
         <v>3.7692307692307692</v>
       </c>
       <c r="U21" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T21=" "," ",IF(T21&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -30103,11 +32604,11 @@
         <v>4.8461538461538458</v>
       </c>
       <c r="U22" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T22=" "," ",IF(T22&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -30173,11 +32674,11 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U23" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T23=" "," ",IF(T23&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -30243,11 +32744,11 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U24" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T24=" "," ",IF(T24&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -30313,11 +32814,11 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U25" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T25=" "," ",IF(T25&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -30383,11 +32884,11 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U26" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T26=" "," ",IF(T26&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -30453,11 +32954,11 @@
         <v>4.4615384615384617</v>
       </c>
       <c r="U27" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T27=" "," ",IF(T27&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -30523,11 +33024,11 @@
         <v>4.8461538461538458</v>
       </c>
       <c r="U28" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T28=" "," ",IF(T28&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -30593,11 +33094,11 @@
         <v>4.8461538461538458</v>
       </c>
       <c r="U29" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T29=" "," ",IF(T29&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -30663,11 +33164,11 @@
         <v>4.615384615384615</v>
       </c>
       <c r="U30" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T30=" "," ",IF(T30&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -30733,11 +33234,11 @@
         <v>5</v>
       </c>
       <c r="U31" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T31=" "," ",IF(T31&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -30803,11 +33304,11 @@
         <v>4.615384615384615</v>
       </c>
       <c r="U32" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T32=" "," ",IF(T32&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -30873,11 +33374,11 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U33" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T33=" "," ",IF(T33&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -30943,11 +33444,11 @@
         <v>4.7692307692307692</v>
       </c>
       <c r="U34" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T34=" "," ",IF(T34&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31013,11 +33514,11 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U35" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T35=" "," ",IF(T35&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31083,11 +33584,11 @@
         <v>4.6923076923076925</v>
       </c>
       <c r="U36" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T36=" "," ",IF(T36&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31153,7 +33654,287 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U37" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(T37=" "," ",IF(T37&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <v>CAMBIA A EQUIPO</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A38" s="50">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B38" s="43" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C38" s="51" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D38" s="52">
+        <v>45899</v>
+      </c>
+      <c r="E38" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="F38" s="54">
+        <v>33204108</v>
+      </c>
+      <c r="G38" s="54">
+        <v>5</v>
+      </c>
+      <c r="H38" s="54">
+        <v>4</v>
+      </c>
+      <c r="I38" s="54">
+        <v>5</v>
+      </c>
+      <c r="J38" s="54">
+        <v>5</v>
+      </c>
+      <c r="K38" s="54">
+        <v>5</v>
+      </c>
+      <c r="L38" s="54">
+        <v>4</v>
+      </c>
+      <c r="M38" s="54">
+        <v>5</v>
+      </c>
+      <c r="N38" s="54">
+        <v>5</v>
+      </c>
+      <c r="O38" s="54">
+        <v>5</v>
+      </c>
+      <c r="P38" s="54">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="54">
+        <v>4</v>
+      </c>
+      <c r="R38" s="54">
+        <v>5</v>
+      </c>
+      <c r="S38" s="54">
+        <v>5</v>
+      </c>
+      <c r="T38" s="24">
+        <f>AVERAGE('NIVEL 3'!G38:S38)</f>
+        <v>4.7692307692307692</v>
+      </c>
+      <c r="U38" s="55" t="str">
+        <f>IF(T38=" "," ",IF(T38&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A39" s="50">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B39" s="43" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C39" s="51" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D39" s="52">
+        <v>45899</v>
+      </c>
+      <c r="E39" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="F39" s="54">
+        <v>1064193109</v>
+      </c>
+      <c r="G39" s="54">
+        <v>5</v>
+      </c>
+      <c r="H39" s="54">
+        <v>5</v>
+      </c>
+      <c r="I39" s="54">
+        <v>5</v>
+      </c>
+      <c r="J39" s="54">
+        <v>5</v>
+      </c>
+      <c r="K39" s="54">
+        <v>5</v>
+      </c>
+      <c r="L39" s="54">
+        <v>4</v>
+      </c>
+      <c r="M39" s="54">
+        <v>5</v>
+      </c>
+      <c r="N39" s="54">
+        <v>5</v>
+      </c>
+      <c r="O39" s="54">
+        <v>5</v>
+      </c>
+      <c r="P39" s="54">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="54">
+        <v>4</v>
+      </c>
+      <c r="R39" s="54">
+        <v>4</v>
+      </c>
+      <c r="S39" s="54">
+        <v>5</v>
+      </c>
+      <c r="T39" s="24">
+        <f>AVERAGE('NIVEL 3'!G39:S39)</f>
+        <v>4.7692307692307692</v>
+      </c>
+      <c r="U39" s="55" t="str">
+        <f>IF(T39=" "," ",IF(T39&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A40" s="50">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B40" s="43" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C40" s="51" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D40" s="52">
+        <v>45899</v>
+      </c>
+      <c r="E40" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="F40" s="54">
+        <v>1067869670</v>
+      </c>
+      <c r="G40" s="54">
+        <v>5</v>
+      </c>
+      <c r="H40" s="54">
+        <v>4</v>
+      </c>
+      <c r="I40" s="54">
+        <v>5</v>
+      </c>
+      <c r="J40" s="54">
+        <v>5</v>
+      </c>
+      <c r="K40" s="54">
+        <v>5</v>
+      </c>
+      <c r="L40" s="54">
+        <v>3</v>
+      </c>
+      <c r="M40" s="54">
+        <v>5</v>
+      </c>
+      <c r="N40" s="54">
+        <v>5</v>
+      </c>
+      <c r="O40" s="54">
+        <v>5</v>
+      </c>
+      <c r="P40" s="54">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="54">
+        <v>5</v>
+      </c>
+      <c r="R40" s="54">
+        <v>5</v>
+      </c>
+      <c r="S40" s="54">
+        <v>5</v>
+      </c>
+      <c r="T40" s="24">
+        <f>AVERAGE('NIVEL 3'!G40:S40)</f>
+        <v>4.7692307692307692</v>
+      </c>
+      <c r="U40" s="55" t="str">
+        <f>IF(T40=" "," ",IF(T40&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A41" s="50">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B41" s="43" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C41" s="51" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D41" s="52">
+        <v>45899</v>
+      </c>
+      <c r="E41" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="F41" s="54">
+        <v>1067925321</v>
+      </c>
+      <c r="G41" s="54">
+        <v>5</v>
+      </c>
+      <c r="H41" s="54">
+        <v>5</v>
+      </c>
+      <c r="I41" s="54">
+        <v>5</v>
+      </c>
+      <c r="J41" s="54">
+        <v>5</v>
+      </c>
+      <c r="K41" s="54">
+        <v>5</v>
+      </c>
+      <c r="L41" s="54">
+        <v>5</v>
+      </c>
+      <c r="M41" s="54">
+        <v>5</v>
+      </c>
+      <c r="N41" s="54">
+        <v>5</v>
+      </c>
+      <c r="O41" s="54">
+        <v>5</v>
+      </c>
+      <c r="P41" s="54">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="54">
+        <v>4</v>
+      </c>
+      <c r="R41" s="54">
+        <v>5</v>
+      </c>
+      <c r="S41" s="54">
+        <v>5</v>
+      </c>
+      <c r="T41" s="24">
+        <f>AVERAGE('NIVEL 3'!G41:S41)</f>
+        <v>4.9230769230769234</v>
+      </c>
+      <c r="U41" s="55" t="str">
+        <f>IF(T41=" "," ",IF(T41&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
@@ -31174,15 +33955,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:D38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5703125" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
@@ -31196,7 +33977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="26">
         <v>2</v>
       </c>
@@ -31210,7 +33991,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="26">
         <v>2</v>
       </c>
@@ -31224,7 +34005,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="26">
         <v>2</v>
       </c>
@@ -31238,7 +34019,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="26">
         <v>2</v>
       </c>
@@ -31252,7 +34033,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="26">
         <v>2</v>
       </c>
@@ -31266,7 +34047,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="26">
         <v>2</v>
       </c>
@@ -31280,7 +34061,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="26">
         <v>2</v>
       </c>
@@ -31294,7 +34075,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="26">
         <v>2</v>
       </c>
@@ -31308,7 +34089,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="26">
         <v>2</v>
       </c>
@@ -31322,7 +34103,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="26">
         <v>2</v>
       </c>
@@ -31336,7 +34117,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="26">
         <v>2</v>
       </c>
@@ -31350,7 +34131,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="26">
         <v>2</v>
       </c>
@@ -31364,7 +34145,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="26">
         <v>2</v>
       </c>
@@ -31378,7 +34159,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="26">
         <v>3</v>
       </c>
@@ -31392,7 +34173,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="26">
         <v>3</v>
       </c>
@@ -31406,7 +34187,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="26">
         <v>3</v>
       </c>
@@ -31420,7 +34201,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="26">
         <v>3</v>
       </c>
@@ -31434,7 +34215,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="26">
         <v>3</v>
       </c>
@@ -31448,7 +34229,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="26">
         <v>3</v>
       </c>
@@ -31462,7 +34243,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="26">
         <v>3</v>
       </c>
@@ -31476,7 +34257,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="26">
         <v>3</v>
       </c>
@@ -31490,7 +34271,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="26">
         <v>3</v>
       </c>
@@ -31504,7 +34285,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="26">
         <v>3</v>
       </c>
@@ -31518,7 +34299,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="26">
         <v>3</v>
       </c>
@@ -31532,7 +34313,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="26">
         <v>3</v>
       </c>
@@ -31546,7 +34327,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="26">
         <v>3</v>
       </c>
@@ -31560,7 +34341,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="26">
         <v>4</v>
       </c>
@@ -31574,7 +34355,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="26">
         <v>4</v>
       </c>
@@ -31588,7 +34369,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="26">
         <v>4</v>
       </c>
@@ -31602,7 +34383,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="26">
         <v>4</v>
       </c>
@@ -31616,7 +34397,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="26">
         <v>4</v>
       </c>
@@ -31630,7 +34411,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="26">
         <v>4</v>
       </c>
@@ -31644,7 +34425,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="26">
         <v>4</v>
       </c>
@@ -31658,7 +34439,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="26">
         <v>4</v>
       </c>
@@ -31672,7 +34453,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="26">
         <v>4</v>
       </c>
@@ -31686,7 +34467,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="26">
         <v>4</v>
       </c>

--- a/documentos/EVALUACIONES MNM 2025.xlsx
+++ b/documentos/EVALUACIONES MNM 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raúl\Dropbox (Personal)\2025\RESPALDO DE BASE DE DATOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCE9CD2-CF0D-4168-87A5-22C08116E03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21FB2E0-33F9-4D17-BFD2-18FD021982C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORTE" sheetId="5" r:id="rId1"/>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="231">
   <si>
     <t>NOMBRE DEL ALUMNO</t>
   </si>
@@ -882,6 +882,42 @@
   <si>
     <t>Jose Alejandro Peña Angulo</t>
   </si>
+  <si>
+    <t>Geraldine Alvarez</t>
+  </si>
+  <si>
+    <t>Thomas Urrea Alvarez</t>
+  </si>
+  <si>
+    <t>Isabela Camarillo Pinto</t>
+  </si>
+  <si>
+    <t>Juan Andres Pineda</t>
+  </si>
+  <si>
+    <t>Alejandra Guzman Perez</t>
+  </si>
+  <si>
+    <t>Luis Alejandro Hernandez Ozuna</t>
+  </si>
+  <si>
+    <t>Salma Suarez Cogollo</t>
+  </si>
+  <si>
+    <t>Erika Zuñiga</t>
+  </si>
+  <si>
+    <t>Joan giraldo</t>
+  </si>
+  <si>
+    <t>Juan Quintana</t>
+  </si>
+  <si>
+    <t>Cesar Lopez Gonzalez</t>
+  </si>
+  <si>
+    <t>Geraldine Sofia Diaz Montes</t>
+  </si>
 </sst>
 </file>
 
@@ -1013,7 +1049,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1142,9 +1178,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1156,6 +1189,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1786,427 +1825,6 @@
       </font>
       <fill>
         <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
@@ -2723,6 +2341,427 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3285,7 +3324,7 @@
                   <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -3488,7 +3527,7 @@
                   <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -3691,7 +3730,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -4094,7 +4133,7 @@
                         <c:v>51</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>63</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -4262,7 +4301,7 @@
                         <c:v>9</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>5</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -4430,7 +4469,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>5</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -4603,7 +4642,7 @@
                         <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -5041,7 +5080,7 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -5249,7 +5288,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -5406,7 +5445,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -5587,7 +5626,7 @@
                         <c:v>51</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>63</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -5755,7 +5794,7 @@
                         <c:v>24</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>28</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -5928,7 +5967,7 @@
                         <c:v>23</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>32</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -6101,7 +6140,7 @@
                         <c:v>4</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>3</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -6776,7 +6815,7 @@
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -6962,7 +7001,7 @@
                         <c:v>24</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>28</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -7135,7 +7174,7 @@
                         <c:v>9</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>5</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -7308,7 +7347,7 @@
                         <c:v>23</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>32</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -7481,7 +7520,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>5</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -7654,7 +7693,7 @@
                         <c:v>4</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>3</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -7827,7 +7866,7 @@
                         <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -12351,37 +12390,37 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O187" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57" tableBorderDxfId="56">
-  <autoFilter ref="A2:O187" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O187">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O216" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40" tableBorderDxfId="39">
+  <autoFilter ref="A2:O216" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O216">
     <sortCondition ref="D3:D107"/>
     <sortCondition ref="A3:A107"/>
     <sortCondition ref="F3:F107"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="55">
+    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="38">
       <calculatedColumnFormula>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="54">
+    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="37">
       <calculatedColumnFormula>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="53">
+    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="36">
       <calculatedColumnFormula>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="47"/>
-    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="45"/>
-    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="43"/>
-    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="42">
+    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="27"/>
+    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="25">
       <calculatedColumnFormula>AVERAGE('NIVEL 1'!G3:M3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="41">
+    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="24">
       <calculatedColumnFormula>IF(N3=" "," ",IF(N3&gt;=4.7,"CAMBIA A NIVEL 2"," "))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12390,36 +12429,36 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O156" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
-  <autoFilter ref="A2:O156" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O156">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O188" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
+  <autoFilter ref="A2:O188" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O188">
     <sortCondition ref="A3:A101"/>
     <sortCondition ref="F3:F101"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="38">
+    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="62">
       <calculatedColumnFormula>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="37">
+    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="61">
       <calculatedColumnFormula>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="36">
+    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="60">
       <calculatedColumnFormula>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="28"/>
-    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="27"/>
-    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="26"/>
-    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="25">
+    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="54"/>
+    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="53"/>
+    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="52"/>
+    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="51"/>
+    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="50"/>
+    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="49">
       <calculatedColumnFormula>AVERAGE('NIVEL 2'!G3:M3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="24">
+    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="48">
       <calculatedColumnFormula>IF(N3=" "," ",IF(N3&gt;=4.7,"CAMBIA A NIVEL 3"," "))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12428,9 +12467,9 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U41" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
-  <autoFilter ref="A2:U41" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U44" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
+  <autoFilter ref="A2:U44" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U44">
     <sortCondition ref="A3"/>
     <sortCondition ref="F3"/>
   </sortState>
@@ -12472,17 +12511,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D38" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D38" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
   <autoFilter ref="A2:D38" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D33">
     <sortCondition ref="A3"/>
     <sortCondition ref="D3"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="62"/>
-    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="60"/>
-    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13091,31 +13130,31 @@
       </c>
       <c r="B10" s="17">
         <f>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C10" s="17">
         <f>COUNTIF('NIVEL 1'!$C:$C,REPORTE!A10)</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D10" s="17">
         <f>COUNTIFS('NIVEL 1'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$O:$O,"CAMBIA A NIVEL 2")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E10" s="17">
         <f>COUNTIF('NIVEL 2'!$C:$C,REPORTE!A10)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F10" s="17">
         <f>COUNTIFS('NIVEL 2'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$O:$O,"CAMBIA A NIVEL 3")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" s="17">
         <f>COUNTIF('NIVEL 3'!$C:$C,REPORTE!A10)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" s="17">
         <f>COUNTIFS('NIVEL 3'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$U:$U,"CAMBIA A EQUIPO")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" s="17">
         <f>COUNTIF(EQUIPO!$C:$C,REPORTE!A10)</f>
@@ -13251,7 +13290,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O187"/>
+  <dimension ref="A1:O216"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" customWidth="1"/>
@@ -21707,1252 +21746,2725 @@
       </c>
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A164" s="42">
+      <c r="A164" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B164" s="43" t="str">
+      <c r="B164" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C164" s="43" t="str">
+      <c r="C164" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D164" s="45">
+      <c r="D164" s="3">
         <v>45899</v>
       </c>
-      <c r="E164" s="46" t="s">
+      <c r="E164" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="F164" s="47">
+      <c r="F164" s="1">
         <v>1001452225</v>
       </c>
-      <c r="G164" s="48">
-        <v>5</v>
-      </c>
-      <c r="H164" s="48">
-        <v>5</v>
-      </c>
-      <c r="I164" s="48">
-        <v>4</v>
-      </c>
-      <c r="J164" s="48">
-        <v>3</v>
-      </c>
-      <c r="K164" s="48">
-        <v>4</v>
-      </c>
-      <c r="L164" s="48">
-        <v>3</v>
-      </c>
-      <c r="M164" s="48">
+      <c r="G164" s="1">
+        <v>5</v>
+      </c>
+      <c r="H164" s="1">
+        <v>5</v>
+      </c>
+      <c r="I164" s="1">
+        <v>4</v>
+      </c>
+      <c r="J164" s="1">
+        <v>3</v>
+      </c>
+      <c r="K164" s="1">
+        <v>4</v>
+      </c>
+      <c r="L164" s="1">
+        <v>3</v>
+      </c>
+      <c r="M164" s="1">
         <v>3</v>
       </c>
       <c r="N164" s="19">
         <f>AVERAGE('NIVEL 1'!G164:M164)</f>
         <v>3.8571428571428572</v>
       </c>
-      <c r="O164" s="44" t="str">
+      <c r="O164" s="18" t="str">
         <f>IF(N164=" "," ",IF(N164&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A165" s="42">
+      <c r="A165" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B165" s="43" t="str">
+      <c r="B165" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C165" s="43" t="str">
+      <c r="C165" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D165" s="45">
+      <c r="D165" s="3">
         <v>45899</v>
       </c>
-      <c r="E165" s="46" t="s">
+      <c r="E165" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="F165" s="47">
+      <c r="F165" s="1">
         <v>1001481017</v>
       </c>
-      <c r="G165" s="48">
-        <v>5</v>
-      </c>
-      <c r="H165" s="48">
-        <v>5</v>
-      </c>
-      <c r="I165" s="48">
-        <v>5</v>
-      </c>
-      <c r="J165" s="48">
-        <v>5</v>
-      </c>
-      <c r="K165" s="48">
-        <v>4</v>
-      </c>
-      <c r="L165" s="48">
-        <v>4</v>
-      </c>
-      <c r="M165" s="48">
+      <c r="G165" s="1">
+        <v>5</v>
+      </c>
+      <c r="H165" s="1">
+        <v>5</v>
+      </c>
+      <c r="I165" s="1">
+        <v>5</v>
+      </c>
+      <c r="J165" s="1">
+        <v>5</v>
+      </c>
+      <c r="K165" s="1">
+        <v>4</v>
+      </c>
+      <c r="L165" s="1">
+        <v>4</v>
+      </c>
+      <c r="M165" s="1">
         <v>5</v>
       </c>
       <c r="N165" s="19">
         <f>AVERAGE('NIVEL 1'!G165:M165)</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O165" s="44" t="str">
+      <c r="O165" s="18" t="str">
         <f>IF(N165=" "," ",IF(N165&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A166" s="42">
+      <c r="A166" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B166" s="43" t="str">
+      <c r="B166" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C166" s="43" t="str">
+      <c r="C166" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D166" s="45">
+      <c r="D166" s="3">
         <v>45899</v>
       </c>
-      <c r="E166" s="46" t="s">
+      <c r="E166" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F166" s="47">
+      <c r="F166" s="1">
         <v>1003049821</v>
       </c>
-      <c r="G166" s="48">
-        <v>5</v>
-      </c>
-      <c r="H166" s="48">
-        <v>5</v>
-      </c>
-      <c r="I166" s="48">
-        <v>5</v>
-      </c>
-      <c r="J166" s="48">
-        <v>5</v>
-      </c>
-      <c r="K166" s="48">
-        <v>5</v>
-      </c>
-      <c r="L166" s="48">
-        <v>4</v>
-      </c>
-      <c r="M166" s="48">
+      <c r="G166" s="1">
+        <v>5</v>
+      </c>
+      <c r="H166" s="1">
+        <v>5</v>
+      </c>
+      <c r="I166" s="1">
+        <v>5</v>
+      </c>
+      <c r="J166" s="1">
+        <v>5</v>
+      </c>
+      <c r="K166" s="1">
+        <v>5</v>
+      </c>
+      <c r="L166" s="1">
+        <v>4</v>
+      </c>
+      <c r="M166" s="1">
         <v>5</v>
       </c>
       <c r="N166" s="19">
         <f>AVERAGE('NIVEL 1'!G166:M166)</f>
         <v>4.8571428571428568</v>
       </c>
-      <c r="O166" s="44" t="str">
+      <c r="O166" s="18" t="str">
         <f>IF(N166=" "," ",IF(N166&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A167" s="42">
+      <c r="A167" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B167" s="43" t="str">
+      <c r="B167" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C167" s="43" t="str">
+      <c r="C167" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D167" s="45">
+      <c r="D167" s="3">
         <v>45899</v>
       </c>
-      <c r="E167" s="46" t="s">
+      <c r="E167" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="F167" s="47">
+      <c r="F167" s="1">
         <v>1034788626</v>
       </c>
-      <c r="G167" s="48">
-        <v>5</v>
-      </c>
-      <c r="H167" s="48">
-        <v>5</v>
-      </c>
-      <c r="I167" s="48">
-        <v>5</v>
-      </c>
-      <c r="J167" s="48">
-        <v>5</v>
-      </c>
-      <c r="K167" s="48">
-        <v>5</v>
-      </c>
-      <c r="L167" s="48">
-        <v>4</v>
-      </c>
-      <c r="M167" s="48">
+      <c r="G167" s="1">
+        <v>5</v>
+      </c>
+      <c r="H167" s="1">
+        <v>5</v>
+      </c>
+      <c r="I167" s="1">
+        <v>5</v>
+      </c>
+      <c r="J167" s="1">
+        <v>5</v>
+      </c>
+      <c r="K167" s="1">
+        <v>5</v>
+      </c>
+      <c r="L167" s="1">
+        <v>4</v>
+      </c>
+      <c r="M167" s="1">
         <v>5</v>
       </c>
       <c r="N167" s="19">
         <f>AVERAGE('NIVEL 1'!G167:M167)</f>
         <v>4.8571428571428568</v>
       </c>
-      <c r="O167" s="44" t="str">
+      <c r="O167" s="18" t="str">
         <f>IF(N167=" "," ",IF(N167&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A168" s="42">
+      <c r="A168" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B168" s="43" t="str">
+      <c r="B168" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C168" s="43" t="str">
+      <c r="C168" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D168" s="45">
+      <c r="D168" s="3">
         <v>45899</v>
       </c>
-      <c r="E168" s="46" t="s">
+      <c r="E168" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F168" s="47">
+      <c r="F168" s="1">
         <v>1044227121</v>
       </c>
-      <c r="G168" s="48">
-        <v>5</v>
-      </c>
-      <c r="H168" s="48">
-        <v>5</v>
-      </c>
-      <c r="I168" s="48">
-        <v>4</v>
-      </c>
-      <c r="J168" s="48">
-        <v>3</v>
-      </c>
-      <c r="K168" s="48">
-        <v>4</v>
-      </c>
-      <c r="L168" s="48">
-        <v>3</v>
-      </c>
-      <c r="M168" s="48">
+      <c r="G168" s="1">
+        <v>5</v>
+      </c>
+      <c r="H168" s="1">
+        <v>5</v>
+      </c>
+      <c r="I168" s="1">
+        <v>4</v>
+      </c>
+      <c r="J168" s="1">
+        <v>3</v>
+      </c>
+      <c r="K168" s="1">
+        <v>4</v>
+      </c>
+      <c r="L168" s="1">
+        <v>3</v>
+      </c>
+      <c r="M168" s="1">
         <v>5</v>
       </c>
       <c r="N168" s="19">
         <f>AVERAGE('NIVEL 1'!G168:M168)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O168" s="44" t="str">
+      <c r="O168" s="18" t="str">
         <f>IF(N168=" "," ",IF(N168&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A169" s="42">
+      <c r="A169" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B169" s="43" t="str">
+      <c r="B169" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C169" s="43" t="str">
+      <c r="C169" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D169" s="45">
+      <c r="D169" s="3">
         <v>45899</v>
       </c>
-      <c r="E169" s="46" t="s">
+      <c r="E169" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="F169" s="47">
+      <c r="F169" s="1">
         <v>1062529919</v>
       </c>
-      <c r="G169" s="48">
-        <v>5</v>
-      </c>
-      <c r="H169" s="48">
-        <v>3</v>
-      </c>
-      <c r="I169" s="48">
-        <v>2</v>
-      </c>
-      <c r="J169" s="48">
+      <c r="G169" s="1">
+        <v>5</v>
+      </c>
+      <c r="H169" s="1">
+        <v>3</v>
+      </c>
+      <c r="I169" s="1">
+        <v>2</v>
+      </c>
+      <c r="J169" s="1">
         <v>1</v>
       </c>
-      <c r="K169" s="48">
-        <v>2</v>
-      </c>
-      <c r="L169" s="48">
+      <c r="K169" s="1">
+        <v>2</v>
+      </c>
+      <c r="L169" s="1">
         <v>1</v>
       </c>
-      <c r="M169" s="48">
+      <c r="M169" s="1">
         <v>4</v>
       </c>
       <c r="N169" s="19">
         <f>AVERAGE('NIVEL 1'!G169:M169)</f>
         <v>2.5714285714285716</v>
       </c>
-      <c r="O169" s="44" t="str">
+      <c r="O169" s="18" t="str">
         <f>IF(N169=" "," ",IF(N169&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A170" s="42">
+      <c r="A170" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B170" s="43" t="str">
+      <c r="B170" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C170" s="43" t="str">
+      <c r="C170" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D170" s="45">
+      <c r="D170" s="3">
         <v>45899</v>
       </c>
-      <c r="E170" s="46" t="s">
+      <c r="E170" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="F170" s="47">
+      <c r="F170" s="1">
         <v>1062531558</v>
       </c>
-      <c r="G170" s="48">
-        <v>5</v>
-      </c>
-      <c r="H170" s="48">
-        <v>3</v>
-      </c>
-      <c r="I170" s="48">
-        <v>2</v>
-      </c>
-      <c r="J170" s="48">
+      <c r="G170" s="1">
+        <v>5</v>
+      </c>
+      <c r="H170" s="1">
+        <v>3</v>
+      </c>
+      <c r="I170" s="1">
+        <v>2</v>
+      </c>
+      <c r="J170" s="1">
         <v>1</v>
       </c>
-      <c r="K170" s="48">
-        <v>2</v>
-      </c>
-      <c r="L170" s="48">
+      <c r="K170" s="1">
+        <v>2</v>
+      </c>
+      <c r="L170" s="1">
         <v>1</v>
       </c>
-      <c r="M170" s="48">
+      <c r="M170" s="1">
         <v>4</v>
       </c>
       <c r="N170" s="19">
         <f>AVERAGE('NIVEL 1'!G170:M170)</f>
         <v>2.5714285714285716</v>
       </c>
-      <c r="O170" s="44" t="str">
+      <c r="O170" s="18" t="str">
         <f>IF(N170=" "," ",IF(N170&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A171" s="42">
+      <c r="A171" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B171" s="43" t="str">
+      <c r="B171" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C171" s="43" t="str">
+      <c r="C171" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D171" s="45">
+      <c r="D171" s="3">
         <v>45899</v>
       </c>
-      <c r="E171" s="46" t="s">
+      <c r="E171" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="F171" s="47">
+      <c r="F171" s="1">
         <v>1062540642</v>
       </c>
-      <c r="G171" s="48">
-        <v>5</v>
-      </c>
-      <c r="H171" s="48">
-        <v>3</v>
-      </c>
-      <c r="I171" s="48">
-        <v>2</v>
-      </c>
-      <c r="J171" s="48">
+      <c r="G171" s="1">
+        <v>5</v>
+      </c>
+      <c r="H171" s="1">
+        <v>3</v>
+      </c>
+      <c r="I171" s="1">
+        <v>2</v>
+      </c>
+      <c r="J171" s="1">
         <v>1</v>
       </c>
-      <c r="K171" s="48">
-        <v>2</v>
-      </c>
-      <c r="L171" s="48">
+      <c r="K171" s="1">
+        <v>2</v>
+      </c>
+      <c r="L171" s="1">
         <v>1</v>
       </c>
-      <c r="M171" s="48">
+      <c r="M171" s="1">
         <v>4</v>
       </c>
       <c r="N171" s="19">
         <f>AVERAGE('NIVEL 1'!G171:M171)</f>
         <v>2.5714285714285716</v>
       </c>
-      <c r="O171" s="44" t="str">
+      <c r="O171" s="18" t="str">
         <f>IF(N171=" "," ",IF(N171&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A172" s="42">
+      <c r="A172" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B172" s="43" t="str">
+      <c r="B172" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C172" s="43" t="str">
+      <c r="C172" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D172" s="45">
+      <c r="D172" s="3">
         <v>45899</v>
       </c>
-      <c r="E172" s="46" t="s">
+      <c r="E172" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="F172" s="47">
+      <c r="F172" s="1">
         <v>1062544508</v>
       </c>
-      <c r="G172" s="48">
-        <v>5</v>
-      </c>
-      <c r="H172" s="48">
-        <v>5</v>
-      </c>
-      <c r="I172" s="48">
-        <v>3</v>
-      </c>
-      <c r="J172" s="48">
-        <v>3</v>
-      </c>
-      <c r="K172" s="48">
-        <v>3</v>
-      </c>
-      <c r="L172" s="48">
-        <v>3</v>
-      </c>
-      <c r="M172" s="48">
+      <c r="G172" s="1">
+        <v>5</v>
+      </c>
+      <c r="H172" s="1">
+        <v>5</v>
+      </c>
+      <c r="I172" s="1">
+        <v>3</v>
+      </c>
+      <c r="J172" s="1">
+        <v>3</v>
+      </c>
+      <c r="K172" s="1">
+        <v>3</v>
+      </c>
+      <c r="L172" s="1">
+        <v>3</v>
+      </c>
+      <c r="M172" s="1">
         <v>5</v>
       </c>
       <c r="N172" s="19">
         <f>AVERAGE('NIVEL 1'!G172:M172)</f>
         <v>3.8571428571428572</v>
       </c>
-      <c r="O172" s="44" t="str">
+      <c r="O172" s="18" t="str">
         <f>IF(N172=" "," ",IF(N172&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A173" s="42">
+      <c r="A173" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B173" s="43" t="str">
+      <c r="B173" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C173" s="43" t="str">
+      <c r="C173" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D173" s="45">
+      <c r="D173" s="3">
         <v>45899</v>
       </c>
-      <c r="E173" s="46" t="s">
+      <c r="E173" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="F173" s="47">
+      <c r="F173" s="1">
         <v>1066523010</v>
       </c>
-      <c r="G173" s="48">
-        <v>5</v>
-      </c>
-      <c r="H173" s="48">
-        <v>5</v>
-      </c>
-      <c r="I173" s="48">
-        <v>5</v>
-      </c>
-      <c r="J173" s="48">
-        <v>4</v>
-      </c>
-      <c r="K173" s="48">
-        <v>5</v>
-      </c>
-      <c r="L173" s="48">
-        <v>4</v>
-      </c>
-      <c r="M173" s="48">
+      <c r="G173" s="1">
+        <v>5</v>
+      </c>
+      <c r="H173" s="1">
+        <v>5</v>
+      </c>
+      <c r="I173" s="1">
+        <v>5</v>
+      </c>
+      <c r="J173" s="1">
+        <v>4</v>
+      </c>
+      <c r="K173" s="1">
+        <v>5</v>
+      </c>
+      <c r="L173" s="1">
+        <v>4</v>
+      </c>
+      <c r="M173" s="1">
         <v>5</v>
       </c>
       <c r="N173" s="19">
         <f>AVERAGE('NIVEL 1'!G173:M173)</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O173" s="44" t="str">
+      <c r="O173" s="18" t="str">
         <f>IF(N173=" "," ",IF(N173&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A174" s="42">
+      <c r="A174" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B174" s="43" t="str">
+      <c r="B174" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C174" s="43" t="str">
+      <c r="C174" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D174" s="45">
+      <c r="D174" s="3">
         <v>45899</v>
       </c>
-      <c r="E174" s="46" t="s">
+      <c r="E174" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="F174" s="47">
+      <c r="F174" s="1">
         <v>1067859838</v>
       </c>
-      <c r="G174" s="48">
-        <v>5</v>
-      </c>
-      <c r="H174" s="48">
-        <v>3</v>
-      </c>
-      <c r="I174" s="48">
-        <v>2</v>
-      </c>
-      <c r="J174" s="48">
-        <v>2</v>
-      </c>
-      <c r="K174" s="48">
+      <c r="G174" s="1">
+        <v>5</v>
+      </c>
+      <c r="H174" s="1">
+        <v>3</v>
+      </c>
+      <c r="I174" s="1">
+        <v>2</v>
+      </c>
+      <c r="J174" s="1">
+        <v>2</v>
+      </c>
+      <c r="K174" s="1">
         <v>1</v>
       </c>
-      <c r="L174" s="48">
+      <c r="L174" s="1">
         <v>1</v>
       </c>
-      <c r="M174" s="48">
+      <c r="M174" s="1">
         <v>2</v>
       </c>
       <c r="N174" s="19">
         <f>AVERAGE('NIVEL 1'!G174:M174)</f>
         <v>2.2857142857142856</v>
       </c>
-      <c r="O174" s="44" t="str">
+      <c r="O174" s="18" t="str">
         <f>IF(N174=" "," ",IF(N174&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A175" s="42">
+      <c r="A175" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B175" s="43" t="str">
+      <c r="B175" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C175" s="43" t="str">
+      <c r="C175" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D175" s="45">
+      <c r="D175" s="3">
         <v>45899</v>
       </c>
-      <c r="E175" s="46" t="s">
+      <c r="E175" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="F175" s="47">
+      <c r="F175" s="1">
         <v>1067872776</v>
       </c>
-      <c r="G175" s="48">
-        <v>5</v>
-      </c>
-      <c r="H175" s="48">
-        <v>5</v>
-      </c>
-      <c r="I175" s="48">
-        <v>5</v>
-      </c>
-      <c r="J175" s="48">
-        <v>5</v>
-      </c>
-      <c r="K175" s="48">
-        <v>4</v>
-      </c>
-      <c r="L175" s="48">
-        <v>4</v>
-      </c>
-      <c r="M175" s="48">
+      <c r="G175" s="1">
+        <v>5</v>
+      </c>
+      <c r="H175" s="1">
+        <v>5</v>
+      </c>
+      <c r="I175" s="1">
+        <v>5</v>
+      </c>
+      <c r="J175" s="1">
+        <v>5</v>
+      </c>
+      <c r="K175" s="1">
+        <v>4</v>
+      </c>
+      <c r="L175" s="1">
+        <v>4</v>
+      </c>
+      <c r="M175" s="1">
         <v>5</v>
       </c>
       <c r="N175" s="19">
         <f>AVERAGE('NIVEL 1'!G175:M175)</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O175" s="44" t="str">
+      <c r="O175" s="18" t="str">
         <f>IF(N175=" "," ",IF(N175&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A176" s="42">
+      <c r="A176" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B176" s="43" t="str">
+      <c r="B176" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C176" s="43" t="str">
+      <c r="C176" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D176" s="45">
+      <c r="D176" s="3">
         <v>45899</v>
       </c>
-      <c r="E176" s="46" t="s">
+      <c r="E176" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="F176" s="47">
+      <c r="F176" s="1">
         <v>1067903477</v>
       </c>
-      <c r="G176" s="48">
-        <v>5</v>
-      </c>
-      <c r="H176" s="48">
-        <v>5</v>
-      </c>
-      <c r="I176" s="48">
-        <v>5</v>
-      </c>
-      <c r="J176" s="48">
-        <v>5</v>
-      </c>
-      <c r="K176" s="48">
-        <v>4</v>
-      </c>
-      <c r="L176" s="48">
-        <v>4</v>
-      </c>
-      <c r="M176" s="48">
+      <c r="G176" s="1">
+        <v>5</v>
+      </c>
+      <c r="H176" s="1">
+        <v>5</v>
+      </c>
+      <c r="I176" s="1">
+        <v>5</v>
+      </c>
+      <c r="J176" s="1">
+        <v>5</v>
+      </c>
+      <c r="K176" s="1">
+        <v>4</v>
+      </c>
+      <c r="L176" s="1">
+        <v>4</v>
+      </c>
+      <c r="M176" s="1">
         <v>5</v>
       </c>
       <c r="N176" s="19">
         <f>AVERAGE('NIVEL 1'!G176:M176)</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O176" s="44" t="str">
+      <c r="O176" s="18" t="str">
         <f>IF(N176=" "," ",IF(N176&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A177" s="42">
+      <c r="A177" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B177" s="43" t="str">
+      <c r="B177" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C177" s="43" t="str">
+      <c r="C177" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D177" s="45">
+      <c r="D177" s="3">
         <v>45899</v>
       </c>
-      <c r="E177" s="46" t="s">
+      <c r="E177" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="F177" s="47">
+      <c r="F177" s="1">
         <v>1068444523</v>
       </c>
-      <c r="G177" s="48">
-        <v>5</v>
-      </c>
-      <c r="H177" s="48">
-        <v>4</v>
-      </c>
-      <c r="I177" s="48">
-        <v>3</v>
-      </c>
-      <c r="J177" s="48">
+      <c r="G177" s="1">
+        <v>5</v>
+      </c>
+      <c r="H177" s="1">
+        <v>4</v>
+      </c>
+      <c r="I177" s="1">
+        <v>3</v>
+      </c>
+      <c r="J177" s="1">
         <v>1</v>
       </c>
-      <c r="K177" s="48">
-        <v>3</v>
-      </c>
-      <c r="L177" s="48">
+      <c r="K177" s="1">
+        <v>3</v>
+      </c>
+      <c r="L177" s="1">
         <v>1</v>
       </c>
-      <c r="M177" s="48">
+      <c r="M177" s="1">
         <v>5</v>
       </c>
       <c r="N177" s="19">
         <f>AVERAGE('NIVEL 1'!G177:M177)</f>
         <v>3.1428571428571428</v>
       </c>
-      <c r="O177" s="44" t="str">
+      <c r="O177" s="18" t="str">
         <f>IF(N177=" "," ",IF(N177&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A178" s="42">
+      <c r="A178" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B178" s="43" t="str">
+      <c r="B178" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C178" s="43" t="str">
+      <c r="C178" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D178" s="45">
+      <c r="D178" s="3">
         <v>45899</v>
       </c>
-      <c r="E178" s="46" t="s">
+      <c r="E178" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="F178" s="47">
+      <c r="F178" s="1">
         <v>1073817245</v>
       </c>
-      <c r="G178" s="48">
-        <v>5</v>
-      </c>
-      <c r="H178" s="48">
-        <v>5</v>
-      </c>
-      <c r="I178" s="48">
-        <v>5</v>
-      </c>
-      <c r="J178" s="48">
-        <v>4</v>
-      </c>
-      <c r="K178" s="48">
-        <v>5</v>
-      </c>
-      <c r="L178" s="48">
-        <v>4</v>
-      </c>
-      <c r="M178" s="48">
+      <c r="G178" s="1">
+        <v>5</v>
+      </c>
+      <c r="H178" s="1">
+        <v>5</v>
+      </c>
+      <c r="I178" s="1">
+        <v>5</v>
+      </c>
+      <c r="J178" s="1">
+        <v>4</v>
+      </c>
+      <c r="K178" s="1">
+        <v>5</v>
+      </c>
+      <c r="L178" s="1">
+        <v>4</v>
+      </c>
+      <c r="M178" s="1">
         <v>5</v>
       </c>
       <c r="N178" s="19">
         <f>AVERAGE('NIVEL 1'!G178:M178)</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O178" s="44" t="str">
+      <c r="O178" s="18" t="str">
         <f>IF(N178=" "," ",IF(N178&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A179" s="42">
+      <c r="A179" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B179" s="43" t="str">
+      <c r="B179" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C179" s="43" t="str">
+      <c r="C179" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D179" s="45">
+      <c r="D179" s="3">
         <v>45899</v>
       </c>
-      <c r="E179" s="46" t="s">
+      <c r="E179" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="F179" s="47">
+      <c r="F179" s="1">
         <v>1074002401</v>
       </c>
-      <c r="G179" s="48">
-        <v>5</v>
-      </c>
-      <c r="H179" s="48">
-        <v>5</v>
-      </c>
-      <c r="I179" s="48">
-        <v>3</v>
-      </c>
-      <c r="J179" s="48">
+      <c r="G179" s="1">
+        <v>5</v>
+      </c>
+      <c r="H179" s="1">
+        <v>5</v>
+      </c>
+      <c r="I179" s="1">
+        <v>3</v>
+      </c>
+      <c r="J179" s="1">
         <v>1</v>
       </c>
-      <c r="K179" s="48">
-        <v>3</v>
-      </c>
-      <c r="L179" s="48">
+      <c r="K179" s="1">
+        <v>3</v>
+      </c>
+      <c r="L179" s="1">
         <v>1</v>
       </c>
-      <c r="M179" s="48">
+      <c r="M179" s="1">
         <v>5</v>
       </c>
       <c r="N179" s="19">
         <f>AVERAGE('NIVEL 1'!G179:M179)</f>
         <v>3.2857142857142856</v>
       </c>
-      <c r="O179" s="44" t="str">
+      <c r="O179" s="18" t="str">
         <f>IF(N179=" "," ",IF(N179&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A180" s="42">
+      <c r="A180" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B180" s="43" t="str">
+      <c r="B180" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C180" s="43" t="str">
+      <c r="C180" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D180" s="45">
+      <c r="D180" s="3">
         <v>45899</v>
       </c>
-      <c r="E180" s="46" t="s">
+      <c r="E180" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="F180" s="47">
+      <c r="F180" s="1">
         <v>1126253349</v>
       </c>
-      <c r="G180" s="48">
-        <v>5</v>
-      </c>
-      <c r="H180" s="48">
+      <c r="G180" s="1">
+        <v>5</v>
+      </c>
+      <c r="H180" s="1">
         <v>1</v>
       </c>
-      <c r="I180" s="48">
+      <c r="I180" s="1">
         <v>1</v>
       </c>
-      <c r="J180" s="48">
+      <c r="J180" s="1">
         <v>1</v>
       </c>
-      <c r="K180" s="48">
+      <c r="K180" s="1">
         <v>1</v>
       </c>
-      <c r="L180" s="48">
+      <c r="L180" s="1">
         <v>1</v>
       </c>
-      <c r="M180" s="48">
+      <c r="M180" s="1">
         <v>1</v>
       </c>
       <c r="N180" s="19">
         <f>AVERAGE('NIVEL 1'!G180:M180)</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="O180" s="44" t="str">
+      <c r="O180" s="18" t="str">
         <f>IF(N180=" "," ",IF(N180&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A181" s="42">
+      <c r="A181" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B181" s="43" t="str">
+      <c r="B181" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C181" s="43" t="str">
+      <c r="C181" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D181" s="45">
+      <c r="D181" s="3">
         <v>45899</v>
       </c>
-      <c r="E181" s="46" t="s">
+      <c r="E181" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="F181" s="47">
+      <c r="F181" s="1">
         <v>1137975547</v>
       </c>
-      <c r="G181" s="48">
-        <v>5</v>
-      </c>
-      <c r="H181" s="48">
-        <v>4</v>
-      </c>
-      <c r="I181" s="48">
-        <v>2</v>
-      </c>
-      <c r="J181" s="48">
-        <v>2</v>
-      </c>
-      <c r="K181" s="48">
+      <c r="G181" s="1">
+        <v>5</v>
+      </c>
+      <c r="H181" s="1">
+        <v>4</v>
+      </c>
+      <c r="I181" s="1">
+        <v>2</v>
+      </c>
+      <c r="J181" s="1">
+        <v>2</v>
+      </c>
+      <c r="K181" s="1">
         <v>1</v>
       </c>
-      <c r="L181" s="48">
+      <c r="L181" s="1">
         <v>1</v>
       </c>
-      <c r="M181" s="48">
+      <c r="M181" s="1">
         <v>2</v>
       </c>
       <c r="N181" s="19">
         <f>AVERAGE('NIVEL 1'!G181:M181)</f>
         <v>2.4285714285714284</v>
       </c>
-      <c r="O181" s="44" t="str">
+      <c r="O181" s="18" t="str">
         <f>IF(N181=" "," ",IF(N181&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A182" s="42">
+      <c r="A182" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B182" s="43" t="str">
+      <c r="B182" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C182" s="43" t="str">
+      <c r="C182" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D182" s="45">
+      <c r="D182" s="3">
         <v>45899</v>
       </c>
-      <c r="E182" s="46" t="s">
+      <c r="E182" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="F182" s="47">
+      <c r="F182" s="1">
         <v>1138031947</v>
       </c>
-      <c r="G182" s="48">
-        <v>5</v>
-      </c>
-      <c r="H182" s="48">
-        <v>5</v>
-      </c>
-      <c r="I182" s="48">
-        <v>3</v>
-      </c>
-      <c r="J182" s="48">
-        <v>2</v>
-      </c>
-      <c r="K182" s="48">
-        <v>3</v>
-      </c>
-      <c r="L182" s="48">
-        <v>2</v>
-      </c>
-      <c r="M182" s="48">
+      <c r="G182" s="1">
+        <v>5</v>
+      </c>
+      <c r="H182" s="1">
+        <v>5</v>
+      </c>
+      <c r="I182" s="1">
+        <v>3</v>
+      </c>
+      <c r="J182" s="1">
+        <v>2</v>
+      </c>
+      <c r="K182" s="1">
+        <v>3</v>
+      </c>
+      <c r="L182" s="1">
+        <v>2</v>
+      </c>
+      <c r="M182" s="1">
         <v>5</v>
       </c>
       <c r="N182" s="19">
         <f>AVERAGE('NIVEL 1'!G182:M182)</f>
         <v>3.5714285714285716</v>
       </c>
-      <c r="O182" s="44" t="str">
+      <c r="O182" s="18" t="str">
         <f>IF(N182=" "," ",IF(N182&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A183" s="42">
+      <c r="A183" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B183" s="43" t="str">
+      <c r="B183" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C183" s="43" t="str">
+      <c r="C183" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D183" s="45">
+      <c r="D183" s="3">
         <v>45899</v>
       </c>
-      <c r="E183" s="46" t="s">
+      <c r="E183" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F183" s="47">
+      <c r="F183" s="1">
         <v>1138032549</v>
       </c>
-      <c r="G183" s="48">
-        <v>5</v>
-      </c>
-      <c r="H183" s="48">
-        <v>5</v>
-      </c>
-      <c r="I183" s="48">
-        <v>5</v>
-      </c>
-      <c r="J183" s="48">
-        <v>4</v>
-      </c>
-      <c r="K183" s="48">
-        <v>4</v>
-      </c>
-      <c r="L183" s="48">
-        <v>4</v>
-      </c>
-      <c r="M183" s="48">
+      <c r="G183" s="1">
+        <v>5</v>
+      </c>
+      <c r="H183" s="1">
+        <v>5</v>
+      </c>
+      <c r="I183" s="1">
+        <v>5</v>
+      </c>
+      <c r="J183" s="1">
+        <v>4</v>
+      </c>
+      <c r="K183" s="1">
+        <v>4</v>
+      </c>
+      <c r="L183" s="1">
+        <v>4</v>
+      </c>
+      <c r="M183" s="1">
         <v>5</v>
       </c>
       <c r="N183" s="19">
         <f>AVERAGE('NIVEL 1'!G183:M183)</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O183" s="44" t="str">
+      <c r="O183" s="18" t="str">
         <f>IF(N183=" "," ",IF(N183&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A184" s="42">
+      <c r="A184" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B184" s="43" t="str">
+      <c r="B184" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C184" s="43" t="str">
+      <c r="C184" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D184" s="45">
+      <c r="D184" s="3">
         <v>45899</v>
       </c>
-      <c r="E184" s="46" t="s">
+      <c r="E184" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="F184" s="47">
+      <c r="F184" s="1">
         <v>1138032702</v>
       </c>
-      <c r="G184" s="48">
-        <v>5</v>
-      </c>
-      <c r="H184" s="48">
-        <v>3</v>
-      </c>
-      <c r="I184" s="48">
-        <v>2</v>
-      </c>
-      <c r="J184" s="48">
-        <v>2</v>
-      </c>
-      <c r="K184" s="48">
-        <v>2</v>
-      </c>
-      <c r="L184" s="48">
-        <v>2</v>
-      </c>
-      <c r="M184" s="48">
+      <c r="G184" s="1">
+        <v>5</v>
+      </c>
+      <c r="H184" s="1">
+        <v>3</v>
+      </c>
+      <c r="I184" s="1">
+        <v>2</v>
+      </c>
+      <c r="J184" s="1">
+        <v>2</v>
+      </c>
+      <c r="K184" s="1">
+        <v>2</v>
+      </c>
+      <c r="L184" s="1">
+        <v>2</v>
+      </c>
+      <c r="M184" s="1">
         <v>2</v>
       </c>
       <c r="N184" s="19">
         <f>AVERAGE('NIVEL 1'!G184:M184)</f>
         <v>2.5714285714285716</v>
       </c>
-      <c r="O184" s="44" t="str">
+      <c r="O184" s="18" t="str">
         <f>IF(N184=" "," ",IF(N184&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A185" s="42">
+      <c r="A185" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B185" s="43" t="str">
+      <c r="B185" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C185" s="43" t="str">
+      <c r="C185" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D185" s="45">
+      <c r="D185" s="3">
         <v>45899</v>
       </c>
-      <c r="E185" s="46" t="s">
+      <c r="E185" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="F185" s="47">
+      <c r="F185" s="1">
         <v>1141358368</v>
       </c>
-      <c r="G185" s="48">
-        <v>5</v>
-      </c>
-      <c r="H185" s="48">
-        <v>5</v>
-      </c>
-      <c r="I185" s="48">
-        <v>5</v>
-      </c>
-      <c r="J185" s="48">
-        <v>5</v>
-      </c>
-      <c r="K185" s="48">
-        <v>5</v>
-      </c>
-      <c r="L185" s="48">
-        <v>5</v>
-      </c>
-      <c r="M185" s="48">
+      <c r="G185" s="1">
+        <v>5</v>
+      </c>
+      <c r="H185" s="1">
+        <v>5</v>
+      </c>
+      <c r="I185" s="1">
+        <v>5</v>
+      </c>
+      <c r="J185" s="1">
+        <v>5</v>
+      </c>
+      <c r="K185" s="1">
+        <v>5</v>
+      </c>
+      <c r="L185" s="1">
+        <v>5</v>
+      </c>
+      <c r="M185" s="1">
         <v>5</v>
       </c>
       <c r="N185" s="19">
         <f>AVERAGE('NIVEL 1'!G185:M185)</f>
         <v>5</v>
       </c>
-      <c r="O185" s="44" t="str">
+      <c r="O185" s="18" t="str">
         <f>IF(N185=" "," ",IF(N185&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A186" s="42">
+      <c r="A186" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B186" s="43" t="str">
+      <c r="B186" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C186" s="43" t="str">
+      <c r="C186" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D186" s="45">
+      <c r="D186" s="3">
         <v>45899</v>
       </c>
-      <c r="E186" s="46" t="s">
+      <c r="E186" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="F186" s="47">
+      <c r="F186" s="1">
         <v>1243758694</v>
       </c>
-      <c r="G186" s="48">
-        <v>5</v>
-      </c>
-      <c r="H186" s="48">
-        <v>3</v>
-      </c>
-      <c r="I186" s="48">
-        <v>2</v>
-      </c>
-      <c r="J186" s="48">
+      <c r="G186" s="1">
+        <v>5</v>
+      </c>
+      <c r="H186" s="1">
+        <v>3</v>
+      </c>
+      <c r="I186" s="1">
+        <v>2</v>
+      </c>
+      <c r="J186" s="1">
         <v>1</v>
       </c>
-      <c r="K186" s="48">
+      <c r="K186" s="1">
         <v>1</v>
       </c>
-      <c r="L186" s="48">
+      <c r="L186" s="1">
         <v>1</v>
       </c>
-      <c r="M186" s="48">
+      <c r="M186" s="1">
         <v>5</v>
       </c>
       <c r="N186" s="19">
         <f>AVERAGE('NIVEL 1'!G186:M186)</f>
         <v>2.5714285714285716</v>
       </c>
-      <c r="O186" s="44" t="str">
+      <c r="O186" s="18" t="str">
         <f>IF(N186=" "," ",IF(N186&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A187" s="42">
+      <c r="A187" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B187" s="43" t="str">
+      <c r="B187" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C187" s="43" t="str">
+      <c r="C187" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D187" s="45">
+      <c r="D187" s="3">
         <v>45899</v>
       </c>
-      <c r="E187" s="46" t="s">
+      <c r="E187" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="F187" s="47">
+      <c r="F187" s="1">
         <v>3226990961</v>
       </c>
-      <c r="G187" s="48">
-        <v>5</v>
-      </c>
-      <c r="H187" s="48">
-        <v>5</v>
-      </c>
-      <c r="I187" s="48">
-        <v>5</v>
-      </c>
-      <c r="J187" s="48">
-        <v>5</v>
-      </c>
-      <c r="K187" s="48">
-        <v>5</v>
-      </c>
-      <c r="L187" s="48">
-        <v>5</v>
-      </c>
-      <c r="M187" s="48">
+      <c r="G187" s="1">
+        <v>5</v>
+      </c>
+      <c r="H187" s="1">
+        <v>5</v>
+      </c>
+      <c r="I187" s="1">
+        <v>5</v>
+      </c>
+      <c r="J187" s="1">
+        <v>5</v>
+      </c>
+      <c r="K187" s="1">
+        <v>5</v>
+      </c>
+      <c r="L187" s="1">
+        <v>5</v>
+      </c>
+      <c r="M187" s="1">
         <v>5</v>
       </c>
       <c r="N187" s="19">
         <f>AVERAGE('NIVEL 1'!G187:M187)</f>
         <v>5</v>
       </c>
-      <c r="O187" s="44" t="str">
+      <c r="O187" s="18" t="str">
         <f>IF(N187=" "," ",IF(N187&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A188" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B188" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C188" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D188" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E188" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="F188" s="46">
+        <v>4731114</v>
+      </c>
+      <c r="G188" s="47">
+        <v>5</v>
+      </c>
+      <c r="H188" s="47">
+        <v>5</v>
+      </c>
+      <c r="I188" s="47">
+        <v>3</v>
+      </c>
+      <c r="J188" s="47">
+        <v>3</v>
+      </c>
+      <c r="K188" s="47">
+        <v>3</v>
+      </c>
+      <c r="L188" s="47">
+        <v>3</v>
+      </c>
+      <c r="M188" s="47">
+        <v>5</v>
+      </c>
+      <c r="N188" s="19">
+        <f>AVERAGE('NIVEL 1'!G188:M188)</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O188" s="48" t="str">
+        <f>IF(N188=" "," ",IF(N188&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A189" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B189" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C189" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D189" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E189" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="F189" s="46">
+        <v>34968791</v>
+      </c>
+      <c r="G189" s="47">
+        <v>5</v>
+      </c>
+      <c r="H189" s="47">
+        <v>5</v>
+      </c>
+      <c r="I189" s="47">
+        <v>5</v>
+      </c>
+      <c r="J189" s="47">
+        <v>3</v>
+      </c>
+      <c r="K189" s="47">
+        <v>3</v>
+      </c>
+      <c r="L189" s="47">
+        <v>2</v>
+      </c>
+      <c r="M189" s="47">
+        <v>3</v>
+      </c>
+      <c r="N189" s="19">
+        <f>AVERAGE('NIVEL 1'!G189:M189)</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O189" s="48" t="str">
+        <f>IF(N189=" "," ",IF(N189&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A190" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B190" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C190" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D190" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E190" s="45" t="s">
+        <v>229</v>
+      </c>
+      <c r="F190" s="46">
+        <v>80875509</v>
+      </c>
+      <c r="G190" s="47">
+        <v>5</v>
+      </c>
+      <c r="H190" s="47">
+        <v>5</v>
+      </c>
+      <c r="I190" s="47">
+        <v>5</v>
+      </c>
+      <c r="J190" s="47">
+        <v>4</v>
+      </c>
+      <c r="K190" s="47">
+        <v>5</v>
+      </c>
+      <c r="L190" s="47">
+        <v>4</v>
+      </c>
+      <c r="M190" s="47">
+        <v>5</v>
+      </c>
+      <c r="N190" s="19">
+        <f>AVERAGE('NIVEL 1'!G190:M190)</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O190" s="48" t="str">
+        <f>IF(N190=" "," ",IF(N190&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A191" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B191" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C191" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D191" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E191" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="F191" s="46">
+        <v>1013366237</v>
+      </c>
+      <c r="G191" s="47">
+        <v>5</v>
+      </c>
+      <c r="H191" s="47">
+        <v>3</v>
+      </c>
+      <c r="I191" s="47">
+        <v>2</v>
+      </c>
+      <c r="J191" s="47">
+        <v>1</v>
+      </c>
+      <c r="K191" s="47">
+        <v>1</v>
+      </c>
+      <c r="L191" s="47">
+        <v>1</v>
+      </c>
+      <c r="M191" s="47">
+        <v>4</v>
+      </c>
+      <c r="N191" s="19">
+        <f>AVERAGE('NIVEL 1'!G191:M191)</f>
+        <v>2.4285714285714284</v>
+      </c>
+      <c r="O191" s="48" t="str">
+        <f>IF(N191=" "," ",IF(N191&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A192" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B192" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C192" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D192" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E192" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="F192" s="46">
+        <v>1062528840</v>
+      </c>
+      <c r="G192" s="47">
+        <v>5</v>
+      </c>
+      <c r="H192" s="47">
+        <v>5</v>
+      </c>
+      <c r="I192" s="47">
+        <v>4</v>
+      </c>
+      <c r="J192" s="47">
+        <v>4</v>
+      </c>
+      <c r="K192" s="47">
+        <v>4</v>
+      </c>
+      <c r="L192" s="47">
+        <v>4</v>
+      </c>
+      <c r="M192" s="47">
+        <v>5</v>
+      </c>
+      <c r="N192" s="19">
+        <f>AVERAGE('NIVEL 1'!G192:M192)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O192" s="48" t="str">
+        <f>IF(N192=" "," ",IF(N192&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A193" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B193" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C193" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D193" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E193" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="F193" s="46">
+        <v>1062529919</v>
+      </c>
+      <c r="G193" s="47">
+        <v>5</v>
+      </c>
+      <c r="H193" s="47">
+        <v>5</v>
+      </c>
+      <c r="I193" s="47">
+        <v>4</v>
+      </c>
+      <c r="J193" s="47">
+        <v>4</v>
+      </c>
+      <c r="K193" s="47">
+        <v>3</v>
+      </c>
+      <c r="L193" s="47">
+        <v>3</v>
+      </c>
+      <c r="M193" s="47">
+        <v>5</v>
+      </c>
+      <c r="N193" s="19">
+        <f>AVERAGE('NIVEL 1'!G193:M193)</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O193" s="48" t="str">
+        <f>IF(N193=" "," ",IF(N193&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A194" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B194" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C194" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D194" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E194" s="45" t="s">
+        <v>212</v>
+      </c>
+      <c r="F194" s="46">
+        <v>1062531558</v>
+      </c>
+      <c r="G194" s="47">
+        <v>5</v>
+      </c>
+      <c r="H194" s="47">
+        <v>5</v>
+      </c>
+      <c r="I194" s="47">
+        <v>4</v>
+      </c>
+      <c r="J194" s="47">
+        <v>4</v>
+      </c>
+      <c r="K194" s="47">
+        <v>4</v>
+      </c>
+      <c r="L194" s="47">
+        <v>4</v>
+      </c>
+      <c r="M194" s="47">
+        <v>5</v>
+      </c>
+      <c r="N194" s="19">
+        <f>AVERAGE('NIVEL 1'!G194:M194)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O194" s="48" t="str">
+        <f>IF(N194=" "," ",IF(N194&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A195" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B195" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C195" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D195" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E195" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="F195" s="46">
+        <v>1062540642</v>
+      </c>
+      <c r="G195" s="47">
+        <v>5</v>
+      </c>
+      <c r="H195" s="47">
+        <v>3</v>
+      </c>
+      <c r="I195" s="47">
+        <v>3</v>
+      </c>
+      <c r="J195" s="47">
+        <v>1</v>
+      </c>
+      <c r="K195" s="47">
+        <v>2</v>
+      </c>
+      <c r="L195" s="47">
+        <v>1</v>
+      </c>
+      <c r="M195" s="47">
+        <v>5</v>
+      </c>
+      <c r="N195" s="19">
+        <f>AVERAGE('NIVEL 1'!G195:M195)</f>
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="O195" s="48" t="str">
+        <f>IF(N195=" "," ",IF(N195&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A196" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B196" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C196" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D196" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E196" s="45" t="s">
+        <v>143</v>
+      </c>
+      <c r="F196" s="46">
+        <v>1062544508</v>
+      </c>
+      <c r="G196" s="47">
+        <v>5</v>
+      </c>
+      <c r="H196" s="47">
+        <v>5</v>
+      </c>
+      <c r="I196" s="47">
+        <v>4</v>
+      </c>
+      <c r="J196" s="47">
+        <v>4</v>
+      </c>
+      <c r="K196" s="47">
+        <v>4</v>
+      </c>
+      <c r="L196" s="47">
+        <v>3</v>
+      </c>
+      <c r="M196" s="47">
+        <v>5</v>
+      </c>
+      <c r="N196" s="19">
+        <f>AVERAGE('NIVEL 1'!G196:M196)</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O196" s="48" t="str">
+        <f>IF(N196=" "," ",IF(N196&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A197" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B197" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C197" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D197" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E197" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="F197" s="46">
+        <v>1062604063</v>
+      </c>
+      <c r="G197" s="47">
+        <v>5</v>
+      </c>
+      <c r="H197" s="47">
+        <v>5</v>
+      </c>
+      <c r="I197" s="47">
+        <v>4</v>
+      </c>
+      <c r="J197" s="47">
+        <v>4</v>
+      </c>
+      <c r="K197" s="47">
+        <v>4</v>
+      </c>
+      <c r="L197" s="47">
+        <v>4</v>
+      </c>
+      <c r="M197" s="47">
+        <v>5</v>
+      </c>
+      <c r="N197" s="19">
+        <f>AVERAGE('NIVEL 1'!G197:M197)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O197" s="48" t="str">
+        <f>IF(N197=" "," ",IF(N197&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A198" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B198" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C198" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D198" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E198" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="F198" s="46">
+        <v>1064188953</v>
+      </c>
+      <c r="G198" s="47">
+        <v>5</v>
+      </c>
+      <c r="H198" s="47">
+        <v>5</v>
+      </c>
+      <c r="I198" s="47">
+        <v>5</v>
+      </c>
+      <c r="J198" s="47">
+        <v>5</v>
+      </c>
+      <c r="K198" s="47">
+        <v>5</v>
+      </c>
+      <c r="L198" s="47">
+        <v>5</v>
+      </c>
+      <c r="M198" s="47">
+        <v>5</v>
+      </c>
+      <c r="N198" s="19">
+        <f>AVERAGE('NIVEL 1'!G198:M198)</f>
+        <v>5</v>
+      </c>
+      <c r="O198" s="48" t="str">
+        <f>IF(N198=" "," ",IF(N198&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A199" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B199" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C199" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D199" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E199" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="F199" s="46">
+        <v>1067859838</v>
+      </c>
+      <c r="G199" s="47">
+        <v>5</v>
+      </c>
+      <c r="H199" s="47">
+        <v>4</v>
+      </c>
+      <c r="I199" s="47">
+        <v>4</v>
+      </c>
+      <c r="J199" s="47">
+        <v>3</v>
+      </c>
+      <c r="K199" s="47">
+        <v>3</v>
+      </c>
+      <c r="L199" s="47">
+        <v>2</v>
+      </c>
+      <c r="M199" s="47">
+        <v>2</v>
+      </c>
+      <c r="N199" s="19">
+        <f>AVERAGE('NIVEL 1'!G199:M199)</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O199" s="48" t="str">
+        <f>IF(N199=" "," ",IF(N199&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A200" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B200" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C200" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D200" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E200" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="F200" s="46">
+        <v>1067898439</v>
+      </c>
+      <c r="G200" s="47">
+        <v>5</v>
+      </c>
+      <c r="H200" s="47">
+        <v>5</v>
+      </c>
+      <c r="I200" s="47">
+        <v>5</v>
+      </c>
+      <c r="J200" s="47">
+        <v>4</v>
+      </c>
+      <c r="K200" s="47">
+        <v>5</v>
+      </c>
+      <c r="L200" s="47">
+        <v>4</v>
+      </c>
+      <c r="M200" s="47">
+        <v>5</v>
+      </c>
+      <c r="N200" s="19">
+        <f>AVERAGE('NIVEL 1'!G200:M200)</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O200" s="48" t="str">
+        <f>IF(N200=" "," ",IF(N200&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A201" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B201" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C201" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D201" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E201" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="F201" s="46">
+        <v>1067936015</v>
+      </c>
+      <c r="G201" s="47">
+        <v>5</v>
+      </c>
+      <c r="H201" s="47">
+        <v>5</v>
+      </c>
+      <c r="I201" s="47">
+        <v>5</v>
+      </c>
+      <c r="J201" s="47">
+        <v>4</v>
+      </c>
+      <c r="K201" s="47">
+        <v>5</v>
+      </c>
+      <c r="L201" s="47">
+        <v>4</v>
+      </c>
+      <c r="M201" s="47">
+        <v>5</v>
+      </c>
+      <c r="N201" s="19">
+        <f>AVERAGE('NIVEL 1'!G201:M201)</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O201" s="48" t="str">
+        <f>IF(N201=" "," ",IF(N201&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A202" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B202" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C202" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D202" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E202" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="F202" s="46">
+        <v>1067947937</v>
+      </c>
+      <c r="G202" s="47">
+        <v>5</v>
+      </c>
+      <c r="H202" s="47">
+        <v>5</v>
+      </c>
+      <c r="I202" s="47">
+        <v>3</v>
+      </c>
+      <c r="J202" s="47">
+        <v>2</v>
+      </c>
+      <c r="K202" s="47">
+        <v>3</v>
+      </c>
+      <c r="L202" s="47">
+        <v>2</v>
+      </c>
+      <c r="M202" s="47">
+        <v>5</v>
+      </c>
+      <c r="N202" s="19">
+        <f>AVERAGE('NIVEL 1'!G202:M202)</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="O202" s="48" t="str">
+        <f>IF(N202=" "," ",IF(N202&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A203" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B203" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C203" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D203" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E203" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="F203" s="46">
+        <v>1068434281</v>
+      </c>
+      <c r="G203" s="47">
+        <v>5</v>
+      </c>
+      <c r="H203" s="47">
+        <v>5</v>
+      </c>
+      <c r="I203" s="47">
+        <v>4</v>
+      </c>
+      <c r="J203" s="47">
+        <v>3</v>
+      </c>
+      <c r="K203" s="47">
+        <v>4</v>
+      </c>
+      <c r="L203" s="47">
+        <v>3</v>
+      </c>
+      <c r="M203" s="47">
+        <v>5</v>
+      </c>
+      <c r="N203" s="19">
+        <f>AVERAGE('NIVEL 1'!G203:M203)</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O203" s="48" t="str">
+        <f>IF(N203=" "," ",IF(N203&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A204" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B204" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C204" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D204" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E204" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="F204" s="46">
+        <v>1068444080</v>
+      </c>
+      <c r="G204" s="47">
+        <v>5</v>
+      </c>
+      <c r="H204" s="47">
+        <v>2</v>
+      </c>
+      <c r="I204" s="47">
+        <v>1</v>
+      </c>
+      <c r="J204" s="47">
+        <v>1</v>
+      </c>
+      <c r="K204" s="47">
+        <v>1</v>
+      </c>
+      <c r="L204" s="47">
+        <v>1</v>
+      </c>
+      <c r="M204" s="47">
+        <v>1</v>
+      </c>
+      <c r="N204" s="19">
+        <f>AVERAGE('NIVEL 1'!G204:M204)</f>
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="O204" s="48" t="str">
+        <f>IF(N204=" "," ",IF(N204&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A205" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B205" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C205" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D205" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E205" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="F205" s="46">
+        <v>1068444523</v>
+      </c>
+      <c r="G205" s="47">
+        <v>5</v>
+      </c>
+      <c r="H205" s="47">
+        <v>5</v>
+      </c>
+      <c r="I205" s="47">
+        <v>3</v>
+      </c>
+      <c r="J205" s="47">
+        <v>2</v>
+      </c>
+      <c r="K205" s="47">
+        <v>3</v>
+      </c>
+      <c r="L205" s="47">
+        <v>1</v>
+      </c>
+      <c r="M205" s="47">
+        <v>5</v>
+      </c>
+      <c r="N205" s="19">
+        <f>AVERAGE('NIVEL 1'!G205:M205)</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O205" s="48" t="str">
+        <f>IF(N205=" "," ",IF(N205&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A206" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B206" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C206" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D206" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E206" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="F206" s="46">
+        <v>1074002401</v>
+      </c>
+      <c r="G206" s="47">
+        <v>5</v>
+      </c>
+      <c r="H206" s="47">
+        <v>5</v>
+      </c>
+      <c r="I206" s="47">
+        <v>4</v>
+      </c>
+      <c r="J206" s="47">
+        <v>4</v>
+      </c>
+      <c r="K206" s="47">
+        <v>4</v>
+      </c>
+      <c r="L206" s="47">
+        <v>4</v>
+      </c>
+      <c r="M206" s="47">
+        <v>5</v>
+      </c>
+      <c r="N206" s="19">
+        <f>AVERAGE('NIVEL 1'!G206:M206)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O206" s="48" t="str">
+        <f>IF(N206=" "," ",IF(N206&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A207" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B207" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C207" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D207" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E207" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="F207" s="46">
+        <v>1104267144</v>
+      </c>
+      <c r="G207" s="47">
+        <v>5</v>
+      </c>
+      <c r="H207" s="47">
+        <v>5</v>
+      </c>
+      <c r="I207" s="47">
+        <v>4</v>
+      </c>
+      <c r="J207" s="47">
+        <v>4</v>
+      </c>
+      <c r="K207" s="47">
+        <v>4</v>
+      </c>
+      <c r="L207" s="47">
+        <v>4</v>
+      </c>
+      <c r="M207" s="47">
+        <v>5</v>
+      </c>
+      <c r="N207" s="19">
+        <f>AVERAGE('NIVEL 1'!G207:M207)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O207" s="48" t="str">
+        <f>IF(N207=" "," ",IF(N207&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A208" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B208" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C208" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D208" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E208" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="F208" s="46">
+        <v>1126253349</v>
+      </c>
+      <c r="G208" s="47">
+        <v>5</v>
+      </c>
+      <c r="H208" s="47">
+        <v>3</v>
+      </c>
+      <c r="I208" s="47">
+        <v>3</v>
+      </c>
+      <c r="J208" s="47">
+        <v>2</v>
+      </c>
+      <c r="K208" s="47">
+        <v>2</v>
+      </c>
+      <c r="L208" s="47">
+        <v>1</v>
+      </c>
+      <c r="M208" s="47">
+        <v>1</v>
+      </c>
+      <c r="N208" s="19">
+        <f>AVERAGE('NIVEL 1'!G208:M208)</f>
+        <v>2.4285714285714284</v>
+      </c>
+      <c r="O208" s="48" t="str">
+        <f>IF(N208=" "," ",IF(N208&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A209" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B209" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C209" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D209" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E209" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="F209" s="46">
+        <v>1137975547</v>
+      </c>
+      <c r="G209" s="47">
+        <v>5</v>
+      </c>
+      <c r="H209" s="47">
+        <v>5</v>
+      </c>
+      <c r="I209" s="47">
+        <v>4</v>
+      </c>
+      <c r="J209" s="47">
+        <v>4</v>
+      </c>
+      <c r="K209" s="47">
+        <v>4</v>
+      </c>
+      <c r="L209" s="47">
+        <v>4</v>
+      </c>
+      <c r="M209" s="47">
+        <v>5</v>
+      </c>
+      <c r="N209" s="19">
+        <f>AVERAGE('NIVEL 1'!G209:M209)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O209" s="48" t="str">
+        <f>IF(N209=" "," ",IF(N209&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A210" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B210" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C210" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D210" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E210" s="45" t="s">
+        <v>222</v>
+      </c>
+      <c r="F210" s="46">
+        <v>1138030747</v>
+      </c>
+      <c r="G210" s="47">
+        <v>5</v>
+      </c>
+      <c r="H210" s="47">
+        <v>5</v>
+      </c>
+      <c r="I210" s="47">
+        <v>4</v>
+      </c>
+      <c r="J210" s="47">
+        <v>4</v>
+      </c>
+      <c r="K210" s="47">
+        <v>4</v>
+      </c>
+      <c r="L210" s="47">
+        <v>4</v>
+      </c>
+      <c r="M210" s="47">
+        <v>5</v>
+      </c>
+      <c r="N210" s="19">
+        <f>AVERAGE('NIVEL 1'!G210:M210)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O210" s="48" t="str">
+        <f>IF(N210=" "," ",IF(N210&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A211" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B211" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C211" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D211" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E211" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="F211" s="46">
+        <v>1138031947</v>
+      </c>
+      <c r="G211" s="47">
+        <v>5</v>
+      </c>
+      <c r="H211" s="47">
+        <v>5</v>
+      </c>
+      <c r="I211" s="47">
+        <v>4</v>
+      </c>
+      <c r="J211" s="47">
+        <v>2</v>
+      </c>
+      <c r="K211" s="47">
+        <v>3</v>
+      </c>
+      <c r="L211" s="47">
+        <v>2</v>
+      </c>
+      <c r="M211" s="47">
+        <v>5</v>
+      </c>
+      <c r="N211" s="19">
+        <f>AVERAGE('NIVEL 1'!G211:M211)</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O211" s="48" t="str">
+        <f>IF(N211=" "," ",IF(N211&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A212" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B212" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C212" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D212" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E212" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="F212" s="46">
+        <v>1138032549</v>
+      </c>
+      <c r="G212" s="47">
+        <v>5</v>
+      </c>
+      <c r="H212" s="47">
+        <v>5</v>
+      </c>
+      <c r="I212" s="47">
+        <v>5</v>
+      </c>
+      <c r="J212" s="47">
+        <v>4</v>
+      </c>
+      <c r="K212" s="47">
+        <v>5</v>
+      </c>
+      <c r="L212" s="47">
+        <v>4</v>
+      </c>
+      <c r="M212" s="47">
+        <v>5</v>
+      </c>
+      <c r="N212" s="19">
+        <f>AVERAGE('NIVEL 1'!G212:M212)</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O212" s="48" t="str">
+        <f>IF(N212=" "," ",IF(N212&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A213" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B213" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C213" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D213" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E213" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="F213" s="46">
+        <v>1138032702</v>
+      </c>
+      <c r="G213" s="47">
+        <v>5</v>
+      </c>
+      <c r="H213" s="47">
+        <v>5</v>
+      </c>
+      <c r="I213" s="47">
+        <v>3</v>
+      </c>
+      <c r="J213" s="47">
+        <v>2</v>
+      </c>
+      <c r="K213" s="47">
+        <v>2</v>
+      </c>
+      <c r="L213" s="47">
+        <v>2</v>
+      </c>
+      <c r="M213" s="47">
+        <v>5</v>
+      </c>
+      <c r="N213" s="19">
+        <f>AVERAGE('NIVEL 1'!G213:M213)</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O213" s="48" t="str">
+        <f>IF(N213=" "," ",IF(N213&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A214" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B214" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C214" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D214" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E214" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="F214" s="46">
+        <v>1243758694</v>
+      </c>
+      <c r="G214" s="47">
+        <v>5</v>
+      </c>
+      <c r="H214" s="47">
+        <v>3</v>
+      </c>
+      <c r="I214" s="47">
+        <v>2</v>
+      </c>
+      <c r="J214" s="47">
+        <v>1</v>
+      </c>
+      <c r="K214" s="47">
+        <v>2</v>
+      </c>
+      <c r="L214" s="47">
+        <v>1</v>
+      </c>
+      <c r="M214" s="47">
+        <v>5</v>
+      </c>
+      <c r="N214" s="19">
+        <f>AVERAGE('NIVEL 1'!G214:M214)</f>
+        <v>2.7142857142857144</v>
+      </c>
+      <c r="O214" s="48" t="str">
+        <f>IF(N214=" "," ",IF(N214&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A215" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B215" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C215" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D215" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E215" s="45" t="s">
+        <v>228</v>
+      </c>
+      <c r="F215" s="49" t="s">
+        <v>228</v>
+      </c>
+      <c r="G215" s="47">
+        <v>5</v>
+      </c>
+      <c r="H215" s="47">
+        <v>5</v>
+      </c>
+      <c r="I215" s="47">
+        <v>4</v>
+      </c>
+      <c r="J215" s="47">
+        <v>3</v>
+      </c>
+      <c r="K215" s="47">
+        <v>4</v>
+      </c>
+      <c r="L215" s="47">
+        <v>3</v>
+      </c>
+      <c r="M215" s="47">
+        <v>5</v>
+      </c>
+      <c r="N215" s="19">
+        <f>AVERAGE('NIVEL 1'!G215:M215)</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O215" s="48" t="str">
+        <f>IF(N215=" "," ",IF(N215&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A216" s="42"/>
+      <c r="B216" s="43"/>
+      <c r="C216" s="43"/>
+      <c r="D216" s="44"/>
+      <c r="E216" s="45"/>
+      <c r="F216" s="46"/>
+      <c r="G216" s="47"/>
+      <c r="H216" s="47"/>
+      <c r="I216" s="47"/>
+      <c r="J216" s="47"/>
+      <c r="K216" s="47"/>
+      <c r="L216" s="47"/>
+      <c r="M216" s="47"/>
+      <c r="N216" s="19"/>
+      <c r="O216" s="48"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -22978,7 +24490,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O156"/>
+  <dimension ref="A1:O188"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -29878,1198 +31390,2862 @@
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A134" s="48">
+      <c r="A134" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B134" s="49" t="str">
+      <c r="B134" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C134" s="49" t="str">
+      <c r="C134" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D134" s="45">
+      <c r="D134" s="3">
         <v>45899</v>
       </c>
-      <c r="E134" s="46" t="s">
+      <c r="E134" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="F134" s="48">
+      <c r="F134" s="1">
         <v>1018813</v>
       </c>
-      <c r="G134" s="48">
-        <v>5</v>
-      </c>
-      <c r="H134" s="48">
-        <v>4</v>
-      </c>
-      <c r="I134" s="48">
-        <v>3</v>
-      </c>
-      <c r="J134" s="48">
-        <v>3</v>
-      </c>
-      <c r="K134" s="48">
-        <v>4</v>
-      </c>
-      <c r="L134" s="48">
-        <v>5</v>
-      </c>
-      <c r="M134" s="48">
+      <c r="G134" s="1">
+        <v>5</v>
+      </c>
+      <c r="H134" s="1">
+        <v>4</v>
+      </c>
+      <c r="I134" s="1">
+        <v>3</v>
+      </c>
+      <c r="J134" s="1">
+        <v>3</v>
+      </c>
+      <c r="K134" s="1">
+        <v>4</v>
+      </c>
+      <c r="L134" s="1">
+        <v>5</v>
+      </c>
+      <c r="M134" s="1">
         <v>2</v>
       </c>
       <c r="N134" s="19">
         <f>AVERAGE('NIVEL 2'!G134:M134)</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O134" s="44" t="str">
+      <c r="O134" s="18" t="str">
         <f>IF(N134=" "," ",IF(N134&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A135" s="48">
+      <c r="A135" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B135" s="49" t="str">
+      <c r="B135" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C135" s="49" t="str">
+      <c r="C135" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D135" s="45">
+      <c r="D135" s="3">
         <v>45899</v>
       </c>
-      <c r="E135" s="46" t="s">
+      <c r="E135" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="F135" s="48">
+      <c r="F135" s="1">
         <v>1418308</v>
       </c>
-      <c r="G135" s="48">
-        <v>5</v>
-      </c>
-      <c r="H135" s="48">
-        <v>5</v>
-      </c>
-      <c r="I135" s="48">
-        <v>4</v>
-      </c>
-      <c r="J135" s="48">
-        <v>5</v>
-      </c>
-      <c r="K135" s="48">
-        <v>5</v>
-      </c>
-      <c r="L135" s="48">
-        <v>5</v>
-      </c>
-      <c r="M135" s="48">
+      <c r="G135" s="1">
+        <v>5</v>
+      </c>
+      <c r="H135" s="1">
+        <v>5</v>
+      </c>
+      <c r="I135" s="1">
+        <v>4</v>
+      </c>
+      <c r="J135" s="1">
+        <v>5</v>
+      </c>
+      <c r="K135" s="1">
+        <v>5</v>
+      </c>
+      <c r="L135" s="1">
+        <v>5</v>
+      </c>
+      <c r="M135" s="1">
         <v>3</v>
       </c>
       <c r="N135" s="19">
         <f>AVERAGE('NIVEL 2'!G135:M135)</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O135" s="44" t="str">
+      <c r="O135" s="18" t="str">
         <f>IF(N135=" "," ",IF(N135&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A136" s="48">
+      <c r="A136" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B136" s="49" t="str">
+      <c r="B136" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C136" s="49" t="str">
+      <c r="C136" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D136" s="45">
+      <c r="D136" s="3">
         <v>45899</v>
       </c>
-      <c r="E136" s="46" t="s">
+      <c r="E136" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="F136" s="48">
+      <c r="F136" s="1">
         <v>7384397</v>
       </c>
-      <c r="G136" s="48">
-        <v>5</v>
-      </c>
-      <c r="H136" s="48">
-        <v>5</v>
-      </c>
-      <c r="I136" s="48">
-        <v>3</v>
-      </c>
-      <c r="J136" s="48">
-        <v>4</v>
-      </c>
-      <c r="K136" s="48">
-        <v>5</v>
-      </c>
-      <c r="L136" s="48">
-        <v>5</v>
-      </c>
-      <c r="M136" s="48">
+      <c r="G136" s="1">
+        <v>5</v>
+      </c>
+      <c r="H136" s="1">
+        <v>5</v>
+      </c>
+      <c r="I136" s="1">
+        <v>3</v>
+      </c>
+      <c r="J136" s="1">
+        <v>4</v>
+      </c>
+      <c r="K136" s="1">
+        <v>5</v>
+      </c>
+      <c r="L136" s="1">
+        <v>5</v>
+      </c>
+      <c r="M136" s="1">
         <v>4</v>
       </c>
       <c r="N136" s="19">
         <f>AVERAGE('NIVEL 2'!G136:M136)</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O136" s="44" t="str">
+      <c r="O136" s="18" t="str">
         <f>IF(N136=" "," ",IF(N136&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A137" s="48">
+      <c r="A137" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B137" s="49" t="str">
+      <c r="B137" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C137" s="49" t="str">
+      <c r="C137" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D137" s="45">
+      <c r="D137" s="3">
         <v>45899</v>
       </c>
-      <c r="E137" s="46" t="s">
+      <c r="E137" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F137" s="48">
+      <c r="F137" s="1">
         <v>10966252</v>
       </c>
-      <c r="G137" s="48">
-        <v>5</v>
-      </c>
-      <c r="H137" s="48">
-        <v>5</v>
-      </c>
-      <c r="I137" s="48">
-        <v>2</v>
-      </c>
-      <c r="J137" s="48">
-        <v>5</v>
-      </c>
-      <c r="K137" s="48">
-        <v>5</v>
-      </c>
-      <c r="L137" s="48">
-        <v>5</v>
-      </c>
-      <c r="M137" s="48">
+      <c r="G137" s="1">
+        <v>5</v>
+      </c>
+      <c r="H137" s="1">
+        <v>5</v>
+      </c>
+      <c r="I137" s="1">
+        <v>2</v>
+      </c>
+      <c r="J137" s="1">
+        <v>5</v>
+      </c>
+      <c r="K137" s="1">
+        <v>5</v>
+      </c>
+      <c r="L137" s="1">
+        <v>5</v>
+      </c>
+      <c r="M137" s="1">
         <v>4</v>
       </c>
       <c r="N137" s="19">
         <f>AVERAGE('NIVEL 2'!G137:M137)</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O137" s="44" t="str">
+      <c r="O137" s="18" t="str">
         <f>IF(N137=" "," ",IF(N137&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A138" s="48">
+      <c r="A138" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B138" s="49" t="str">
+      <c r="B138" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C138" s="49" t="str">
+      <c r="C138" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D138" s="45">
+      <c r="D138" s="3">
         <v>45899</v>
       </c>
-      <c r="E138" s="46" t="s">
+      <c r="E138" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F138" s="48">
+      <c r="F138" s="1">
         <v>1007822238</v>
       </c>
-      <c r="G138" s="48">
-        <v>5</v>
-      </c>
-      <c r="H138" s="48">
-        <v>5</v>
-      </c>
-      <c r="I138" s="48">
-        <v>3</v>
-      </c>
-      <c r="J138" s="48">
-        <v>5</v>
-      </c>
-      <c r="K138" s="48">
-        <v>5</v>
-      </c>
-      <c r="L138" s="48">
-        <v>5</v>
-      </c>
-      <c r="M138" s="48">
+      <c r="G138" s="1">
+        <v>5</v>
+      </c>
+      <c r="H138" s="1">
+        <v>5</v>
+      </c>
+      <c r="I138" s="1">
+        <v>3</v>
+      </c>
+      <c r="J138" s="1">
+        <v>5</v>
+      </c>
+      <c r="K138" s="1">
+        <v>5</v>
+      </c>
+      <c r="L138" s="1">
+        <v>5</v>
+      </c>
+      <c r="M138" s="1">
         <v>3</v>
       </c>
       <c r="N138" s="19">
         <f>AVERAGE('NIVEL 2'!G138:M138)</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O138" s="44" t="str">
+      <c r="O138" s="18" t="str">
         <f>IF(N138=" "," ",IF(N138&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A139" s="48">
+      <c r="A139" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B139" s="49" t="str">
+      <c r="B139" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C139" s="49" t="str">
+      <c r="C139" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D139" s="45">
+      <c r="D139" s="3">
         <v>45899</v>
       </c>
-      <c r="E139" s="46" t="s">
+      <c r="E139" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="F139" s="48">
+      <c r="F139" s="1">
         <v>1027663882</v>
       </c>
-      <c r="G139" s="48">
-        <v>4</v>
-      </c>
-      <c r="H139" s="48">
-        <v>3</v>
-      </c>
-      <c r="I139" s="48">
-        <v>4</v>
-      </c>
-      <c r="J139" s="48">
-        <v>4</v>
-      </c>
-      <c r="K139" s="48">
-        <v>3</v>
-      </c>
-      <c r="L139" s="48">
-        <v>5</v>
-      </c>
-      <c r="M139" s="48">
+      <c r="G139" s="1">
+        <v>4</v>
+      </c>
+      <c r="H139" s="1">
+        <v>3</v>
+      </c>
+      <c r="I139" s="1">
+        <v>4</v>
+      </c>
+      <c r="J139" s="1">
+        <v>4</v>
+      </c>
+      <c r="K139" s="1">
+        <v>3</v>
+      </c>
+      <c r="L139" s="1">
+        <v>5</v>
+      </c>
+      <c r="M139" s="1">
         <v>3</v>
       </c>
       <c r="N139" s="19">
         <f>AVERAGE('NIVEL 2'!G139:M139)</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O139" s="44" t="str">
+      <c r="O139" s="18" t="str">
         <f>IF(N139=" "," ",IF(N139&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A140" s="48">
+      <c r="A140" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B140" s="49" t="str">
+      <c r="B140" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C140" s="49" t="str">
+      <c r="C140" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D140" s="45">
+      <c r="D140" s="3">
         <v>45899</v>
       </c>
-      <c r="E140" s="46" t="s">
+      <c r="E140" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="F140" s="48">
+      <c r="F140" s="1">
         <v>1029722943</v>
       </c>
-      <c r="G140" s="48">
-        <v>5</v>
-      </c>
-      <c r="H140" s="48">
-        <v>4</v>
-      </c>
-      <c r="I140" s="48">
-        <v>4</v>
-      </c>
-      <c r="J140" s="48">
-        <v>4</v>
-      </c>
-      <c r="K140" s="48">
-        <v>5</v>
-      </c>
-      <c r="L140" s="48">
-        <v>5</v>
-      </c>
-      <c r="M140" s="48">
+      <c r="G140" s="1">
+        <v>5</v>
+      </c>
+      <c r="H140" s="1">
+        <v>4</v>
+      </c>
+      <c r="I140" s="1">
+        <v>4</v>
+      </c>
+      <c r="J140" s="1">
+        <v>4</v>
+      </c>
+      <c r="K140" s="1">
+        <v>5</v>
+      </c>
+      <c r="L140" s="1">
+        <v>5</v>
+      </c>
+      <c r="M140" s="1">
         <v>3</v>
       </c>
       <c r="N140" s="19">
         <f>AVERAGE('NIVEL 2'!G140:M140)</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O140" s="44" t="str">
+      <c r="O140" s="18" t="str">
         <f>IF(N140=" "," ",IF(N140&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A141" s="48">
+      <c r="A141" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B141" s="49" t="str">
+      <c r="B141" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C141" s="49" t="str">
+      <c r="C141" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D141" s="45">
+      <c r="D141" s="3">
         <v>45899</v>
       </c>
-      <c r="E141" s="46" t="s">
+      <c r="E141" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="F141" s="48">
+      <c r="F141" s="1">
         <v>1031543523</v>
       </c>
-      <c r="G141" s="48">
-        <v>5</v>
-      </c>
-      <c r="H141" s="48">
-        <v>5</v>
-      </c>
-      <c r="I141" s="48">
-        <v>4</v>
-      </c>
-      <c r="J141" s="48">
-        <v>4</v>
-      </c>
-      <c r="K141" s="48">
-        <v>5</v>
-      </c>
-      <c r="L141" s="48">
-        <v>5</v>
-      </c>
-      <c r="M141" s="48">
+      <c r="G141" s="1">
+        <v>5</v>
+      </c>
+      <c r="H141" s="1">
+        <v>5</v>
+      </c>
+      <c r="I141" s="1">
+        <v>4</v>
+      </c>
+      <c r="J141" s="1">
+        <v>4</v>
+      </c>
+      <c r="K141" s="1">
+        <v>5</v>
+      </c>
+      <c r="L141" s="1">
+        <v>5</v>
+      </c>
+      <c r="M141" s="1">
         <v>3</v>
       </c>
       <c r="N141" s="19">
         <f>AVERAGE('NIVEL 2'!G141:M141)</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O141" s="44" t="str">
+      <c r="O141" s="18" t="str">
         <f>IF(N141=" "," ",IF(N141&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A142" s="48">
+      <c r="A142" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B142" s="49" t="str">
+      <c r="B142" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C142" s="49" t="str">
+      <c r="C142" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D142" s="45">
+      <c r="D142" s="3">
         <v>45899</v>
       </c>
-      <c r="E142" s="46" t="s">
+      <c r="E142" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="F142" s="48">
+      <c r="F142" s="1">
         <v>1062432000</v>
       </c>
-      <c r="G142" s="48">
-        <v>5</v>
-      </c>
-      <c r="H142" s="48">
-        <v>5</v>
-      </c>
-      <c r="I142" s="48">
-        <v>3</v>
-      </c>
-      <c r="J142" s="48">
-        <v>4</v>
-      </c>
-      <c r="K142" s="48">
-        <v>3</v>
-      </c>
-      <c r="L142" s="48">
-        <v>5</v>
-      </c>
-      <c r="M142" s="48">
+      <c r="G142" s="1">
+        <v>5</v>
+      </c>
+      <c r="H142" s="1">
+        <v>5</v>
+      </c>
+      <c r="I142" s="1">
+        <v>3</v>
+      </c>
+      <c r="J142" s="1">
+        <v>4</v>
+      </c>
+      <c r="K142" s="1">
+        <v>3</v>
+      </c>
+      <c r="L142" s="1">
+        <v>5</v>
+      </c>
+      <c r="M142" s="1">
         <v>2</v>
       </c>
       <c r="N142" s="19">
         <f>AVERAGE('NIVEL 2'!G142:M142)</f>
         <v>3.8571428571428572</v>
       </c>
-      <c r="O142" s="44" t="str">
+      <c r="O142" s="18" t="str">
         <f>IF(N142=" "," ",IF(N142&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A143" s="48">
+      <c r="A143" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B143" s="49" t="str">
+      <c r="B143" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C143" s="49" t="str">
+      <c r="C143" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D143" s="45">
+      <c r="D143" s="3">
         <v>45899</v>
       </c>
-      <c r="E143" s="46" t="s">
+      <c r="E143" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="F143" s="48">
+      <c r="F143" s="1">
         <v>1062539643</v>
       </c>
-      <c r="G143" s="48">
-        <v>5</v>
-      </c>
-      <c r="H143" s="48">
-        <v>4</v>
-      </c>
-      <c r="I143" s="48">
-        <v>4</v>
-      </c>
-      <c r="J143" s="48">
-        <v>4</v>
-      </c>
-      <c r="K143" s="48">
-        <v>4</v>
-      </c>
-      <c r="L143" s="48">
-        <v>5</v>
-      </c>
-      <c r="M143" s="48">
+      <c r="G143" s="1">
+        <v>5</v>
+      </c>
+      <c r="H143" s="1">
+        <v>4</v>
+      </c>
+      <c r="I143" s="1">
+        <v>4</v>
+      </c>
+      <c r="J143" s="1">
+        <v>4</v>
+      </c>
+      <c r="K143" s="1">
+        <v>4</v>
+      </c>
+      <c r="L143" s="1">
+        <v>5</v>
+      </c>
+      <c r="M143" s="1">
         <v>5</v>
       </c>
       <c r="N143" s="19">
         <f>AVERAGE('NIVEL 2'!G143:M143)</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O143" s="44" t="str">
+      <c r="O143" s="18" t="str">
         <f>IF(N143=" "," ",IF(N143&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A144" s="48">
+      <c r="A144" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B144" s="49" t="str">
+      <c r="B144" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C144" s="49" t="str">
+      <c r="C144" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D144" s="45">
+      <c r="D144" s="3">
         <v>45899</v>
       </c>
-      <c r="E144" s="46" t="s">
+      <c r="E144" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="F144" s="48">
+      <c r="F144" s="1">
         <v>1062980565</v>
       </c>
-      <c r="G144" s="48">
-        <v>4</v>
-      </c>
-      <c r="H144" s="48">
-        <v>4</v>
-      </c>
-      <c r="I144" s="48">
-        <v>3</v>
-      </c>
-      <c r="J144" s="48">
-        <v>4</v>
-      </c>
-      <c r="K144" s="48">
-        <v>4</v>
-      </c>
-      <c r="L144" s="48">
-        <v>5</v>
-      </c>
-      <c r="M144" s="48">
+      <c r="G144" s="1">
+        <v>4</v>
+      </c>
+      <c r="H144" s="1">
+        <v>4</v>
+      </c>
+      <c r="I144" s="1">
+        <v>3</v>
+      </c>
+      <c r="J144" s="1">
+        <v>4</v>
+      </c>
+      <c r="K144" s="1">
+        <v>4</v>
+      </c>
+      <c r="L144" s="1">
+        <v>5</v>
+      </c>
+      <c r="M144" s="1">
         <v>4</v>
       </c>
       <c r="N144" s="19">
         <f>AVERAGE('NIVEL 2'!G144:M144)</f>
         <v>4</v>
       </c>
-      <c r="O144" s="44" t="str">
+      <c r="O144" s="18" t="str">
         <f>IF(N144=" "," ",IF(N144&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A145" s="48">
+      <c r="A145" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B145" s="49" t="str">
+      <c r="B145" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C145" s="49" t="str">
+      <c r="C145" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D145" s="45">
+      <c r="D145" s="3">
         <v>45899</v>
       </c>
-      <c r="E145" s="46" t="s">
+      <c r="E145" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="F145" s="48">
+      <c r="F145" s="1">
         <v>1062984834</v>
       </c>
-      <c r="G145" s="48">
-        <v>5</v>
-      </c>
-      <c r="H145" s="48">
-        <v>4</v>
-      </c>
-      <c r="I145" s="48">
-        <v>3</v>
-      </c>
-      <c r="J145" s="48">
-        <v>4</v>
-      </c>
-      <c r="K145" s="48">
-        <v>5</v>
-      </c>
-      <c r="L145" s="48">
-        <v>5</v>
-      </c>
-      <c r="M145" s="48">
+      <c r="G145" s="1">
+        <v>5</v>
+      </c>
+      <c r="H145" s="1">
+        <v>4</v>
+      </c>
+      <c r="I145" s="1">
+        <v>3</v>
+      </c>
+      <c r="J145" s="1">
+        <v>4</v>
+      </c>
+      <c r="K145" s="1">
+        <v>5</v>
+      </c>
+      <c r="L145" s="1">
+        <v>5</v>
+      </c>
+      <c r="M145" s="1">
         <v>3</v>
       </c>
       <c r="N145" s="19">
         <f>AVERAGE('NIVEL 2'!G145:M145)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O145" s="44" t="str">
+      <c r="O145" s="18" t="str">
         <f>IF(N145=" "," ",IF(N145&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A146" s="48">
+      <c r="A146" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B146" s="49" t="str">
+      <c r="B146" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C146" s="49" t="str">
+      <c r="C146" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D146" s="45">
+      <c r="D146" s="3">
         <v>45899</v>
       </c>
-      <c r="E146" s="46" t="s">
+      <c r="E146" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="F146" s="48">
+      <c r="F146" s="1">
         <v>1062986616</v>
       </c>
-      <c r="G146" s="48">
-        <v>5</v>
-      </c>
-      <c r="H146" s="48">
-        <v>4</v>
-      </c>
-      <c r="I146" s="48">
-        <v>3</v>
-      </c>
-      <c r="J146" s="48">
-        <v>3</v>
-      </c>
-      <c r="K146" s="48">
-        <v>3</v>
-      </c>
-      <c r="L146" s="48">
-        <v>4</v>
-      </c>
-      <c r="M146" s="48">
+      <c r="G146" s="1">
+        <v>5</v>
+      </c>
+      <c r="H146" s="1">
+        <v>4</v>
+      </c>
+      <c r="I146" s="1">
+        <v>3</v>
+      </c>
+      <c r="J146" s="1">
+        <v>3</v>
+      </c>
+      <c r="K146" s="1">
+        <v>3</v>
+      </c>
+      <c r="L146" s="1">
+        <v>4</v>
+      </c>
+      <c r="M146" s="1">
         <v>2</v>
       </c>
       <c r="N146" s="19">
         <f>AVERAGE('NIVEL 2'!G146:M146)</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O146" s="44" t="str">
+      <c r="O146" s="18" t="str">
         <f>IF(N146=" "," ",IF(N146&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A147" s="48">
+      <c r="A147" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B147" s="49" t="str">
+      <c r="B147" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C147" s="49" t="str">
+      <c r="C147" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D147" s="45">
+      <c r="D147" s="3">
         <v>45899</v>
       </c>
-      <c r="E147" s="46" t="s">
+      <c r="E147" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="F147" s="48">
+      <c r="F147" s="1">
         <v>1064990474</v>
       </c>
-      <c r="G147" s="48">
-        <v>5</v>
-      </c>
-      <c r="H147" s="48">
-        <v>4</v>
-      </c>
-      <c r="I147" s="48">
-        <v>3</v>
-      </c>
-      <c r="J147" s="48">
-        <v>4</v>
-      </c>
-      <c r="K147" s="48">
-        <v>5</v>
-      </c>
-      <c r="L147" s="48">
-        <v>5</v>
-      </c>
-      <c r="M147" s="48">
+      <c r="G147" s="1">
+        <v>5</v>
+      </c>
+      <c r="H147" s="1">
+        <v>4</v>
+      </c>
+      <c r="I147" s="1">
+        <v>3</v>
+      </c>
+      <c r="J147" s="1">
+        <v>4</v>
+      </c>
+      <c r="K147" s="1">
+        <v>5</v>
+      </c>
+      <c r="L147" s="1">
+        <v>5</v>
+      </c>
+      <c r="M147" s="1">
         <v>3</v>
       </c>
       <c r="N147" s="19">
         <f>AVERAGE('NIVEL 2'!G147:M147)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O147" s="44" t="str">
+      <c r="O147" s="18" t="str">
         <f>IF(N147=" "," ",IF(N147&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A148" s="48">
+      <c r="A148" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B148" s="49" t="str">
+      <c r="B148" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C148" s="49" t="str">
+      <c r="C148" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D148" s="45">
+      <c r="D148" s="3">
         <v>45899</v>
       </c>
-      <c r="E148" s="46" t="s">
+      <c r="E148" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F148" s="48">
+      <c r="F148" s="1">
         <v>1066512697</v>
       </c>
-      <c r="G148" s="48">
-        <v>4</v>
-      </c>
-      <c r="H148" s="48">
-        <v>3</v>
-      </c>
-      <c r="I148" s="48">
-        <v>2</v>
-      </c>
-      <c r="J148" s="48">
-        <v>3</v>
-      </c>
-      <c r="K148" s="48">
-        <v>2</v>
-      </c>
-      <c r="L148" s="48">
-        <v>4</v>
-      </c>
-      <c r="M148" s="48">
+      <c r="G148" s="1">
+        <v>4</v>
+      </c>
+      <c r="H148" s="1">
+        <v>3</v>
+      </c>
+      <c r="I148" s="1">
+        <v>2</v>
+      </c>
+      <c r="J148" s="1">
+        <v>3</v>
+      </c>
+      <c r="K148" s="1">
+        <v>2</v>
+      </c>
+      <c r="L148" s="1">
+        <v>4</v>
+      </c>
+      <c r="M148" s="1">
         <v>2</v>
       </c>
       <c r="N148" s="19">
         <f>AVERAGE('NIVEL 2'!G148:M148)</f>
         <v>2.8571428571428572</v>
       </c>
-      <c r="O148" s="44" t="str">
+      <c r="O148" s="18" t="str">
         <f>IF(N148=" "," ",IF(N148&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A149" s="48">
+      <c r="A149" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B149" s="49" t="str">
+      <c r="B149" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C149" s="49" t="str">
+      <c r="C149" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D149" s="45">
+      <c r="D149" s="3">
         <v>45899</v>
       </c>
-      <c r="E149" s="46" t="s">
+      <c r="E149" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="F149" s="48">
+      <c r="F149" s="1">
         <v>1066747786</v>
       </c>
-      <c r="G149" s="48">
-        <v>5</v>
-      </c>
-      <c r="H149" s="48">
-        <v>5</v>
-      </c>
-      <c r="I149" s="48">
-        <v>3</v>
-      </c>
-      <c r="J149" s="48">
-        <v>4</v>
-      </c>
-      <c r="K149" s="48">
-        <v>5</v>
-      </c>
-      <c r="L149" s="48">
-        <v>5</v>
-      </c>
-      <c r="M149" s="48">
+      <c r="G149" s="1">
+        <v>5</v>
+      </c>
+      <c r="H149" s="1">
+        <v>5</v>
+      </c>
+      <c r="I149" s="1">
+        <v>3</v>
+      </c>
+      <c r="J149" s="1">
+        <v>4</v>
+      </c>
+      <c r="K149" s="1">
+        <v>5</v>
+      </c>
+      <c r="L149" s="1">
+        <v>5</v>
+      </c>
+      <c r="M149" s="1">
         <v>3</v>
       </c>
       <c r="N149" s="19">
         <f>AVERAGE('NIVEL 2'!G149:M149)</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O149" s="44" t="str">
+      <c r="O149" s="18" t="str">
         <f>IF(N149=" "," ",IF(N149&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A150" s="48">
+      <c r="A150" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B150" s="49" t="str">
+      <c r="B150" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C150" s="49" t="str">
+      <c r="C150" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D150" s="45">
+      <c r="D150" s="3">
         <v>45899</v>
       </c>
-      <c r="E150" s="46" t="s">
+      <c r="E150" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F150" s="48">
+      <c r="F150" s="1">
         <v>1067849965</v>
       </c>
-      <c r="G150" s="48">
-        <v>5</v>
-      </c>
-      <c r="H150" s="48">
-        <v>5</v>
-      </c>
-      <c r="I150" s="48">
-        <v>3</v>
-      </c>
-      <c r="J150" s="48">
-        <v>4</v>
-      </c>
-      <c r="K150" s="48">
-        <v>5</v>
-      </c>
-      <c r="L150" s="48">
-        <v>5</v>
-      </c>
-      <c r="M150" s="48">
+      <c r="G150" s="1">
+        <v>5</v>
+      </c>
+      <c r="H150" s="1">
+        <v>5</v>
+      </c>
+      <c r="I150" s="1">
+        <v>3</v>
+      </c>
+      <c r="J150" s="1">
+        <v>4</v>
+      </c>
+      <c r="K150" s="1">
+        <v>5</v>
+      </c>
+      <c r="L150" s="1">
+        <v>5</v>
+      </c>
+      <c r="M150" s="1">
         <v>2</v>
       </c>
       <c r="N150" s="19">
         <f>AVERAGE('NIVEL 2'!G150:M150)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O150" s="44" t="str">
+      <c r="O150" s="18" t="str">
         <f>IF(N150=" "," ",IF(N150&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A151" s="48">
+      <c r="A151" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B151" s="49" t="str">
+      <c r="B151" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C151" s="49" t="str">
+      <c r="C151" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D151" s="45">
+      <c r="D151" s="3">
         <v>45899</v>
       </c>
-      <c r="E151" s="46" t="s">
+      <c r="E151" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F151" s="48">
+      <c r="F151" s="1">
         <v>1068439668</v>
       </c>
-      <c r="G151" s="48">
-        <v>5</v>
-      </c>
-      <c r="H151" s="48">
-        <v>5</v>
-      </c>
-      <c r="I151" s="48">
-        <v>5</v>
-      </c>
-      <c r="J151" s="48">
-        <v>4</v>
-      </c>
-      <c r="K151" s="48">
-        <v>3</v>
-      </c>
-      <c r="L151" s="48">
-        <v>5</v>
-      </c>
-      <c r="M151" s="48">
+      <c r="G151" s="1">
+        <v>5</v>
+      </c>
+      <c r="H151" s="1">
+        <v>5</v>
+      </c>
+      <c r="I151" s="1">
+        <v>5</v>
+      </c>
+      <c r="J151" s="1">
+        <v>4</v>
+      </c>
+      <c r="K151" s="1">
+        <v>3</v>
+      </c>
+      <c r="L151" s="1">
+        <v>5</v>
+      </c>
+      <c r="M151" s="1">
         <v>2</v>
       </c>
       <c r="N151" s="19">
         <f>AVERAGE('NIVEL 2'!G151:M151)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O151" s="44" t="str">
+      <c r="O151" s="18" t="str">
         <f>IF(N151=" "," ",IF(N151&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A152" s="48">
+      <c r="A152" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B152" s="49" t="str">
+      <c r="B152" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C152" s="49" t="str">
+      <c r="C152" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D152" s="45">
+      <c r="D152" s="3">
         <v>45899</v>
       </c>
-      <c r="E152" s="46" t="s">
+      <c r="E152" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="F152" s="48">
+      <c r="F152" s="1">
         <v>1138031207</v>
       </c>
-      <c r="G152" s="48">
-        <v>5</v>
-      </c>
-      <c r="H152" s="48">
-        <v>5</v>
-      </c>
-      <c r="I152" s="48">
-        <v>4</v>
-      </c>
-      <c r="J152" s="48">
-        <v>4</v>
-      </c>
-      <c r="K152" s="48">
-        <v>4</v>
-      </c>
-      <c r="L152" s="48">
-        <v>5</v>
-      </c>
-      <c r="M152" s="48">
+      <c r="G152" s="1">
+        <v>5</v>
+      </c>
+      <c r="H152" s="1">
+        <v>5</v>
+      </c>
+      <c r="I152" s="1">
+        <v>4</v>
+      </c>
+      <c r="J152" s="1">
+        <v>4</v>
+      </c>
+      <c r="K152" s="1">
+        <v>4</v>
+      </c>
+      <c r="L152" s="1">
+        <v>5</v>
+      </c>
+      <c r="M152" s="1">
         <v>2</v>
       </c>
       <c r="N152" s="19">
         <f>AVERAGE('NIVEL 2'!G152:M152)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O152" s="44" t="str">
+      <c r="O152" s="18" t="str">
         <f>IF(N152=" "," ",IF(N152&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A153" s="48">
+      <c r="A153" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B153" s="49" t="str">
+      <c r="B153" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C153" s="49" t="str">
+      <c r="C153" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D153" s="45">
+      <c r="D153" s="3">
         <v>45899</v>
       </c>
-      <c r="E153" s="46" t="s">
+      <c r="E153" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="F153" s="48">
+      <c r="F153" s="1">
         <v>1138032406</v>
       </c>
-      <c r="G153" s="48">
-        <v>5</v>
-      </c>
-      <c r="H153" s="48">
-        <v>5</v>
-      </c>
-      <c r="I153" s="48">
-        <v>4</v>
-      </c>
-      <c r="J153" s="48">
-        <v>4</v>
-      </c>
-      <c r="K153" s="48">
-        <v>3</v>
-      </c>
-      <c r="L153" s="48">
-        <v>5</v>
-      </c>
-      <c r="M153" s="48">
+      <c r="G153" s="1">
+        <v>5</v>
+      </c>
+      <c r="H153" s="1">
+        <v>5</v>
+      </c>
+      <c r="I153" s="1">
+        <v>4</v>
+      </c>
+      <c r="J153" s="1">
+        <v>4</v>
+      </c>
+      <c r="K153" s="1">
+        <v>3</v>
+      </c>
+      <c r="L153" s="1">
+        <v>5</v>
+      </c>
+      <c r="M153" s="1">
         <v>2</v>
       </c>
       <c r="N153" s="19">
         <f>AVERAGE('NIVEL 2'!G153:M153)</f>
         <v>4</v>
       </c>
-      <c r="O153" s="44" t="str">
+      <c r="O153" s="18" t="str">
         <f>IF(N153=" "," ",IF(N153&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A154" s="48">
+      <c r="A154" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B154" s="49" t="str">
+      <c r="B154" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C154" s="49" t="str">
+      <c r="C154" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D154" s="45">
+      <c r="D154" s="3">
         <v>45899</v>
       </c>
-      <c r="E154" s="46" t="s">
+      <c r="E154" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="F154" s="48">
+      <c r="F154" s="1">
         <v>1138032417</v>
       </c>
-      <c r="G154" s="48">
-        <v>5</v>
-      </c>
-      <c r="H154" s="48">
-        <v>5</v>
-      </c>
-      <c r="I154" s="48">
-        <v>3</v>
-      </c>
-      <c r="J154" s="48">
-        <v>4</v>
-      </c>
-      <c r="K154" s="48">
+      <c r="G154" s="1">
+        <v>5</v>
+      </c>
+      <c r="H154" s="1">
+        <v>5</v>
+      </c>
+      <c r="I154" s="1">
+        <v>3</v>
+      </c>
+      <c r="J154" s="1">
+        <v>4</v>
+      </c>
+      <c r="K154" s="1">
         <v>1</v>
       </c>
-      <c r="L154" s="48">
-        <v>5</v>
-      </c>
-      <c r="M154" s="48">
+      <c r="L154" s="1">
+        <v>5</v>
+      </c>
+      <c r="M154" s="1">
         <v>1</v>
       </c>
       <c r="N154" s="19">
         <f>AVERAGE('NIVEL 2'!G154:M154)</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O154" s="44" t="str">
+      <c r="O154" s="18" t="str">
         <f>IF(N154=" "," ",IF(N154&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A155" s="48">
+      <c r="A155" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B155" s="49" t="str">
+      <c r="B155" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C155" s="49" t="str">
+      <c r="C155" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D155" s="45">
+      <c r="D155" s="3">
         <v>45899</v>
       </c>
-      <c r="E155" s="46" t="s">
+      <c r="E155" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="F155" s="48">
+      <c r="F155" s="1">
         <v>1140444971</v>
       </c>
-      <c r="G155" s="48">
-        <v>5</v>
-      </c>
-      <c r="H155" s="48">
-        <v>5</v>
-      </c>
-      <c r="I155" s="48">
-        <v>3</v>
-      </c>
-      <c r="J155" s="48">
-        <v>3</v>
-      </c>
-      <c r="K155" s="48">
-        <v>3</v>
-      </c>
-      <c r="L155" s="48">
-        <v>4</v>
-      </c>
-      <c r="M155" s="48">
+      <c r="G155" s="1">
+        <v>5</v>
+      </c>
+      <c r="H155" s="1">
+        <v>5</v>
+      </c>
+      <c r="I155" s="1">
+        <v>3</v>
+      </c>
+      <c r="J155" s="1">
+        <v>3</v>
+      </c>
+      <c r="K155" s="1">
+        <v>3</v>
+      </c>
+      <c r="L155" s="1">
+        <v>4</v>
+      </c>
+      <c r="M155" s="1">
         <v>2</v>
       </c>
       <c r="N155" s="19">
         <f>AVERAGE('NIVEL 2'!G155:M155)</f>
         <v>3.5714285714285716</v>
       </c>
-      <c r="O155" s="44" t="str">
+      <c r="O155" s="18" t="str">
         <f>IF(N155=" "," ",IF(N155&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A156" s="48">
+      <c r="A156" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B156" s="49" t="str">
+      <c r="B156" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C156" s="49" t="str">
+      <c r="C156" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D156" s="45">
+      <c r="D156" s="3">
         <v>45899</v>
       </c>
-      <c r="E156" s="46" t="s">
+      <c r="E156" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="F156" s="48">
+      <c r="F156" s="1">
         <v>1142930859</v>
       </c>
-      <c r="G156" s="48">
-        <v>5</v>
-      </c>
-      <c r="H156" s="48">
-        <v>4</v>
-      </c>
-      <c r="I156" s="48">
-        <v>3</v>
-      </c>
-      <c r="J156" s="48">
-        <v>3</v>
-      </c>
-      <c r="K156" s="48">
-        <v>3</v>
-      </c>
-      <c r="L156" s="48">
-        <v>5</v>
-      </c>
-      <c r="M156" s="48">
+      <c r="G156" s="1">
+        <v>5</v>
+      </c>
+      <c r="H156" s="1">
+        <v>4</v>
+      </c>
+      <c r="I156" s="1">
+        <v>3</v>
+      </c>
+      <c r="J156" s="1">
+        <v>3</v>
+      </c>
+      <c r="K156" s="1">
+        <v>3</v>
+      </c>
+      <c r="L156" s="1">
+        <v>5</v>
+      </c>
+      <c r="M156" s="1">
         <v>3</v>
       </c>
       <c r="N156" s="19">
         <f>AVERAGE('NIVEL 2'!G156:M156)</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O156" s="44" t="str">
+      <c r="O156" s="18" t="str">
         <f>IF(N156=" "," ",IF(N156&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A157" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B157" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C157" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D157" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E157" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="F157" s="47">
+        <v>1018813</v>
+      </c>
+      <c r="G157" s="47">
+        <v>5</v>
+      </c>
+      <c r="H157" s="47">
+        <v>4</v>
+      </c>
+      <c r="I157" s="47">
+        <v>3</v>
+      </c>
+      <c r="J157" s="47">
+        <v>3</v>
+      </c>
+      <c r="K157" s="47">
+        <v>4</v>
+      </c>
+      <c r="L157" s="47">
+        <v>5</v>
+      </c>
+      <c r="M157" s="47">
+        <v>2</v>
+      </c>
+      <c r="N157" s="19">
+        <f>AVERAGE('NIVEL 2'!G157:M157)</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O157" s="48" t="str">
+        <f>IF(N157=" "," ",IF(N157&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A158" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B158" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C158" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D158" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E158" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="F158" s="47">
+        <v>1418308</v>
+      </c>
+      <c r="G158" s="47">
+        <v>5</v>
+      </c>
+      <c r="H158" s="47">
+        <v>5</v>
+      </c>
+      <c r="I158" s="47">
+        <v>4</v>
+      </c>
+      <c r="J158" s="47">
+        <v>5</v>
+      </c>
+      <c r="K158" s="47">
+        <v>5</v>
+      </c>
+      <c r="L158" s="47">
+        <v>5</v>
+      </c>
+      <c r="M158" s="47">
+        <v>3</v>
+      </c>
+      <c r="N158" s="19">
+        <f>AVERAGE('NIVEL 2'!G158:M158)</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O158" s="48" t="str">
+        <f>IF(N158=" "," ",IF(N158&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A159" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B159" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C159" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D159" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E159" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="F159" s="47">
+        <v>7384397</v>
+      </c>
+      <c r="G159" s="47">
+        <v>5</v>
+      </c>
+      <c r="H159" s="47">
+        <v>5</v>
+      </c>
+      <c r="I159" s="47">
+        <v>3</v>
+      </c>
+      <c r="J159" s="47">
+        <v>5</v>
+      </c>
+      <c r="K159" s="47">
+        <v>5</v>
+      </c>
+      <c r="L159" s="47">
+        <v>5</v>
+      </c>
+      <c r="M159" s="47">
+        <v>5</v>
+      </c>
+      <c r="N159" s="19">
+        <f>AVERAGE('NIVEL 2'!G159:M159)</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O159" s="48" t="str">
+        <f>IF(N159=" "," ",IF(N159&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A160" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B160" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C160" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D160" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E160" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="F160" s="47">
+        <v>10966252</v>
+      </c>
+      <c r="G160" s="47">
+        <v>5</v>
+      </c>
+      <c r="H160" s="47">
+        <v>5</v>
+      </c>
+      <c r="I160" s="47">
+        <v>4</v>
+      </c>
+      <c r="J160" s="47">
+        <v>5</v>
+      </c>
+      <c r="K160" s="47">
+        <v>5</v>
+      </c>
+      <c r="L160" s="47">
+        <v>5</v>
+      </c>
+      <c r="M160" s="47">
+        <v>4</v>
+      </c>
+      <c r="N160" s="19">
+        <f>AVERAGE('NIVEL 2'!G160:M160)</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O160" s="48" t="str">
+        <f>IF(N160=" "," ",IF(N160&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A161" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B161" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C161" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D161" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E161" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="F161" s="47">
+        <v>22668392</v>
+      </c>
+      <c r="G161" s="47">
+        <v>4</v>
+      </c>
+      <c r="H161" s="47">
+        <v>3</v>
+      </c>
+      <c r="I161" s="47">
+        <v>2</v>
+      </c>
+      <c r="J161" s="47">
+        <v>2</v>
+      </c>
+      <c r="K161" s="47">
+        <v>2</v>
+      </c>
+      <c r="L161" s="47">
+        <v>3</v>
+      </c>
+      <c r="M161" s="47">
+        <v>1</v>
+      </c>
+      <c r="N161" s="19">
+        <f>AVERAGE('NIVEL 2'!G161:M161)</f>
+        <v>2.4285714285714284</v>
+      </c>
+      <c r="O161" s="48" t="str">
+        <f>IF(N161=" "," ",IF(N161&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A162" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B162" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C162" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D162" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E162" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="F162" s="47">
+        <v>1001481017</v>
+      </c>
+      <c r="G162" s="47">
+        <v>4</v>
+      </c>
+      <c r="H162" s="47">
+        <v>4</v>
+      </c>
+      <c r="I162" s="47">
+        <v>2</v>
+      </c>
+      <c r="J162" s="47">
+        <v>3</v>
+      </c>
+      <c r="K162" s="47">
+        <v>4</v>
+      </c>
+      <c r="L162" s="47">
+        <v>4</v>
+      </c>
+      <c r="M162" s="47">
+        <v>2</v>
+      </c>
+      <c r="N162" s="19">
+        <f>AVERAGE('NIVEL 2'!G162:M162)</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O162" s="48" t="str">
+        <f>IF(N162=" "," ",IF(N162&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A163" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B163" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C163" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D163" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E163" s="45" t="s">
+        <v>196</v>
+      </c>
+      <c r="F163" s="47">
+        <v>1003049821</v>
+      </c>
+      <c r="G163" s="47">
+        <v>5</v>
+      </c>
+      <c r="H163" s="47">
+        <v>4</v>
+      </c>
+      <c r="I163" s="47">
+        <v>3</v>
+      </c>
+      <c r="J163" s="47">
+        <v>4</v>
+      </c>
+      <c r="K163" s="47">
+        <v>4</v>
+      </c>
+      <c r="L163" s="47">
+        <v>5</v>
+      </c>
+      <c r="M163" s="47">
+        <v>2</v>
+      </c>
+      <c r="N163" s="19">
+        <f>AVERAGE('NIVEL 2'!G163:M163)</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O163" s="48" t="str">
+        <f>IF(N163=" "," ",IF(N163&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A164" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B164" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C164" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D164" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E164" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="F164" s="47">
+        <v>1007676028</v>
+      </c>
+      <c r="G164" s="47">
+        <v>5</v>
+      </c>
+      <c r="H164" s="47">
+        <v>4</v>
+      </c>
+      <c r="I164" s="47">
+        <v>3</v>
+      </c>
+      <c r="J164" s="47">
+        <v>4</v>
+      </c>
+      <c r="K164" s="47">
+        <v>3</v>
+      </c>
+      <c r="L164" s="47">
+        <v>4</v>
+      </c>
+      <c r="M164" s="47">
+        <v>2</v>
+      </c>
+      <c r="N164" s="19">
+        <f>AVERAGE('NIVEL 2'!G164:M164)</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="O164" s="48" t="str">
+        <f>IF(N164=" "," ",IF(N164&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A165" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B165" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C165" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D165" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E165" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F165" s="47">
+        <v>1007822238</v>
+      </c>
+      <c r="G165" s="47">
+        <v>5</v>
+      </c>
+      <c r="H165" s="47">
+        <v>5</v>
+      </c>
+      <c r="I165" s="47">
+        <v>3</v>
+      </c>
+      <c r="J165" s="47">
+        <v>5</v>
+      </c>
+      <c r="K165" s="47">
+        <v>5</v>
+      </c>
+      <c r="L165" s="47">
+        <v>5</v>
+      </c>
+      <c r="M165" s="47">
+        <v>5</v>
+      </c>
+      <c r="N165" s="19">
+        <f>AVERAGE('NIVEL 2'!G165:M165)</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O165" s="48" t="str">
+        <f>IF(N165=" "," ",IF(N165&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A166" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B166" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C166" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D166" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E166" s="45" t="s">
+        <v>63</v>
+      </c>
+      <c r="F166" s="47">
+        <v>1027663882</v>
+      </c>
+      <c r="G166" s="47">
+        <v>4</v>
+      </c>
+      <c r="H166" s="47">
+        <v>4</v>
+      </c>
+      <c r="I166" s="47">
+        <v>5</v>
+      </c>
+      <c r="J166" s="47">
+        <v>4</v>
+      </c>
+      <c r="K166" s="47">
+        <v>4</v>
+      </c>
+      <c r="L166" s="47">
+        <v>5</v>
+      </c>
+      <c r="M166" s="47">
+        <v>3</v>
+      </c>
+      <c r="N166" s="19">
+        <f>AVERAGE('NIVEL 2'!G166:M166)</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O166" s="48" t="str">
+        <f>IF(N166=" "," ",IF(N166&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A167" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B167" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C167" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D167" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E167" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="F167" s="47">
+        <v>1029722943</v>
+      </c>
+      <c r="G167" s="47">
+        <v>5</v>
+      </c>
+      <c r="H167" s="47">
+        <v>5</v>
+      </c>
+      <c r="I167" s="47">
+        <v>5</v>
+      </c>
+      <c r="J167" s="47">
+        <v>4</v>
+      </c>
+      <c r="K167" s="47">
+        <v>5</v>
+      </c>
+      <c r="L167" s="47">
+        <v>5</v>
+      </c>
+      <c r="M167" s="47">
+        <v>3</v>
+      </c>
+      <c r="N167" s="19">
+        <f>AVERAGE('NIVEL 2'!G167:M167)</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O167" s="48" t="str">
+        <f>IF(N167=" "," ",IF(N167&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A168" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B168" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C168" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D168" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E168" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="F168" s="47">
+        <v>1031543523</v>
+      </c>
+      <c r="G168" s="47">
+        <v>5</v>
+      </c>
+      <c r="H168" s="47">
+        <v>5</v>
+      </c>
+      <c r="I168" s="47">
+        <v>5</v>
+      </c>
+      <c r="J168" s="47">
+        <v>5</v>
+      </c>
+      <c r="K168" s="47">
+        <v>5</v>
+      </c>
+      <c r="L168" s="47">
+        <v>5</v>
+      </c>
+      <c r="M168" s="47">
+        <v>3</v>
+      </c>
+      <c r="N168" s="19">
+        <f>AVERAGE('NIVEL 2'!G168:M168)</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O168" s="48" t="str">
+        <f>IF(N168=" "," ",IF(N168&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A169" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B169" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C169" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D169" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E169" s="45" t="s">
+        <v>76</v>
+      </c>
+      <c r="F169" s="47">
+        <v>1062432000</v>
+      </c>
+      <c r="G169" s="47">
+        <v>5</v>
+      </c>
+      <c r="H169" s="47">
+        <v>5</v>
+      </c>
+      <c r="I169" s="47">
+        <v>3</v>
+      </c>
+      <c r="J169" s="47">
+        <v>4</v>
+      </c>
+      <c r="K169" s="47">
+        <v>4</v>
+      </c>
+      <c r="L169" s="47">
+        <v>5</v>
+      </c>
+      <c r="M169" s="47">
+        <v>2</v>
+      </c>
+      <c r="N169" s="19">
+        <f>AVERAGE('NIVEL 2'!G169:M169)</f>
+        <v>4</v>
+      </c>
+      <c r="O169" s="48" t="str">
+        <f>IF(N169=" "," ",IF(N169&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A170" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B170" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C170" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D170" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E170" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="F170" s="47">
+        <v>1062433188</v>
+      </c>
+      <c r="G170" s="47">
+        <v>5</v>
+      </c>
+      <c r="H170" s="47">
+        <v>5</v>
+      </c>
+      <c r="I170" s="47">
+        <v>3</v>
+      </c>
+      <c r="J170" s="47">
+        <v>3</v>
+      </c>
+      <c r="K170" s="47">
+        <v>3</v>
+      </c>
+      <c r="L170" s="47">
+        <v>5</v>
+      </c>
+      <c r="M170" s="47">
+        <v>2</v>
+      </c>
+      <c r="N170" s="19">
+        <f>AVERAGE('NIVEL 2'!G170:M170)</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O170" s="48" t="str">
+        <f>IF(N170=" "," ",IF(N170&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A171" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B171" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C171" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D171" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E171" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="F171" s="47">
+        <v>1062539643</v>
+      </c>
+      <c r="G171" s="47">
+        <v>5</v>
+      </c>
+      <c r="H171" s="47">
+        <v>4</v>
+      </c>
+      <c r="I171" s="47">
+        <v>4</v>
+      </c>
+      <c r="J171" s="47">
+        <v>5</v>
+      </c>
+      <c r="K171" s="47">
+        <v>5</v>
+      </c>
+      <c r="L171" s="47">
+        <v>5</v>
+      </c>
+      <c r="M171" s="47">
+        <v>5</v>
+      </c>
+      <c r="N171" s="19">
+        <f>AVERAGE('NIVEL 2'!G171:M171)</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O171" s="48" t="str">
+        <f>IF(N171=" "," ",IF(N171&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A172" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B172" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C172" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D172" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E172" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="F172" s="47">
+        <v>1062980565</v>
+      </c>
+      <c r="G172" s="47">
+        <v>5</v>
+      </c>
+      <c r="H172" s="47">
+        <v>4</v>
+      </c>
+      <c r="I172" s="47">
+        <v>3</v>
+      </c>
+      <c r="J172" s="47">
+        <v>4</v>
+      </c>
+      <c r="K172" s="47">
+        <v>4</v>
+      </c>
+      <c r="L172" s="47">
+        <v>5</v>
+      </c>
+      <c r="M172" s="47">
+        <v>4</v>
+      </c>
+      <c r="N172" s="19">
+        <f>AVERAGE('NIVEL 2'!G172:M172)</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O172" s="48" t="str">
+        <f>IF(N172=" "," ",IF(N172&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A173" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B173" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C173" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D173" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E173" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="F173" s="47">
+        <v>1062986616</v>
+      </c>
+      <c r="G173" s="47">
+        <v>5</v>
+      </c>
+      <c r="H173" s="47">
+        <v>5</v>
+      </c>
+      <c r="I173" s="47">
+        <v>3</v>
+      </c>
+      <c r="J173" s="47">
+        <v>3</v>
+      </c>
+      <c r="K173" s="47">
+        <v>3</v>
+      </c>
+      <c r="L173" s="47">
+        <v>4</v>
+      </c>
+      <c r="M173" s="47">
+        <v>2</v>
+      </c>
+      <c r="N173" s="19">
+        <f>AVERAGE('NIVEL 2'!G173:M173)</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="O173" s="48" t="str">
+        <f>IF(N173=" "," ",IF(N173&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A174" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B174" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C174" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D174" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E174" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="F174" s="47">
+        <v>1063157522</v>
+      </c>
+      <c r="G174" s="47">
+        <v>5</v>
+      </c>
+      <c r="H174" s="47">
+        <v>5</v>
+      </c>
+      <c r="I174" s="47">
+        <v>3</v>
+      </c>
+      <c r="J174" s="47">
+        <v>3</v>
+      </c>
+      <c r="K174" s="47">
+        <v>2</v>
+      </c>
+      <c r="L174" s="47">
+        <v>5</v>
+      </c>
+      <c r="M174" s="47">
+        <v>2</v>
+      </c>
+      <c r="N174" s="19">
+        <f>AVERAGE('NIVEL 2'!G174:M174)</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="O174" s="48" t="str">
+        <f>IF(N174=" "," ",IF(N174&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A175" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B175" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C175" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D175" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E175" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="F175" s="47">
+        <v>1064990474</v>
+      </c>
+      <c r="G175" s="47">
+        <v>5</v>
+      </c>
+      <c r="H175" s="47">
+        <v>5</v>
+      </c>
+      <c r="I175" s="47">
+        <v>3</v>
+      </c>
+      <c r="J175" s="47">
+        <v>4</v>
+      </c>
+      <c r="K175" s="47">
+        <v>5</v>
+      </c>
+      <c r="L175" s="47">
+        <v>5</v>
+      </c>
+      <c r="M175" s="47">
+        <v>4</v>
+      </c>
+      <c r="N175" s="19">
+        <f>AVERAGE('NIVEL 2'!G175:M175)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O175" s="48" t="str">
+        <f>IF(N175=" "," ",IF(N175&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A176" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B176" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C176" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D176" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E176" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="F176" s="47">
+        <v>1066512697</v>
+      </c>
+      <c r="G176" s="47">
+        <v>5</v>
+      </c>
+      <c r="H176" s="47">
+        <v>4</v>
+      </c>
+      <c r="I176" s="47">
+        <v>2</v>
+      </c>
+      <c r="J176" s="47">
+        <v>4</v>
+      </c>
+      <c r="K176" s="47">
+        <v>4</v>
+      </c>
+      <c r="L176" s="47">
+        <v>5</v>
+      </c>
+      <c r="M176" s="47">
+        <v>2</v>
+      </c>
+      <c r="N176" s="19">
+        <f>AVERAGE('NIVEL 2'!G176:M176)</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O176" s="48" t="str">
+        <f>IF(N176=" "," ",IF(N176&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A177" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B177" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C177" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D177" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E177" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="F177" s="47">
+        <v>1066523010</v>
+      </c>
+      <c r="G177" s="47">
+        <v>5</v>
+      </c>
+      <c r="H177" s="47">
+        <v>4</v>
+      </c>
+      <c r="I177" s="47">
+        <v>2</v>
+      </c>
+      <c r="J177" s="47">
+        <v>3</v>
+      </c>
+      <c r="K177" s="47">
+        <v>2</v>
+      </c>
+      <c r="L177" s="47">
+        <v>5</v>
+      </c>
+      <c r="M177" s="47">
+        <v>2</v>
+      </c>
+      <c r="N177" s="19">
+        <f>AVERAGE('NIVEL 2'!G177:M177)</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O177" s="48" t="str">
+        <f>IF(N177=" "," ",IF(N177&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A178" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B178" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C178" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D178" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E178" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="F178" s="47">
+        <v>1066747786</v>
+      </c>
+      <c r="G178" s="47">
+        <v>5</v>
+      </c>
+      <c r="H178" s="47">
+        <v>5</v>
+      </c>
+      <c r="I178" s="47">
+        <v>3</v>
+      </c>
+      <c r="J178" s="47">
+        <v>5</v>
+      </c>
+      <c r="K178" s="47">
+        <v>5</v>
+      </c>
+      <c r="L178" s="47">
+        <v>5</v>
+      </c>
+      <c r="M178" s="47">
+        <v>3</v>
+      </c>
+      <c r="N178" s="19">
+        <f>AVERAGE('NIVEL 2'!G178:M178)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O178" s="48" t="str">
+        <f>IF(N178=" "," ",IF(N178&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A179" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B179" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C179" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D179" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E179" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="F179" s="47">
+        <v>1067849965</v>
+      </c>
+      <c r="G179" s="47">
+        <v>5</v>
+      </c>
+      <c r="H179" s="47">
+        <v>5</v>
+      </c>
+      <c r="I179" s="47">
+        <v>3</v>
+      </c>
+      <c r="J179" s="47">
+        <v>4</v>
+      </c>
+      <c r="K179" s="47">
+        <v>5</v>
+      </c>
+      <c r="L179" s="47">
+        <v>5</v>
+      </c>
+      <c r="M179" s="47">
+        <v>2</v>
+      </c>
+      <c r="N179" s="19">
+        <f>AVERAGE('NIVEL 2'!G179:M179)</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O179" s="48" t="str">
+        <f>IF(N179=" "," ",IF(N179&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A180" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B180" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C180" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D180" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E180" s="45" t="s">
+        <v>201</v>
+      </c>
+      <c r="F180" s="47">
+        <v>1067955099</v>
+      </c>
+      <c r="G180" s="47">
+        <v>5</v>
+      </c>
+      <c r="H180" s="47">
+        <v>4</v>
+      </c>
+      <c r="I180" s="47">
+        <v>2</v>
+      </c>
+      <c r="J180" s="47">
+        <v>4</v>
+      </c>
+      <c r="K180" s="47">
+        <v>5</v>
+      </c>
+      <c r="L180" s="47">
+        <v>5</v>
+      </c>
+      <c r="M180" s="47">
+        <v>2</v>
+      </c>
+      <c r="N180" s="19">
+        <f>AVERAGE('NIVEL 2'!G180:M180)</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O180" s="48" t="str">
+        <f>IF(N180=" "," ",IF(N180&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A181" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B181" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C181" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D181" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E181" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="F181" s="47">
+        <v>1068439668</v>
+      </c>
+      <c r="G181" s="47">
+        <v>5</v>
+      </c>
+      <c r="H181" s="47">
+        <v>5</v>
+      </c>
+      <c r="I181" s="47">
+        <v>5</v>
+      </c>
+      <c r="J181" s="47">
+        <v>5</v>
+      </c>
+      <c r="K181" s="47">
+        <v>3</v>
+      </c>
+      <c r="L181" s="47">
+        <v>5</v>
+      </c>
+      <c r="M181" s="47">
+        <v>2</v>
+      </c>
+      <c r="N181" s="19">
+        <f>AVERAGE('NIVEL 2'!G181:M181)</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O181" s="48" t="str">
+        <f>IF(N181=" "," ",IF(N181&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A182" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B182" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C182" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D182" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E182" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="F182" s="47">
+        <v>1073817245</v>
+      </c>
+      <c r="G182" s="47">
+        <v>4</v>
+      </c>
+      <c r="H182" s="47">
+        <v>3</v>
+      </c>
+      <c r="I182" s="47">
+        <v>2</v>
+      </c>
+      <c r="J182" s="47">
+        <v>2</v>
+      </c>
+      <c r="K182" s="47">
+        <v>1</v>
+      </c>
+      <c r="L182" s="47">
+        <v>4</v>
+      </c>
+      <c r="M182" s="47">
+        <v>1</v>
+      </c>
+      <c r="N182" s="19">
+        <f>AVERAGE('NIVEL 2'!G182:M182)</f>
+        <v>2.4285714285714284</v>
+      </c>
+      <c r="O182" s="48" t="str">
+        <f>IF(N182=" "," ",IF(N182&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A183" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B183" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C183" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D183" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E183" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="F183" s="47">
+        <v>1138031207</v>
+      </c>
+      <c r="G183" s="47">
+        <v>5</v>
+      </c>
+      <c r="H183" s="47">
+        <v>5</v>
+      </c>
+      <c r="I183" s="47">
+        <v>5</v>
+      </c>
+      <c r="J183" s="47">
+        <v>4</v>
+      </c>
+      <c r="K183" s="47">
+        <v>4</v>
+      </c>
+      <c r="L183" s="47">
+        <v>5</v>
+      </c>
+      <c r="M183" s="47">
+        <v>2</v>
+      </c>
+      <c r="N183" s="19">
+        <f>AVERAGE('NIVEL 2'!G183:M183)</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O183" s="48" t="str">
+        <f>IF(N183=" "," ",IF(N183&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A184" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B184" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C184" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D184" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E184" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="F184" s="47">
+        <v>1138032406</v>
+      </c>
+      <c r="G184" s="47">
+        <v>5</v>
+      </c>
+      <c r="H184" s="47">
+        <v>5</v>
+      </c>
+      <c r="I184" s="47">
+        <v>4</v>
+      </c>
+      <c r="J184" s="47">
+        <v>5</v>
+      </c>
+      <c r="K184" s="47">
+        <v>4</v>
+      </c>
+      <c r="L184" s="47">
+        <v>5</v>
+      </c>
+      <c r="M184" s="47">
+        <v>2</v>
+      </c>
+      <c r="N184" s="19">
+        <f>AVERAGE('NIVEL 2'!G184:M184)</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O184" s="48" t="str">
+        <f>IF(N184=" "," ",IF(N184&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A185" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B185" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C185" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D185" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E185" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="F185" s="47">
+        <v>1138032417</v>
+      </c>
+      <c r="G185" s="47">
+        <v>5</v>
+      </c>
+      <c r="H185" s="47">
+        <v>5</v>
+      </c>
+      <c r="I185" s="47">
+        <v>3</v>
+      </c>
+      <c r="J185" s="47">
+        <v>4</v>
+      </c>
+      <c r="K185" s="47">
+        <v>3</v>
+      </c>
+      <c r="L185" s="47">
+        <v>5</v>
+      </c>
+      <c r="M185" s="47">
+        <v>2</v>
+      </c>
+      <c r="N185" s="19">
+        <f>AVERAGE('NIVEL 2'!G185:M185)</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O185" s="48" t="str">
+        <f>IF(N185=" "," ",IF(N185&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A186" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B186" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C186" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D186" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E186" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="F186" s="47">
+        <v>1140444971</v>
+      </c>
+      <c r="G186" s="47">
+        <v>5</v>
+      </c>
+      <c r="H186" s="47">
+        <v>5</v>
+      </c>
+      <c r="I186" s="47">
+        <v>3</v>
+      </c>
+      <c r="J186" s="47">
+        <v>3</v>
+      </c>
+      <c r="K186" s="47">
+        <v>3</v>
+      </c>
+      <c r="L186" s="47">
+        <v>5</v>
+      </c>
+      <c r="M186" s="47">
+        <v>2</v>
+      </c>
+      <c r="N186" s="19">
+        <f>AVERAGE('NIVEL 2'!G186:M186)</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O186" s="48" t="str">
+        <f>IF(N186=" "," ",IF(N186&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A187" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B187" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C187" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D187" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E187" s="45" t="s">
+        <v>194</v>
+      </c>
+      <c r="F187" s="47">
+        <v>1141358368</v>
+      </c>
+      <c r="G187" s="47">
+        <v>5</v>
+      </c>
+      <c r="H187" s="47">
+        <v>5</v>
+      </c>
+      <c r="I187" s="47">
+        <v>3</v>
+      </c>
+      <c r="J187" s="47">
+        <v>4</v>
+      </c>
+      <c r="K187" s="47">
+        <v>5</v>
+      </c>
+      <c r="L187" s="47">
+        <v>5</v>
+      </c>
+      <c r="M187" s="47">
+        <v>2</v>
+      </c>
+      <c r="N187" s="19">
+        <f>AVERAGE('NIVEL 2'!G187:M187)</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O187" s="48" t="str">
+        <f>IF(N187=" "," ",IF(N187&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A188" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B188" s="50" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C188" s="50" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D188" s="44">
+        <v>45929</v>
+      </c>
+      <c r="E188" s="45" t="s">
+        <v>172</v>
+      </c>
+      <c r="F188" s="47">
+        <v>1142930859</v>
+      </c>
+      <c r="G188" s="47">
+        <v>5</v>
+      </c>
+      <c r="H188" s="47">
+        <v>4</v>
+      </c>
+      <c r="I188" s="47">
+        <v>3</v>
+      </c>
+      <c r="J188" s="47">
+        <v>4</v>
+      </c>
+      <c r="K188" s="47">
+        <v>4</v>
+      </c>
+      <c r="L188" s="47">
+        <v>5</v>
+      </c>
+      <c r="M188" s="47">
+        <v>3</v>
+      </c>
+      <c r="N188" s="19">
+        <f>AVERAGE('NIVEL 2'!G188:M188)</f>
+        <v>4</v>
+      </c>
+      <c r="O188" s="48" t="str">
+        <f>IF(N188=" "," ",IF(N188&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -31097,7 +34273,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U41"/>
+  <dimension ref="A1:U44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" customWidth="1"/>
@@ -33659,282 +36835,492 @@
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A38" s="50">
+      <c r="A38" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B38" s="43" t="str">
+      <c r="B38" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C38" s="51" t="str">
+      <c r="C38" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D38" s="52">
+      <c r="D38" s="21">
         <v>45899</v>
       </c>
-      <c r="E38" s="53" t="s">
+      <c r="E38" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F38" s="54">
+      <c r="F38" s="23">
         <v>33204108</v>
       </c>
-      <c r="G38" s="54">
-        <v>5</v>
-      </c>
-      <c r="H38" s="54">
-        <v>4</v>
-      </c>
-      <c r="I38" s="54">
-        <v>5</v>
-      </c>
-      <c r="J38" s="54">
-        <v>5</v>
-      </c>
-      <c r="K38" s="54">
-        <v>5</v>
-      </c>
-      <c r="L38" s="54">
-        <v>4</v>
-      </c>
-      <c r="M38" s="54">
-        <v>5</v>
-      </c>
-      <c r="N38" s="54">
-        <v>5</v>
-      </c>
-      <c r="O38" s="54">
-        <v>5</v>
-      </c>
-      <c r="P38" s="54">
-        <v>5</v>
-      </c>
-      <c r="Q38" s="54">
-        <v>4</v>
-      </c>
-      <c r="R38" s="54">
-        <v>5</v>
-      </c>
-      <c r="S38" s="54">
+      <c r="G38" s="23">
+        <v>5</v>
+      </c>
+      <c r="H38" s="23">
+        <v>4</v>
+      </c>
+      <c r="I38" s="23">
+        <v>5</v>
+      </c>
+      <c r="J38" s="23">
+        <v>5</v>
+      </c>
+      <c r="K38" s="23">
+        <v>5</v>
+      </c>
+      <c r="L38" s="23">
+        <v>4</v>
+      </c>
+      <c r="M38" s="23">
+        <v>5</v>
+      </c>
+      <c r="N38" s="23">
+        <v>5</v>
+      </c>
+      <c r="O38" s="23">
+        <v>5</v>
+      </c>
+      <c r="P38" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="23">
+        <v>4</v>
+      </c>
+      <c r="R38" s="23">
+        <v>5</v>
+      </c>
+      <c r="S38" s="23">
         <v>5</v>
       </c>
       <c r="T38" s="24">
         <f>AVERAGE('NIVEL 3'!G38:S38)</f>
         <v>4.7692307692307692</v>
       </c>
-      <c r="U38" s="55" t="str">
+      <c r="U38" s="32" t="str">
         <f>IF(T38=" "," ",IF(T38&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A39" s="50">
+      <c r="A39" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B39" s="43" t="str">
+      <c r="B39" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C39" s="51" t="str">
+      <c r="C39" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D39" s="52">
+      <c r="D39" s="21">
         <v>45899</v>
       </c>
-      <c r="E39" s="53" t="s">
+      <c r="E39" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="F39" s="54">
+      <c r="F39" s="23">
         <v>1064193109</v>
       </c>
-      <c r="G39" s="54">
-        <v>5</v>
-      </c>
-      <c r="H39" s="54">
-        <v>5</v>
-      </c>
-      <c r="I39" s="54">
-        <v>5</v>
-      </c>
-      <c r="J39" s="54">
-        <v>5</v>
-      </c>
-      <c r="K39" s="54">
-        <v>5</v>
-      </c>
-      <c r="L39" s="54">
-        <v>4</v>
-      </c>
-      <c r="M39" s="54">
-        <v>5</v>
-      </c>
-      <c r="N39" s="54">
-        <v>5</v>
-      </c>
-      <c r="O39" s="54">
-        <v>5</v>
-      </c>
-      <c r="P39" s="54">
-        <v>5</v>
-      </c>
-      <c r="Q39" s="54">
-        <v>4</v>
-      </c>
-      <c r="R39" s="54">
-        <v>4</v>
-      </c>
-      <c r="S39" s="54">
+      <c r="G39" s="23">
+        <v>5</v>
+      </c>
+      <c r="H39" s="23">
+        <v>5</v>
+      </c>
+      <c r="I39" s="23">
+        <v>5</v>
+      </c>
+      <c r="J39" s="23">
+        <v>5</v>
+      </c>
+      <c r="K39" s="23">
+        <v>5</v>
+      </c>
+      <c r="L39" s="23">
+        <v>4</v>
+      </c>
+      <c r="M39" s="23">
+        <v>5</v>
+      </c>
+      <c r="N39" s="23">
+        <v>5</v>
+      </c>
+      <c r="O39" s="23">
+        <v>5</v>
+      </c>
+      <c r="P39" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="23">
+        <v>4</v>
+      </c>
+      <c r="R39" s="23">
+        <v>4</v>
+      </c>
+      <c r="S39" s="23">
         <v>5</v>
       </c>
       <c r="T39" s="24">
         <f>AVERAGE('NIVEL 3'!G39:S39)</f>
         <v>4.7692307692307692</v>
       </c>
-      <c r="U39" s="55" t="str">
+      <c r="U39" s="32" t="str">
         <f>IF(T39=" "," ",IF(T39&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A40" s="50">
+      <c r="A40" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B40" s="43" t="str">
+      <c r="B40" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C40" s="51" t="str">
+      <c r="C40" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D40" s="52">
+      <c r="D40" s="21">
         <v>45899</v>
       </c>
-      <c r="E40" s="53" t="s">
+      <c r="E40" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="F40" s="54">
+      <c r="F40" s="23">
         <v>1067869670</v>
       </c>
-      <c r="G40" s="54">
-        <v>5</v>
-      </c>
-      <c r="H40" s="54">
-        <v>4</v>
-      </c>
-      <c r="I40" s="54">
-        <v>5</v>
-      </c>
-      <c r="J40" s="54">
-        <v>5</v>
-      </c>
-      <c r="K40" s="54">
-        <v>5</v>
-      </c>
-      <c r="L40" s="54">
-        <v>3</v>
-      </c>
-      <c r="M40" s="54">
-        <v>5</v>
-      </c>
-      <c r="N40" s="54">
-        <v>5</v>
-      </c>
-      <c r="O40" s="54">
-        <v>5</v>
-      </c>
-      <c r="P40" s="54">
-        <v>5</v>
-      </c>
-      <c r="Q40" s="54">
-        <v>5</v>
-      </c>
-      <c r="R40" s="54">
-        <v>5</v>
-      </c>
-      <c r="S40" s="54">
+      <c r="G40" s="23">
+        <v>5</v>
+      </c>
+      <c r="H40" s="23">
+        <v>4</v>
+      </c>
+      <c r="I40" s="23">
+        <v>5</v>
+      </c>
+      <c r="J40" s="23">
+        <v>5</v>
+      </c>
+      <c r="K40" s="23">
+        <v>5</v>
+      </c>
+      <c r="L40" s="23">
+        <v>3</v>
+      </c>
+      <c r="M40" s="23">
+        <v>5</v>
+      </c>
+      <c r="N40" s="23">
+        <v>5</v>
+      </c>
+      <c r="O40" s="23">
+        <v>5</v>
+      </c>
+      <c r="P40" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="23">
+        <v>5</v>
+      </c>
+      <c r="R40" s="23">
+        <v>5</v>
+      </c>
+      <c r="S40" s="23">
         <v>5</v>
       </c>
       <c r="T40" s="24">
         <f>AVERAGE('NIVEL 3'!G40:S40)</f>
         <v>4.7692307692307692</v>
       </c>
-      <c r="U40" s="55" t="str">
+      <c r="U40" s="32" t="str">
         <f>IF(T40=" "," ",IF(T40&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A41" s="50">
+      <c r="A41" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
       </c>
-      <c r="B41" s="43" t="str">
+      <c r="B41" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C41" s="51" t="str">
+      <c r="C41" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>agosto</v>
       </c>
-      <c r="D41" s="52">
+      <c r="D41" s="21">
         <v>45899</v>
       </c>
-      <c r="E41" s="53" t="s">
+      <c r="E41" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="F41" s="54">
+      <c r="F41" s="23">
         <v>1067925321</v>
       </c>
-      <c r="G41" s="54">
-        <v>5</v>
-      </c>
-      <c r="H41" s="54">
-        <v>5</v>
-      </c>
-      <c r="I41" s="54">
-        <v>5</v>
-      </c>
-      <c r="J41" s="54">
-        <v>5</v>
-      </c>
-      <c r="K41" s="54">
-        <v>5</v>
-      </c>
-      <c r="L41" s="54">
-        <v>5</v>
-      </c>
-      <c r="M41" s="54">
-        <v>5</v>
-      </c>
-      <c r="N41" s="54">
-        <v>5</v>
-      </c>
-      <c r="O41" s="54">
-        <v>5</v>
-      </c>
-      <c r="P41" s="54">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="54">
-        <v>4</v>
-      </c>
-      <c r="R41" s="54">
-        <v>5</v>
-      </c>
-      <c r="S41" s="54">
+      <c r="G41" s="23">
+        <v>5</v>
+      </c>
+      <c r="H41" s="23">
+        <v>5</v>
+      </c>
+      <c r="I41" s="23">
+        <v>5</v>
+      </c>
+      <c r="J41" s="23">
+        <v>5</v>
+      </c>
+      <c r="K41" s="23">
+        <v>5</v>
+      </c>
+      <c r="L41" s="23">
+        <v>5</v>
+      </c>
+      <c r="M41" s="23">
+        <v>5</v>
+      </c>
+      <c r="N41" s="23">
+        <v>5</v>
+      </c>
+      <c r="O41" s="23">
+        <v>5</v>
+      </c>
+      <c r="P41" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="23">
+        <v>4</v>
+      </c>
+      <c r="R41" s="23">
+        <v>5</v>
+      </c>
+      <c r="S41" s="23">
         <v>5</v>
       </c>
       <c r="T41" s="24">
         <f>AVERAGE('NIVEL 3'!G41:S41)</f>
         <v>4.9230769230769234</v>
       </c>
-      <c r="U41" s="55" t="str">
+      <c r="U41" s="32" t="str">
         <f>IF(T41=" "," ",IF(T41&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <v>CAMBIA A EQUIPO</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A42" s="51">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B42" s="43" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C42" s="52" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D42" s="53">
+        <v>45929</v>
+      </c>
+      <c r="E42" s="54" t="s">
+        <v>110</v>
+      </c>
+      <c r="F42" s="55">
+        <v>33204108</v>
+      </c>
+      <c r="G42" s="55">
+        <v>5</v>
+      </c>
+      <c r="H42" s="55">
+        <v>5</v>
+      </c>
+      <c r="I42" s="55">
+        <v>5</v>
+      </c>
+      <c r="J42" s="55">
+        <v>5</v>
+      </c>
+      <c r="K42" s="55">
+        <v>5</v>
+      </c>
+      <c r="L42" s="55">
+        <v>5</v>
+      </c>
+      <c r="M42" s="55">
+        <v>5</v>
+      </c>
+      <c r="N42" s="55">
+        <v>5</v>
+      </c>
+      <c r="O42" s="55">
+        <v>5</v>
+      </c>
+      <c r="P42" s="55">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="55">
+        <v>4</v>
+      </c>
+      <c r="R42" s="55">
+        <v>5</v>
+      </c>
+      <c r="S42" s="55">
+        <v>5</v>
+      </c>
+      <c r="T42" s="24">
+        <f>AVERAGE('NIVEL 3'!G42:S42)</f>
+        <v>4.9230769230769234</v>
+      </c>
+      <c r="U42" s="56" t="str">
+        <f>IF(T42=" "," ",IF(T42&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <v>CAMBIA A EQUIPO</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A43" s="51">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B43" s="43" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C43" s="52" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D43" s="53">
+        <v>45929</v>
+      </c>
+      <c r="E43" s="54" t="s">
+        <v>191</v>
+      </c>
+      <c r="F43" s="55">
+        <v>1064193109</v>
+      </c>
+      <c r="G43" s="55">
+        <v>5</v>
+      </c>
+      <c r="H43" s="55">
+        <v>5</v>
+      </c>
+      <c r="I43" s="55">
+        <v>5</v>
+      </c>
+      <c r="J43" s="55">
+        <v>5</v>
+      </c>
+      <c r="K43" s="55">
+        <v>5</v>
+      </c>
+      <c r="L43" s="55">
+        <v>5</v>
+      </c>
+      <c r="M43" s="55">
+        <v>5</v>
+      </c>
+      <c r="N43" s="55">
+        <v>5</v>
+      </c>
+      <c r="O43" s="55">
+        <v>5</v>
+      </c>
+      <c r="P43" s="55">
+        <v>5</v>
+      </c>
+      <c r="Q43" s="55">
+        <v>4</v>
+      </c>
+      <c r="R43" s="55">
+        <v>4</v>
+      </c>
+      <c r="S43" s="55">
+        <v>5</v>
+      </c>
+      <c r="T43" s="24">
+        <f>AVERAGE('NIVEL 3'!G43:S43)</f>
+        <v>4.8461538461538458</v>
+      </c>
+      <c r="U43" s="56" t="str">
+        <f>IF(T43=" "," ",IF(T43&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A44" s="51">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B44" s="43" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C44" s="52" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D44" s="53">
+        <v>45929</v>
+      </c>
+      <c r="E44" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="F44" s="55">
+        <v>1067869670</v>
+      </c>
+      <c r="G44" s="55">
+        <v>5</v>
+      </c>
+      <c r="H44" s="55">
+        <v>5</v>
+      </c>
+      <c r="I44" s="55">
+        <v>5</v>
+      </c>
+      <c r="J44" s="55">
+        <v>5</v>
+      </c>
+      <c r="K44" s="55">
+        <v>5</v>
+      </c>
+      <c r="L44" s="55">
+        <v>4</v>
+      </c>
+      <c r="M44" s="55">
+        <v>5</v>
+      </c>
+      <c r="N44" s="55">
+        <v>5</v>
+      </c>
+      <c r="O44" s="55">
+        <v>5</v>
+      </c>
+      <c r="P44" s="55">
+        <v>5</v>
+      </c>
+      <c r="Q44" s="55">
+        <v>5</v>
+      </c>
+      <c r="R44" s="55">
+        <v>5</v>
+      </c>
+      <c r="S44" s="55">
+        <v>5</v>
+      </c>
+      <c r="T44" s="24">
+        <f>AVERAGE('NIVEL 3'!G44:S44)</f>
+        <v>4.9230769230769234</v>
+      </c>
+      <c r="U44" s="56" t="str">
+        <f>IF(T44=" "," ",IF(T44&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>

--- a/documentos/EVALUACIONES MNM 2025.xlsx
+++ b/documentos/EVALUACIONES MNM 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29617"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raúl\Dropbox (Personal)\2025\RESPALDO DE BASE DE DATOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21FB2E0-33F9-4D17-BFD2-18FD021982C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8729E6C1-C6DC-484D-A0A2-EF1AB70C5AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="238">
   <si>
     <t>NOMBRE DEL ALUMNO</t>
   </si>
@@ -918,6 +918,27 @@
   <si>
     <t>Geraldine Sofia Diaz Montes</t>
   </si>
+  <si>
+    <t>Angel Coneo</t>
+  </si>
+  <si>
+    <t>Antonio Coneo</t>
+  </si>
+  <si>
+    <t>Benjamin Argel Serpa</t>
+  </si>
+  <si>
+    <t>Jerónimo Urueta</t>
+  </si>
+  <si>
+    <t>Nicolas David Perez Cerra</t>
+  </si>
+  <si>
+    <t>Maria Gabriela Zabala Tafur</t>
+  </si>
+  <si>
+    <t>Olaris Oriza Solera Cavadía</t>
+  </si>
 </sst>
 </file>
 
@@ -1194,9 +1215,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1214,6 +1232,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1222,6 +1243,563 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="76">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2227,563 +2805,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3333,7 +3354,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3536,7 +3557,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3739,7 +3760,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4142,7 +4163,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="11">
-                        <c:v>0</c:v>
+                        <c:v>16</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -4478,7 +4499,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="11">
-                        <c:v>0</c:v>
+                        <c:v>1</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -5297,7 +5318,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5635,7 +5656,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="11">
-                        <c:v>0</c:v>
+                        <c:v>16</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -5803,7 +5824,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="11">
-                        <c:v>0</c:v>
+                        <c:v>6</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -5976,7 +5997,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="11">
-                        <c:v>0</c:v>
+                        <c:v>9</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -6149,7 +6170,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="11">
-                        <c:v>0</c:v>
+                        <c:v>1</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -6824,7 +6845,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7010,7 +7031,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="11">
-                        <c:v>0</c:v>
+                        <c:v>6</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -7356,7 +7377,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="11">
-                        <c:v>0</c:v>
+                        <c:v>9</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -7529,7 +7550,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="11">
-                        <c:v>0</c:v>
+                        <c:v>1</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -7702,7 +7723,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="11">
-                        <c:v>0</c:v>
+                        <c:v>1</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -12390,37 +12411,37 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O216" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40" tableBorderDxfId="39">
-  <autoFilter ref="A2:O216" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O216">
-    <sortCondition ref="D3:D107"/>
-    <sortCondition ref="A3:A107"/>
-    <sortCondition ref="F3:F107"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O221" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63" tableBorderDxfId="62">
+  <autoFilter ref="A2:O221" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O221">
+    <sortCondition ref="D3:D221"/>
+    <sortCondition ref="A3:A221"/>
+    <sortCondition ref="F3:F221"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="38">
+    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="61">
       <calculatedColumnFormula>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="37">
+    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="60">
       <calculatedColumnFormula>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="36">
+    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="59">
       <calculatedColumnFormula>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="28"/>
-    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="27"/>
-    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="26"/>
-    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="25">
+    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="58"/>
+    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="57"/>
+    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="56"/>
+    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="51"/>
+    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="50"/>
+    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="49"/>
+    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="48">
       <calculatedColumnFormula>AVERAGE('NIVEL 1'!G3:M3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="24">
+    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="47">
       <calculatedColumnFormula>IF(N3=" "," ",IF(N3&gt;=4.7,"CAMBIA A NIVEL 2"," "))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12429,36 +12450,36 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O188" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
-  <autoFilter ref="A2:O188" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O188">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O197" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A2:O197" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O197">
     <sortCondition ref="A3:A101"/>
     <sortCondition ref="F3:F101"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="62">
+    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="14">
       <calculatedColumnFormula>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="61">
+    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="13">
       <calculatedColumnFormula>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="60">
+    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="12">
       <calculatedColumnFormula>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="56"/>
-    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="55"/>
-    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="54"/>
-    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="53"/>
-    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="52"/>
-    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="51"/>
-    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="50"/>
-    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="49">
+    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="1">
       <calculatedColumnFormula>AVERAGE('NIVEL 2'!G3:M3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="48">
+    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="0">
       <calculatedColumnFormula>IF(N3=" "," ",IF(N3&gt;=4.7,"CAMBIA A NIVEL 3"," "))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12467,42 +12488,42 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U44" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
-  <autoFilter ref="A2:U44" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U45" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45" tableBorderDxfId="44">
+  <autoFilter ref="A2:U45" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U44">
     <sortCondition ref="A3"/>
     <sortCondition ref="F3"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="20">
+    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="43">
       <calculatedColumnFormula>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="19">
+    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="42">
       <calculatedColumnFormula>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="18">
+    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="41">
       <calculatedColumnFormula>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="32"/>
+    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="31"/>
+    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="30"/>
+    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="29"/>
+    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="28"/>
+    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="27"/>
+    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="26"/>
+    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="25"/>
+    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="24">
       <calculatedColumnFormula>AVERAGE('NIVEL 3'!G3:S3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="0">
+    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="23">
       <calculatedColumnFormula>IF(T3=" "," ",IF(T3&gt;=4.9,"CAMBIA A EQUIPO"," "))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12511,17 +12532,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D38" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D38" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="A2:D38" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D33">
     <sortCondition ref="A3"/>
     <sortCondition ref="D3"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="45"/>
-    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13241,11 +13262,11 @@
       </c>
       <c r="B13" s="17">
         <f>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C13" s="17">
         <f>COUNTIF('NIVEL 1'!$C:$C,REPORTE!A13)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D13" s="17">
         <f>COUNTIFS('NIVEL 1'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$O:$O,"CAMBIA A NIVEL 2")</f>
@@ -13253,15 +13274,15 @@
       </c>
       <c r="E13" s="17">
         <f>COUNTIF('NIVEL 2'!$C:$C,REPORTE!A13)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F13" s="17">
         <f>COUNTIFS('NIVEL 2'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$O:$O,"CAMBIA A NIVEL 3")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="17">
         <f>COUNTIF('NIVEL 3'!$C:$C,REPORTE!A13)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="17">
         <f>COUNTIFS('NIVEL 3'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$U:$U,"CAMBIA A EQUIPO")</f>
@@ -13290,7 +13311,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O216"/>
+  <dimension ref="A1:O221"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" customWidth="1"/>
@@ -22994,1477 +23015,1769 @@
       </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A188" s="42">
+      <c r="A188" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B188" s="43" t="str">
+      <c r="B188" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C188" s="43" t="str">
+      <c r="C188" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D188" s="44">
+      <c r="D188" s="3">
         <v>45929</v>
       </c>
-      <c r="E188" s="45" t="s">
+      <c r="E188" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="F188" s="46">
+      <c r="F188" s="1">
         <v>4731114</v>
       </c>
-      <c r="G188" s="47">
-        <v>5</v>
-      </c>
-      <c r="H188" s="47">
-        <v>5</v>
-      </c>
-      <c r="I188" s="47">
-        <v>3</v>
-      </c>
-      <c r="J188" s="47">
-        <v>3</v>
-      </c>
-      <c r="K188" s="47">
-        <v>3</v>
-      </c>
-      <c r="L188" s="47">
-        <v>3</v>
-      </c>
-      <c r="M188" s="47">
+      <c r="G188" s="1">
+        <v>5</v>
+      </c>
+      <c r="H188" s="1">
+        <v>5</v>
+      </c>
+      <c r="I188" s="1">
+        <v>3</v>
+      </c>
+      <c r="J188" s="1">
+        <v>3</v>
+      </c>
+      <c r="K188" s="1">
+        <v>3</v>
+      </c>
+      <c r="L188" s="1">
+        <v>3</v>
+      </c>
+      <c r="M188" s="1">
         <v>5</v>
       </c>
       <c r="N188" s="19">
         <f>AVERAGE('NIVEL 1'!G188:M188)</f>
         <v>3.8571428571428572</v>
       </c>
-      <c r="O188" s="48" t="str">
+      <c r="O188" s="18" t="str">
         <f>IF(N188=" "," ",IF(N188&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A189" s="42">
+      <c r="A189" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B189" s="43" t="str">
+      <c r="B189" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C189" s="43" t="str">
+      <c r="C189" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D189" s="44">
+      <c r="D189" s="3">
         <v>45929</v>
       </c>
-      <c r="E189" s="45" t="s">
+      <c r="E189" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="F189" s="46">
+      <c r="F189" s="1">
         <v>34968791</v>
       </c>
-      <c r="G189" s="47">
-        <v>5</v>
-      </c>
-      <c r="H189" s="47">
-        <v>5</v>
-      </c>
-      <c r="I189" s="47">
-        <v>5</v>
-      </c>
-      <c r="J189" s="47">
-        <v>3</v>
-      </c>
-      <c r="K189" s="47">
-        <v>3</v>
-      </c>
-      <c r="L189" s="47">
-        <v>2</v>
-      </c>
-      <c r="M189" s="47">
+      <c r="G189" s="1">
+        <v>5</v>
+      </c>
+      <c r="H189" s="1">
+        <v>5</v>
+      </c>
+      <c r="I189" s="1">
+        <v>5</v>
+      </c>
+      <c r="J189" s="1">
+        <v>3</v>
+      </c>
+      <c r="K189" s="1">
+        <v>3</v>
+      </c>
+      <c r="L189" s="1">
+        <v>2</v>
+      </c>
+      <c r="M189" s="1">
         <v>3</v>
       </c>
       <c r="N189" s="19">
         <f>AVERAGE('NIVEL 1'!G189:M189)</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O189" s="48" t="str">
+      <c r="O189" s="18" t="str">
         <f>IF(N189=" "," ",IF(N189&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A190" s="42">
+      <c r="A190" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B190" s="43" t="str">
+      <c r="B190" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C190" s="43" t="str">
+      <c r="C190" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D190" s="44">
+      <c r="D190" s="3">
         <v>45929</v>
       </c>
-      <c r="E190" s="45" t="s">
+      <c r="E190" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="F190" s="46">
+      <c r="F190" s="1">
         <v>80875509</v>
       </c>
-      <c r="G190" s="47">
-        <v>5</v>
-      </c>
-      <c r="H190" s="47">
-        <v>5</v>
-      </c>
-      <c r="I190" s="47">
-        <v>5</v>
-      </c>
-      <c r="J190" s="47">
-        <v>4</v>
-      </c>
-      <c r="K190" s="47">
-        <v>5</v>
-      </c>
-      <c r="L190" s="47">
-        <v>4</v>
-      </c>
-      <c r="M190" s="47">
+      <c r="G190" s="1">
+        <v>5</v>
+      </c>
+      <c r="H190" s="1">
+        <v>5</v>
+      </c>
+      <c r="I190" s="1">
+        <v>5</v>
+      </c>
+      <c r="J190" s="1">
+        <v>4</v>
+      </c>
+      <c r="K190" s="1">
+        <v>5</v>
+      </c>
+      <c r="L190" s="1">
+        <v>4</v>
+      </c>
+      <c r="M190" s="1">
         <v>5</v>
       </c>
       <c r="N190" s="19">
         <f>AVERAGE('NIVEL 1'!G190:M190)</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O190" s="48" t="str">
+      <c r="O190" s="18" t="str">
         <f>IF(N190=" "," ",IF(N190&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A191" s="42">
+      <c r="A191" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B191" s="43" t="str">
+      <c r="B191" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C191" s="43" t="str">
+      <c r="C191" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D191" s="44">
+      <c r="D191" s="3">
         <v>45929</v>
       </c>
-      <c r="E191" s="45" t="s">
+      <c r="E191" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="F191" s="46">
+      <c r="F191" s="1">
         <v>1013366237</v>
       </c>
-      <c r="G191" s="47">
-        <v>5</v>
-      </c>
-      <c r="H191" s="47">
-        <v>3</v>
-      </c>
-      <c r="I191" s="47">
-        <v>2</v>
-      </c>
-      <c r="J191" s="47">
+      <c r="G191" s="1">
+        <v>5</v>
+      </c>
+      <c r="H191" s="1">
+        <v>3</v>
+      </c>
+      <c r="I191" s="1">
+        <v>2</v>
+      </c>
+      <c r="J191" s="1">
         <v>1</v>
       </c>
-      <c r="K191" s="47">
+      <c r="K191" s="1">
         <v>1</v>
       </c>
-      <c r="L191" s="47">
+      <c r="L191" s="1">
         <v>1</v>
       </c>
-      <c r="M191" s="47">
+      <c r="M191" s="1">
         <v>4</v>
       </c>
       <c r="N191" s="19">
         <f>AVERAGE('NIVEL 1'!G191:M191)</f>
         <v>2.4285714285714284</v>
       </c>
-      <c r="O191" s="48" t="str">
+      <c r="O191" s="18" t="str">
         <f>IF(N191=" "," ",IF(N191&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A192" s="42">
+      <c r="A192" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B192" s="43" t="str">
+      <c r="B192" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C192" s="43" t="str">
+      <c r="C192" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D192" s="44">
+      <c r="D192" s="3">
         <v>45929</v>
       </c>
-      <c r="E192" s="45" t="s">
+      <c r="E192" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="F192" s="46">
+      <c r="F192" s="1">
         <v>1062528840</v>
       </c>
-      <c r="G192" s="47">
-        <v>5</v>
-      </c>
-      <c r="H192" s="47">
-        <v>5</v>
-      </c>
-      <c r="I192" s="47">
-        <v>4</v>
-      </c>
-      <c r="J192" s="47">
-        <v>4</v>
-      </c>
-      <c r="K192" s="47">
-        <v>4</v>
-      </c>
-      <c r="L192" s="47">
-        <v>4</v>
-      </c>
-      <c r="M192" s="47">
+      <c r="G192" s="1">
+        <v>5</v>
+      </c>
+      <c r="H192" s="1">
+        <v>5</v>
+      </c>
+      <c r="I192" s="1">
+        <v>4</v>
+      </c>
+      <c r="J192" s="1">
+        <v>4</v>
+      </c>
+      <c r="K192" s="1">
+        <v>4</v>
+      </c>
+      <c r="L192" s="1">
+        <v>4</v>
+      </c>
+      <c r="M192" s="1">
         <v>5</v>
       </c>
       <c r="N192" s="19">
         <f>AVERAGE('NIVEL 1'!G192:M192)</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O192" s="48" t="str">
+      <c r="O192" s="18" t="str">
         <f>IF(N192=" "," ",IF(N192&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="193" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A193" s="42">
+      <c r="A193" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B193" s="43" t="str">
+      <c r="B193" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C193" s="43" t="str">
+      <c r="C193" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D193" s="44">
+      <c r="D193" s="3">
         <v>45929</v>
       </c>
-      <c r="E193" s="45" t="s">
+      <c r="E193" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="F193" s="46">
+      <c r="F193" s="1">
         <v>1062529919</v>
       </c>
-      <c r="G193" s="47">
-        <v>5</v>
-      </c>
-      <c r="H193" s="47">
-        <v>5</v>
-      </c>
-      <c r="I193" s="47">
-        <v>4</v>
-      </c>
-      <c r="J193" s="47">
-        <v>4</v>
-      </c>
-      <c r="K193" s="47">
-        <v>3</v>
-      </c>
-      <c r="L193" s="47">
-        <v>3</v>
-      </c>
-      <c r="M193" s="47">
+      <c r="G193" s="1">
+        <v>5</v>
+      </c>
+      <c r="H193" s="1">
+        <v>5</v>
+      </c>
+      <c r="I193" s="1">
+        <v>4</v>
+      </c>
+      <c r="J193" s="1">
+        <v>4</v>
+      </c>
+      <c r="K193" s="1">
+        <v>3</v>
+      </c>
+      <c r="L193" s="1">
+        <v>3</v>
+      </c>
+      <c r="M193" s="1">
         <v>5</v>
       </c>
       <c r="N193" s="19">
         <f>AVERAGE('NIVEL 1'!G193:M193)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O193" s="48" t="str">
+      <c r="O193" s="18" t="str">
         <f>IF(N193=" "," ",IF(N193&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="194" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A194" s="42">
+      <c r="A194" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B194" s="43" t="str">
+      <c r="B194" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C194" s="43" t="str">
+      <c r="C194" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D194" s="44">
+      <c r="D194" s="3">
         <v>45929</v>
       </c>
-      <c r="E194" s="45" t="s">
+      <c r="E194" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="F194" s="46">
+      <c r="F194" s="1">
         <v>1062531558</v>
       </c>
-      <c r="G194" s="47">
-        <v>5</v>
-      </c>
-      <c r="H194" s="47">
-        <v>5</v>
-      </c>
-      <c r="I194" s="47">
-        <v>4</v>
-      </c>
-      <c r="J194" s="47">
-        <v>4</v>
-      </c>
-      <c r="K194" s="47">
-        <v>4</v>
-      </c>
-      <c r="L194" s="47">
-        <v>4</v>
-      </c>
-      <c r="M194" s="47">
+      <c r="G194" s="1">
+        <v>5</v>
+      </c>
+      <c r="H194" s="1">
+        <v>5</v>
+      </c>
+      <c r="I194" s="1">
+        <v>4</v>
+      </c>
+      <c r="J194" s="1">
+        <v>4</v>
+      </c>
+      <c r="K194" s="1">
+        <v>4</v>
+      </c>
+      <c r="L194" s="1">
+        <v>4</v>
+      </c>
+      <c r="M194" s="1">
         <v>5</v>
       </c>
       <c r="N194" s="19">
         <f>AVERAGE('NIVEL 1'!G194:M194)</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O194" s="48" t="str">
+      <c r="O194" s="18" t="str">
         <f>IF(N194=" "," ",IF(N194&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="195" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A195" s="42">
+      <c r="A195" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B195" s="43" t="str">
+      <c r="B195" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C195" s="43" t="str">
+      <c r="C195" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D195" s="44">
+      <c r="D195" s="3">
         <v>45929</v>
       </c>
-      <c r="E195" s="45" t="s">
+      <c r="E195" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="F195" s="46">
+      <c r="F195" s="1">
         <v>1062540642</v>
       </c>
-      <c r="G195" s="47">
-        <v>5</v>
-      </c>
-      <c r="H195" s="47">
-        <v>3</v>
-      </c>
-      <c r="I195" s="47">
-        <v>3</v>
-      </c>
-      <c r="J195" s="47">
+      <c r="G195" s="1">
+        <v>5</v>
+      </c>
+      <c r="H195" s="1">
+        <v>3</v>
+      </c>
+      <c r="I195" s="1">
+        <v>3</v>
+      </c>
+      <c r="J195" s="1">
         <v>1</v>
       </c>
-      <c r="K195" s="47">
-        <v>2</v>
-      </c>
-      <c r="L195" s="47">
+      <c r="K195" s="1">
+        <v>2</v>
+      </c>
+      <c r="L195" s="1">
         <v>1</v>
       </c>
-      <c r="M195" s="47">
+      <c r="M195" s="1">
         <v>5</v>
       </c>
       <c r="N195" s="19">
         <f>AVERAGE('NIVEL 1'!G195:M195)</f>
         <v>2.8571428571428572</v>
       </c>
-      <c r="O195" s="48" t="str">
+      <c r="O195" s="18" t="str">
         <f>IF(N195=" "," ",IF(N195&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="196" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A196" s="42">
+      <c r="A196" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B196" s="43" t="str">
+      <c r="B196" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C196" s="43" t="str">
+      <c r="C196" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D196" s="44">
+      <c r="D196" s="3">
         <v>45929</v>
       </c>
-      <c r="E196" s="45" t="s">
+      <c r="E196" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="F196" s="46">
+      <c r="F196" s="1">
         <v>1062544508</v>
       </c>
-      <c r="G196" s="47">
-        <v>5</v>
-      </c>
-      <c r="H196" s="47">
-        <v>5</v>
-      </c>
-      <c r="I196" s="47">
-        <v>4</v>
-      </c>
-      <c r="J196" s="47">
-        <v>4</v>
-      </c>
-      <c r="K196" s="47">
-        <v>4</v>
-      </c>
-      <c r="L196" s="47">
-        <v>3</v>
-      </c>
-      <c r="M196" s="47">
+      <c r="G196" s="1">
+        <v>5</v>
+      </c>
+      <c r="H196" s="1">
+        <v>5</v>
+      </c>
+      <c r="I196" s="1">
+        <v>4</v>
+      </c>
+      <c r="J196" s="1">
+        <v>4</v>
+      </c>
+      <c r="K196" s="1">
+        <v>4</v>
+      </c>
+      <c r="L196" s="1">
+        <v>3</v>
+      </c>
+      <c r="M196" s="1">
         <v>5</v>
       </c>
       <c r="N196" s="19">
         <f>AVERAGE('NIVEL 1'!G196:M196)</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O196" s="48" t="str">
+      <c r="O196" s="18" t="str">
         <f>IF(N196=" "," ",IF(N196&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="197" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A197" s="42">
+      <c r="A197" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B197" s="43" t="str">
+      <c r="B197" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C197" s="43" t="str">
+      <c r="C197" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D197" s="44">
+      <c r="D197" s="3">
         <v>45929</v>
       </c>
-      <c r="E197" s="45" t="s">
+      <c r="E197" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="F197" s="46">
+      <c r="F197" s="1">
         <v>1062604063</v>
       </c>
-      <c r="G197" s="47">
-        <v>5</v>
-      </c>
-      <c r="H197" s="47">
-        <v>5</v>
-      </c>
-      <c r="I197" s="47">
-        <v>4</v>
-      </c>
-      <c r="J197" s="47">
-        <v>4</v>
-      </c>
-      <c r="K197" s="47">
-        <v>4</v>
-      </c>
-      <c r="L197" s="47">
-        <v>4</v>
-      </c>
-      <c r="M197" s="47">
+      <c r="G197" s="1">
+        <v>5</v>
+      </c>
+      <c r="H197" s="1">
+        <v>5</v>
+      </c>
+      <c r="I197" s="1">
+        <v>4</v>
+      </c>
+      <c r="J197" s="1">
+        <v>4</v>
+      </c>
+      <c r="K197" s="1">
+        <v>4</v>
+      </c>
+      <c r="L197" s="1">
+        <v>4</v>
+      </c>
+      <c r="M197" s="1">
         <v>5</v>
       </c>
       <c r="N197" s="19">
         <f>AVERAGE('NIVEL 1'!G197:M197)</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O197" s="48" t="str">
+      <c r="O197" s="18" t="str">
         <f>IF(N197=" "," ",IF(N197&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="198" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A198" s="42">
+      <c r="A198" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B198" s="43" t="str">
+      <c r="B198" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C198" s="43" t="str">
+      <c r="C198" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D198" s="44">
+      <c r="D198" s="3">
         <v>45929</v>
       </c>
-      <c r="E198" s="45" t="s">
+      <c r="E198" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="F198" s="46">
+      <c r="F198" s="1">
         <v>1064188953</v>
       </c>
-      <c r="G198" s="47">
-        <v>5</v>
-      </c>
-      <c r="H198" s="47">
-        <v>5</v>
-      </c>
-      <c r="I198" s="47">
-        <v>5</v>
-      </c>
-      <c r="J198" s="47">
-        <v>5</v>
-      </c>
-      <c r="K198" s="47">
-        <v>5</v>
-      </c>
-      <c r="L198" s="47">
-        <v>5</v>
-      </c>
-      <c r="M198" s="47">
+      <c r="G198" s="1">
+        <v>5</v>
+      </c>
+      <c r="H198" s="1">
+        <v>5</v>
+      </c>
+      <c r="I198" s="1">
+        <v>5</v>
+      </c>
+      <c r="J198" s="1">
+        <v>5</v>
+      </c>
+      <c r="K198" s="1">
+        <v>5</v>
+      </c>
+      <c r="L198" s="1">
+        <v>5</v>
+      </c>
+      <c r="M198" s="1">
         <v>5</v>
       </c>
       <c r="N198" s="19">
         <f>AVERAGE('NIVEL 1'!G198:M198)</f>
         <v>5</v>
       </c>
-      <c r="O198" s="48" t="str">
+      <c r="O198" s="18" t="str">
         <f>IF(N198=" "," ",IF(N198&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="199" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A199" s="42">
+      <c r="A199" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B199" s="43" t="str">
+      <c r="B199" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C199" s="43" t="str">
+      <c r="C199" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D199" s="44">
+      <c r="D199" s="3">
         <v>45929</v>
       </c>
-      <c r="E199" s="45" t="s">
+      <c r="E199" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="F199" s="46">
+      <c r="F199" s="1">
         <v>1067859838</v>
       </c>
-      <c r="G199" s="47">
-        <v>5</v>
-      </c>
-      <c r="H199" s="47">
-        <v>4</v>
-      </c>
-      <c r="I199" s="47">
-        <v>4</v>
-      </c>
-      <c r="J199" s="47">
-        <v>3</v>
-      </c>
-      <c r="K199" s="47">
-        <v>3</v>
-      </c>
-      <c r="L199" s="47">
-        <v>2</v>
-      </c>
-      <c r="M199" s="47">
+      <c r="G199" s="1">
+        <v>5</v>
+      </c>
+      <c r="H199" s="1">
+        <v>4</v>
+      </c>
+      <c r="I199" s="1">
+        <v>4</v>
+      </c>
+      <c r="J199" s="1">
+        <v>3</v>
+      </c>
+      <c r="K199" s="1">
+        <v>3</v>
+      </c>
+      <c r="L199" s="1">
+        <v>2</v>
+      </c>
+      <c r="M199" s="1">
         <v>2</v>
       </c>
       <c r="N199" s="19">
         <f>AVERAGE('NIVEL 1'!G199:M199)</f>
         <v>3.2857142857142856</v>
       </c>
-      <c r="O199" s="48" t="str">
+      <c r="O199" s="18" t="str">
         <f>IF(N199=" "," ",IF(N199&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="200" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A200" s="42">
+      <c r="A200" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B200" s="43" t="str">
+      <c r="B200" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C200" s="43" t="str">
+      <c r="C200" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D200" s="44">
+      <c r="D200" s="3">
         <v>45929</v>
       </c>
-      <c r="E200" s="45" t="s">
+      <c r="E200" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="F200" s="46">
+      <c r="F200" s="1">
         <v>1067898439</v>
       </c>
-      <c r="G200" s="47">
-        <v>5</v>
-      </c>
-      <c r="H200" s="47">
-        <v>5</v>
-      </c>
-      <c r="I200" s="47">
-        <v>5</v>
-      </c>
-      <c r="J200" s="47">
-        <v>4</v>
-      </c>
-      <c r="K200" s="47">
-        <v>5</v>
-      </c>
-      <c r="L200" s="47">
-        <v>4</v>
-      </c>
-      <c r="M200" s="47">
+      <c r="G200" s="1">
+        <v>5</v>
+      </c>
+      <c r="H200" s="1">
+        <v>5</v>
+      </c>
+      <c r="I200" s="1">
+        <v>5</v>
+      </c>
+      <c r="J200" s="1">
+        <v>4</v>
+      </c>
+      <c r="K200" s="1">
+        <v>5</v>
+      </c>
+      <c r="L200" s="1">
+        <v>4</v>
+      </c>
+      <c r="M200" s="1">
         <v>5</v>
       </c>
       <c r="N200" s="19">
         <f>AVERAGE('NIVEL 1'!G200:M200)</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O200" s="48" t="str">
+      <c r="O200" s="18" t="str">
         <f>IF(N200=" "," ",IF(N200&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="201" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A201" s="42">
+      <c r="A201" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B201" s="43" t="str">
+      <c r="B201" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C201" s="43" t="str">
+      <c r="C201" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D201" s="44">
+      <c r="D201" s="3">
         <v>45929</v>
       </c>
-      <c r="E201" s="45" t="s">
+      <c r="E201" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="F201" s="46">
+      <c r="F201" s="1">
         <v>1067936015</v>
       </c>
-      <c r="G201" s="47">
-        <v>5</v>
-      </c>
-      <c r="H201" s="47">
-        <v>5</v>
-      </c>
-      <c r="I201" s="47">
-        <v>5</v>
-      </c>
-      <c r="J201" s="47">
-        <v>4</v>
-      </c>
-      <c r="K201" s="47">
-        <v>5</v>
-      </c>
-      <c r="L201" s="47">
-        <v>4</v>
-      </c>
-      <c r="M201" s="47">
+      <c r="G201" s="1">
+        <v>5</v>
+      </c>
+      <c r="H201" s="1">
+        <v>5</v>
+      </c>
+      <c r="I201" s="1">
+        <v>5</v>
+      </c>
+      <c r="J201" s="1">
+        <v>4</v>
+      </c>
+      <c r="K201" s="1">
+        <v>5</v>
+      </c>
+      <c r="L201" s="1">
+        <v>4</v>
+      </c>
+      <c r="M201" s="1">
         <v>5</v>
       </c>
       <c r="N201" s="19">
         <f>AVERAGE('NIVEL 1'!G201:M201)</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O201" s="48" t="str">
+      <c r="O201" s="18" t="str">
         <f>IF(N201=" "," ",IF(N201&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A202" s="42">
+      <c r="A202" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B202" s="43" t="str">
+      <c r="B202" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C202" s="43" t="str">
+      <c r="C202" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D202" s="44">
+      <c r="D202" s="3">
         <v>45929</v>
       </c>
-      <c r="E202" s="45" t="s">
+      <c r="E202" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="F202" s="46">
+      <c r="F202" s="1">
         <v>1067947937</v>
       </c>
-      <c r="G202" s="47">
-        <v>5</v>
-      </c>
-      <c r="H202" s="47">
-        <v>5</v>
-      </c>
-      <c r="I202" s="47">
-        <v>3</v>
-      </c>
-      <c r="J202" s="47">
-        <v>2</v>
-      </c>
-      <c r="K202" s="47">
-        <v>3</v>
-      </c>
-      <c r="L202" s="47">
-        <v>2</v>
-      </c>
-      <c r="M202" s="47">
+      <c r="G202" s="1">
+        <v>5</v>
+      </c>
+      <c r="H202" s="1">
+        <v>5</v>
+      </c>
+      <c r="I202" s="1">
+        <v>3</v>
+      </c>
+      <c r="J202" s="1">
+        <v>2</v>
+      </c>
+      <c r="K202" s="1">
+        <v>3</v>
+      </c>
+      <c r="L202" s="1">
+        <v>2</v>
+      </c>
+      <c r="M202" s="1">
         <v>5</v>
       </c>
       <c r="N202" s="19">
         <f>AVERAGE('NIVEL 1'!G202:M202)</f>
         <v>3.5714285714285716</v>
       </c>
-      <c r="O202" s="48" t="str">
+      <c r="O202" s="18" t="str">
         <f>IF(N202=" "," ",IF(N202&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="203" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A203" s="42">
+      <c r="A203" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B203" s="43" t="str">
+      <c r="B203" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C203" s="43" t="str">
+      <c r="C203" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D203" s="44">
+      <c r="D203" s="3">
         <v>45929</v>
       </c>
-      <c r="E203" s="45" t="s">
+      <c r="E203" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="F203" s="46">
+      <c r="F203" s="1">
         <v>1068434281</v>
       </c>
-      <c r="G203" s="47">
-        <v>5</v>
-      </c>
-      <c r="H203" s="47">
-        <v>5</v>
-      </c>
-      <c r="I203" s="47">
-        <v>4</v>
-      </c>
-      <c r="J203" s="47">
-        <v>3</v>
-      </c>
-      <c r="K203" s="47">
-        <v>4</v>
-      </c>
-      <c r="L203" s="47">
-        <v>3</v>
-      </c>
-      <c r="M203" s="47">
+      <c r="G203" s="1">
+        <v>5</v>
+      </c>
+      <c r="H203" s="1">
+        <v>5</v>
+      </c>
+      <c r="I203" s="1">
+        <v>4</v>
+      </c>
+      <c r="J203" s="1">
+        <v>3</v>
+      </c>
+      <c r="K203" s="1">
+        <v>4</v>
+      </c>
+      <c r="L203" s="1">
+        <v>3</v>
+      </c>
+      <c r="M203" s="1">
         <v>5</v>
       </c>
       <c r="N203" s="19">
         <f>AVERAGE('NIVEL 1'!G203:M203)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O203" s="48" t="str">
+      <c r="O203" s="18" t="str">
         <f>IF(N203=" "," ",IF(N203&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="204" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A204" s="42">
+      <c r="A204" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B204" s="43" t="str">
+      <c r="B204" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C204" s="43" t="str">
+      <c r="C204" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D204" s="44">
+      <c r="D204" s="3">
         <v>45929</v>
       </c>
-      <c r="E204" s="45" t="s">
+      <c r="E204" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="F204" s="46">
+      <c r="F204" s="1">
         <v>1068444080</v>
       </c>
-      <c r="G204" s="47">
-        <v>5</v>
-      </c>
-      <c r="H204" s="47">
-        <v>2</v>
-      </c>
-      <c r="I204" s="47">
+      <c r="G204" s="1">
+        <v>5</v>
+      </c>
+      <c r="H204" s="1">
+        <v>2</v>
+      </c>
+      <c r="I204" s="1">
         <v>1</v>
       </c>
-      <c r="J204" s="47">
+      <c r="J204" s="1">
         <v>1</v>
       </c>
-      <c r="K204" s="47">
+      <c r="K204" s="1">
         <v>1</v>
       </c>
-      <c r="L204" s="47">
+      <c r="L204" s="1">
         <v>1</v>
       </c>
-      <c r="M204" s="47">
+      <c r="M204" s="1">
         <v>1</v>
       </c>
       <c r="N204" s="19">
         <f>AVERAGE('NIVEL 1'!G204:M204)</f>
         <v>1.7142857142857142</v>
       </c>
-      <c r="O204" s="48" t="str">
+      <c r="O204" s="18" t="str">
         <f>IF(N204=" "," ",IF(N204&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="205" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A205" s="42">
+      <c r="A205" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B205" s="43" t="str">
+      <c r="B205" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C205" s="43" t="str">
+      <c r="C205" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D205" s="44">
+      <c r="D205" s="3">
         <v>45929</v>
       </c>
-      <c r="E205" s="45" t="s">
+      <c r="E205" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="F205" s="46">
+      <c r="F205" s="1">
         <v>1068444523</v>
       </c>
-      <c r="G205" s="47">
-        <v>5</v>
-      </c>
-      <c r="H205" s="47">
-        <v>5</v>
-      </c>
-      <c r="I205" s="47">
-        <v>3</v>
-      </c>
-      <c r="J205" s="47">
-        <v>2</v>
-      </c>
-      <c r="K205" s="47">
-        <v>3</v>
-      </c>
-      <c r="L205" s="47">
+      <c r="G205" s="1">
+        <v>5</v>
+      </c>
+      <c r="H205" s="1">
+        <v>5</v>
+      </c>
+      <c r="I205" s="1">
+        <v>3</v>
+      </c>
+      <c r="J205" s="1">
+        <v>2</v>
+      </c>
+      <c r="K205" s="1">
+        <v>3</v>
+      </c>
+      <c r="L205" s="1">
         <v>1</v>
       </c>
-      <c r="M205" s="47">
+      <c r="M205" s="1">
         <v>5</v>
       </c>
       <c r="N205" s="19">
         <f>AVERAGE('NIVEL 1'!G205:M205)</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O205" s="48" t="str">
+      <c r="O205" s="18" t="str">
         <f>IF(N205=" "," ",IF(N205&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="206" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A206" s="42">
+      <c r="A206" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B206" s="43" t="str">
+      <c r="B206" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C206" s="43" t="str">
+      <c r="C206" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D206" s="44">
+      <c r="D206" s="3">
         <v>45929</v>
       </c>
-      <c r="E206" s="45" t="s">
+      <c r="E206" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="F206" s="46">
+      <c r="F206" s="1">
         <v>1074002401</v>
       </c>
-      <c r="G206" s="47">
-        <v>5</v>
-      </c>
-      <c r="H206" s="47">
-        <v>5</v>
-      </c>
-      <c r="I206" s="47">
-        <v>4</v>
-      </c>
-      <c r="J206" s="47">
-        <v>4</v>
-      </c>
-      <c r="K206" s="47">
-        <v>4</v>
-      </c>
-      <c r="L206" s="47">
-        <v>4</v>
-      </c>
-      <c r="M206" s="47">
+      <c r="G206" s="1">
+        <v>5</v>
+      </c>
+      <c r="H206" s="1">
+        <v>5</v>
+      </c>
+      <c r="I206" s="1">
+        <v>4</v>
+      </c>
+      <c r="J206" s="1">
+        <v>4</v>
+      </c>
+      <c r="K206" s="1">
+        <v>4</v>
+      </c>
+      <c r="L206" s="1">
+        <v>4</v>
+      </c>
+      <c r="M206" s="1">
         <v>5</v>
       </c>
       <c r="N206" s="19">
         <f>AVERAGE('NIVEL 1'!G206:M206)</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O206" s="48" t="str">
+      <c r="O206" s="18" t="str">
         <f>IF(N206=" "," ",IF(N206&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="207" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A207" s="42">
+      <c r="A207" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B207" s="43" t="str">
+      <c r="B207" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C207" s="43" t="str">
+      <c r="C207" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D207" s="44">
+      <c r="D207" s="3">
         <v>45929</v>
       </c>
-      <c r="E207" s="45" t="s">
+      <c r="E207" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F207" s="46">
+      <c r="F207" s="1">
         <v>1104267144</v>
       </c>
-      <c r="G207" s="47">
-        <v>5</v>
-      </c>
-      <c r="H207" s="47">
-        <v>5</v>
-      </c>
-      <c r="I207" s="47">
-        <v>4</v>
-      </c>
-      <c r="J207" s="47">
-        <v>4</v>
-      </c>
-      <c r="K207" s="47">
-        <v>4</v>
-      </c>
-      <c r="L207" s="47">
-        <v>4</v>
-      </c>
-      <c r="M207" s="47">
+      <c r="G207" s="1">
+        <v>5</v>
+      </c>
+      <c r="H207" s="1">
+        <v>5</v>
+      </c>
+      <c r="I207" s="1">
+        <v>4</v>
+      </c>
+      <c r="J207" s="1">
+        <v>4</v>
+      </c>
+      <c r="K207" s="1">
+        <v>4</v>
+      </c>
+      <c r="L207" s="1">
+        <v>4</v>
+      </c>
+      <c r="M207" s="1">
         <v>5</v>
       </c>
       <c r="N207" s="19">
         <f>AVERAGE('NIVEL 1'!G207:M207)</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O207" s="48" t="str">
+      <c r="O207" s="18" t="str">
         <f>IF(N207=" "," ",IF(N207&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="208" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A208" s="42">
+      <c r="A208" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B208" s="43" t="str">
+      <c r="B208" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C208" s="43" t="str">
+      <c r="C208" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D208" s="44">
+      <c r="D208" s="3">
         <v>45929</v>
       </c>
-      <c r="E208" s="45" t="s">
+      <c r="E208" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="F208" s="46">
+      <c r="F208" s="1">
         <v>1126253349</v>
       </c>
-      <c r="G208" s="47">
-        <v>5</v>
-      </c>
-      <c r="H208" s="47">
-        <v>3</v>
-      </c>
-      <c r="I208" s="47">
-        <v>3</v>
-      </c>
-      <c r="J208" s="47">
-        <v>2</v>
-      </c>
-      <c r="K208" s="47">
-        <v>2</v>
-      </c>
-      <c r="L208" s="47">
+      <c r="G208" s="1">
+        <v>5</v>
+      </c>
+      <c r="H208" s="1">
+        <v>3</v>
+      </c>
+      <c r="I208" s="1">
+        <v>3</v>
+      </c>
+      <c r="J208" s="1">
+        <v>2</v>
+      </c>
+      <c r="K208" s="1">
+        <v>2</v>
+      </c>
+      <c r="L208" s="1">
         <v>1</v>
       </c>
-      <c r="M208" s="47">
+      <c r="M208" s="1">
         <v>1</v>
       </c>
       <c r="N208" s="19">
         <f>AVERAGE('NIVEL 1'!G208:M208)</f>
         <v>2.4285714285714284</v>
       </c>
-      <c r="O208" s="48" t="str">
+      <c r="O208" s="18" t="str">
         <f>IF(N208=" "," ",IF(N208&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="209" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A209" s="42">
+      <c r="A209" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B209" s="43" t="str">
+      <c r="B209" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C209" s="43" t="str">
+      <c r="C209" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D209" s="44">
+      <c r="D209" s="3">
         <v>45929</v>
       </c>
-      <c r="E209" s="45" t="s">
+      <c r="E209" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="F209" s="46">
+      <c r="F209" s="1">
         <v>1137975547</v>
       </c>
-      <c r="G209" s="47">
-        <v>5</v>
-      </c>
-      <c r="H209" s="47">
-        <v>5</v>
-      </c>
-      <c r="I209" s="47">
-        <v>4</v>
-      </c>
-      <c r="J209" s="47">
-        <v>4</v>
-      </c>
-      <c r="K209" s="47">
-        <v>4</v>
-      </c>
-      <c r="L209" s="47">
-        <v>4</v>
-      </c>
-      <c r="M209" s="47">
+      <c r="G209" s="1">
+        <v>5</v>
+      </c>
+      <c r="H209" s="1">
+        <v>5</v>
+      </c>
+      <c r="I209" s="1">
+        <v>4</v>
+      </c>
+      <c r="J209" s="1">
+        <v>4</v>
+      </c>
+      <c r="K209" s="1">
+        <v>4</v>
+      </c>
+      <c r="L209" s="1">
+        <v>4</v>
+      </c>
+      <c r="M209" s="1">
         <v>5</v>
       </c>
       <c r="N209" s="19">
         <f>AVERAGE('NIVEL 1'!G209:M209)</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O209" s="48" t="str">
+      <c r="O209" s="18" t="str">
         <f>IF(N209=" "," ",IF(N209&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="210" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A210" s="42">
+      <c r="A210" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B210" s="43" t="str">
+      <c r="B210" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C210" s="43" t="str">
+      <c r="C210" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D210" s="44">
+      <c r="D210" s="3">
         <v>45929</v>
       </c>
-      <c r="E210" s="45" t="s">
+      <c r="E210" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="F210" s="46">
+      <c r="F210" s="1">
         <v>1138030747</v>
       </c>
-      <c r="G210" s="47">
-        <v>5</v>
-      </c>
-      <c r="H210" s="47">
-        <v>5</v>
-      </c>
-      <c r="I210" s="47">
-        <v>4</v>
-      </c>
-      <c r="J210" s="47">
-        <v>4</v>
-      </c>
-      <c r="K210" s="47">
-        <v>4</v>
-      </c>
-      <c r="L210" s="47">
-        <v>4</v>
-      </c>
-      <c r="M210" s="47">
+      <c r="G210" s="1">
+        <v>5</v>
+      </c>
+      <c r="H210" s="1">
+        <v>5</v>
+      </c>
+      <c r="I210" s="1">
+        <v>4</v>
+      </c>
+      <c r="J210" s="1">
+        <v>4</v>
+      </c>
+      <c r="K210" s="1">
+        <v>4</v>
+      </c>
+      <c r="L210" s="1">
+        <v>4</v>
+      </c>
+      <c r="M210" s="1">
         <v>5</v>
       </c>
       <c r="N210" s="19">
         <f>AVERAGE('NIVEL 1'!G210:M210)</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O210" s="48" t="str">
+      <c r="O210" s="18" t="str">
         <f>IF(N210=" "," ",IF(N210&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="211" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A211" s="42">
+      <c r="A211" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B211" s="43" t="str">
+      <c r="B211" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C211" s="43" t="str">
+      <c r="C211" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D211" s="44">
+      <c r="D211" s="3">
         <v>45929</v>
       </c>
-      <c r="E211" s="45" t="s">
+      <c r="E211" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="F211" s="46">
+      <c r="F211" s="1">
         <v>1138031947</v>
       </c>
-      <c r="G211" s="47">
-        <v>5</v>
-      </c>
-      <c r="H211" s="47">
-        <v>5</v>
-      </c>
-      <c r="I211" s="47">
-        <v>4</v>
-      </c>
-      <c r="J211" s="47">
-        <v>2</v>
-      </c>
-      <c r="K211" s="47">
-        <v>3</v>
-      </c>
-      <c r="L211" s="47">
-        <v>2</v>
-      </c>
-      <c r="M211" s="47">
+      <c r="G211" s="1">
+        <v>5</v>
+      </c>
+      <c r="H211" s="1">
+        <v>5</v>
+      </c>
+      <c r="I211" s="1">
+        <v>4</v>
+      </c>
+      <c r="J211" s="1">
+        <v>2</v>
+      </c>
+      <c r="K211" s="1">
+        <v>3</v>
+      </c>
+      <c r="L211" s="1">
+        <v>2</v>
+      </c>
+      <c r="M211" s="1">
         <v>5</v>
       </c>
       <c r="N211" s="19">
         <f>AVERAGE('NIVEL 1'!G211:M211)</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O211" s="48" t="str">
+      <c r="O211" s="18" t="str">
         <f>IF(N211=" "," ",IF(N211&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="212" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A212" s="42">
+      <c r="A212" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B212" s="43" t="str">
+      <c r="B212" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C212" s="43" t="str">
+      <c r="C212" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D212" s="44">
+      <c r="D212" s="3">
         <v>45929</v>
       </c>
-      <c r="E212" s="45" t="s">
+      <c r="E212" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F212" s="46">
+      <c r="F212" s="1">
         <v>1138032549</v>
       </c>
-      <c r="G212" s="47">
-        <v>5</v>
-      </c>
-      <c r="H212" s="47">
-        <v>5</v>
-      </c>
-      <c r="I212" s="47">
-        <v>5</v>
-      </c>
-      <c r="J212" s="47">
-        <v>4</v>
-      </c>
-      <c r="K212" s="47">
-        <v>5</v>
-      </c>
-      <c r="L212" s="47">
-        <v>4</v>
-      </c>
-      <c r="M212" s="47">
+      <c r="G212" s="1">
+        <v>5</v>
+      </c>
+      <c r="H212" s="1">
+        <v>5</v>
+      </c>
+      <c r="I212" s="1">
+        <v>5</v>
+      </c>
+      <c r="J212" s="1">
+        <v>4</v>
+      </c>
+      <c r="K212" s="1">
+        <v>5</v>
+      </c>
+      <c r="L212" s="1">
+        <v>4</v>
+      </c>
+      <c r="M212" s="1">
         <v>5</v>
       </c>
       <c r="N212" s="19">
         <f>AVERAGE('NIVEL 1'!G212:M212)</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O212" s="48" t="str">
+      <c r="O212" s="18" t="str">
         <f>IF(N212=" "," ",IF(N212&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A213" s="42">
+      <c r="A213" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B213" s="43" t="str">
+      <c r="B213" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C213" s="43" t="str">
+      <c r="C213" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D213" s="44">
+      <c r="D213" s="3">
         <v>45929</v>
       </c>
-      <c r="E213" s="45" t="s">
+      <c r="E213" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="F213" s="46">
+      <c r="F213" s="1">
         <v>1138032702</v>
       </c>
-      <c r="G213" s="47">
-        <v>5</v>
-      </c>
-      <c r="H213" s="47">
-        <v>5</v>
-      </c>
-      <c r="I213" s="47">
-        <v>3</v>
-      </c>
-      <c r="J213" s="47">
-        <v>2</v>
-      </c>
-      <c r="K213" s="47">
-        <v>2</v>
-      </c>
-      <c r="L213" s="47">
-        <v>2</v>
-      </c>
-      <c r="M213" s="47">
+      <c r="G213" s="1">
+        <v>5</v>
+      </c>
+      <c r="H213" s="1">
+        <v>5</v>
+      </c>
+      <c r="I213" s="1">
+        <v>3</v>
+      </c>
+      <c r="J213" s="1">
+        <v>2</v>
+      </c>
+      <c r="K213" s="1">
+        <v>2</v>
+      </c>
+      <c r="L213" s="1">
+        <v>2</v>
+      </c>
+      <c r="M213" s="1">
         <v>5</v>
       </c>
       <c r="N213" s="19">
         <f>AVERAGE('NIVEL 1'!G213:M213)</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O213" s="48" t="str">
+      <c r="O213" s="18" t="str">
         <f>IF(N213=" "," ",IF(N213&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="214" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A214" s="42">
+      <c r="A214" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B214" s="43" t="str">
+      <c r="B214" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C214" s="43" t="str">
+      <c r="C214" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D214" s="44">
+      <c r="D214" s="3">
         <v>45929</v>
       </c>
-      <c r="E214" s="45" t="s">
+      <c r="E214" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="F214" s="46">
+      <c r="F214" s="1">
         <v>1243758694</v>
       </c>
-      <c r="G214" s="47">
-        <v>5</v>
-      </c>
-      <c r="H214" s="47">
-        <v>3</v>
-      </c>
-      <c r="I214" s="47">
-        <v>2</v>
-      </c>
-      <c r="J214" s="47">
+      <c r="G214" s="1">
+        <v>5</v>
+      </c>
+      <c r="H214" s="1">
+        <v>3</v>
+      </c>
+      <c r="I214" s="1">
+        <v>2</v>
+      </c>
+      <c r="J214" s="1">
         <v>1</v>
       </c>
-      <c r="K214" s="47">
-        <v>2</v>
-      </c>
-      <c r="L214" s="47">
+      <c r="K214" s="1">
+        <v>2</v>
+      </c>
+      <c r="L214" s="1">
         <v>1</v>
       </c>
-      <c r="M214" s="47">
+      <c r="M214" s="1">
         <v>5</v>
       </c>
       <c r="N214" s="19">
         <f>AVERAGE('NIVEL 1'!G214:M214)</f>
         <v>2.7142857142857144</v>
       </c>
-      <c r="O214" s="48" t="str">
+      <c r="O214" s="18" t="str">
         <f>IF(N214=" "," ",IF(N214&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="215" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A215" s="42">
+      <c r="A215" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B215" s="43" t="str">
+      <c r="B215" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C215" s="43" t="str">
+      <c r="C215" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D215" s="44">
+      <c r="D215" s="3">
         <v>45929</v>
       </c>
-      <c r="E215" s="45" t="s">
+      <c r="E215" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="F215" s="49" t="s">
+      <c r="F215" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="G215" s="47">
-        <v>5</v>
-      </c>
-      <c r="H215" s="47">
-        <v>5</v>
-      </c>
-      <c r="I215" s="47">
-        <v>4</v>
-      </c>
-      <c r="J215" s="47">
-        <v>3</v>
-      </c>
-      <c r="K215" s="47">
-        <v>4</v>
-      </c>
-      <c r="L215" s="47">
-        <v>3</v>
-      </c>
-      <c r="M215" s="47">
+      <c r="G215" s="1">
+        <v>5</v>
+      </c>
+      <c r="H215" s="1">
+        <v>5</v>
+      </c>
+      <c r="I215" s="1">
+        <v>4</v>
+      </c>
+      <c r="J215" s="1">
+        <v>3</v>
+      </c>
+      <c r="K215" s="1">
+        <v>4</v>
+      </c>
+      <c r="L215" s="1">
+        <v>3</v>
+      </c>
+      <c r="M215" s="1">
         <v>5</v>
       </c>
       <c r="N215" s="19">
         <f>AVERAGE('NIVEL 1'!G215:M215)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O215" s="48" t="str">
+      <c r="O215" s="18" t="str">
         <f>IF(N215=" "," ",IF(N215&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="216" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A216" s="42"/>
-      <c r="B216" s="43"/>
-      <c r="C216" s="43"/>
-      <c r="D216" s="44"/>
-      <c r="E216" s="45"/>
-      <c r="F216" s="46"/>
-      <c r="G216" s="47"/>
-      <c r="H216" s="47"/>
-      <c r="I216" s="47"/>
-      <c r="J216" s="47"/>
-      <c r="K216" s="47"/>
-      <c r="L216" s="47"/>
-      <c r="M216" s="47"/>
-      <c r="N216" s="19"/>
-      <c r="O216" s="48"/>
+      <c r="A216" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B216" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C216" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D216" s="3">
+        <v>46012</v>
+      </c>
+      <c r="E216" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="F216" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="G216" s="1">
+        <v>5</v>
+      </c>
+      <c r="H216" s="1">
+        <v>5</v>
+      </c>
+      <c r="I216" s="1">
+        <v>5</v>
+      </c>
+      <c r="J216" s="1">
+        <v>4</v>
+      </c>
+      <c r="K216" s="1">
+        <v>3</v>
+      </c>
+      <c r="L216" s="1">
+        <v>4</v>
+      </c>
+      <c r="M216" s="1">
+        <v>5</v>
+      </c>
+      <c r="N216" s="19">
+        <f>AVERAGE('NIVEL 1'!G216:M216)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O216" s="18"/>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A217" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B217" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C217" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D217" s="44">
+        <v>46012</v>
+      </c>
+      <c r="E217" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="F217" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="G217" s="47">
+        <v>5</v>
+      </c>
+      <c r="H217" s="47">
+        <v>5</v>
+      </c>
+      <c r="I217" s="47">
+        <v>5</v>
+      </c>
+      <c r="J217" s="47">
+        <v>4</v>
+      </c>
+      <c r="K217" s="47">
+        <v>4</v>
+      </c>
+      <c r="L217" s="47">
+        <v>4</v>
+      </c>
+      <c r="M217" s="47">
+        <v>5</v>
+      </c>
+      <c r="N217" s="19">
+        <f>AVERAGE('NIVEL 1'!G217:M217)</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O217" s="48" t="str">
+        <f>IF(N217=" "," ",IF(N217&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A218" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B218" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C218" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D218" s="44">
+        <v>46013</v>
+      </c>
+      <c r="E218" s="45" t="s">
+        <v>236</v>
+      </c>
+      <c r="F218" s="46">
+        <v>1038649739</v>
+      </c>
+      <c r="G218" s="47">
+        <v>5</v>
+      </c>
+      <c r="H218" s="47">
+        <v>1</v>
+      </c>
+      <c r="I218" s="47">
+        <v>1</v>
+      </c>
+      <c r="J218" s="47">
+        <v>1</v>
+      </c>
+      <c r="K218" s="47">
+        <v>1</v>
+      </c>
+      <c r="L218" s="47">
+        <v>1</v>
+      </c>
+      <c r="M218" s="47">
+        <v>1</v>
+      </c>
+      <c r="N218" s="19">
+        <f>AVERAGE('NIVEL 1'!G218:M218)</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O218" s="48" t="str">
+        <f>IF(N218=" "," ",IF(N218&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A219" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B219" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C219" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D219" s="44">
+        <v>46013</v>
+      </c>
+      <c r="E219" s="45" t="s">
+        <v>233</v>
+      </c>
+      <c r="F219" s="46">
+        <v>1062989283</v>
+      </c>
+      <c r="G219" s="47">
+        <v>5</v>
+      </c>
+      <c r="H219" s="47">
+        <v>1</v>
+      </c>
+      <c r="I219" s="47">
+        <v>1</v>
+      </c>
+      <c r="J219" s="47">
+        <v>1</v>
+      </c>
+      <c r="K219" s="47">
+        <v>1</v>
+      </c>
+      <c r="L219" s="47">
+        <v>1</v>
+      </c>
+      <c r="M219" s="47">
+        <v>1</v>
+      </c>
+      <c r="N219" s="19">
+        <f>AVERAGE('NIVEL 1'!G219:M219)</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O219" s="48" t="str">
+        <f>IF(N219=" "," ",IF(N219&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A220" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B220" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C220" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D220" s="44">
+        <v>46013</v>
+      </c>
+      <c r="E220" s="45" t="s">
+        <v>235</v>
+      </c>
+      <c r="F220" s="46">
+        <v>1062990441</v>
+      </c>
+      <c r="G220" s="47">
+        <v>3</v>
+      </c>
+      <c r="H220" s="47">
+        <v>1</v>
+      </c>
+      <c r="I220" s="47">
+        <v>1</v>
+      </c>
+      <c r="J220" s="47">
+        <v>1</v>
+      </c>
+      <c r="K220" s="47">
+        <v>1</v>
+      </c>
+      <c r="L220" s="47">
+        <v>1</v>
+      </c>
+      <c r="M220" s="47">
+        <v>1</v>
+      </c>
+      <c r="N220" s="19">
+        <f>AVERAGE('NIVEL 1'!G220:M220)</f>
+        <v>1.2857142857142858</v>
+      </c>
+      <c r="O220" s="48" t="str">
+        <f>IF(N220=" "," ",IF(N220&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A221" s="42">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B221" s="43" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C221" s="43" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D221" s="44">
+        <v>46013</v>
+      </c>
+      <c r="E221" s="45" t="s">
+        <v>234</v>
+      </c>
+      <c r="F221" s="46">
+        <v>1068444953</v>
+      </c>
+      <c r="G221" s="47">
+        <v>5</v>
+      </c>
+      <c r="H221" s="47">
+        <v>1</v>
+      </c>
+      <c r="I221" s="47">
+        <v>1</v>
+      </c>
+      <c r="J221" s="47">
+        <v>1</v>
+      </c>
+      <c r="K221" s="47">
+        <v>1</v>
+      </c>
+      <c r="L221" s="47">
+        <v>1</v>
+      </c>
+      <c r="M221" s="47">
+        <v>1</v>
+      </c>
+      <c r="N221" s="19">
+        <f>AVERAGE('NIVEL 1'!G221:M221)</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O221" s="48" t="str">
+        <f>IF(N221=" "," ",IF(N221&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -24490,7 +24803,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O188"/>
+  <dimension ref="A1:O197"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -32586,1666 +32899,2134 @@
       </c>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A157" s="47">
+      <c r="A157" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B157" s="50" t="str">
+      <c r="B157" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C157" s="50" t="str">
+      <c r="C157" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D157" s="44">
+      <c r="D157" s="3">
         <v>45929</v>
       </c>
-      <c r="E157" s="45" t="s">
+      <c r="E157" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="F157" s="47">
+      <c r="F157" s="1">
         <v>1018813</v>
       </c>
-      <c r="G157" s="47">
-        <v>5</v>
-      </c>
-      <c r="H157" s="47">
-        <v>4</v>
-      </c>
-      <c r="I157" s="47">
-        <v>3</v>
-      </c>
-      <c r="J157" s="47">
-        <v>3</v>
-      </c>
-      <c r="K157" s="47">
-        <v>4</v>
-      </c>
-      <c r="L157" s="47">
-        <v>5</v>
-      </c>
-      <c r="M157" s="47">
+      <c r="G157" s="1">
+        <v>5</v>
+      </c>
+      <c r="H157" s="1">
+        <v>4</v>
+      </c>
+      <c r="I157" s="1">
+        <v>3</v>
+      </c>
+      <c r="J157" s="1">
+        <v>3</v>
+      </c>
+      <c r="K157" s="1">
+        <v>4</v>
+      </c>
+      <c r="L157" s="1">
+        <v>5</v>
+      </c>
+      <c r="M157" s="1">
         <v>2</v>
       </c>
       <c r="N157" s="19">
         <f>AVERAGE('NIVEL 2'!G157:M157)</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O157" s="48" t="str">
+      <c r="O157" s="18" t="str">
         <f>IF(N157=" "," ",IF(N157&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A158" s="47">
+      <c r="A158" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B158" s="50" t="str">
+      <c r="B158" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C158" s="50" t="str">
+      <c r="C158" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D158" s="44">
+      <c r="D158" s="3">
         <v>45929</v>
       </c>
-      <c r="E158" s="45" t="s">
+      <c r="E158" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="F158" s="47">
+      <c r="F158" s="1">
         <v>1418308</v>
       </c>
-      <c r="G158" s="47">
-        <v>5</v>
-      </c>
-      <c r="H158" s="47">
-        <v>5</v>
-      </c>
-      <c r="I158" s="47">
-        <v>4</v>
-      </c>
-      <c r="J158" s="47">
-        <v>5</v>
-      </c>
-      <c r="K158" s="47">
-        <v>5</v>
-      </c>
-      <c r="L158" s="47">
-        <v>5</v>
-      </c>
-      <c r="M158" s="47">
+      <c r="G158" s="1">
+        <v>5</v>
+      </c>
+      <c r="H158" s="1">
+        <v>5</v>
+      </c>
+      <c r="I158" s="1">
+        <v>4</v>
+      </c>
+      <c r="J158" s="1">
+        <v>5</v>
+      </c>
+      <c r="K158" s="1">
+        <v>5</v>
+      </c>
+      <c r="L158" s="1">
+        <v>5</v>
+      </c>
+      <c r="M158" s="1">
         <v>3</v>
       </c>
       <c r="N158" s="19">
         <f>AVERAGE('NIVEL 2'!G158:M158)</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O158" s="48" t="str">
+      <c r="O158" s="18" t="str">
         <f>IF(N158=" "," ",IF(N158&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A159" s="47">
+      <c r="A159" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B159" s="50" t="str">
+      <c r="B159" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C159" s="50" t="str">
+      <c r="C159" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D159" s="44">
+      <c r="D159" s="3">
         <v>45929</v>
       </c>
-      <c r="E159" s="45" t="s">
+      <c r="E159" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="F159" s="47">
+      <c r="F159" s="1">
         <v>7384397</v>
       </c>
-      <c r="G159" s="47">
-        <v>5</v>
-      </c>
-      <c r="H159" s="47">
-        <v>5</v>
-      </c>
-      <c r="I159" s="47">
-        <v>3</v>
-      </c>
-      <c r="J159" s="47">
-        <v>5</v>
-      </c>
-      <c r="K159" s="47">
-        <v>5</v>
-      </c>
-      <c r="L159" s="47">
-        <v>5</v>
-      </c>
-      <c r="M159" s="47">
+      <c r="G159" s="1">
+        <v>5</v>
+      </c>
+      <c r="H159" s="1">
+        <v>5</v>
+      </c>
+      <c r="I159" s="1">
+        <v>3</v>
+      </c>
+      <c r="J159" s="1">
+        <v>5</v>
+      </c>
+      <c r="K159" s="1">
+        <v>5</v>
+      </c>
+      <c r="L159" s="1">
+        <v>5</v>
+      </c>
+      <c r="M159" s="1">
         <v>5</v>
       </c>
       <c r="N159" s="19">
         <f>AVERAGE('NIVEL 2'!G159:M159)</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O159" s="48" t="str">
+      <c r="O159" s="18" t="str">
         <f>IF(N159=" "," ",IF(N159&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A160" s="47">
+      <c r="A160" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B160" s="50" t="str">
+      <c r="B160" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C160" s="50" t="str">
+      <c r="C160" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D160" s="44">
+      <c r="D160" s="3">
         <v>45929</v>
       </c>
-      <c r="E160" s="45" t="s">
+      <c r="E160" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F160" s="47">
+      <c r="F160" s="1">
         <v>10966252</v>
       </c>
-      <c r="G160" s="47">
-        <v>5</v>
-      </c>
-      <c r="H160" s="47">
-        <v>5</v>
-      </c>
-      <c r="I160" s="47">
-        <v>4</v>
-      </c>
-      <c r="J160" s="47">
-        <v>5</v>
-      </c>
-      <c r="K160" s="47">
-        <v>5</v>
-      </c>
-      <c r="L160" s="47">
-        <v>5</v>
-      </c>
-      <c r="M160" s="47">
+      <c r="G160" s="1">
+        <v>5</v>
+      </c>
+      <c r="H160" s="1">
+        <v>5</v>
+      </c>
+      <c r="I160" s="1">
+        <v>4</v>
+      </c>
+      <c r="J160" s="1">
+        <v>5</v>
+      </c>
+      <c r="K160" s="1">
+        <v>5</v>
+      </c>
+      <c r="L160" s="1">
+        <v>5</v>
+      </c>
+      <c r="M160" s="1">
         <v>4</v>
       </c>
       <c r="N160" s="19">
         <f>AVERAGE('NIVEL 2'!G160:M160)</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O160" s="48" t="str">
+      <c r="O160" s="18" t="str">
         <f>IF(N160=" "," ",IF(N160&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A161" s="47">
+      <c r="A161" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B161" s="50" t="str">
+      <c r="B161" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C161" s="50" t="str">
+      <c r="C161" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D161" s="44">
+      <c r="D161" s="3">
         <v>45929</v>
       </c>
-      <c r="E161" s="45" t="s">
+      <c r="E161" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="F161" s="47">
+      <c r="F161" s="1">
         <v>22668392</v>
       </c>
-      <c r="G161" s="47">
-        <v>4</v>
-      </c>
-      <c r="H161" s="47">
-        <v>3</v>
-      </c>
-      <c r="I161" s="47">
-        <v>2</v>
-      </c>
-      <c r="J161" s="47">
-        <v>2</v>
-      </c>
-      <c r="K161" s="47">
-        <v>2</v>
-      </c>
-      <c r="L161" s="47">
-        <v>3</v>
-      </c>
-      <c r="M161" s="47">
+      <c r="G161" s="1">
+        <v>4</v>
+      </c>
+      <c r="H161" s="1">
+        <v>3</v>
+      </c>
+      <c r="I161" s="1">
+        <v>2</v>
+      </c>
+      <c r="J161" s="1">
+        <v>2</v>
+      </c>
+      <c r="K161" s="1">
+        <v>2</v>
+      </c>
+      <c r="L161" s="1">
+        <v>3</v>
+      </c>
+      <c r="M161" s="1">
         <v>1</v>
       </c>
       <c r="N161" s="19">
         <f>AVERAGE('NIVEL 2'!G161:M161)</f>
         <v>2.4285714285714284</v>
       </c>
-      <c r="O161" s="48" t="str">
+      <c r="O161" s="18" t="str">
         <f>IF(N161=" "," ",IF(N161&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A162" s="47">
+      <c r="A162" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B162" s="50" t="str">
+      <c r="B162" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C162" s="50" t="str">
+      <c r="C162" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D162" s="44">
+      <c r="D162" s="3">
         <v>45929</v>
       </c>
-      <c r="E162" s="45" t="s">
+      <c r="E162" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="F162" s="47">
+      <c r="F162" s="1">
         <v>1001481017</v>
       </c>
-      <c r="G162" s="47">
-        <v>4</v>
-      </c>
-      <c r="H162" s="47">
-        <v>4</v>
-      </c>
-      <c r="I162" s="47">
-        <v>2</v>
-      </c>
-      <c r="J162" s="47">
-        <v>3</v>
-      </c>
-      <c r="K162" s="47">
-        <v>4</v>
-      </c>
-      <c r="L162" s="47">
-        <v>4</v>
-      </c>
-      <c r="M162" s="47">
+      <c r="G162" s="1">
+        <v>4</v>
+      </c>
+      <c r="H162" s="1">
+        <v>4</v>
+      </c>
+      <c r="I162" s="1">
+        <v>2</v>
+      </c>
+      <c r="J162" s="1">
+        <v>3</v>
+      </c>
+      <c r="K162" s="1">
+        <v>4</v>
+      </c>
+      <c r="L162" s="1">
+        <v>4</v>
+      </c>
+      <c r="M162" s="1">
         <v>2</v>
       </c>
       <c r="N162" s="19">
         <f>AVERAGE('NIVEL 2'!G162:M162)</f>
         <v>3.2857142857142856</v>
       </c>
-      <c r="O162" s="48" t="str">
+      <c r="O162" s="18" t="str">
         <f>IF(N162=" "," ",IF(N162&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A163" s="47">
+      <c r="A163" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B163" s="50" t="str">
+      <c r="B163" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C163" s="50" t="str">
+      <c r="C163" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D163" s="44">
+      <c r="D163" s="3">
         <v>45929</v>
       </c>
-      <c r="E163" s="45" t="s">
+      <c r="E163" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F163" s="47">
+      <c r="F163" s="1">
         <v>1003049821</v>
       </c>
-      <c r="G163" s="47">
-        <v>5</v>
-      </c>
-      <c r="H163" s="47">
-        <v>4</v>
-      </c>
-      <c r="I163" s="47">
-        <v>3</v>
-      </c>
-      <c r="J163" s="47">
-        <v>4</v>
-      </c>
-      <c r="K163" s="47">
-        <v>4</v>
-      </c>
-      <c r="L163" s="47">
-        <v>5</v>
-      </c>
-      <c r="M163" s="47">
+      <c r="G163" s="1">
+        <v>5</v>
+      </c>
+      <c r="H163" s="1">
+        <v>4</v>
+      </c>
+      <c r="I163" s="1">
+        <v>3</v>
+      </c>
+      <c r="J163" s="1">
+        <v>4</v>
+      </c>
+      <c r="K163" s="1">
+        <v>4</v>
+      </c>
+      <c r="L163" s="1">
+        <v>5</v>
+      </c>
+      <c r="M163" s="1">
         <v>2</v>
       </c>
       <c r="N163" s="19">
         <f>AVERAGE('NIVEL 2'!G163:M163)</f>
         <v>3.8571428571428572</v>
       </c>
-      <c r="O163" s="48" t="str">
+      <c r="O163" s="18" t="str">
         <f>IF(N163=" "," ",IF(N163&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A164" s="47">
+      <c r="A164" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B164" s="50" t="str">
+      <c r="B164" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C164" s="50" t="str">
+      <c r="C164" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D164" s="44">
+      <c r="D164" s="3">
         <v>45929</v>
       </c>
-      <c r="E164" s="45" t="s">
+      <c r="E164" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F164" s="47">
+      <c r="F164" s="1">
         <v>1007676028</v>
       </c>
-      <c r="G164" s="47">
-        <v>5</v>
-      </c>
-      <c r="H164" s="47">
-        <v>4</v>
-      </c>
-      <c r="I164" s="47">
-        <v>3</v>
-      </c>
-      <c r="J164" s="47">
-        <v>4</v>
-      </c>
-      <c r="K164" s="47">
-        <v>3</v>
-      </c>
-      <c r="L164" s="47">
-        <v>4</v>
-      </c>
-      <c r="M164" s="47">
+      <c r="G164" s="1">
+        <v>5</v>
+      </c>
+      <c r="H164" s="1">
+        <v>4</v>
+      </c>
+      <c r="I164" s="1">
+        <v>3</v>
+      </c>
+      <c r="J164" s="1">
+        <v>4</v>
+      </c>
+      <c r="K164" s="1">
+        <v>3</v>
+      </c>
+      <c r="L164" s="1">
+        <v>4</v>
+      </c>
+      <c r="M164" s="1">
         <v>2</v>
       </c>
       <c r="N164" s="19">
         <f>AVERAGE('NIVEL 2'!G164:M164)</f>
         <v>3.5714285714285716</v>
       </c>
-      <c r="O164" s="48" t="str">
+      <c r="O164" s="18" t="str">
         <f>IF(N164=" "," ",IF(N164&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A165" s="47">
+      <c r="A165" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B165" s="50" t="str">
+      <c r="B165" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C165" s="50" t="str">
+      <c r="C165" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D165" s="44">
+      <c r="D165" s="3">
         <v>45929</v>
       </c>
-      <c r="E165" s="45" t="s">
+      <c r="E165" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F165" s="47">
+      <c r="F165" s="1">
         <v>1007822238</v>
       </c>
-      <c r="G165" s="47">
-        <v>5</v>
-      </c>
-      <c r="H165" s="47">
-        <v>5</v>
-      </c>
-      <c r="I165" s="47">
-        <v>3</v>
-      </c>
-      <c r="J165" s="47">
-        <v>5</v>
-      </c>
-      <c r="K165" s="47">
-        <v>5</v>
-      </c>
-      <c r="L165" s="47">
-        <v>5</v>
-      </c>
-      <c r="M165" s="47">
+      <c r="G165" s="1">
+        <v>5</v>
+      </c>
+      <c r="H165" s="1">
+        <v>5</v>
+      </c>
+      <c r="I165" s="1">
+        <v>3</v>
+      </c>
+      <c r="J165" s="1">
+        <v>5</v>
+      </c>
+      <c r="K165" s="1">
+        <v>5</v>
+      </c>
+      <c r="L165" s="1">
+        <v>5</v>
+      </c>
+      <c r="M165" s="1">
         <v>5</v>
       </c>
       <c r="N165" s="19">
         <f>AVERAGE('NIVEL 2'!G165:M165)</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O165" s="48" t="str">
+      <c r="O165" s="18" t="str">
         <f>IF(N165=" "," ",IF(N165&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A166" s="47">
+      <c r="A166" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B166" s="50" t="str">
+      <c r="B166" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C166" s="50" t="str">
+      <c r="C166" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D166" s="44">
+      <c r="D166" s="3">
         <v>45929</v>
       </c>
-      <c r="E166" s="45" t="s">
+      <c r="E166" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="F166" s="47">
+      <c r="F166" s="1">
         <v>1027663882</v>
       </c>
-      <c r="G166" s="47">
-        <v>4</v>
-      </c>
-      <c r="H166" s="47">
-        <v>4</v>
-      </c>
-      <c r="I166" s="47">
-        <v>5</v>
-      </c>
-      <c r="J166" s="47">
-        <v>4</v>
-      </c>
-      <c r="K166" s="47">
-        <v>4</v>
-      </c>
-      <c r="L166" s="47">
-        <v>5</v>
-      </c>
-      <c r="M166" s="47">
+      <c r="G166" s="1">
+        <v>4</v>
+      </c>
+      <c r="H166" s="1">
+        <v>4</v>
+      </c>
+      <c r="I166" s="1">
+        <v>5</v>
+      </c>
+      <c r="J166" s="1">
+        <v>4</v>
+      </c>
+      <c r="K166" s="1">
+        <v>4</v>
+      </c>
+      <c r="L166" s="1">
+        <v>5</v>
+      </c>
+      <c r="M166" s="1">
         <v>3</v>
       </c>
       <c r="N166" s="19">
         <f>AVERAGE('NIVEL 2'!G166:M166)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O166" s="48" t="str">
+      <c r="O166" s="18" t="str">
         <f>IF(N166=" "," ",IF(N166&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A167" s="47">
+      <c r="A167" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B167" s="50" t="str">
+      <c r="B167" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C167" s="50" t="str">
+      <c r="C167" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D167" s="44">
+      <c r="D167" s="3">
         <v>45929</v>
       </c>
-      <c r="E167" s="45" t="s">
+      <c r="E167" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="F167" s="47">
+      <c r="F167" s="1">
         <v>1029722943</v>
       </c>
-      <c r="G167" s="47">
-        <v>5</v>
-      </c>
-      <c r="H167" s="47">
-        <v>5</v>
-      </c>
-      <c r="I167" s="47">
-        <v>5</v>
-      </c>
-      <c r="J167" s="47">
-        <v>4</v>
-      </c>
-      <c r="K167" s="47">
-        <v>5</v>
-      </c>
-      <c r="L167" s="47">
-        <v>5</v>
-      </c>
-      <c r="M167" s="47">
+      <c r="G167" s="1">
+        <v>5</v>
+      </c>
+      <c r="H167" s="1">
+        <v>5</v>
+      </c>
+      <c r="I167" s="1">
+        <v>5</v>
+      </c>
+      <c r="J167" s="1">
+        <v>4</v>
+      </c>
+      <c r="K167" s="1">
+        <v>5</v>
+      </c>
+      <c r="L167" s="1">
+        <v>5</v>
+      </c>
+      <c r="M167" s="1">
         <v>3</v>
       </c>
       <c r="N167" s="19">
         <f>AVERAGE('NIVEL 2'!G167:M167)</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O167" s="48" t="str">
+      <c r="O167" s="18" t="str">
         <f>IF(N167=" "," ",IF(N167&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A168" s="47">
+      <c r="A168" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B168" s="50" t="str">
+      <c r="B168" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C168" s="50" t="str">
+      <c r="C168" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D168" s="44">
+      <c r="D168" s="3">
         <v>45929</v>
       </c>
-      <c r="E168" s="45" t="s">
+      <c r="E168" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="F168" s="47">
+      <c r="F168" s="1">
         <v>1031543523</v>
       </c>
-      <c r="G168" s="47">
-        <v>5</v>
-      </c>
-      <c r="H168" s="47">
-        <v>5</v>
-      </c>
-      <c r="I168" s="47">
-        <v>5</v>
-      </c>
-      <c r="J168" s="47">
-        <v>5</v>
-      </c>
-      <c r="K168" s="47">
-        <v>5</v>
-      </c>
-      <c r="L168" s="47">
-        <v>5</v>
-      </c>
-      <c r="M168" s="47">
+      <c r="G168" s="1">
+        <v>5</v>
+      </c>
+      <c r="H168" s="1">
+        <v>5</v>
+      </c>
+      <c r="I168" s="1">
+        <v>5</v>
+      </c>
+      <c r="J168" s="1">
+        <v>5</v>
+      </c>
+      <c r="K168" s="1">
+        <v>5</v>
+      </c>
+      <c r="L168" s="1">
+        <v>5</v>
+      </c>
+      <c r="M168" s="1">
         <v>3</v>
       </c>
       <c r="N168" s="19">
         <f>AVERAGE('NIVEL 2'!G168:M168)</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O168" s="48" t="str">
+      <c r="O168" s="18" t="str">
         <f>IF(N168=" "," ",IF(N168&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A169" s="47">
+      <c r="A169" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B169" s="50" t="str">
+      <c r="B169" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C169" s="50" t="str">
+      <c r="C169" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D169" s="44">
+      <c r="D169" s="3">
         <v>45929</v>
       </c>
-      <c r="E169" s="45" t="s">
+      <c r="E169" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="F169" s="47">
+      <c r="F169" s="1">
         <v>1062432000</v>
       </c>
-      <c r="G169" s="47">
-        <v>5</v>
-      </c>
-      <c r="H169" s="47">
-        <v>5</v>
-      </c>
-      <c r="I169" s="47">
-        <v>3</v>
-      </c>
-      <c r="J169" s="47">
-        <v>4</v>
-      </c>
-      <c r="K169" s="47">
-        <v>4</v>
-      </c>
-      <c r="L169" s="47">
-        <v>5</v>
-      </c>
-      <c r="M169" s="47">
+      <c r="G169" s="1">
+        <v>5</v>
+      </c>
+      <c r="H169" s="1">
+        <v>5</v>
+      </c>
+      <c r="I169" s="1">
+        <v>3</v>
+      </c>
+      <c r="J169" s="1">
+        <v>4</v>
+      </c>
+      <c r="K169" s="1">
+        <v>4</v>
+      </c>
+      <c r="L169" s="1">
+        <v>5</v>
+      </c>
+      <c r="M169" s="1">
         <v>2</v>
       </c>
       <c r="N169" s="19">
         <f>AVERAGE('NIVEL 2'!G169:M169)</f>
         <v>4</v>
       </c>
-      <c r="O169" s="48" t="str">
+      <c r="O169" s="18" t="str">
         <f>IF(N169=" "," ",IF(N169&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A170" s="47">
+      <c r="A170" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B170" s="50" t="str">
+      <c r="B170" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C170" s="50" t="str">
+      <c r="C170" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D170" s="44">
+      <c r="D170" s="3">
         <v>45929</v>
       </c>
-      <c r="E170" s="45" t="s">
+      <c r="E170" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="F170" s="47">
+      <c r="F170" s="1">
         <v>1062433188</v>
       </c>
-      <c r="G170" s="47">
-        <v>5</v>
-      </c>
-      <c r="H170" s="47">
-        <v>5</v>
-      </c>
-      <c r="I170" s="47">
-        <v>3</v>
-      </c>
-      <c r="J170" s="47">
-        <v>3</v>
-      </c>
-      <c r="K170" s="47">
-        <v>3</v>
-      </c>
-      <c r="L170" s="47">
-        <v>5</v>
-      </c>
-      <c r="M170" s="47">
+      <c r="G170" s="1">
+        <v>5</v>
+      </c>
+      <c r="H170" s="1">
+        <v>5</v>
+      </c>
+      <c r="I170" s="1">
+        <v>3</v>
+      </c>
+      <c r="J170" s="1">
+        <v>3</v>
+      </c>
+      <c r="K170" s="1">
+        <v>3</v>
+      </c>
+      <c r="L170" s="1">
+        <v>5</v>
+      </c>
+      <c r="M170" s="1">
         <v>2</v>
       </c>
       <c r="N170" s="19">
         <f>AVERAGE('NIVEL 2'!G170:M170)</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O170" s="48" t="str">
+      <c r="O170" s="18" t="str">
         <f>IF(N170=" "," ",IF(N170&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A171" s="47">
+      <c r="A171" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B171" s="50" t="str">
+      <c r="B171" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C171" s="50" t="str">
+      <c r="C171" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D171" s="44">
+      <c r="D171" s="3">
         <v>45929</v>
       </c>
-      <c r="E171" s="45" t="s">
+      <c r="E171" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="F171" s="47">
+      <c r="F171" s="1">
         <v>1062539643</v>
       </c>
-      <c r="G171" s="47">
-        <v>5</v>
-      </c>
-      <c r="H171" s="47">
-        <v>4</v>
-      </c>
-      <c r="I171" s="47">
-        <v>4</v>
-      </c>
-      <c r="J171" s="47">
-        <v>5</v>
-      </c>
-      <c r="K171" s="47">
-        <v>5</v>
-      </c>
-      <c r="L171" s="47">
-        <v>5</v>
-      </c>
-      <c r="M171" s="47">
+      <c r="G171" s="1">
+        <v>5</v>
+      </c>
+      <c r="H171" s="1">
+        <v>4</v>
+      </c>
+      <c r="I171" s="1">
+        <v>4</v>
+      </c>
+      <c r="J171" s="1">
+        <v>5</v>
+      </c>
+      <c r="K171" s="1">
+        <v>5</v>
+      </c>
+      <c r="L171" s="1">
+        <v>5</v>
+      </c>
+      <c r="M171" s="1">
         <v>5</v>
       </c>
       <c r="N171" s="19">
         <f>AVERAGE('NIVEL 2'!G171:M171)</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O171" s="48" t="str">
+      <c r="O171" s="18" t="str">
         <f>IF(N171=" "," ",IF(N171&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A172" s="47">
+      <c r="A172" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B172" s="50" t="str">
+      <c r="B172" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C172" s="50" t="str">
+      <c r="C172" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D172" s="44">
+      <c r="D172" s="3">
         <v>45929</v>
       </c>
-      <c r="E172" s="45" t="s">
+      <c r="E172" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="F172" s="47">
+      <c r="F172" s="1">
         <v>1062980565</v>
       </c>
-      <c r="G172" s="47">
-        <v>5</v>
-      </c>
-      <c r="H172" s="47">
-        <v>4</v>
-      </c>
-      <c r="I172" s="47">
-        <v>3</v>
-      </c>
-      <c r="J172" s="47">
-        <v>4</v>
-      </c>
-      <c r="K172" s="47">
-        <v>4</v>
-      </c>
-      <c r="L172" s="47">
-        <v>5</v>
-      </c>
-      <c r="M172" s="47">
+      <c r="G172" s="1">
+        <v>5</v>
+      </c>
+      <c r="H172" s="1">
+        <v>4</v>
+      </c>
+      <c r="I172" s="1">
+        <v>3</v>
+      </c>
+      <c r="J172" s="1">
+        <v>4</v>
+      </c>
+      <c r="K172" s="1">
+        <v>4</v>
+      </c>
+      <c r="L172" s="1">
+        <v>5</v>
+      </c>
+      <c r="M172" s="1">
         <v>4</v>
       </c>
       <c r="N172" s="19">
         <f>AVERAGE('NIVEL 2'!G172:M172)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O172" s="48" t="str">
+      <c r="O172" s="18" t="str">
         <f>IF(N172=" "," ",IF(N172&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A173" s="47">
+      <c r="A173" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B173" s="50" t="str">
+      <c r="B173" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C173" s="50" t="str">
+      <c r="C173" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D173" s="44">
+      <c r="D173" s="3">
         <v>45929</v>
       </c>
-      <c r="E173" s="45" t="s">
+      <c r="E173" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="F173" s="47">
+      <c r="F173" s="1">
         <v>1062986616</v>
       </c>
-      <c r="G173" s="47">
-        <v>5</v>
-      </c>
-      <c r="H173" s="47">
-        <v>5</v>
-      </c>
-      <c r="I173" s="47">
-        <v>3</v>
-      </c>
-      <c r="J173" s="47">
-        <v>3</v>
-      </c>
-      <c r="K173" s="47">
-        <v>3</v>
-      </c>
-      <c r="L173" s="47">
-        <v>4</v>
-      </c>
-      <c r="M173" s="47">
+      <c r="G173" s="1">
+        <v>5</v>
+      </c>
+      <c r="H173" s="1">
+        <v>5</v>
+      </c>
+      <c r="I173" s="1">
+        <v>3</v>
+      </c>
+      <c r="J173" s="1">
+        <v>3</v>
+      </c>
+      <c r="K173" s="1">
+        <v>3</v>
+      </c>
+      <c r="L173" s="1">
+        <v>4</v>
+      </c>
+      <c r="M173" s="1">
         <v>2</v>
       </c>
       <c r="N173" s="19">
         <f>AVERAGE('NIVEL 2'!G173:M173)</f>
         <v>3.5714285714285716</v>
       </c>
-      <c r="O173" s="48" t="str">
+      <c r="O173" s="18" t="str">
         <f>IF(N173=" "," ",IF(N173&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A174" s="47">
+      <c r="A174" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B174" s="50" t="str">
+      <c r="B174" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C174" s="50" t="str">
+      <c r="C174" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D174" s="44">
+      <c r="D174" s="3">
         <v>45929</v>
       </c>
-      <c r="E174" s="45" t="s">
+      <c r="E174" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="F174" s="47">
+      <c r="F174" s="1">
         <v>1063157522</v>
       </c>
-      <c r="G174" s="47">
-        <v>5</v>
-      </c>
-      <c r="H174" s="47">
-        <v>5</v>
-      </c>
-      <c r="I174" s="47">
-        <v>3</v>
-      </c>
-      <c r="J174" s="47">
-        <v>3</v>
-      </c>
-      <c r="K174" s="47">
-        <v>2</v>
-      </c>
-      <c r="L174" s="47">
-        <v>5</v>
-      </c>
-      <c r="M174" s="47">
+      <c r="G174" s="1">
+        <v>5</v>
+      </c>
+      <c r="H174" s="1">
+        <v>5</v>
+      </c>
+      <c r="I174" s="1">
+        <v>3</v>
+      </c>
+      <c r="J174" s="1">
+        <v>3</v>
+      </c>
+      <c r="K174" s="1">
+        <v>2</v>
+      </c>
+      <c r="L174" s="1">
+        <v>5</v>
+      </c>
+      <c r="M174" s="1">
         <v>2</v>
       </c>
       <c r="N174" s="19">
         <f>AVERAGE('NIVEL 2'!G174:M174)</f>
         <v>3.5714285714285716</v>
       </c>
-      <c r="O174" s="48" t="str">
+      <c r="O174" s="18" t="str">
         <f>IF(N174=" "," ",IF(N174&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A175" s="47">
+      <c r="A175" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B175" s="50" t="str">
+      <c r="B175" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C175" s="50" t="str">
+      <c r="C175" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D175" s="44">
+      <c r="D175" s="3">
         <v>45929</v>
       </c>
-      <c r="E175" s="45" t="s">
+      <c r="E175" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="F175" s="47">
+      <c r="F175" s="1">
         <v>1064990474</v>
       </c>
-      <c r="G175" s="47">
-        <v>5</v>
-      </c>
-      <c r="H175" s="47">
-        <v>5</v>
-      </c>
-      <c r="I175" s="47">
-        <v>3</v>
-      </c>
-      <c r="J175" s="47">
-        <v>4</v>
-      </c>
-      <c r="K175" s="47">
-        <v>5</v>
-      </c>
-      <c r="L175" s="47">
-        <v>5</v>
-      </c>
-      <c r="M175" s="47">
+      <c r="G175" s="1">
+        <v>5</v>
+      </c>
+      <c r="H175" s="1">
+        <v>5</v>
+      </c>
+      <c r="I175" s="1">
+        <v>3</v>
+      </c>
+      <c r="J175" s="1">
+        <v>4</v>
+      </c>
+      <c r="K175" s="1">
+        <v>5</v>
+      </c>
+      <c r="L175" s="1">
+        <v>5</v>
+      </c>
+      <c r="M175" s="1">
         <v>4</v>
       </c>
       <c r="N175" s="19">
         <f>AVERAGE('NIVEL 2'!G175:M175)</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O175" s="48" t="str">
+      <c r="O175" s="18" t="str">
         <f>IF(N175=" "," ",IF(N175&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A176" s="47">
+      <c r="A176" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B176" s="50" t="str">
+      <c r="B176" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C176" s="50" t="str">
+      <c r="C176" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D176" s="44">
+      <c r="D176" s="3">
         <v>45929</v>
       </c>
-      <c r="E176" s="45" t="s">
+      <c r="E176" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F176" s="47">
+      <c r="F176" s="1">
         <v>1066512697</v>
       </c>
-      <c r="G176" s="47">
-        <v>5</v>
-      </c>
-      <c r="H176" s="47">
-        <v>4</v>
-      </c>
-      <c r="I176" s="47">
-        <v>2</v>
-      </c>
-      <c r="J176" s="47">
-        <v>4</v>
-      </c>
-      <c r="K176" s="47">
-        <v>4</v>
-      </c>
-      <c r="L176" s="47">
-        <v>5</v>
-      </c>
-      <c r="M176" s="47">
+      <c r="G176" s="1">
+        <v>5</v>
+      </c>
+      <c r="H176" s="1">
+        <v>4</v>
+      </c>
+      <c r="I176" s="1">
+        <v>2</v>
+      </c>
+      <c r="J176" s="1">
+        <v>4</v>
+      </c>
+      <c r="K176" s="1">
+        <v>4</v>
+      </c>
+      <c r="L176" s="1">
+        <v>5</v>
+      </c>
+      <c r="M176" s="1">
         <v>2</v>
       </c>
       <c r="N176" s="19">
         <f>AVERAGE('NIVEL 2'!G176:M176)</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O176" s="48" t="str">
+      <c r="O176" s="18" t="str">
         <f>IF(N176=" "," ",IF(N176&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A177" s="47">
+      <c r="A177" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B177" s="50" t="str">
+      <c r="B177" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C177" s="50" t="str">
+      <c r="C177" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D177" s="44">
+      <c r="D177" s="3">
         <v>45929</v>
       </c>
-      <c r="E177" s="45" t="s">
+      <c r="E177" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="F177" s="47">
+      <c r="F177" s="1">
         <v>1066523010</v>
       </c>
-      <c r="G177" s="47">
-        <v>5</v>
-      </c>
-      <c r="H177" s="47">
-        <v>4</v>
-      </c>
-      <c r="I177" s="47">
-        <v>2</v>
-      </c>
-      <c r="J177" s="47">
-        <v>3</v>
-      </c>
-      <c r="K177" s="47">
-        <v>2</v>
-      </c>
-      <c r="L177" s="47">
-        <v>5</v>
-      </c>
-      <c r="M177" s="47">
+      <c r="G177" s="1">
+        <v>5</v>
+      </c>
+      <c r="H177" s="1">
+        <v>4</v>
+      </c>
+      <c r="I177" s="1">
+        <v>2</v>
+      </c>
+      <c r="J177" s="1">
+        <v>3</v>
+      </c>
+      <c r="K177" s="1">
+        <v>2</v>
+      </c>
+      <c r="L177" s="1">
+        <v>5</v>
+      </c>
+      <c r="M177" s="1">
         <v>2</v>
       </c>
       <c r="N177" s="19">
         <f>AVERAGE('NIVEL 2'!G177:M177)</f>
         <v>3.2857142857142856</v>
       </c>
-      <c r="O177" s="48" t="str">
+      <c r="O177" s="18" t="str">
         <f>IF(N177=" "," ",IF(N177&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A178" s="47">
+      <c r="A178" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B178" s="50" t="str">
+      <c r="B178" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C178" s="50" t="str">
+      <c r="C178" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D178" s="44">
+      <c r="D178" s="3">
         <v>45929</v>
       </c>
-      <c r="E178" s="45" t="s">
+      <c r="E178" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="F178" s="47">
+      <c r="F178" s="1">
         <v>1066747786</v>
       </c>
-      <c r="G178" s="47">
-        <v>5</v>
-      </c>
-      <c r="H178" s="47">
-        <v>5</v>
-      </c>
-      <c r="I178" s="47">
-        <v>3</v>
-      </c>
-      <c r="J178" s="47">
-        <v>5</v>
-      </c>
-      <c r="K178" s="47">
-        <v>5</v>
-      </c>
-      <c r="L178" s="47">
-        <v>5</v>
-      </c>
-      <c r="M178" s="47">
+      <c r="G178" s="1">
+        <v>5</v>
+      </c>
+      <c r="H178" s="1">
+        <v>5</v>
+      </c>
+      <c r="I178" s="1">
+        <v>3</v>
+      </c>
+      <c r="J178" s="1">
+        <v>5</v>
+      </c>
+      <c r="K178" s="1">
+        <v>5</v>
+      </c>
+      <c r="L178" s="1">
+        <v>5</v>
+      </c>
+      <c r="M178" s="1">
         <v>3</v>
       </c>
       <c r="N178" s="19">
         <f>AVERAGE('NIVEL 2'!G178:M178)</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O178" s="48" t="str">
+      <c r="O178" s="18" t="str">
         <f>IF(N178=" "," ",IF(N178&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A179" s="47">
+      <c r="A179" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B179" s="50" t="str">
+      <c r="B179" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C179" s="50" t="str">
+      <c r="C179" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D179" s="44">
+      <c r="D179" s="3">
         <v>45929</v>
       </c>
-      <c r="E179" s="45" t="s">
+      <c r="E179" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F179" s="47">
+      <c r="F179" s="1">
         <v>1067849965</v>
       </c>
-      <c r="G179" s="47">
-        <v>5</v>
-      </c>
-      <c r="H179" s="47">
-        <v>5</v>
-      </c>
-      <c r="I179" s="47">
-        <v>3</v>
-      </c>
-      <c r="J179" s="47">
-        <v>4</v>
-      </c>
-      <c r="K179" s="47">
-        <v>5</v>
-      </c>
-      <c r="L179" s="47">
-        <v>5</v>
-      </c>
-      <c r="M179" s="47">
+      <c r="G179" s="1">
+        <v>5</v>
+      </c>
+      <c r="H179" s="1">
+        <v>5</v>
+      </c>
+      <c r="I179" s="1">
+        <v>3</v>
+      </c>
+      <c r="J179" s="1">
+        <v>4</v>
+      </c>
+      <c r="K179" s="1">
+        <v>5</v>
+      </c>
+      <c r="L179" s="1">
+        <v>5</v>
+      </c>
+      <c r="M179" s="1">
         <v>2</v>
       </c>
       <c r="N179" s="19">
         <f>AVERAGE('NIVEL 2'!G179:M179)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O179" s="48" t="str">
+      <c r="O179" s="18" t="str">
         <f>IF(N179=" "," ",IF(N179&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A180" s="47">
+      <c r="A180" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B180" s="50" t="str">
+      <c r="B180" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C180" s="50" t="str">
+      <c r="C180" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D180" s="44">
+      <c r="D180" s="3">
         <v>45929</v>
       </c>
-      <c r="E180" s="45" t="s">
+      <c r="E180" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="F180" s="47">
+      <c r="F180" s="1">
         <v>1067955099</v>
       </c>
-      <c r="G180" s="47">
-        <v>5</v>
-      </c>
-      <c r="H180" s="47">
-        <v>4</v>
-      </c>
-      <c r="I180" s="47">
-        <v>2</v>
-      </c>
-      <c r="J180" s="47">
-        <v>4</v>
-      </c>
-      <c r="K180" s="47">
-        <v>5</v>
-      </c>
-      <c r="L180" s="47">
-        <v>5</v>
-      </c>
-      <c r="M180" s="47">
+      <c r="G180" s="1">
+        <v>5</v>
+      </c>
+      <c r="H180" s="1">
+        <v>4</v>
+      </c>
+      <c r="I180" s="1">
+        <v>2</v>
+      </c>
+      <c r="J180" s="1">
+        <v>4</v>
+      </c>
+      <c r="K180" s="1">
+        <v>5</v>
+      </c>
+      <c r="L180" s="1">
+        <v>5</v>
+      </c>
+      <c r="M180" s="1">
         <v>2</v>
       </c>
       <c r="N180" s="19">
         <f>AVERAGE('NIVEL 2'!G180:M180)</f>
         <v>3.8571428571428572</v>
       </c>
-      <c r="O180" s="48" t="str">
+      <c r="O180" s="18" t="str">
         <f>IF(N180=" "," ",IF(N180&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A181" s="47">
+      <c r="A181" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B181" s="50" t="str">
+      <c r="B181" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C181" s="50" t="str">
+      <c r="C181" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D181" s="44">
+      <c r="D181" s="3">
         <v>45929</v>
       </c>
-      <c r="E181" s="45" t="s">
+      <c r="E181" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F181" s="47">
+      <c r="F181" s="1">
         <v>1068439668</v>
       </c>
-      <c r="G181" s="47">
-        <v>5</v>
-      </c>
-      <c r="H181" s="47">
-        <v>5</v>
-      </c>
-      <c r="I181" s="47">
-        <v>5</v>
-      </c>
-      <c r="J181" s="47">
-        <v>5</v>
-      </c>
-      <c r="K181" s="47">
-        <v>3</v>
-      </c>
-      <c r="L181" s="47">
-        <v>5</v>
-      </c>
-      <c r="M181" s="47">
+      <c r="G181" s="1">
+        <v>5</v>
+      </c>
+      <c r="H181" s="1">
+        <v>5</v>
+      </c>
+      <c r="I181" s="1">
+        <v>5</v>
+      </c>
+      <c r="J181" s="1">
+        <v>5</v>
+      </c>
+      <c r="K181" s="1">
+        <v>3</v>
+      </c>
+      <c r="L181" s="1">
+        <v>5</v>
+      </c>
+      <c r="M181" s="1">
         <v>2</v>
       </c>
       <c r="N181" s="19">
         <f>AVERAGE('NIVEL 2'!G181:M181)</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O181" s="48" t="str">
+      <c r="O181" s="18" t="str">
         <f>IF(N181=" "," ",IF(N181&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A182" s="47">
+      <c r="A182" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B182" s="50" t="str">
+      <c r="B182" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C182" s="50" t="str">
+      <c r="C182" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D182" s="44">
+      <c r="D182" s="3">
         <v>45929</v>
       </c>
-      <c r="E182" s="45" t="s">
+      <c r="E182" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="F182" s="47">
+      <c r="F182" s="1">
         <v>1073817245</v>
       </c>
-      <c r="G182" s="47">
-        <v>4</v>
-      </c>
-      <c r="H182" s="47">
-        <v>3</v>
-      </c>
-      <c r="I182" s="47">
-        <v>2</v>
-      </c>
-      <c r="J182" s="47">
-        <v>2</v>
-      </c>
-      <c r="K182" s="47">
+      <c r="G182" s="1">
+        <v>4</v>
+      </c>
+      <c r="H182" s="1">
+        <v>3</v>
+      </c>
+      <c r="I182" s="1">
+        <v>2</v>
+      </c>
+      <c r="J182" s="1">
+        <v>2</v>
+      </c>
+      <c r="K182" s="1">
         <v>1</v>
       </c>
-      <c r="L182" s="47">
-        <v>4</v>
-      </c>
-      <c r="M182" s="47">
+      <c r="L182" s="1">
+        <v>4</v>
+      </c>
+      <c r="M182" s="1">
         <v>1</v>
       </c>
       <c r="N182" s="19">
         <f>AVERAGE('NIVEL 2'!G182:M182)</f>
         <v>2.4285714285714284</v>
       </c>
-      <c r="O182" s="48" t="str">
+      <c r="O182" s="18" t="str">
         <f>IF(N182=" "," ",IF(N182&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A183" s="47">
+      <c r="A183" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B183" s="50" t="str">
+      <c r="B183" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C183" s="50" t="str">
+      <c r="C183" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D183" s="44">
+      <c r="D183" s="3">
         <v>45929</v>
       </c>
-      <c r="E183" s="45" t="s">
+      <c r="E183" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="F183" s="47">
+      <c r="F183" s="1">
         <v>1138031207</v>
       </c>
-      <c r="G183" s="47">
-        <v>5</v>
-      </c>
-      <c r="H183" s="47">
-        <v>5</v>
-      </c>
-      <c r="I183" s="47">
-        <v>5</v>
-      </c>
-      <c r="J183" s="47">
-        <v>4</v>
-      </c>
-      <c r="K183" s="47">
-        <v>4</v>
-      </c>
-      <c r="L183" s="47">
-        <v>5</v>
-      </c>
-      <c r="M183" s="47">
+      <c r="G183" s="1">
+        <v>5</v>
+      </c>
+      <c r="H183" s="1">
+        <v>5</v>
+      </c>
+      <c r="I183" s="1">
+        <v>5</v>
+      </c>
+      <c r="J183" s="1">
+        <v>4</v>
+      </c>
+      <c r="K183" s="1">
+        <v>4</v>
+      </c>
+      <c r="L183" s="1">
+        <v>5</v>
+      </c>
+      <c r="M183" s="1">
         <v>2</v>
       </c>
       <c r="N183" s="19">
         <f>AVERAGE('NIVEL 2'!G183:M183)</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O183" s="48" t="str">
+      <c r="O183" s="18" t="str">
         <f>IF(N183=" "," ",IF(N183&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A184" s="47">
+      <c r="A184" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B184" s="50" t="str">
+      <c r="B184" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C184" s="50" t="str">
+      <c r="C184" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D184" s="44">
+      <c r="D184" s="3">
         <v>45929</v>
       </c>
-      <c r="E184" s="45" t="s">
+      <c r="E184" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="F184" s="47">
+      <c r="F184" s="1">
         <v>1138032406</v>
       </c>
-      <c r="G184" s="47">
-        <v>5</v>
-      </c>
-      <c r="H184" s="47">
-        <v>5</v>
-      </c>
-      <c r="I184" s="47">
-        <v>4</v>
-      </c>
-      <c r="J184" s="47">
-        <v>5</v>
-      </c>
-      <c r="K184" s="47">
-        <v>4</v>
-      </c>
-      <c r="L184" s="47">
-        <v>5</v>
-      </c>
-      <c r="M184" s="47">
+      <c r="G184" s="1">
+        <v>5</v>
+      </c>
+      <c r="H184" s="1">
+        <v>5</v>
+      </c>
+      <c r="I184" s="1">
+        <v>4</v>
+      </c>
+      <c r="J184" s="1">
+        <v>5</v>
+      </c>
+      <c r="K184" s="1">
+        <v>4</v>
+      </c>
+      <c r="L184" s="1">
+        <v>5</v>
+      </c>
+      <c r="M184" s="1">
         <v>2</v>
       </c>
       <c r="N184" s="19">
         <f>AVERAGE('NIVEL 2'!G184:M184)</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O184" s="48" t="str">
+      <c r="O184" s="18" t="str">
         <f>IF(N184=" "," ",IF(N184&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A185" s="47">
+      <c r="A185" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B185" s="50" t="str">
+      <c r="B185" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C185" s="50" t="str">
+      <c r="C185" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D185" s="44">
+      <c r="D185" s="3">
         <v>45929</v>
       </c>
-      <c r="E185" s="45" t="s">
+      <c r="E185" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="F185" s="47">
+      <c r="F185" s="1">
         <v>1138032417</v>
       </c>
-      <c r="G185" s="47">
-        <v>5</v>
-      </c>
-      <c r="H185" s="47">
-        <v>5</v>
-      </c>
-      <c r="I185" s="47">
-        <v>3</v>
-      </c>
-      <c r="J185" s="47">
-        <v>4</v>
-      </c>
-      <c r="K185" s="47">
-        <v>3</v>
-      </c>
-      <c r="L185" s="47">
-        <v>5</v>
-      </c>
-      <c r="M185" s="47">
+      <c r="G185" s="1">
+        <v>5</v>
+      </c>
+      <c r="H185" s="1">
+        <v>5</v>
+      </c>
+      <c r="I185" s="1">
+        <v>3</v>
+      </c>
+      <c r="J185" s="1">
+        <v>4</v>
+      </c>
+      <c r="K185" s="1">
+        <v>3</v>
+      </c>
+      <c r="L185" s="1">
+        <v>5</v>
+      </c>
+      <c r="M185" s="1">
         <v>2</v>
       </c>
       <c r="N185" s="19">
         <f>AVERAGE('NIVEL 2'!G185:M185)</f>
         <v>3.8571428571428572</v>
       </c>
-      <c r="O185" s="48" t="str">
+      <c r="O185" s="18" t="str">
         <f>IF(N185=" "," ",IF(N185&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A186" s="47">
+      <c r="A186" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B186" s="50" t="str">
+      <c r="B186" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C186" s="50" t="str">
+      <c r="C186" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D186" s="44">
+      <c r="D186" s="3">
         <v>45929</v>
       </c>
-      <c r="E186" s="45" t="s">
+      <c r="E186" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="F186" s="47">
+      <c r="F186" s="1">
         <v>1140444971</v>
       </c>
-      <c r="G186" s="47">
-        <v>5</v>
-      </c>
-      <c r="H186" s="47">
-        <v>5</v>
-      </c>
-      <c r="I186" s="47">
-        <v>3</v>
-      </c>
-      <c r="J186" s="47">
-        <v>3</v>
-      </c>
-      <c r="K186" s="47">
-        <v>3</v>
-      </c>
-      <c r="L186" s="47">
-        <v>5</v>
-      </c>
-      <c r="M186" s="47">
+      <c r="G186" s="1">
+        <v>5</v>
+      </c>
+      <c r="H186" s="1">
+        <v>5</v>
+      </c>
+      <c r="I186" s="1">
+        <v>3</v>
+      </c>
+      <c r="J186" s="1">
+        <v>3</v>
+      </c>
+      <c r="K186" s="1">
+        <v>3</v>
+      </c>
+      <c r="L186" s="1">
+        <v>5</v>
+      </c>
+      <c r="M186" s="1">
         <v>2</v>
       </c>
       <c r="N186" s="19">
         <f>AVERAGE('NIVEL 2'!G186:M186)</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O186" s="48" t="str">
+      <c r="O186" s="18" t="str">
         <f>IF(N186=" "," ",IF(N186&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A187" s="47">
+      <c r="A187" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B187" s="50" t="str">
+      <c r="B187" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C187" s="50" t="str">
+      <c r="C187" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D187" s="44">
+      <c r="D187" s="3">
         <v>45929</v>
       </c>
-      <c r="E187" s="45" t="s">
+      <c r="E187" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="F187" s="47">
+      <c r="F187" s="1">
         <v>1141358368</v>
       </c>
-      <c r="G187" s="47">
-        <v>5</v>
-      </c>
-      <c r="H187" s="47">
-        <v>5</v>
-      </c>
-      <c r="I187" s="47">
-        <v>3</v>
-      </c>
-      <c r="J187" s="47">
-        <v>4</v>
-      </c>
-      <c r="K187" s="47">
-        <v>5</v>
-      </c>
-      <c r="L187" s="47">
-        <v>5</v>
-      </c>
-      <c r="M187" s="47">
+      <c r="G187" s="1">
+        <v>5</v>
+      </c>
+      <c r="H187" s="1">
+        <v>5</v>
+      </c>
+      <c r="I187" s="1">
+        <v>3</v>
+      </c>
+      <c r="J187" s="1">
+        <v>4</v>
+      </c>
+      <c r="K187" s="1">
+        <v>5</v>
+      </c>
+      <c r="L187" s="1">
+        <v>5</v>
+      </c>
+      <c r="M187" s="1">
         <v>2</v>
       </c>
       <c r="N187" s="19">
         <f>AVERAGE('NIVEL 2'!G187:M187)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O187" s="48" t="str">
+      <c r="O187" s="18" t="str">
         <f>IF(N187=" "," ",IF(N187&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A188" s="47">
+      <c r="A188" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B188" s="50" t="str">
+      <c r="B188" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C188" s="50" t="str">
+      <c r="C188" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D188" s="44">
+      <c r="D188" s="3">
         <v>45929</v>
       </c>
-      <c r="E188" s="45" t="s">
+      <c r="E188" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="F188" s="47">
+      <c r="F188" s="1">
         <v>1142930859</v>
       </c>
-      <c r="G188" s="47">
-        <v>5</v>
-      </c>
-      <c r="H188" s="47">
-        <v>4</v>
-      </c>
-      <c r="I188" s="47">
-        <v>3</v>
-      </c>
-      <c r="J188" s="47">
-        <v>4</v>
-      </c>
-      <c r="K188" s="47">
-        <v>4</v>
-      </c>
-      <c r="L188" s="47">
-        <v>5</v>
-      </c>
-      <c r="M188" s="47">
+      <c r="G188" s="1">
+        <v>5</v>
+      </c>
+      <c r="H188" s="1">
+        <v>4</v>
+      </c>
+      <c r="I188" s="1">
+        <v>3</v>
+      </c>
+      <c r="J188" s="1">
+        <v>4</v>
+      </c>
+      <c r="K188" s="1">
+        <v>4</v>
+      </c>
+      <c r="L188" s="1">
+        <v>5</v>
+      </c>
+      <c r="M188" s="1">
         <v>3</v>
       </c>
       <c r="N188" s="19">
         <f>AVERAGE('NIVEL 2'!G188:M188)</f>
         <v>4</v>
       </c>
-      <c r="O188" s="48" t="str">
+      <c r="O188" s="18" t="str">
         <f>IF(N188=" "," ",IF(N188&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A189" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B189" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C189" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D189" s="44">
+        <v>46012</v>
+      </c>
+      <c r="E189" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="F189" s="47">
+        <v>1007676028</v>
+      </c>
+      <c r="G189" s="47">
+        <v>5</v>
+      </c>
+      <c r="H189" s="47">
+        <v>5</v>
+      </c>
+      <c r="I189" s="47">
+        <v>4</v>
+      </c>
+      <c r="J189" s="47">
+        <v>4</v>
+      </c>
+      <c r="K189" s="47">
+        <v>3</v>
+      </c>
+      <c r="L189" s="47">
+        <v>5</v>
+      </c>
+      <c r="M189" s="47">
+        <v>2</v>
+      </c>
+      <c r="N189" s="19">
+        <f>AVERAGE('NIVEL 2'!G189:M189)</f>
+        <v>4</v>
+      </c>
+      <c r="O189" s="48" t="str">
+        <f>IF(N189=" "," ",IF(N189&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A190" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B190" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C190" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D190" s="44">
+        <v>46012</v>
+      </c>
+      <c r="E190" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="F190" s="47">
+        <v>1064990474</v>
+      </c>
+      <c r="G190" s="47">
+        <v>5</v>
+      </c>
+      <c r="H190" s="47">
+        <v>4</v>
+      </c>
+      <c r="I190" s="47">
+        <v>4</v>
+      </c>
+      <c r="J190" s="47">
+        <v>5</v>
+      </c>
+      <c r="K190" s="47">
+        <v>5</v>
+      </c>
+      <c r="L190" s="47">
+        <v>5</v>
+      </c>
+      <c r="M190" s="47">
+        <v>5</v>
+      </c>
+      <c r="N190" s="19">
+        <f>AVERAGE('NIVEL 2'!G190:M190)</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O190" s="48" t="str">
+        <f>IF(N190=" "," ",IF(N190&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A191" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B191" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C191" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D191" s="44">
+        <v>46012</v>
+      </c>
+      <c r="E191" s="45" t="s">
+        <v>237</v>
+      </c>
+      <c r="F191" s="47">
+        <v>1065007500</v>
+      </c>
+      <c r="G191" s="47">
+        <v>5</v>
+      </c>
+      <c r="H191" s="47">
+        <v>4</v>
+      </c>
+      <c r="I191" s="47">
+        <v>4</v>
+      </c>
+      <c r="J191" s="47">
+        <v>4</v>
+      </c>
+      <c r="K191" s="47">
+        <v>4</v>
+      </c>
+      <c r="L191" s="47">
+        <v>5</v>
+      </c>
+      <c r="M191" s="47">
+        <v>2</v>
+      </c>
+      <c r="N191" s="19">
+        <f>AVERAGE('NIVEL 2'!G191:M191)</f>
+        <v>4</v>
+      </c>
+      <c r="O191" s="48" t="str">
+        <f>IF(N191=" "," ",IF(N191&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A192" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B192" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C192" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D192" s="44">
+        <v>46012</v>
+      </c>
+      <c r="E192" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="F192" s="47">
+        <v>1066747786</v>
+      </c>
+      <c r="G192" s="47">
+        <v>5</v>
+      </c>
+      <c r="H192" s="47">
+        <v>5</v>
+      </c>
+      <c r="I192" s="47">
+        <v>4</v>
+      </c>
+      <c r="J192" s="47">
+        <v>4</v>
+      </c>
+      <c r="K192" s="47">
+        <v>5</v>
+      </c>
+      <c r="L192" s="47">
+        <v>5</v>
+      </c>
+      <c r="M192" s="47">
+        <v>4</v>
+      </c>
+      <c r="N192" s="19">
+        <f>AVERAGE('NIVEL 2'!G192:M192)</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O192" s="48" t="str">
+        <f>IF(N192=" "," ",IF(N192&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A193" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B193" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C193" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D193" s="44">
+        <v>46012</v>
+      </c>
+      <c r="E193" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="F193" s="47">
+        <v>1067936015</v>
+      </c>
+      <c r="G193" s="47">
+        <v>5</v>
+      </c>
+      <c r="H193" s="47">
+        <v>5</v>
+      </c>
+      <c r="I193" s="47">
+        <v>3</v>
+      </c>
+      <c r="J193" s="47">
+        <v>4</v>
+      </c>
+      <c r="K193" s="47">
+        <v>3</v>
+      </c>
+      <c r="L193" s="47">
+        <v>4</v>
+      </c>
+      <c r="M193" s="47">
+        <v>2</v>
+      </c>
+      <c r="N193" s="19">
+        <f>AVERAGE('NIVEL 2'!G193:M193)</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O193" s="48" t="str">
+        <f>IF(N193=" "," ",IF(N193&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A194" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B194" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C194" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D194" s="44">
+        <v>46012</v>
+      </c>
+      <c r="E194" s="45" t="s">
+        <v>201</v>
+      </c>
+      <c r="F194" s="47">
+        <v>1067955099</v>
+      </c>
+      <c r="G194" s="47">
+        <v>5</v>
+      </c>
+      <c r="H194" s="47">
+        <v>5</v>
+      </c>
+      <c r="I194" s="47">
+        <v>3</v>
+      </c>
+      <c r="J194" s="47">
+        <v>4</v>
+      </c>
+      <c r="K194" s="47">
+        <v>5</v>
+      </c>
+      <c r="L194" s="47">
+        <v>5</v>
+      </c>
+      <c r="M194" s="47">
+        <v>3</v>
+      </c>
+      <c r="N194" s="19">
+        <f>AVERAGE('NIVEL 2'!G194:M194)</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O194" s="48" t="str">
+        <f>IF(N194=" "," ",IF(N194&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A195" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B195" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C195" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D195" s="44">
+        <v>46012</v>
+      </c>
+      <c r="E195" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="F195" s="47">
+        <v>1138032406</v>
+      </c>
+      <c r="G195" s="47">
+        <v>5</v>
+      </c>
+      <c r="H195" s="47">
+        <v>5</v>
+      </c>
+      <c r="I195" s="47">
+        <v>4</v>
+      </c>
+      <c r="J195" s="47">
+        <v>4</v>
+      </c>
+      <c r="K195" s="47">
+        <v>4</v>
+      </c>
+      <c r="L195" s="47">
+        <v>5</v>
+      </c>
+      <c r="M195" s="47">
+        <v>3</v>
+      </c>
+      <c r="N195" s="19">
+        <f>AVERAGE('NIVEL 2'!G195:M195)</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O195" s="48" t="str">
+        <f>IF(N195=" "," ",IF(N195&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A196" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B196" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C196" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D196" s="44">
+        <v>46012</v>
+      </c>
+      <c r="E196" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="F196" s="47">
+        <v>1138032549</v>
+      </c>
+      <c r="G196" s="47">
+        <v>5</v>
+      </c>
+      <c r="H196" s="47">
+        <v>4</v>
+      </c>
+      <c r="I196" s="47">
+        <v>3</v>
+      </c>
+      <c r="J196" s="47">
+        <v>3</v>
+      </c>
+      <c r="K196" s="47">
+        <v>5</v>
+      </c>
+      <c r="L196" s="47">
+        <v>4</v>
+      </c>
+      <c r="M196" s="47">
+        <v>4</v>
+      </c>
+      <c r="N196" s="19">
+        <f>AVERAGE('NIVEL 2'!G196:M196)</f>
+        <v>4</v>
+      </c>
+      <c r="O196" s="48" t="str">
+        <f>IF(N196=" "," ",IF(N196&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A197" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B197" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C197" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D197" s="44">
+        <v>46012</v>
+      </c>
+      <c r="E197" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="F197" s="47">
+        <v>1140444971</v>
+      </c>
+      <c r="G197" s="47">
+        <v>5</v>
+      </c>
+      <c r="H197" s="47">
+        <v>5</v>
+      </c>
+      <c r="I197" s="47">
+        <v>5</v>
+      </c>
+      <c r="J197" s="47">
+        <v>4</v>
+      </c>
+      <c r="K197" s="47">
+        <v>4</v>
+      </c>
+      <c r="L197" s="47">
+        <v>5</v>
+      </c>
+      <c r="M197" s="47">
+        <v>3</v>
+      </c>
+      <c r="N197" s="19">
+        <f>AVERAGE('NIVEL 2'!G197:M197)</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O197" s="48" t="str">
+        <f>IF(N197=" "," ",IF(N197&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -34273,7 +35054,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U44"/>
+  <dimension ref="A1:U45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" customWidth="1"/>
@@ -34450,7 +35231,7 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U3" s="32" t="str">
-        <f>IF(T3=" "," ",IF(T3&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" ref="U3:U44" si="0">IF(T3=" "," ",IF(T3&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
@@ -34520,7 +35301,7 @@
         <v>4.384615384615385</v>
       </c>
       <c r="U4" s="32" t="str">
-        <f>IF(T4=" "," ",IF(T4&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -34590,7 +35371,7 @@
         <v>4.4615384615384617</v>
       </c>
       <c r="U5" s="32" t="str">
-        <f>IF(T5=" "," ",IF(T5&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -34660,7 +35441,7 @@
         <v>4.5384615384615383</v>
       </c>
       <c r="U6" s="32" t="str">
-        <f>IF(T6=" "," ",IF(T6&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -34730,7 +35511,7 @@
         <v>4.6923076923076925</v>
       </c>
       <c r="U7" s="32" t="str">
-        <f>IF(T7=" "," ",IF(T7&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -34800,7 +35581,7 @@
         <v>4.615384615384615</v>
       </c>
       <c r="U8" s="32" t="str">
-        <f>IF(T8=" "," ",IF(T8&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -34870,7 +35651,7 @@
         <v>4.7692307692307692</v>
       </c>
       <c r="U9" s="32" t="str">
-        <f>IF(T9=" "," ",IF(T9&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -34940,7 +35721,7 @@
         <v>4.615384615384615</v>
       </c>
       <c r="U10" s="32" t="str">
-        <f>IF(T10=" "," ",IF(T10&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -35010,7 +35791,7 @@
         <v>4.5384615384615383</v>
       </c>
       <c r="U11" s="32" t="str">
-        <f>IF(T11=" "," ",IF(T11&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -35080,7 +35861,7 @@
         <v>4.3076923076923075</v>
       </c>
       <c r="U12" s="32" t="str">
-        <f>IF(T12=" "," ",IF(T12&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -35150,7 +35931,7 @@
         <v>4.6923076923076925</v>
       </c>
       <c r="U13" s="32" t="str">
-        <f>IF(T13=" "," ",IF(T13&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -35220,7 +36001,7 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U14" s="32" t="str">
-        <f>IF(T14=" "," ",IF(T14&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
@@ -35290,7 +36071,7 @@
         <v>4.8461538461538458</v>
       </c>
       <c r="U15" s="32" t="str">
-        <f>IF(T15=" "," ",IF(T15&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -35360,7 +36141,7 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U16" s="32" t="str">
-        <f>IF(T16=" "," ",IF(T16&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
@@ -35430,7 +36211,7 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U17" s="32" t="str">
-        <f>IF(T17=" "," ",IF(T17&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
@@ -35500,7 +36281,7 @@
         <v>4.7692307692307692</v>
       </c>
       <c r="U18" s="32" t="str">
-        <f>IF(T18=" "," ",IF(T18&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -35570,7 +36351,7 @@
         <v>4.7692307692307692</v>
       </c>
       <c r="U19" s="32" t="str">
-        <f>IF(T19=" "," ",IF(T19&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -35640,7 +36421,7 @@
         <v>4.6923076923076925</v>
       </c>
       <c r="U20" s="32" t="str">
-        <f>IF(T20=" "," ",IF(T20&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -35710,7 +36491,7 @@
         <v>3.7692307692307692</v>
       </c>
       <c r="U21" s="32" t="str">
-        <f>IF(T21=" "," ",IF(T21&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -35780,7 +36561,7 @@
         <v>4.8461538461538458</v>
       </c>
       <c r="U22" s="32" t="str">
-        <f>IF(T22=" "," ",IF(T22&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -35850,7 +36631,7 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U23" s="32" t="str">
-        <f>IF(T23=" "," ",IF(T23&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
@@ -35920,7 +36701,7 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U24" s="32" t="str">
-        <f>IF(T24=" "," ",IF(T24&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
@@ -35990,7 +36771,7 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U25" s="32" t="str">
-        <f>IF(T25=" "," ",IF(T25&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
@@ -36060,7 +36841,7 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U26" s="32" t="str">
-        <f>IF(T26=" "," ",IF(T26&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
@@ -36130,7 +36911,7 @@
         <v>4.4615384615384617</v>
       </c>
       <c r="U27" s="32" t="str">
-        <f>IF(T27=" "," ",IF(T27&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -36200,7 +36981,7 @@
         <v>4.8461538461538458</v>
       </c>
       <c r="U28" s="32" t="str">
-        <f>IF(T28=" "," ",IF(T28&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -36270,7 +37051,7 @@
         <v>4.8461538461538458</v>
       </c>
       <c r="U29" s="32" t="str">
-        <f>IF(T29=" "," ",IF(T29&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -36340,7 +37121,7 @@
         <v>4.615384615384615</v>
       </c>
       <c r="U30" s="32" t="str">
-        <f>IF(T30=" "," ",IF(T30&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -36410,7 +37191,7 @@
         <v>5</v>
       </c>
       <c r="U31" s="32" t="str">
-        <f>IF(T31=" "," ",IF(T31&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
@@ -36480,7 +37261,7 @@
         <v>4.615384615384615</v>
       </c>
       <c r="U32" s="32" t="str">
-        <f>IF(T32=" "," ",IF(T32&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -36550,7 +37331,7 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U33" s="32" t="str">
-        <f>IF(T33=" "," ",IF(T33&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
@@ -36620,7 +37401,7 @@
         <v>4.7692307692307692</v>
       </c>
       <c r="U34" s="32" t="str">
-        <f>IF(T34=" "," ",IF(T34&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -36690,7 +37471,7 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U35" s="32" t="str">
-        <f>IF(T35=" "," ",IF(T35&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
@@ -36760,7 +37541,7 @@
         <v>4.6923076923076925</v>
       </c>
       <c r="U36" s="32" t="str">
-        <f>IF(T36=" "," ",IF(T36&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -36830,7 +37611,7 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U37" s="32" t="str">
-        <f>IF(T37=" "," ",IF(T37&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
@@ -36900,7 +37681,7 @@
         <v>4.7692307692307692</v>
       </c>
       <c r="U38" s="32" t="str">
-        <f>IF(T38=" "," ",IF(T38&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -36970,7 +37751,7 @@
         <v>4.7692307692307692</v>
       </c>
       <c r="U39" s="32" t="str">
-        <f>IF(T39=" "," ",IF(T39&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -37040,7 +37821,7 @@
         <v>4.7692307692307692</v>
       </c>
       <c r="U40" s="32" t="str">
-        <f>IF(T40=" "," ",IF(T40&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -37110,218 +37891,288 @@
         <v>4.9230769230769234</v>
       </c>
       <c r="U41" s="32" t="str">
-        <f>IF(T41=" "," ",IF(T41&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A42" s="51">
+      <c r="A42" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B42" s="43" t="str">
+      <c r="B42" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C42" s="52" t="str">
+      <c r="C42" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D42" s="53">
+      <c r="D42" s="21">
         <v>45929</v>
       </c>
-      <c r="E42" s="54" t="s">
+      <c r="E42" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F42" s="55">
+      <c r="F42" s="23">
         <v>33204108</v>
       </c>
-      <c r="G42" s="55">
-        <v>5</v>
-      </c>
-      <c r="H42" s="55">
-        <v>5</v>
-      </c>
-      <c r="I42" s="55">
-        <v>5</v>
-      </c>
-      <c r="J42" s="55">
-        <v>5</v>
-      </c>
-      <c r="K42" s="55">
-        <v>5</v>
-      </c>
-      <c r="L42" s="55">
-        <v>5</v>
-      </c>
-      <c r="M42" s="55">
-        <v>5</v>
-      </c>
-      <c r="N42" s="55">
-        <v>5</v>
-      </c>
-      <c r="O42" s="55">
-        <v>5</v>
-      </c>
-      <c r="P42" s="55">
-        <v>5</v>
-      </c>
-      <c r="Q42" s="55">
-        <v>4</v>
-      </c>
-      <c r="R42" s="55">
-        <v>5</v>
-      </c>
-      <c r="S42" s="55">
+      <c r="G42" s="23">
+        <v>5</v>
+      </c>
+      <c r="H42" s="23">
+        <v>5</v>
+      </c>
+      <c r="I42" s="23">
+        <v>5</v>
+      </c>
+      <c r="J42" s="23">
+        <v>5</v>
+      </c>
+      <c r="K42" s="23">
+        <v>5</v>
+      </c>
+      <c r="L42" s="23">
+        <v>5</v>
+      </c>
+      <c r="M42" s="23">
+        <v>5</v>
+      </c>
+      <c r="N42" s="23">
+        <v>5</v>
+      </c>
+      <c r="O42" s="23">
+        <v>5</v>
+      </c>
+      <c r="P42" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="23">
+        <v>4</v>
+      </c>
+      <c r="R42" s="23">
+        <v>5</v>
+      </c>
+      <c r="S42" s="23">
         <v>5</v>
       </c>
       <c r="T42" s="24">
         <f>AVERAGE('NIVEL 3'!G42:S42)</f>
         <v>4.9230769230769234</v>
       </c>
-      <c r="U42" s="56" t="str">
-        <f>IF(T42=" "," ",IF(T42&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+      <c r="U42" s="32" t="str">
+        <f t="shared" si="0"/>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A43" s="51">
+      <c r="A43" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B43" s="43" t="str">
+      <c r="B43" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C43" s="52" t="str">
+      <c r="C43" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D43" s="53">
+      <c r="D43" s="21">
         <v>45929</v>
       </c>
-      <c r="E43" s="54" t="s">
+      <c r="E43" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="F43" s="55">
+      <c r="F43" s="23">
         <v>1064193109</v>
       </c>
-      <c r="G43" s="55">
-        <v>5</v>
-      </c>
-      <c r="H43" s="55">
-        <v>5</v>
-      </c>
-      <c r="I43" s="55">
-        <v>5</v>
-      </c>
-      <c r="J43" s="55">
-        <v>5</v>
-      </c>
-      <c r="K43" s="55">
-        <v>5</v>
-      </c>
-      <c r="L43" s="55">
-        <v>5</v>
-      </c>
-      <c r="M43" s="55">
-        <v>5</v>
-      </c>
-      <c r="N43" s="55">
-        <v>5</v>
-      </c>
-      <c r="O43" s="55">
-        <v>5</v>
-      </c>
-      <c r="P43" s="55">
-        <v>5</v>
-      </c>
-      <c r="Q43" s="55">
-        <v>4</v>
-      </c>
-      <c r="R43" s="55">
-        <v>4</v>
-      </c>
-      <c r="S43" s="55">
+      <c r="G43" s="23">
+        <v>5</v>
+      </c>
+      <c r="H43" s="23">
+        <v>5</v>
+      </c>
+      <c r="I43" s="23">
+        <v>5</v>
+      </c>
+      <c r="J43" s="23">
+        <v>5</v>
+      </c>
+      <c r="K43" s="23">
+        <v>5</v>
+      </c>
+      <c r="L43" s="23">
+        <v>5</v>
+      </c>
+      <c r="M43" s="23">
+        <v>5</v>
+      </c>
+      <c r="N43" s="23">
+        <v>5</v>
+      </c>
+      <c r="O43" s="23">
+        <v>5</v>
+      </c>
+      <c r="P43" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q43" s="23">
+        <v>4</v>
+      </c>
+      <c r="R43" s="23">
+        <v>4</v>
+      </c>
+      <c r="S43" s="23">
         <v>5</v>
       </c>
       <c r="T43" s="24">
         <f>AVERAGE('NIVEL 3'!G43:S43)</f>
         <v>4.8461538461538458</v>
       </c>
-      <c r="U43" s="56" t="str">
-        <f>IF(T43=" "," ",IF(T43&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+      <c r="U43" s="32" t="str">
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A44" s="51">
+      <c r="A44" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
       </c>
-      <c r="B44" s="43" t="str">
+      <c r="B44" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C44" s="52" t="str">
+      <c r="C44" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>septiembre</v>
       </c>
-      <c r="D44" s="53">
+      <c r="D44" s="21">
         <v>45929</v>
       </c>
-      <c r="E44" s="54" t="s">
+      <c r="E44" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="F44" s="55">
+      <c r="F44" s="23">
         <v>1067869670</v>
       </c>
-      <c r="G44" s="55">
-        <v>5</v>
-      </c>
-      <c r="H44" s="55">
-        <v>5</v>
-      </c>
-      <c r="I44" s="55">
-        <v>5</v>
-      </c>
-      <c r="J44" s="55">
-        <v>5</v>
-      </c>
-      <c r="K44" s="55">
-        <v>5</v>
-      </c>
-      <c r="L44" s="55">
-        <v>4</v>
-      </c>
-      <c r="M44" s="55">
-        <v>5</v>
-      </c>
-      <c r="N44" s="55">
-        <v>5</v>
-      </c>
-      <c r="O44" s="55">
-        <v>5</v>
-      </c>
-      <c r="P44" s="55">
-        <v>5</v>
-      </c>
-      <c r="Q44" s="55">
-        <v>5</v>
-      </c>
-      <c r="R44" s="55">
-        <v>5</v>
-      </c>
-      <c r="S44" s="55">
+      <c r="G44" s="23">
+        <v>5</v>
+      </c>
+      <c r="H44" s="23">
+        <v>5</v>
+      </c>
+      <c r="I44" s="23">
+        <v>5</v>
+      </c>
+      <c r="J44" s="23">
+        <v>5</v>
+      </c>
+      <c r="K44" s="23">
+        <v>5</v>
+      </c>
+      <c r="L44" s="23">
+        <v>4</v>
+      </c>
+      <c r="M44" s="23">
+        <v>5</v>
+      </c>
+      <c r="N44" s="23">
+        <v>5</v>
+      </c>
+      <c r="O44" s="23">
+        <v>5</v>
+      </c>
+      <c r="P44" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q44" s="23">
+        <v>5</v>
+      </c>
+      <c r="R44" s="23">
+        <v>5</v>
+      </c>
+      <c r="S44" s="23">
         <v>5</v>
       </c>
       <c r="T44" s="24">
         <f>AVERAGE('NIVEL 3'!G44:S44)</f>
         <v>4.9230769230769234</v>
       </c>
-      <c r="U44" s="56" t="str">
-        <f>IF(T44=" "," ",IF(T44&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+      <c r="U44" s="32" t="str">
+        <f t="shared" si="0"/>
         <v>CAMBIA A EQUIPO</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A45" s="50">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>12</v>
+      </c>
+      <c r="B45" s="43" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C45" s="51" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>diciembre</v>
+      </c>
+      <c r="D45" s="52">
+        <v>46012</v>
+      </c>
+      <c r="E45" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="F45" s="54">
+        <v>10966252</v>
+      </c>
+      <c r="G45" s="54">
+        <v>5</v>
+      </c>
+      <c r="H45" s="54">
+        <v>5</v>
+      </c>
+      <c r="I45" s="54">
+        <v>5</v>
+      </c>
+      <c r="J45" s="54">
+        <v>5</v>
+      </c>
+      <c r="K45" s="54">
+        <v>4</v>
+      </c>
+      <c r="L45" s="54">
+        <v>3</v>
+      </c>
+      <c r="M45" s="54">
+        <v>5</v>
+      </c>
+      <c r="N45" s="54">
+        <v>5</v>
+      </c>
+      <c r="O45" s="54">
+        <v>4</v>
+      </c>
+      <c r="P45" s="54">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="54">
+        <v>3</v>
+      </c>
+      <c r="R45" s="54">
+        <v>3</v>
+      </c>
+      <c r="S45" s="54">
+        <v>5</v>
+      </c>
+      <c r="T45" s="55">
+        <f>AVERAGE('NIVEL 3'!G45:S45)</f>
+        <v>4.384615384615385</v>
+      </c>
+      <c r="U45" s="56" t="str">
+        <f>IF(T45=" "," ",IF(T45&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
   </sheetData>

--- a/documentos/EVALUACIONES MNM 2025.xlsx
+++ b/documentos/EVALUACIONES MNM 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29617"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raúl\Dropbox (Personal)\2025\RESPALDO DE BASE DE DATOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\LandingPage\Landing_MNM\documentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8729E6C1-C6DC-484D-A0A2-EF1AB70C5AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B128C858-BE14-428E-84AB-7434A74E55A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1650" yWindow="5880" windowWidth="21600" windowHeight="11333" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORTE" sheetId="5" r:id="rId1"/>
@@ -20,9 +20,9 @@
     <sheet name="EQUIPO" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11" hidden="1">NIVEL_1[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21" hidden="1">NIVEL_2[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31" hidden="1">NIVEL_3[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1" hidden="1">NIVEL_1[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2" hidden="1">NIVEL_2[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3" hidden="1">NIVEL_3[]</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">EQUIPO!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'NIVEL 1'!$F$164:$O$187</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'NIVEL 2'!$F$134:$N$156</definedName>
@@ -90,7 +90,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -99,7 +99,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_2">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -108,7 +108,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_3">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -1070,7 +1070,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1193,477 +1193,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="76">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2403,6 +1937,427 @@
       </font>
       <fill>
         <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
@@ -3093,7 +3048,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4849,7 +4804,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6579,7 +6534,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8301,7 +8256,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12450,36 +12405,36 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O197" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O197" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
   <autoFilter ref="A2:O197" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O197">
     <sortCondition ref="A3:A101"/>
     <sortCondition ref="F3:F101"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="14">
+    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="44">
       <calculatedColumnFormula>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="43">
       <calculatedColumnFormula>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="12">
+    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="42">
       <calculatedColumnFormula>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="1">
+    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="31">
       <calculatedColumnFormula>AVERAGE('NIVEL 2'!G3:M3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="0">
+    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="30">
       <calculatedColumnFormula>IF(N3=" "," ",IF(N3&gt;=4.7,"CAMBIA A NIVEL 3"," "))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12488,42 +12443,42 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U45" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45" tableBorderDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U45" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" tableBorderDxfId="27">
   <autoFilter ref="A2:U45" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U44">
     <sortCondition ref="A3"/>
     <sortCondition ref="F3"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="43">
+    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="26">
       <calculatedColumnFormula>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="42">
+    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="25">
       <calculatedColumnFormula>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="41">
+    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="24">
       <calculatedColumnFormula>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="36"/>
-    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="35"/>
-    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="34"/>
-    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="33"/>
-    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="32"/>
-    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="31"/>
-    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="30"/>
-    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="29"/>
-    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="28"/>
-    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="27"/>
-    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="26"/>
-    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="25"/>
-    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="24">
+    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="7">
       <calculatedColumnFormula>AVERAGE('NIVEL 3'!G3:S3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="23">
+    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="6">
       <calculatedColumnFormula>IF(T3=" "," ",IF(T3&gt;=4.9,"CAMBIA A EQUIPO"," "))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12532,17 +12487,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D38" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D38" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="A2:D38" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D33">
     <sortCondition ref="A3"/>
     <sortCondition ref="D3"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="20"/>
-    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12812,14 +12767,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2031510B-662C-4B68-8770-DE372FF29377}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="11.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="4" max="4" width="12.53125" customWidth="1"/>
+    <col min="6" max="6" width="12.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -12849,7 +12804,7 @@
       </c>
       <c r="J1" s="16"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
@@ -12886,7 +12841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="16" t="s">
         <v>36</v>
       </c>
@@ -12923,7 +12878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="16" t="s">
         <v>37</v>
       </c>
@@ -12960,7 +12915,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="16" t="s">
         <v>38</v>
       </c>
@@ -12997,7 +12952,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="16" t="s">
         <v>39</v>
       </c>
@@ -13034,7 +12989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="16" t="s">
         <v>40</v>
       </c>
@@ -13071,7 +13026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="16" t="s">
         <v>41</v>
       </c>
@@ -13108,7 +13063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
         <v>42</v>
       </c>
@@ -13145,7 +13100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="16" t="s">
         <v>43</v>
       </c>
@@ -13182,7 +13137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="16" t="s">
         <v>44</v>
       </c>
@@ -13219,7 +13174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="16" t="s">
         <v>45</v>
       </c>
@@ -13256,7 +13211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="16" t="s">
         <v>46</v>
       </c>
@@ -13312,25 +13267,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O221"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7.33203125" customWidth="1"/>
     <col min="2" max="2" width="5.6640625" style="10" customWidth="1"/>
     <col min="3" max="3" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.46484375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.46484375" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.53125" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.86328125" style="1" customWidth="1"/>
     <col min="12" max="13" width="6.33203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="6.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.46484375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="16.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="E1" s="25" t="s">
         <v>48</v>
       </c>
@@ -13347,7 +13302,7 @@
       <c r="N1" s="33"/>
       <c r="O1" s="34"/>
     </row>
-    <row r="2" spans="1:15" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
         <v>62</v>
       </c>
@@ -13394,7 +13349,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13442,11 +13397,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O3" s="18" t="str">
-        <f>IF(N3=" "," ",IF(N3&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" ref="O3:O66" si="0">IF(N3=" "," ",IF(N3&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13494,11 +13449,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O4" s="18" t="str">
-        <f>IF(N4=" "," ",IF(N4&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13546,11 +13501,11 @@
         <v>2.7142857142857144</v>
       </c>
       <c r="O5" s="18" t="str">
-        <f>IF(N5=" "," ",IF(N5&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13598,11 +13553,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O6" s="18" t="str">
-        <f>IF(N6=" "," ",IF(N6&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13650,11 +13605,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O7" s="18" t="str">
-        <f>IF(N7=" "," ",IF(N7&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13702,11 +13657,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O8" s="18" t="str">
-        <f>IF(N8=" "," ",IF(N8&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13754,11 +13709,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O9" s="18" t="str">
-        <f>IF(N9=" "," ",IF(N9&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13806,11 +13761,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O10" s="18" t="str">
-        <f>IF(N10=" "," ",IF(N10&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13858,11 +13813,11 @@
         <v>5</v>
       </c>
       <c r="O11" s="18" t="str">
-        <f>IF(N11=" "," ",IF(N11&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13910,11 +13865,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O12" s="18" t="str">
-        <f>IF(N12=" "," ",IF(N12&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13962,11 +13917,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O13" s="18" t="str">
-        <f>IF(N13=" "," ",IF(N13&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14014,11 +13969,11 @@
         <v>5</v>
       </c>
       <c r="O14" s="18" t="str">
-        <f>IF(N14=" "," ",IF(N14&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14066,11 +14021,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O15" s="18" t="str">
-        <f>IF(N15=" "," ",IF(N15&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14118,11 +14073,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O16" s="18" t="str">
-        <f>IF(N16=" "," ",IF(N16&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14170,11 +14125,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O17" s="18" t="str">
-        <f>IF(N17=" "," ",IF(N17&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14222,11 +14177,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O18" s="18" t="str">
-        <f>IF(N18=" "," ",IF(N18&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14274,11 +14229,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O19" s="18" t="str">
-        <f>IF(N19=" "," ",IF(N19&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14326,11 +14281,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O20" s="18" t="str">
-        <f>IF(N20=" "," ",IF(N20&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14378,11 +14333,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O21" s="18" t="str">
-        <f>IF(N21=" "," ",IF(N21&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14430,11 +14385,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O22" s="18" t="str">
-        <f>IF(N22=" "," ",IF(N22&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14482,11 +14437,11 @@
         <v>2.7142857142857144</v>
       </c>
       <c r="O23" s="18" t="str">
-        <f>IF(N23=" "," ",IF(N23&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14534,11 +14489,11 @@
         <v>3</v>
       </c>
       <c r="O24" s="18" t="str">
-        <f>IF(N24=" "," ",IF(N24&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14586,11 +14541,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O25" s="18" t="str">
-        <f>IF(N25=" "," ",IF(N25&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14638,11 +14593,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O26" s="18" t="str">
-        <f>IF(N26=" "," ",IF(N26&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14690,11 +14645,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O27" s="18" t="str">
-        <f>IF(N27=" "," ",IF(N27&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14742,11 +14697,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O28" s="18" t="str">
-        <f>IF(N28=" "," ",IF(N28&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A29" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14794,11 +14749,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O29" s="18" t="str">
-        <f>IF(N29=" "," ",IF(N29&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A30" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14846,11 +14801,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O30" s="18" t="str">
-        <f>IF(N30=" "," ",IF(N30&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A31" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14898,11 +14853,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O31" s="18" t="str">
-        <f>IF(N31=" "," ",IF(N31&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A32" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14950,11 +14905,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O32" s="18" t="str">
-        <f>IF(N32=" "," ",IF(N32&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A33" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15002,11 +14957,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O33" s="18" t="str">
-        <f>IF(N33=" "," ",IF(N33&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A34" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15054,11 +15009,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O34" s="18" t="str">
-        <f>IF(N34=" "," ",IF(N34&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A35" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15106,11 +15061,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="O35" s="18" t="str">
-        <f>IF(N35=" "," ",IF(N35&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A36" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15158,11 +15113,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O36" s="18" t="str">
-        <f>IF(N36=" "," ",IF(N36&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A37" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15210,11 +15165,11 @@
         <v>4</v>
       </c>
       <c r="O37" s="18" t="str">
-        <f>IF(N37=" "," ",IF(N37&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A38" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15262,11 +15217,11 @@
         <v>5</v>
       </c>
       <c r="O38" s="18" t="str">
-        <f>IF(N38=" "," ",IF(N38&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A39" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15314,11 +15269,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O39" s="18" t="str">
-        <f>IF(N39=" "," ",IF(N39&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A40" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15366,11 +15321,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O40" s="18" t="str">
-        <f>IF(N40=" "," ",IF(N40&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A41" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15418,11 +15373,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O41" s="18" t="str">
-        <f>IF(N41=" "," ",IF(N41&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A42" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15470,11 +15425,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O42" s="18" t="str">
-        <f>IF(N42=" "," ",IF(N42&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A43" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15522,11 +15477,11 @@
         <v>4</v>
       </c>
       <c r="O43" s="18" t="str">
-        <f>IF(N43=" "," ",IF(N43&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A44" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15574,11 +15529,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O44" s="18" t="str">
-        <f>IF(N44=" "," ",IF(N44&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A45" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15626,11 +15581,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O45" s="18" t="str">
-        <f>IF(N45=" "," ",IF(N45&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A46" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15678,11 +15633,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O46" s="18" t="str">
-        <f>IF(N46=" "," ",IF(N46&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A47" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15730,11 +15685,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O47" s="18" t="str">
-        <f>IF(N47=" "," ",IF(N47&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A48" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15782,11 +15737,11 @@
         <v>5</v>
       </c>
       <c r="O48" s="18" t="str">
-        <f>IF(N48=" "," ",IF(N48&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A49" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15834,11 +15789,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O49" s="18" t="str">
-        <f>IF(N49=" "," ",IF(N49&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A50" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15886,11 +15841,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O50" s="18" t="str">
-        <f>IF(N50=" "," ",IF(N50&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A51" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15938,11 +15893,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O51" s="18" t="str">
-        <f>IF(N51=" "," ",IF(N51&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A52" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15990,11 +15945,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O52" s="18" t="str">
-        <f>IF(N52=" "," ",IF(N52&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A53" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16042,11 +15997,11 @@
         <v>5</v>
       </c>
       <c r="O53" s="18" t="str">
-        <f>IF(N53=" "," ",IF(N53&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A54" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16094,11 +16049,11 @@
         <v>3</v>
       </c>
       <c r="O54" s="18" t="str">
-        <f>IF(N54=" "," ",IF(N54&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A55" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16146,11 +16101,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O55" s="18" t="str">
-        <f>IF(N55=" "," ",IF(N55&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A56" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16198,11 +16153,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O56" s="18" t="str">
-        <f>IF(N56=" "," ",IF(N56&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A57" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16250,11 +16205,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O57" s="18" t="str">
-        <f>IF(N57=" "," ",IF(N57&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A58" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16302,11 +16257,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O58" s="18" t="str">
-        <f>IF(N58=" "," ",IF(N58&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A59" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16354,11 +16309,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O59" s="18" t="str">
-        <f>IF(N59=" "," ",IF(N59&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A60" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -16406,11 +16361,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O60" s="18" t="str">
-        <f>IF(N60=" "," ",IF(N60&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A61" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16458,11 +16413,11 @@
         <v>5</v>
       </c>
       <c r="O61" s="18" t="str">
-        <f>IF(N61=" "," ",IF(N61&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A62" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16510,11 +16465,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O62" s="18" t="str">
-        <f>IF(N62=" "," ",IF(N62&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A63" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16562,11 +16517,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O63" s="18" t="str">
-        <f>IF(N63=" "," ",IF(N63&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A64" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16614,11 +16569,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O64" s="18" t="str">
-        <f>IF(N64=" "," ",IF(N64&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A65" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16666,11 +16621,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O65" s="18" t="str">
-        <f>IF(N65=" "," ",IF(N65&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A66" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16718,11 +16673,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O66" s="18" t="str">
-        <f>IF(N66=" "," ",IF(N66&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A67" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16770,11 +16725,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O67" s="18" t="str">
-        <f>IF(N67=" "," ",IF(N67&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" ref="O67:O130" si="1">IF(N67=" "," ",IF(N67&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A68" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16822,11 +16777,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O68" s="18" t="str">
-        <f>IF(N68=" "," ",IF(N68&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A69" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16874,11 +16829,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O69" s="18" t="str">
-        <f>IF(N69=" "," ",IF(N69&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A70" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16926,11 +16881,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O70" s="18" t="str">
-        <f>IF(N70=" "," ",IF(N70&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A71" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16978,11 +16933,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O71" s="18" t="str">
-        <f>IF(N71=" "," ",IF(N71&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A72" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17030,11 +16985,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O72" s="18" t="str">
-        <f>IF(N72=" "," ",IF(N72&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A73" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17082,11 +17037,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O73" s="18" t="str">
-        <f>IF(N73=" "," ",IF(N73&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A74" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17134,11 +17089,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O74" s="18" t="str">
-        <f>IF(N74=" "," ",IF(N74&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A75" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17186,11 +17141,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O75" s="18" t="str">
-        <f>IF(N75=" "," ",IF(N75&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A76" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17238,11 +17193,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O76" s="18" t="str">
-        <f>IF(N76=" "," ",IF(N76&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A77" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17290,11 +17245,11 @@
         <v>1.8571428571428572</v>
       </c>
       <c r="O77" s="18" t="str">
-        <f>IF(N77=" "," ",IF(N77&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A78" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17342,11 +17297,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O78" s="18" t="str">
-        <f>IF(N78=" "," ",IF(N78&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A79" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17394,11 +17349,11 @@
         <v>2.7142857142857144</v>
       </c>
       <c r="O79" s="18" t="str">
-        <f>IF(N79=" "," ",IF(N79&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A80" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17446,11 +17401,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O80" s="18" t="str">
-        <f>IF(N80=" "," ",IF(N80&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A81" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17498,11 +17453,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O81" s="18" t="str">
-        <f>IF(N81=" "," ",IF(N81&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A82" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17550,11 +17505,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O82" s="18" t="str">
-        <f>IF(N82=" "," ",IF(N82&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A83" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17602,11 +17557,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O83" s="18" t="str">
-        <f>IF(N83=" "," ",IF(N83&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A84" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17654,11 +17609,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O84" s="18" t="str">
-        <f>IF(N84=" "," ",IF(N84&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A85" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17706,11 +17661,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O85" s="18" t="str">
-        <f>IF(N85=" "," ",IF(N85&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A86" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17758,11 +17713,11 @@
         <v>4.2857142857142856</v>
       </c>
       <c r="O86" s="18" t="str">
-        <f>IF(N86=" "," ",IF(N86&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A87" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17810,11 +17765,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O87" s="18" t="str">
-        <f>IF(N87=" "," ",IF(N87&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A88" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17862,11 +17817,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O88" s="18" t="str">
-        <f>IF(N88=" "," ",IF(N88&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A89" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17914,11 +17869,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O89" s="18" t="str">
-        <f>IF(N89=" "," ",IF(N89&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A90" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17966,11 +17921,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O90" s="18" t="str">
-        <f>IF(N90=" "," ",IF(N90&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A91" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18018,11 +17973,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O91" s="18" t="str">
-        <f>IF(N91=" "," ",IF(N91&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A92" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18070,11 +18025,11 @@
         <v>3</v>
       </c>
       <c r="O92" s="18" t="str">
-        <f>IF(N92=" "," ",IF(N92&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A93" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18122,11 +18077,11 @@
         <v>5</v>
       </c>
       <c r="O93" s="18" t="str">
-        <f>IF(N93=" "," ",IF(N93&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A94" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18174,11 +18129,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O94" s="18" t="str">
-        <f>IF(N94=" "," ",IF(N94&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A95" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18226,11 +18181,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O95" s="18" t="str">
-        <f>IF(N95=" "," ",IF(N95&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A96" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18278,11 +18233,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O96" s="18" t="str">
-        <f>IF(N96=" "," ",IF(N96&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A97" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18330,11 +18285,11 @@
         <v>2.1428571428571428</v>
       </c>
       <c r="O97" s="18" t="str">
-        <f>IF(N97=" "," ",IF(N97&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A98" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18382,11 +18337,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O98" s="18" t="str">
-        <f>IF(N98=" "," ",IF(N98&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A99" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18434,11 +18389,11 @@
         <v>5</v>
       </c>
       <c r="O99" s="18" t="str">
-        <f>IF(N99=" "," ",IF(N99&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A100" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18486,11 +18441,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O100" s="18" t="str">
-        <f>IF(N100=" "," ",IF(N100&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A101" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18538,11 +18493,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O101" s="18" t="str">
-        <f>IF(N101=" "," ",IF(N101&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A102" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18590,11 +18545,11 @@
         <v>4.8571428571428568</v>
       </c>
       <c r="O102" s="18" t="str">
-        <f>IF(N102=" "," ",IF(N102&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A103" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18642,11 +18597,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O103" s="18" t="str">
-        <f>IF(N103=" "," ",IF(N103&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A104" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18694,11 +18649,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O104" s="18" t="str">
-        <f>IF(N104=" "," ",IF(N104&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A105" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18746,11 +18701,11 @@
         <v>4</v>
       </c>
       <c r="O105" s="18" t="str">
-        <f>IF(N105=" "," ",IF(N105&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A106" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18798,11 +18753,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O106" s="18" t="str">
-        <f>IF(N106=" "," ",IF(N106&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A107" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18850,11 +18805,11 @@
         <v>2.7142857142857144</v>
       </c>
       <c r="O107" s="18" t="str">
-        <f>IF(N107=" "," ",IF(N107&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A108" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -18902,11 +18857,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O108" s="18" t="str">
-        <f>IF(N108=" "," ",IF(N108&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A109" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -18954,11 +18909,11 @@
         <v>5</v>
       </c>
       <c r="O109" s="18" t="str">
-        <f>IF(N109=" "," ",IF(N109&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A110" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19006,11 +18961,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O110" s="18" t="str">
-        <f>IF(N110=" "," ",IF(N110&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A111" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19058,11 +19013,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O111" s="18" t="str">
-        <f>IF(N111=" "," ",IF(N111&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A112" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19110,11 +19065,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O112" s="18" t="str">
-        <f>IF(N112=" "," ",IF(N112&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A113" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19162,11 +19117,11 @@
         <v>5</v>
       </c>
       <c r="O113" s="18" t="str">
-        <f>IF(N113=" "," ",IF(N113&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A114" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19214,11 +19169,11 @@
         <v>5</v>
       </c>
       <c r="O114" s="18" t="str">
-        <f>IF(N114=" "," ",IF(N114&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A115" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19266,11 +19221,11 @@
         <v>5</v>
       </c>
       <c r="O115" s="18" t="str">
-        <f>IF(N115=" "," ",IF(N115&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A116" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19318,11 +19273,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O116" s="18" t="str">
-        <f>IF(N116=" "," ",IF(N116&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A117" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19370,11 +19325,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O117" s="18" t="str">
-        <f>IF(N117=" "," ",IF(N117&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A118" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19422,11 +19377,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O118" s="18" t="str">
-        <f>IF(N118=" "," ",IF(N118&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A119" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19474,11 +19429,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O119" s="18" t="str">
-        <f>IF(N119=" "," ",IF(N119&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A120" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19526,11 +19481,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O120" s="18" t="str">
-        <f>IF(N120=" "," ",IF(N120&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A121" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19578,11 +19533,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O121" s="18" t="str">
-        <f>IF(N121=" "," ",IF(N121&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A122" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19630,11 +19585,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O122" s="18" t="str">
-        <f>IF(N122=" "," ",IF(N122&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A123" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19682,11 +19637,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O123" s="18" t="str">
-        <f>IF(N123=" "," ",IF(N123&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A124" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19734,11 +19689,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="O124" s="18" t="str">
-        <f>IF(N124=" "," ",IF(N124&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A125" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19786,11 +19741,11 @@
         <v>3</v>
       </c>
       <c r="O125" s="18" t="str">
-        <f>IF(N125=" "," ",IF(N125&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A126" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19838,11 +19793,11 @@
         <v>2.7142857142857144</v>
       </c>
       <c r="O126" s="18" t="str">
-        <f>IF(N126=" "," ",IF(N126&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A127" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19890,11 +19845,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O127" s="18" t="str">
-        <f>IF(N127=" "," ",IF(N127&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A128" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -19942,11 +19897,11 @@
         <v>2.2857142857142856</v>
       </c>
       <c r="O128" s="18" t="str">
-        <f>IF(N128=" "," ",IF(N128&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A129" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -19994,11 +19949,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O129" s="18" t="str">
-        <f>IF(N129=" "," ",IF(N129&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A130" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20046,11 +20001,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O130" s="18" t="str">
-        <f>IF(N130=" "," ",IF(N130&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A131" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20098,11 +20053,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O131" s="18" t="str">
-        <f>IF(N131=" "," ",IF(N131&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" ref="O131:O194" si="2">IF(N131=" "," ",IF(N131&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A132" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20150,11 +20105,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O132" s="18" t="str">
-        <f>IF(N132=" "," ",IF(N132&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A133" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20202,11 +20157,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O133" s="18" t="str">
-        <f>IF(N133=" "," ",IF(N133&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A134" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20254,11 +20209,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O134" s="18" t="str">
-        <f>IF(N134=" "," ",IF(N134&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A135" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20306,11 +20261,11 @@
         <v>2.2857142857142856</v>
       </c>
       <c r="O135" s="18" t="str">
-        <f>IF(N135=" "," ",IF(N135&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A136" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20358,11 +20313,11 @@
         <v>4.2857142857142856</v>
       </c>
       <c r="O136" s="18" t="str">
-        <f>IF(N136=" "," ",IF(N136&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A137" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20410,11 +20365,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O137" s="18" t="str">
-        <f>IF(N137=" "," ",IF(N137&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A138" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20462,11 +20417,11 @@
         <v>2.1428571428571428</v>
       </c>
       <c r="O138" s="18" t="str">
-        <f>IF(N138=" "," ",IF(N138&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A139" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20514,11 +20469,11 @@
         <v>2</v>
       </c>
       <c r="O139" s="18" t="str">
-        <f>IF(N139=" "," ",IF(N139&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A140" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20566,11 +20521,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O140" s="18" t="str">
-        <f>IF(N140=" "," ",IF(N140&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A141" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20618,11 +20573,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O141" s="18" t="str">
-        <f>IF(N141=" "," ",IF(N141&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A142" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20670,11 +20625,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O142" s="18" t="str">
-        <f>IF(N142=" "," ",IF(N142&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A143" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20722,11 +20677,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O143" s="18" t="str">
-        <f>IF(N143=" "," ",IF(N143&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A144" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20774,11 +20729,11 @@
         <v>3</v>
       </c>
       <c r="O144" s="18" t="str">
-        <f>IF(N144=" "," ",IF(N144&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A145" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20826,11 +20781,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O145" s="18" t="str">
-        <f>IF(N145=" "," ",IF(N145&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A146" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20878,11 +20833,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O146" s="18" t="str">
-        <f>IF(N146=" "," ",IF(N146&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A147" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20930,11 +20885,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O147" s="18" t="str">
-        <f>IF(N147=" "," ",IF(N147&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A148" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -20982,11 +20937,11 @@
         <v>5</v>
       </c>
       <c r="O148" s="18" t="str">
-        <f>IF(N148=" "," ",IF(N148&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A149" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21034,11 +20989,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O149" s="18" t="str">
-        <f>IF(N149=" "," ",IF(N149&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A150" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21086,11 +21041,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O150" s="18" t="str">
-        <f>IF(N150=" "," ",IF(N150&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A151" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21138,11 +21093,11 @@
         <v>1.2857142857142858</v>
       </c>
       <c r="O151" s="18" t="str">
-        <f>IF(N151=" "," ",IF(N151&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A152" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21190,11 +21145,11 @@
         <v>1.2857142857142858</v>
       </c>
       <c r="O152" s="18" t="str">
-        <f>IF(N152=" "," ",IF(N152&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A153" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21242,11 +21197,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O153" s="18" t="str">
-        <f>IF(N153=" "," ",IF(N153&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A154" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21294,11 +21249,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O154" s="18" t="str">
-        <f>IF(N154=" "," ",IF(N154&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A155" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21346,11 +21301,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O155" s="18" t="str">
-        <f>IF(N155=" "," ",IF(N155&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A156" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21398,11 +21353,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O156" s="18" t="str">
-        <f>IF(N156=" "," ",IF(N156&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A157" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21450,11 +21405,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O157" s="18" t="str">
-        <f>IF(N157=" "," ",IF(N157&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A158" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21502,11 +21457,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O158" s="18" t="str">
-        <f>IF(N158=" "," ",IF(N158&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A159" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21554,11 +21509,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O159" s="18" t="str">
-        <f>IF(N159=" "," ",IF(N159&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A160" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21606,11 +21561,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O160" s="18" t="str">
-        <f>IF(N160=" "," ",IF(N160&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A161" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21658,11 +21613,11 @@
         <v>5</v>
       </c>
       <c r="O161" s="18" t="str">
-        <f>IF(N161=" "," ",IF(N161&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A162" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21710,11 +21665,11 @@
         <v>2.1428571428571428</v>
       </c>
       <c r="O162" s="18" t="str">
-        <f>IF(N162=" "," ",IF(N162&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A163" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -21762,11 +21717,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O163" s="18" t="str">
-        <f>IF(N163=" "," ",IF(N163&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A164" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -21814,11 +21769,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O164" s="18" t="str">
-        <f>IF(N164=" "," ",IF(N164&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A165" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -21866,11 +21821,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O165" s="18" t="str">
-        <f>IF(N165=" "," ",IF(N165&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A166" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -21918,11 +21873,11 @@
         <v>4.8571428571428568</v>
       </c>
       <c r="O166" s="18" t="str">
-        <f>IF(N166=" "," ",IF(N166&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A167" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -21970,11 +21925,11 @@
         <v>4.8571428571428568</v>
       </c>
       <c r="O167" s="18" t="str">
-        <f>IF(N167=" "," ",IF(N167&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A168" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22022,11 +21977,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O168" s="18" t="str">
-        <f>IF(N168=" "," ",IF(N168&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A169" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22074,11 +22029,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O169" s="18" t="str">
-        <f>IF(N169=" "," ",IF(N169&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A170" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22126,11 +22081,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O170" s="18" t="str">
-        <f>IF(N170=" "," ",IF(N170&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A171" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22178,11 +22133,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O171" s="18" t="str">
-        <f>IF(N171=" "," ",IF(N171&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A172" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22230,11 +22185,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O172" s="18" t="str">
-        <f>IF(N172=" "," ",IF(N172&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A173" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22282,11 +22237,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O173" s="18" t="str">
-        <f>IF(N173=" "," ",IF(N173&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A174" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22334,11 +22289,11 @@
         <v>2.2857142857142856</v>
       </c>
       <c r="O174" s="18" t="str">
-        <f>IF(N174=" "," ",IF(N174&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A175" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22386,11 +22341,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O175" s="18" t="str">
-        <f>IF(N175=" "," ",IF(N175&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A176" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22438,11 +22393,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O176" s="18" t="str">
-        <f>IF(N176=" "," ",IF(N176&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A177" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22490,11 +22445,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O177" s="18" t="str">
-        <f>IF(N177=" "," ",IF(N177&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A178" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22542,11 +22497,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O178" s="18" t="str">
-        <f>IF(N178=" "," ",IF(N178&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A179" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22594,11 +22549,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O179" s="18" t="str">
-        <f>IF(N179=" "," ",IF(N179&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A180" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22646,11 +22601,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="O180" s="18" t="str">
-        <f>IF(N180=" "," ",IF(N180&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A181" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22698,11 +22653,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O181" s="18" t="str">
-        <f>IF(N181=" "," ",IF(N181&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A182" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22750,11 +22705,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O182" s="18" t="str">
-        <f>IF(N182=" "," ",IF(N182&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A183" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22802,11 +22757,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O183" s="18" t="str">
-        <f>IF(N183=" "," ",IF(N183&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A184" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22854,11 +22809,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O184" s="18" t="str">
-        <f>IF(N184=" "," ",IF(N184&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A185" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22906,11 +22861,11 @@
         <v>5</v>
       </c>
       <c r="O185" s="18" t="str">
-        <f>IF(N185=" "," ",IF(N185&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A186" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -22958,11 +22913,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O186" s="18" t="str">
-        <f>IF(N186=" "," ",IF(N186&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A187" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -23010,11 +22965,11 @@
         <v>5</v>
       </c>
       <c r="O187" s="18" t="str">
-        <f>IF(N187=" "," ",IF(N187&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A188" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23062,11 +23017,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O188" s="18" t="str">
-        <f>IF(N188=" "," ",IF(N188&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A189" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23114,11 +23069,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O189" s="18" t="str">
-        <f>IF(N189=" "," ",IF(N189&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A190" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23166,11 +23121,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O190" s="18" t="str">
-        <f>IF(N190=" "," ",IF(N190&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A191" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23218,11 +23173,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O191" s="18" t="str">
-        <f>IF(N191=" "," ",IF(N191&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A192" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23270,11 +23225,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O192" s="18" t="str">
-        <f>IF(N192=" "," ",IF(N192&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A193" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23322,11 +23277,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O193" s="18" t="str">
-        <f>IF(N193=" "," ",IF(N193&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A194" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23374,11 +23329,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O194" s="18" t="str">
-        <f>IF(N194=" "," ",IF(N194&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A195" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23426,11 +23381,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O195" s="18" t="str">
-        <f>IF(N195=" "," ",IF(N195&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" ref="O195:O258" si="3">IF(N195=" "," ",IF(N195&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A196" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23478,11 +23433,11 @@
         <v>4.2857142857142856</v>
       </c>
       <c r="O196" s="18" t="str">
-        <f>IF(N196=" "," ",IF(N196&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A197" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23530,11 +23485,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O197" s="18" t="str">
-        <f>IF(N197=" "," ",IF(N197&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A198" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23582,11 +23537,11 @@
         <v>5</v>
       </c>
       <c r="O198" s="18" t="str">
-        <f>IF(N198=" "," ",IF(N198&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A199" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23634,11 +23589,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O199" s="18" t="str">
-        <f>IF(N199=" "," ",IF(N199&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A200" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23686,11 +23641,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O200" s="18" t="str">
-        <f>IF(N200=" "," ",IF(N200&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A201" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23738,11 +23693,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O201" s="18" t="str">
-        <f>IF(N201=" "," ",IF(N201&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A202" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23790,11 +23745,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O202" s="18" t="str">
-        <f>IF(N202=" "," ",IF(N202&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A203" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23842,11 +23797,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O203" s="18" t="str">
-        <f>IF(N203=" "," ",IF(N203&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A204" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23894,11 +23849,11 @@
         <v>1.7142857142857142</v>
       </c>
       <c r="O204" s="18" t="str">
-        <f>IF(N204=" "," ",IF(N204&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A205" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23946,11 +23901,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O205" s="18" t="str">
-        <f>IF(N205=" "," ",IF(N205&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A206" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -23998,11 +23953,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O206" s="18" t="str">
-        <f>IF(N206=" "," ",IF(N206&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A207" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -24050,11 +24005,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O207" s="18" t="str">
-        <f>IF(N207=" "," ",IF(N207&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A208" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -24102,11 +24057,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O208" s="18" t="str">
-        <f>IF(N208=" "," ",IF(N208&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A209" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -24154,11 +24109,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O209" s="18" t="str">
-        <f>IF(N209=" "," ",IF(N209&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A210" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -24206,11 +24161,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O210" s="18" t="str">
-        <f>IF(N210=" "," ",IF(N210&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A211" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -24258,11 +24213,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O211" s="18" t="str">
-        <f>IF(N211=" "," ",IF(N211&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A212" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -24310,11 +24265,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O212" s="18" t="str">
-        <f>IF(N212=" "," ",IF(N212&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A213" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -24362,11 +24317,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O213" s="18" t="str">
-        <f>IF(N213=" "," ",IF(N213&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A214" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -24414,11 +24369,11 @@
         <v>2.7142857142857144</v>
       </c>
       <c r="O214" s="18" t="str">
-        <f>IF(N214=" "," ",IF(N214&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A215" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -24466,11 +24421,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O215" s="18" t="str">
-        <f>IF(N215=" "," ",IF(N215&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A216" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
@@ -24519,262 +24474,262 @@
       </c>
       <c r="O216" s="18"/>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A217" s="42">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A217" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
       </c>
-      <c r="B217" s="43" t="str">
+      <c r="B217" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C217" s="43" t="str">
+      <c r="C217" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>diciembre</v>
       </c>
-      <c r="D217" s="44">
+      <c r="D217" s="3">
         <v>46012</v>
       </c>
-      <c r="E217" s="45" t="s">
+      <c r="E217" s="20" t="s">
         <v>232</v>
       </c>
       <c r="F217" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="G217" s="47">
-        <v>5</v>
-      </c>
-      <c r="H217" s="47">
-        <v>5</v>
-      </c>
-      <c r="I217" s="47">
-        <v>5</v>
-      </c>
-      <c r="J217" s="47">
-        <v>4</v>
-      </c>
-      <c r="K217" s="47">
-        <v>4</v>
-      </c>
-      <c r="L217" s="47">
-        <v>4</v>
-      </c>
-      <c r="M217" s="47">
+      <c r="G217" s="1">
+        <v>5</v>
+      </c>
+      <c r="H217" s="1">
+        <v>5</v>
+      </c>
+      <c r="I217" s="1">
+        <v>5</v>
+      </c>
+      <c r="J217" s="1">
+        <v>4</v>
+      </c>
+      <c r="K217" s="1">
+        <v>4</v>
+      </c>
+      <c r="L217" s="1">
+        <v>4</v>
+      </c>
+      <c r="M217" s="1">
         <v>5</v>
       </c>
       <c r="N217" s="19">
         <f>AVERAGE('NIVEL 1'!G217:M217)</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O217" s="48" t="str">
+      <c r="O217" s="18" t="str">
         <f>IF(N217=" "," ",IF(N217&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A218" s="42">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A218" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
       </c>
-      <c r="B218" s="43" t="str">
+      <c r="B218" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C218" s="43" t="str">
+      <c r="C218" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>diciembre</v>
       </c>
-      <c r="D218" s="44">
+      <c r="D218" s="3">
         <v>46013</v>
       </c>
-      <c r="E218" s="45" t="s">
+      <c r="E218" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="F218" s="46">
+      <c r="F218" s="1">
         <v>1038649739</v>
       </c>
-      <c r="G218" s="47">
-        <v>5</v>
-      </c>
-      <c r="H218" s="47">
+      <c r="G218" s="1">
+        <v>5</v>
+      </c>
+      <c r="H218" s="1">
         <v>1</v>
       </c>
-      <c r="I218" s="47">
+      <c r="I218" s="1">
         <v>1</v>
       </c>
-      <c r="J218" s="47">
+      <c r="J218" s="1">
         <v>1</v>
       </c>
-      <c r="K218" s="47">
+      <c r="K218" s="1">
         <v>1</v>
       </c>
-      <c r="L218" s="47">
+      <c r="L218" s="1">
         <v>1</v>
       </c>
-      <c r="M218" s="47">
+      <c r="M218" s="1">
         <v>1</v>
       </c>
       <c r="N218" s="19">
         <f>AVERAGE('NIVEL 1'!G218:M218)</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="O218" s="48" t="str">
+      <c r="O218" s="18" t="str">
         <f>IF(N218=" "," ",IF(N218&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A219" s="42">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A219" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
       </c>
-      <c r="B219" s="43" t="str">
+      <c r="B219" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C219" s="43" t="str">
+      <c r="C219" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>diciembre</v>
       </c>
-      <c r="D219" s="44">
+      <c r="D219" s="3">
         <v>46013</v>
       </c>
-      <c r="E219" s="45" t="s">
+      <c r="E219" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="F219" s="46">
+      <c r="F219" s="1">
         <v>1062989283</v>
       </c>
-      <c r="G219" s="47">
-        <v>5</v>
-      </c>
-      <c r="H219" s="47">
+      <c r="G219" s="1">
+        <v>5</v>
+      </c>
+      <c r="H219" s="1">
         <v>1</v>
       </c>
-      <c r="I219" s="47">
+      <c r="I219" s="1">
         <v>1</v>
       </c>
-      <c r="J219" s="47">
+      <c r="J219" s="1">
         <v>1</v>
       </c>
-      <c r="K219" s="47">
+      <c r="K219" s="1">
         <v>1</v>
       </c>
-      <c r="L219" s="47">
+      <c r="L219" s="1">
         <v>1</v>
       </c>
-      <c r="M219" s="47">
+      <c r="M219" s="1">
         <v>1</v>
       </c>
       <c r="N219" s="19">
         <f>AVERAGE('NIVEL 1'!G219:M219)</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="O219" s="48" t="str">
+      <c r="O219" s="18" t="str">
         <f>IF(N219=" "," ",IF(N219&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A220" s="42">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A220" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
       </c>
-      <c r="B220" s="43" t="str">
+      <c r="B220" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C220" s="43" t="str">
+      <c r="C220" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>diciembre</v>
       </c>
-      <c r="D220" s="44">
+      <c r="D220" s="3">
         <v>46013</v>
       </c>
-      <c r="E220" s="45" t="s">
+      <c r="E220" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="F220" s="46">
+      <c r="F220" s="1">
         <v>1062990441</v>
       </c>
-      <c r="G220" s="47">
-        <v>3</v>
-      </c>
-      <c r="H220" s="47">
+      <c r="G220" s="1">
+        <v>3</v>
+      </c>
+      <c r="H220" s="1">
         <v>1</v>
       </c>
-      <c r="I220" s="47">
+      <c r="I220" s="1">
         <v>1</v>
       </c>
-      <c r="J220" s="47">
+      <c r="J220" s="1">
         <v>1</v>
       </c>
-      <c r="K220" s="47">
+      <c r="K220" s="1">
         <v>1</v>
       </c>
-      <c r="L220" s="47">
+      <c r="L220" s="1">
         <v>1</v>
       </c>
-      <c r="M220" s="47">
+      <c r="M220" s="1">
         <v>1</v>
       </c>
       <c r="N220" s="19">
         <f>AVERAGE('NIVEL 1'!G220:M220)</f>
         <v>1.2857142857142858</v>
       </c>
-      <c r="O220" s="48" t="str">
+      <c r="O220" s="18" t="str">
         <f>IF(N220=" "," ",IF(N220&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A221" s="42">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A221" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
       </c>
-      <c r="B221" s="43" t="str">
+      <c r="B221" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C221" s="43" t="str">
+      <c r="C221" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>diciembre</v>
       </c>
-      <c r="D221" s="44">
+      <c r="D221" s="3">
         <v>46013</v>
       </c>
-      <c r="E221" s="45" t="s">
+      <c r="E221" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F221" s="46">
+      <c r="F221" s="1">
         <v>1068444953</v>
       </c>
-      <c r="G221" s="47">
-        <v>5</v>
-      </c>
-      <c r="H221" s="47">
+      <c r="G221" s="1">
+        <v>5</v>
+      </c>
+      <c r="H221" s="1">
         <v>1</v>
       </c>
-      <c r="I221" s="47">
+      <c r="I221" s="1">
         <v>1</v>
       </c>
-      <c r="J221" s="47">
+      <c r="J221" s="1">
         <v>1</v>
       </c>
-      <c r="K221" s="47">
+      <c r="K221" s="1">
         <v>1</v>
       </c>
-      <c r="L221" s="47">
+      <c r="L221" s="1">
         <v>1</v>
       </c>
-      <c r="M221" s="47">
+      <c r="M221" s="1">
         <v>1</v>
       </c>
       <c r="N221" s="19">
         <f>AVERAGE('NIVEL 1'!G221:M221)</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="O221" s="48" t="str">
+      <c r="O221" s="18" t="str">
         <f>IF(N221=" "," ",IF(N221&gt;=4.7,"CAMBIA A NIVEL 2"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -24804,28 +24759,28 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O197"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.46484375" customWidth="1"/>
     <col min="2" max="2" width="5.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" customWidth="1"/>
-    <col min="5" max="5" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.53125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="7" max="7" width="9.53125" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" customWidth="1"/>
+    <col min="9" max="9" width="8.53125" customWidth="1"/>
     <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" customWidth="1"/>
+    <col min="11" max="11" width="7.86328125" customWidth="1"/>
     <col min="12" max="12" width="6.33203125" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" customWidth="1"/>
-    <col min="14" max="14" width="7.109375" customWidth="1"/>
+    <col min="13" max="13" width="9.53125" customWidth="1"/>
+    <col min="14" max="14" width="7.1328125" customWidth="1"/>
     <col min="15" max="15" width="15.6640625" customWidth="1"/>
     <col min="16" max="16" width="15.33203125" customWidth="1"/>
-    <col min="17" max="17" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C1" s="3"/>
       <c r="E1" s="25" t="s">
         <v>59</v>
@@ -24843,7 +24798,7 @@
       <c r="N1" s="35"/>
       <c r="O1" s="34"/>
     </row>
-    <row r="2" spans="1:15" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
         <v>62</v>
       </c>
@@ -24890,7 +24845,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -24938,11 +24893,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O3" s="18" t="str">
-        <f>IF(N3=" "," ",IF(N3&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" ref="O3:O34" si="0">IF(N3=" "," ",IF(N3&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -24990,11 +24945,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O4" s="18" t="str">
-        <f>IF(N4=" "," ",IF(N4&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25042,11 +24997,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O5" s="18" t="str">
-        <f>IF(N5=" "," ",IF(N5&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25094,11 +25049,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O6" s="18" t="str">
-        <f>IF(N6=" "," ",IF(N6&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25146,11 +25101,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O7" s="18" t="str">
-        <f>IF(N7=" "," ",IF(N7&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25198,11 +25153,11 @@
         <v>3</v>
       </c>
       <c r="O8" s="18" t="str">
-        <f>IF(N8=" "," ",IF(N8&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25250,11 +25205,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O9" s="18" t="str">
-        <f>IF(N9=" "," ",IF(N9&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25302,11 +25257,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O10" s="18" t="str">
-        <f>IF(N10=" "," ",IF(N10&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25354,11 +25309,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O11" s="18" t="str">
-        <f>IF(N11=" "," ",IF(N11&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25406,11 +25361,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O12" s="18" t="str">
-        <f>IF(N12=" "," ",IF(N12&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25458,11 +25413,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O13" s="18" t="str">
-        <f>IF(N13=" "," ",IF(N13&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25510,11 +25465,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O14" s="18" t="str">
-        <f>IF(N14=" "," ",IF(N14&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25562,11 +25517,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O15" s="18" t="str">
-        <f>IF(N15=" "," ",IF(N15&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25614,11 +25569,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O16" s="18" t="str">
-        <f>IF(N16=" "," ",IF(N16&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25666,11 +25621,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O17" s="18" t="str">
-        <f>IF(N17=" "," ",IF(N17&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25718,11 +25673,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O18" s="18" t="str">
-        <f>IF(N18=" "," ",IF(N18&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25770,11 +25725,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O19" s="18" t="str">
-        <f>IF(N19=" "," ",IF(N19&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25822,11 +25777,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O20" s="18" t="str">
-        <f>IF(N20=" "," ",IF(N20&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25874,11 +25829,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O21" s="18" t="str">
-        <f>IF(N21=" "," ",IF(N21&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -25926,11 +25881,11 @@
         <v>3</v>
       </c>
       <c r="O22" s="18" t="str">
-        <f>IF(N22=" "," ",IF(N22&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -25978,11 +25933,11 @@
         <v>3</v>
       </c>
       <c r="O23" s="18" t="str">
-        <f>IF(N23=" "," ",IF(N23&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26030,11 +25985,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O24" s="18" t="str">
-        <f>IF(N24=" "," ",IF(N24&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26082,11 +26037,11 @@
         <v>4</v>
       </c>
       <c r="O25" s="18" t="str">
-        <f>IF(N25=" "," ",IF(N25&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26134,11 +26089,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O26" s="18" t="str">
-        <f>IF(N26=" "," ",IF(N26&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26186,11 +26141,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O27" s="18" t="str">
-        <f>IF(N27=" "," ",IF(N27&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26238,11 +26193,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O28" s="18" t="str">
-        <f>IF(N28=" "," ",IF(N28&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A29" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26290,11 +26245,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O29" s="18" t="str">
-        <f>IF(N29=" "," ",IF(N29&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A30" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26342,11 +26297,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O30" s="18" t="str">
-        <f>IF(N30=" "," ",IF(N30&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A31" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26394,11 +26349,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O31" s="18" t="str">
-        <f>IF(N31=" "," ",IF(N31&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A32" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26446,11 +26401,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O32" s="18" t="str">
-        <f>IF(N32=" "," ",IF(N32&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A33" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26498,11 +26453,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O33" s="18" t="str">
-        <f>IF(N33=" "," ",IF(N33&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A34" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26550,11 +26505,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O34" s="18" t="str">
-        <f>IF(N34=" "," ",IF(N34&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A35" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26602,11 +26557,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O35" s="18" t="str">
-        <f>IF(N35=" "," ",IF(N35&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" ref="O35:O66" si="1">IF(N35=" "," ",IF(N35&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A36" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26654,11 +26609,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O36" s="18" t="str">
-        <f>IF(N36=" "," ",IF(N36&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A37" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26706,11 +26661,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O37" s="18" t="str">
-        <f>IF(N37=" "," ",IF(N37&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A38" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26758,11 +26713,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O38" s="18" t="str">
-        <f>IF(N38=" "," ",IF(N38&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A39" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26810,11 +26765,11 @@
         <v>2.5714285714285716</v>
       </c>
       <c r="O39" s="18" t="str">
-        <f>IF(N39=" "," ",IF(N39&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A40" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26862,11 +26817,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O40" s="18" t="str">
-        <f>IF(N40=" "," ",IF(N40&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A41" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26914,11 +26869,11 @@
         <v>4.8571428571428568</v>
       </c>
       <c r="O41" s="18" t="str">
-        <f>IF(N41=" "," ",IF(N41&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A42" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -26966,11 +26921,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O42" s="18" t="str">
-        <f>IF(N42=" "," ",IF(N42&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A43" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -27018,11 +26973,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O43" s="18" t="str">
-        <f>IF(N43=" "," ",IF(N43&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A44" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -27070,11 +27025,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O44" s="18" t="str">
-        <f>IF(N44=" "," ",IF(N44&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A45" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -27122,11 +27077,11 @@
         <v>2.7142857142857144</v>
       </c>
       <c r="O45" s="18" t="str">
-        <f>IF(N45=" "," ",IF(N45&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A46" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -27174,11 +27129,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O46" s="18" t="str">
-        <f>IF(N46=" "," ",IF(N46&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A47" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -27226,11 +27181,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O47" s="18" t="str">
-        <f>IF(N47=" "," ",IF(N47&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A48" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -27278,11 +27233,11 @@
         <v>3</v>
       </c>
       <c r="O48" s="18" t="str">
-        <f>IF(N48=" "," ",IF(N48&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A49" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -27330,11 +27285,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O49" s="18" t="str">
-        <f>IF(N49=" "," ",IF(N49&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A50" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -27382,11 +27337,11 @@
         <v>2.7142857142857144</v>
       </c>
       <c r="O50" s="18" t="str">
-        <f>IF(N50=" "," ",IF(N50&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A51" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -27434,11 +27389,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O51" s="18" t="str">
-        <f>IF(N51=" "," ",IF(N51&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A52" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -27486,11 +27441,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O52" s="18" t="str">
-        <f>IF(N52=" "," ",IF(N52&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A53" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -27538,11 +27493,11 @@
         <v>4.2857142857142856</v>
       </c>
       <c r="O53" s="18" t="str">
-        <f>IF(N53=" "," ",IF(N53&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A54" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -27590,11 +27545,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O54" s="18" t="str">
-        <f>IF(N54=" "," ",IF(N54&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A55" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -27642,11 +27597,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O55" s="18" t="str">
-        <f>IF(N55=" "," ",IF(N55&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A56" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -27694,11 +27649,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O56" s="18" t="str">
-        <f>IF(N56=" "," ",IF(N56&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A57" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -27746,11 +27701,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O57" s="18" t="str">
-        <f>IF(N57=" "," ",IF(N57&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A58" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -27798,11 +27753,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O58" s="18" t="str">
-        <f>IF(N58=" "," ",IF(N58&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A59" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -27850,11 +27805,11 @@
         <v>3</v>
       </c>
       <c r="O59" s="18" t="str">
-        <f>IF(N59=" "," ",IF(N59&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A60" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -27902,11 +27857,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O60" s="18" t="str">
-        <f>IF(N60=" "," ",IF(N60&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A61" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -27954,11 +27909,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O61" s="18" t="str">
-        <f>IF(N61=" "," ",IF(N61&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A62" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -28006,11 +27961,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O62" s="18" t="str">
-        <f>IF(N62=" "," ",IF(N62&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A63" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -28058,11 +28013,11 @@
         <v>5</v>
       </c>
       <c r="O63" s="18" t="str">
-        <f>IF(N63=" "," ",IF(N63&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A64" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -28110,11 +28065,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O64" s="18" t="str">
-        <f>IF(N64=" "," ",IF(N64&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A65" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -28162,11 +28117,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O65" s="18" t="str">
-        <f>IF(N65=" "," ",IF(N65&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A66" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -28214,11 +28169,11 @@
         <v>5</v>
       </c>
       <c r="O66" s="18" t="str">
-        <f>IF(N66=" "," ",IF(N66&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="1"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A67" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -28266,11 +28221,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O67" s="18" t="str">
-        <f>IF(N67=" "," ",IF(N67&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" ref="O67:O98" si="2">IF(N67=" "," ",IF(N67&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A68" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -28318,11 +28273,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O68" s="18" t="str">
-        <f>IF(N68=" "," ",IF(N68&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A69" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -28370,11 +28325,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O69" s="18" t="str">
-        <f>IF(N69=" "," ",IF(N69&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A70" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -28422,11 +28377,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O70" s="18" t="str">
-        <f>IF(N70=" "," ",IF(N70&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A71" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -28474,11 +28429,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O71" s="18" t="str">
-        <f>IF(N71=" "," ",IF(N71&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A72" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -28526,11 +28481,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O72" s="18" t="str">
-        <f>IF(N72=" "," ",IF(N72&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A73" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -28578,11 +28533,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O73" s="18" t="str">
-        <f>IF(N73=" "," ",IF(N73&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A74" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -28630,11 +28585,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O74" s="18" t="str">
-        <f>IF(N74=" "," ",IF(N74&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A75" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -28682,11 +28637,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O75" s="18" t="str">
-        <f>IF(N75=" "," ",IF(N75&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A76" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -28734,11 +28689,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O76" s="18" t="str">
-        <f>IF(N76=" "," ",IF(N76&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A77" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -28786,11 +28741,11 @@
         <v>2</v>
       </c>
       <c r="O77" s="18" t="str">
-        <f>IF(N77=" "," ",IF(N77&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A78" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -28838,11 +28793,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O78" s="18" t="str">
-        <f>IF(N78=" "," ",IF(N78&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A79" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -28890,11 +28845,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O79" s="18" t="str">
-        <f>IF(N79=" "," ",IF(N79&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A80" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -28942,11 +28897,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O80" s="18" t="str">
-        <f>IF(N80=" "," ",IF(N80&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A81" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -28994,11 +28949,11 @@
         <v>3</v>
       </c>
       <c r="O81" s="18" t="str">
-        <f>IF(N81=" "," ",IF(N81&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A82" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29046,11 +29001,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O82" s="18" t="str">
-        <f>IF(N82=" "," ",IF(N82&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A83" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29098,11 +29053,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O83" s="18" t="str">
-        <f>IF(N83=" "," ",IF(N83&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A84" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29150,11 +29105,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O84" s="18" t="str">
-        <f>IF(N84=" "," ",IF(N84&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A85" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29202,11 +29157,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O85" s="18" t="str">
-        <f>IF(N85=" "," ",IF(N85&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A86" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29254,11 +29209,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O86" s="18" t="str">
-        <f>IF(N86=" "," ",IF(N86&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A87" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29306,11 +29261,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O87" s="18" t="str">
-        <f>IF(N87=" "," ",IF(N87&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A88" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29358,11 +29313,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O88" s="18" t="str">
-        <f>IF(N88=" "," ",IF(N88&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A89" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29410,11 +29365,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O89" s="18" t="str">
-        <f>IF(N89=" "," ",IF(N89&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A90" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29462,11 +29417,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O90" s="18" t="str">
-        <f>IF(N90=" "," ",IF(N90&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A91" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29514,11 +29469,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O91" s="18" t="str">
-        <f>IF(N91=" "," ",IF(N91&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A92" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29566,11 +29521,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O92" s="18" t="str">
-        <f>IF(N92=" "," ",IF(N92&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A93" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29618,11 +29573,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O93" s="18" t="str">
-        <f>IF(N93=" "," ",IF(N93&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A94" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29670,11 +29625,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O94" s="18" t="str">
-        <f>IF(N94=" "," ",IF(N94&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A95" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29722,11 +29677,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O95" s="18" t="str">
-        <f>IF(N95=" "," ",IF(N95&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A96" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29774,11 +29729,11 @@
         <v>4</v>
       </c>
       <c r="O96" s="18" t="str">
-        <f>IF(N96=" "," ",IF(N96&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A97" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29826,11 +29781,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O97" s="18" t="str">
-        <f>IF(N97=" "," ",IF(N97&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A98" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29878,11 +29833,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O98" s="18" t="str">
-        <f>IF(N98=" "," ",IF(N98&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A99" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29930,11 +29885,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O99" s="18" t="str">
-        <f>IF(N99=" "," ",IF(N99&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" ref="O99:O130" si="3">IF(N99=" "," ",IF(N99&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A100" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -29982,11 +29937,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O100" s="18" t="str">
-        <f>IF(N100=" "," ",IF(N100&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A101" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -30034,11 +29989,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O101" s="18" t="str">
-        <f>IF(N101=" "," ",IF(N101&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A102" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -30086,11 +30041,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O102" s="18" t="str">
-        <f>IF(N102=" "," ",IF(N102&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A103" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -30138,11 +30093,11 @@
         <v>4</v>
       </c>
       <c r="O103" s="18" t="str">
-        <f>IF(N103=" "," ",IF(N103&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A104" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -30190,11 +30145,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O104" s="18" t="str">
-        <f>IF(N104=" "," ",IF(N104&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A105" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -30242,11 +30197,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O105" s="18" t="str">
-        <f>IF(N105=" "," ",IF(N105&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A106" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -30294,11 +30249,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O106" s="18" t="str">
-        <f>IF(N106=" "," ",IF(N106&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A107" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -30346,11 +30301,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O107" s="18" t="str">
-        <f>IF(N107=" "," ",IF(N107&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A108" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -30398,11 +30353,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O108" s="18" t="str">
-        <f>IF(N108=" "," ",IF(N108&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A109" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -30450,11 +30405,11 @@
         <v>4</v>
       </c>
       <c r="O109" s="18" t="str">
-        <f>IF(N109=" "," ",IF(N109&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A110" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -30502,11 +30457,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O110" s="18" t="str">
-        <f>IF(N110=" "," ",IF(N110&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A111" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -30554,11 +30509,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O111" s="18" t="str">
-        <f>IF(N111=" "," ",IF(N111&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A112" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -30606,11 +30561,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O112" s="18" t="str">
-        <f>IF(N112=" "," ",IF(N112&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A113" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -30658,11 +30613,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O113" s="18" t="str">
-        <f>IF(N113=" "," ",IF(N113&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A114" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -30710,11 +30665,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O114" s="18" t="str">
-        <f>IF(N114=" "," ",IF(N114&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A115" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -30762,11 +30717,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O115" s="18" t="str">
-        <f>IF(N115=" "," ",IF(N115&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A116" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -30814,11 +30769,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O116" s="18" t="str">
-        <f>IF(N116=" "," ",IF(N116&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A117" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -30866,11 +30821,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O117" s="18" t="str">
-        <f>IF(N117=" "," ",IF(N117&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A118" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -30918,11 +30873,11 @@
         <v>4.2857142857142856</v>
       </c>
       <c r="O118" s="18" t="str">
-        <f>IF(N118=" "," ",IF(N118&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A119" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -30970,11 +30925,11 @@
         <v>4</v>
       </c>
       <c r="O119" s="18" t="str">
-        <f>IF(N119=" "," ",IF(N119&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A120" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31022,11 +30977,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O120" s="18" t="str">
-        <f>IF(N120=" "," ",IF(N120&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A121" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31074,11 +31029,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O121" s="18" t="str">
-        <f>IF(N121=" "," ",IF(N121&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A122" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31126,11 +31081,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O122" s="18" t="str">
-        <f>IF(N122=" "," ",IF(N122&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A123" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31178,11 +31133,11 @@
         <v>4</v>
       </c>
       <c r="O123" s="18" t="str">
-        <f>IF(N123=" "," ",IF(N123&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A124" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31230,11 +31185,11 @@
         <v>5</v>
       </c>
       <c r="O124" s="18" t="str">
-        <f>IF(N124=" "," ",IF(N124&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A125" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31282,11 +31237,11 @@
         <v>5</v>
       </c>
       <c r="O125" s="18" t="str">
-        <f>IF(N125=" "," ",IF(N125&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A126" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31334,11 +31289,11 @@
         <v>4</v>
       </c>
       <c r="O126" s="18" t="str">
-        <f>IF(N126=" "," ",IF(N126&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A127" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31386,11 +31341,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O127" s="18" t="str">
-        <f>IF(N127=" "," ",IF(N127&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A128" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31438,11 +31393,11 @@
         <v>5</v>
       </c>
       <c r="O128" s="18" t="str">
-        <f>IF(N128=" "," ",IF(N128&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A129" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31490,11 +31445,11 @@
         <v>4</v>
       </c>
       <c r="O129" s="18" t="str">
-        <f>IF(N129=" "," ",IF(N129&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A130" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31542,11 +31497,11 @@
         <v>4</v>
       </c>
       <c r="O130" s="18" t="str">
-        <f>IF(N130=" "," ",IF(N130&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A131" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31594,11 +31549,11 @@
         <v>4</v>
       </c>
       <c r="O131" s="18" t="str">
-        <f>IF(N131=" "," ",IF(N131&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" ref="O131:O162" si="4">IF(N131=" "," ",IF(N131&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A132" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31646,11 +31601,11 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="O132" s="18" t="str">
-        <f>IF(N132=" "," ",IF(N132&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A133" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -31698,11 +31653,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O133" s="18" t="str">
-        <f>IF(N133=" "," ",IF(N133&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A134" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -31750,11 +31705,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O134" s="18" t="str">
-        <f>IF(N134=" "," ",IF(N134&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A135" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -31802,11 +31757,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O135" s="18" t="str">
-        <f>IF(N135=" "," ",IF(N135&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A136" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -31854,11 +31809,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O136" s="18" t="str">
-        <f>IF(N136=" "," ",IF(N136&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A137" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -31906,11 +31861,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O137" s="18" t="str">
-        <f>IF(N137=" "," ",IF(N137&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A138" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -31958,11 +31913,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O138" s="18" t="str">
-        <f>IF(N138=" "," ",IF(N138&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A139" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32010,11 +31965,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O139" s="18" t="str">
-        <f>IF(N139=" "," ",IF(N139&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A140" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32062,11 +32017,11 @@
         <v>4.2857142857142856</v>
       </c>
       <c r="O140" s="18" t="str">
-        <f>IF(N140=" "," ",IF(N140&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A141" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32114,11 +32069,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O141" s="18" t="str">
-        <f>IF(N141=" "," ",IF(N141&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A142" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32166,11 +32121,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O142" s="18" t="str">
-        <f>IF(N142=" "," ",IF(N142&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A143" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32218,11 +32173,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O143" s="18" t="str">
-        <f>IF(N143=" "," ",IF(N143&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A144" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32270,11 +32225,11 @@
         <v>4</v>
       </c>
       <c r="O144" s="18" t="str">
-        <f>IF(N144=" "," ",IF(N144&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A145" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32322,11 +32277,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O145" s="18" t="str">
-        <f>IF(N145=" "," ",IF(N145&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A146" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32374,11 +32329,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O146" s="18" t="str">
-        <f>IF(N146=" "," ",IF(N146&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A147" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32426,11 +32381,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O147" s="18" t="str">
-        <f>IF(N147=" "," ",IF(N147&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A148" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32478,11 +32433,11 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="O148" s="18" t="str">
-        <f>IF(N148=" "," ",IF(N148&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A149" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32530,11 +32485,11 @@
         <v>4.2857142857142856</v>
       </c>
       <c r="O149" s="18" t="str">
-        <f>IF(N149=" "," ",IF(N149&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A150" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32582,11 +32537,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O150" s="18" t="str">
-        <f>IF(N150=" "," ",IF(N150&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A151" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32634,11 +32589,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O151" s="18" t="str">
-        <f>IF(N151=" "," ",IF(N151&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A152" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32686,11 +32641,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O152" s="18" t="str">
-        <f>IF(N152=" "," ",IF(N152&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A153" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32738,11 +32693,11 @@
         <v>4</v>
       </c>
       <c r="O153" s="18" t="str">
-        <f>IF(N153=" "," ",IF(N153&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A154" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32790,11 +32745,11 @@
         <v>3.4285714285714284</v>
       </c>
       <c r="O154" s="18" t="str">
-        <f>IF(N154=" "," ",IF(N154&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A155" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32842,11 +32797,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O155" s="18" t="str">
-        <f>IF(N155=" "," ",IF(N155&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A156" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -32894,11 +32849,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O156" s="18" t="str">
-        <f>IF(N156=" "," ",IF(N156&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A157" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -32946,11 +32901,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O157" s="18" t="str">
-        <f>IF(N157=" "," ",IF(N157&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A158" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -32998,11 +32953,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O158" s="18" t="str">
-        <f>IF(N158=" "," ",IF(N158&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A159" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33050,11 +33005,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O159" s="18" t="str">
-        <f>IF(N159=" "," ",IF(N159&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A160" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33102,11 +33057,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O160" s="18" t="str">
-        <f>IF(N160=" "," ",IF(N160&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A161" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33154,11 +33109,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O161" s="18" t="str">
-        <f>IF(N161=" "," ",IF(N161&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A162" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33206,11 +33161,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O162" s="18" t="str">
-        <f>IF(N162=" "," ",IF(N162&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A163" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33258,11 +33213,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O163" s="18" t="str">
-        <f>IF(N163=" "," ",IF(N163&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" ref="O163:O194" si="5">IF(N163=" "," ",IF(N163&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A164" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33310,11 +33265,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O164" s="18" t="str">
-        <f>IF(N164=" "," ",IF(N164&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A165" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33362,11 +33317,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O165" s="18" t="str">
-        <f>IF(N165=" "," ",IF(N165&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A166" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33414,11 +33369,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O166" s="18" t="str">
-        <f>IF(N166=" "," ",IF(N166&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A167" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33466,11 +33421,11 @@
         <v>4.5714285714285712</v>
       </c>
       <c r="O167" s="18" t="str">
-        <f>IF(N167=" "," ",IF(N167&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A168" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33518,11 +33473,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O168" s="18" t="str">
-        <f>IF(N168=" "," ",IF(N168&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A169" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33570,11 +33525,11 @@
         <v>4</v>
       </c>
       <c r="O169" s="18" t="str">
-        <f>IF(N169=" "," ",IF(N169&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A170" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33622,11 +33577,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O170" s="18" t="str">
-        <f>IF(N170=" "," ",IF(N170&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A171" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33674,11 +33629,11 @@
         <v>4.7142857142857144</v>
       </c>
       <c r="O171" s="18" t="str">
-        <f>IF(N171=" "," ",IF(N171&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A172" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33726,11 +33681,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O172" s="18" t="str">
-        <f>IF(N172=" "," ",IF(N172&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A173" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33778,11 +33733,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O173" s="18" t="str">
-        <f>IF(N173=" "," ",IF(N173&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A174" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33830,11 +33785,11 @@
         <v>3.5714285714285716</v>
       </c>
       <c r="O174" s="18" t="str">
-        <f>IF(N174=" "," ",IF(N174&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A175" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33882,11 +33837,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O175" s="18" t="str">
-        <f>IF(N175=" "," ",IF(N175&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A176" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33934,11 +33889,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O176" s="18" t="str">
-        <f>IF(N176=" "," ",IF(N176&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A177" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -33986,11 +33941,11 @@
         <v>3.2857142857142856</v>
       </c>
       <c r="O177" s="18" t="str">
-        <f>IF(N177=" "," ",IF(N177&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A178" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -34038,11 +33993,11 @@
         <v>4.4285714285714288</v>
       </c>
       <c r="O178" s="18" t="str">
-        <f>IF(N178=" "," ",IF(N178&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A179" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -34090,11 +34045,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O179" s="18" t="str">
-        <f>IF(N179=" "," ",IF(N179&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A180" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -34142,11 +34097,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O180" s="18" t="str">
-        <f>IF(N180=" "," ",IF(N180&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A181" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -34194,11 +34149,11 @@
         <v>4.2857142857142856</v>
       </c>
       <c r="O181" s="18" t="str">
-        <f>IF(N181=" "," ",IF(N181&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A182" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -34246,11 +34201,11 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="O182" s="18" t="str">
-        <f>IF(N182=" "," ",IF(N182&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A183" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -34298,11 +34253,11 @@
         <v>4.2857142857142856</v>
       </c>
       <c r="O183" s="18" t="str">
-        <f>IF(N183=" "," ",IF(N183&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A184" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -34350,11 +34305,11 @@
         <v>4.2857142857142856</v>
       </c>
       <c r="O184" s="18" t="str">
-        <f>IF(N184=" "," ",IF(N184&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A185" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -34402,11 +34357,11 @@
         <v>3.8571428571428572</v>
       </c>
       <c r="O185" s="18" t="str">
-        <f>IF(N185=" "," ",IF(N185&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A186" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -34454,11 +34409,11 @@
         <v>3.7142857142857144</v>
       </c>
       <c r="O186" s="18" t="str">
-        <f>IF(N186=" "," ",IF(N186&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A187" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -34506,11 +34461,11 @@
         <v>4.1428571428571432</v>
       </c>
       <c r="O187" s="18" t="str">
-        <f>IF(N187=" "," ",IF(N187&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A188" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -34558,475 +34513,475 @@
         <v>4</v>
       </c>
       <c r="O188" s="18" t="str">
-        <f>IF(N188=" "," ",IF(N188&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A189" s="47">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A189" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
       </c>
-      <c r="B189" s="49" t="str">
+      <c r="B189" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C189" s="49" t="str">
+      <c r="C189" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>diciembre</v>
       </c>
-      <c r="D189" s="44">
+      <c r="D189" s="3">
         <v>46012</v>
       </c>
-      <c r="E189" s="45" t="s">
+      <c r="E189" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F189" s="47">
+      <c r="F189" s="1">
         <v>1007676028</v>
       </c>
-      <c r="G189" s="47">
-        <v>5</v>
-      </c>
-      <c r="H189" s="47">
-        <v>5</v>
-      </c>
-      <c r="I189" s="47">
-        <v>4</v>
-      </c>
-      <c r="J189" s="47">
-        <v>4</v>
-      </c>
-      <c r="K189" s="47">
-        <v>3</v>
-      </c>
-      <c r="L189" s="47">
-        <v>5</v>
-      </c>
-      <c r="M189" s="47">
+      <c r="G189" s="1">
+        <v>5</v>
+      </c>
+      <c r="H189" s="1">
+        <v>5</v>
+      </c>
+      <c r="I189" s="1">
+        <v>4</v>
+      </c>
+      <c r="J189" s="1">
+        <v>4</v>
+      </c>
+      <c r="K189" s="1">
+        <v>3</v>
+      </c>
+      <c r="L189" s="1">
+        <v>5</v>
+      </c>
+      <c r="M189" s="1">
         <v>2</v>
       </c>
       <c r="N189" s="19">
         <f>AVERAGE('NIVEL 2'!G189:M189)</f>
         <v>4</v>
       </c>
-      <c r="O189" s="48" t="str">
-        <f>IF(N189=" "," ",IF(N189&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+      <c r="O189" s="18" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A190" s="47">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A190" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
       </c>
-      <c r="B190" s="49" t="str">
+      <c r="B190" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C190" s="49" t="str">
+      <c r="C190" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>diciembre</v>
       </c>
-      <c r="D190" s="44">
+      <c r="D190" s="3">
         <v>46012</v>
       </c>
-      <c r="E190" s="45" t="s">
+      <c r="E190" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="F190" s="47">
+      <c r="F190" s="1">
         <v>1064990474</v>
       </c>
-      <c r="G190" s="47">
-        <v>5</v>
-      </c>
-      <c r="H190" s="47">
-        <v>4</v>
-      </c>
-      <c r="I190" s="47">
-        <v>4</v>
-      </c>
-      <c r="J190" s="47">
-        <v>5</v>
-      </c>
-      <c r="K190" s="47">
-        <v>5</v>
-      </c>
-      <c r="L190" s="47">
-        <v>5</v>
-      </c>
-      <c r="M190" s="47">
+      <c r="G190" s="1">
+        <v>5</v>
+      </c>
+      <c r="H190" s="1">
+        <v>4</v>
+      </c>
+      <c r="I190" s="1">
+        <v>4</v>
+      </c>
+      <c r="J190" s="1">
+        <v>5</v>
+      </c>
+      <c r="K190" s="1">
+        <v>5</v>
+      </c>
+      <c r="L190" s="1">
+        <v>5</v>
+      </c>
+      <c r="M190" s="1">
         <v>5</v>
       </c>
       <c r="N190" s="19">
         <f>AVERAGE('NIVEL 2'!G190:M190)</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O190" s="48" t="str">
-        <f>IF(N190=" "," ",IF(N190&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+      <c r="O190" s="18" t="str">
+        <f t="shared" si="5"/>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A191" s="47">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A191" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
       </c>
-      <c r="B191" s="49" t="str">
+      <c r="B191" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C191" s="49" t="str">
+      <c r="C191" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>diciembre</v>
       </c>
-      <c r="D191" s="44">
+      <c r="D191" s="3">
         <v>46012</v>
       </c>
-      <c r="E191" s="45" t="s">
+      <c r="E191" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="F191" s="47">
+      <c r="F191" s="1">
         <v>1065007500</v>
       </c>
-      <c r="G191" s="47">
-        <v>5</v>
-      </c>
-      <c r="H191" s="47">
-        <v>4</v>
-      </c>
-      <c r="I191" s="47">
-        <v>4</v>
-      </c>
-      <c r="J191" s="47">
-        <v>4</v>
-      </c>
-      <c r="K191" s="47">
-        <v>4</v>
-      </c>
-      <c r="L191" s="47">
-        <v>5</v>
-      </c>
-      <c r="M191" s="47">
+      <c r="G191" s="1">
+        <v>5</v>
+      </c>
+      <c r="H191" s="1">
+        <v>4</v>
+      </c>
+      <c r="I191" s="1">
+        <v>4</v>
+      </c>
+      <c r="J191" s="1">
+        <v>4</v>
+      </c>
+      <c r="K191" s="1">
+        <v>4</v>
+      </c>
+      <c r="L191" s="1">
+        <v>5</v>
+      </c>
+      <c r="M191" s="1">
         <v>2</v>
       </c>
       <c r="N191" s="19">
         <f>AVERAGE('NIVEL 2'!G191:M191)</f>
         <v>4</v>
       </c>
-      <c r="O191" s="48" t="str">
-        <f>IF(N191=" "," ",IF(N191&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+      <c r="O191" s="18" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A192" s="47">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A192" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
       </c>
-      <c r="B192" s="49" t="str">
+      <c r="B192" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C192" s="49" t="str">
+      <c r="C192" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>diciembre</v>
       </c>
-      <c r="D192" s="44">
+      <c r="D192" s="3">
         <v>46012</v>
       </c>
-      <c r="E192" s="45" t="s">
+      <c r="E192" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="F192" s="47">
+      <c r="F192" s="1">
         <v>1066747786</v>
       </c>
-      <c r="G192" s="47">
-        <v>5</v>
-      </c>
-      <c r="H192" s="47">
-        <v>5</v>
-      </c>
-      <c r="I192" s="47">
-        <v>4</v>
-      </c>
-      <c r="J192" s="47">
-        <v>4</v>
-      </c>
-      <c r="K192" s="47">
-        <v>5</v>
-      </c>
-      <c r="L192" s="47">
-        <v>5</v>
-      </c>
-      <c r="M192" s="47">
+      <c r="G192" s="1">
+        <v>5</v>
+      </c>
+      <c r="H192" s="1">
+        <v>5</v>
+      </c>
+      <c r="I192" s="1">
+        <v>4</v>
+      </c>
+      <c r="J192" s="1">
+        <v>4</v>
+      </c>
+      <c r="K192" s="1">
+        <v>5</v>
+      </c>
+      <c r="L192" s="1">
+        <v>5</v>
+      </c>
+      <c r="M192" s="1">
         <v>4</v>
       </c>
       <c r="N192" s="19">
         <f>AVERAGE('NIVEL 2'!G192:M192)</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O192" s="48" t="str">
-        <f>IF(N192=" "," ",IF(N192&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+      <c r="O192" s="18" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A193" s="47">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A193" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
       </c>
-      <c r="B193" s="49" t="str">
+      <c r="B193" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C193" s="49" t="str">
+      <c r="C193" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>diciembre</v>
       </c>
-      <c r="D193" s="44">
+      <c r="D193" s="3">
         <v>46012</v>
       </c>
-      <c r="E193" s="45" t="s">
+      <c r="E193" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="F193" s="47">
+      <c r="F193" s="1">
         <v>1067936015</v>
       </c>
-      <c r="G193" s="47">
-        <v>5</v>
-      </c>
-      <c r="H193" s="47">
-        <v>5</v>
-      </c>
-      <c r="I193" s="47">
-        <v>3</v>
-      </c>
-      <c r="J193" s="47">
-        <v>4</v>
-      </c>
-      <c r="K193" s="47">
-        <v>3</v>
-      </c>
-      <c r="L193" s="47">
-        <v>4</v>
-      </c>
-      <c r="M193" s="47">
+      <c r="G193" s="1">
+        <v>5</v>
+      </c>
+      <c r="H193" s="1">
+        <v>5</v>
+      </c>
+      <c r="I193" s="1">
+        <v>3</v>
+      </c>
+      <c r="J193" s="1">
+        <v>4</v>
+      </c>
+      <c r="K193" s="1">
+        <v>3</v>
+      </c>
+      <c r="L193" s="1">
+        <v>4</v>
+      </c>
+      <c r="M193" s="1">
         <v>2</v>
       </c>
       <c r="N193" s="19">
         <f>AVERAGE('NIVEL 2'!G193:M193)</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O193" s="48" t="str">
-        <f>IF(N193=" "," ",IF(N193&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+      <c r="O193" s="18" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A194" s="47">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A194" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
       </c>
-      <c r="B194" s="49" t="str">
+      <c r="B194" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C194" s="49" t="str">
+      <c r="C194" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>diciembre</v>
       </c>
-      <c r="D194" s="44">
+      <c r="D194" s="3">
         <v>46012</v>
       </c>
-      <c r="E194" s="45" t="s">
+      <c r="E194" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="F194" s="47">
+      <c r="F194" s="1">
         <v>1067955099</v>
       </c>
-      <c r="G194" s="47">
-        <v>5</v>
-      </c>
-      <c r="H194" s="47">
-        <v>5</v>
-      </c>
-      <c r="I194" s="47">
-        <v>3</v>
-      </c>
-      <c r="J194" s="47">
-        <v>4</v>
-      </c>
-      <c r="K194" s="47">
-        <v>5</v>
-      </c>
-      <c r="L194" s="47">
-        <v>5</v>
-      </c>
-      <c r="M194" s="47">
+      <c r="G194" s="1">
+        <v>5</v>
+      </c>
+      <c r="H194" s="1">
+        <v>5</v>
+      </c>
+      <c r="I194" s="1">
+        <v>3</v>
+      </c>
+      <c r="J194" s="1">
+        <v>4</v>
+      </c>
+      <c r="K194" s="1">
+        <v>5</v>
+      </c>
+      <c r="L194" s="1">
+        <v>5</v>
+      </c>
+      <c r="M194" s="1">
         <v>3</v>
       </c>
       <c r="N194" s="19">
         <f>AVERAGE('NIVEL 2'!G194:M194)</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O194" s="48" t="str">
-        <f>IF(N194=" "," ",IF(N194&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+      <c r="O194" s="18" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A195" s="47">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A195" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
       </c>
-      <c r="B195" s="49" t="str">
+      <c r="B195" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C195" s="49" t="str">
+      <c r="C195" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>diciembre</v>
       </c>
-      <c r="D195" s="44">
+      <c r="D195" s="3">
         <v>46012</v>
       </c>
-      <c r="E195" s="45" t="s">
+      <c r="E195" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="F195" s="47">
+      <c r="F195" s="1">
         <v>1138032406</v>
       </c>
-      <c r="G195" s="47">
-        <v>5</v>
-      </c>
-      <c r="H195" s="47">
-        <v>5</v>
-      </c>
-      <c r="I195" s="47">
-        <v>4</v>
-      </c>
-      <c r="J195" s="47">
-        <v>4</v>
-      </c>
-      <c r="K195" s="47">
-        <v>4</v>
-      </c>
-      <c r="L195" s="47">
-        <v>5</v>
-      </c>
-      <c r="M195" s="47">
+      <c r="G195" s="1">
+        <v>5</v>
+      </c>
+      <c r="H195" s="1">
+        <v>5</v>
+      </c>
+      <c r="I195" s="1">
+        <v>4</v>
+      </c>
+      <c r="J195" s="1">
+        <v>4</v>
+      </c>
+      <c r="K195" s="1">
+        <v>4</v>
+      </c>
+      <c r="L195" s="1">
+        <v>5</v>
+      </c>
+      <c r="M195" s="1">
         <v>3</v>
       </c>
       <c r="N195" s="19">
         <f>AVERAGE('NIVEL 2'!G195:M195)</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O195" s="48" t="str">
-        <f>IF(N195=" "," ",IF(N195&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+      <c r="O195" s="18" t="str">
+        <f t="shared" ref="O195:O226" si="6">IF(N195=" "," ",IF(N195&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A196" s="47">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A196" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
       </c>
-      <c r="B196" s="49" t="str">
+      <c r="B196" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C196" s="49" t="str">
+      <c r="C196" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>diciembre</v>
       </c>
-      <c r="D196" s="44">
+      <c r="D196" s="3">
         <v>46012</v>
       </c>
-      <c r="E196" s="45" t="s">
+      <c r="E196" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F196" s="47">
+      <c r="F196" s="1">
         <v>1138032549</v>
       </c>
-      <c r="G196" s="47">
-        <v>5</v>
-      </c>
-      <c r="H196" s="47">
-        <v>4</v>
-      </c>
-      <c r="I196" s="47">
-        <v>3</v>
-      </c>
-      <c r="J196" s="47">
-        <v>3</v>
-      </c>
-      <c r="K196" s="47">
-        <v>5</v>
-      </c>
-      <c r="L196" s="47">
-        <v>4</v>
-      </c>
-      <c r="M196" s="47">
+      <c r="G196" s="1">
+        <v>5</v>
+      </c>
+      <c r="H196" s="1">
+        <v>4</v>
+      </c>
+      <c r="I196" s="1">
+        <v>3</v>
+      </c>
+      <c r="J196" s="1">
+        <v>3</v>
+      </c>
+      <c r="K196" s="1">
+        <v>5</v>
+      </c>
+      <c r="L196" s="1">
+        <v>4</v>
+      </c>
+      <c r="M196" s="1">
         <v>4</v>
       </c>
       <c r="N196" s="19">
         <f>AVERAGE('NIVEL 2'!G196:M196)</f>
         <v>4</v>
       </c>
-      <c r="O196" s="48" t="str">
-        <f>IF(N196=" "," ",IF(N196&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+      <c r="O196" s="18" t="str">
+        <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A197" s="47">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A197" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
       </c>
-      <c r="B197" s="49" t="str">
+      <c r="B197" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C197" s="49" t="str">
+      <c r="C197" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>diciembre</v>
       </c>
-      <c r="D197" s="44">
+      <c r="D197" s="3">
         <v>46012</v>
       </c>
-      <c r="E197" s="45" t="s">
+      <c r="E197" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="F197" s="47">
+      <c r="F197" s="1">
         <v>1140444971</v>
       </c>
-      <c r="G197" s="47">
-        <v>5</v>
-      </c>
-      <c r="H197" s="47">
-        <v>5</v>
-      </c>
-      <c r="I197" s="47">
-        <v>5</v>
-      </c>
-      <c r="J197" s="47">
-        <v>4</v>
-      </c>
-      <c r="K197" s="47">
-        <v>4</v>
-      </c>
-      <c r="L197" s="47">
-        <v>5</v>
-      </c>
-      <c r="M197" s="47">
+      <c r="G197" s="1">
+        <v>5</v>
+      </c>
+      <c r="H197" s="1">
+        <v>5</v>
+      </c>
+      <c r="I197" s="1">
+        <v>5</v>
+      </c>
+      <c r="J197" s="1">
+        <v>4</v>
+      </c>
+      <c r="K197" s="1">
+        <v>4</v>
+      </c>
+      <c r="L197" s="1">
+        <v>5</v>
+      </c>
+      <c r="M197" s="1">
         <v>3</v>
       </c>
       <c r="N197" s="19">
         <f>AVERAGE('NIVEL 2'!G197:M197)</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O197" s="48" t="str">
-        <f>IF(N197=" "," ",IF(N197&gt;=4.7,"CAMBIA A NIVEL 3"," "))</f>
+      <c r="O197" s="18" t="str">
+        <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -35055,31 +35010,31 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.33203125" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="2" customWidth="1"/>
-    <col min="7" max="7" width="7.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.86328125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.53125" style="2" customWidth="1"/>
     <col min="10" max="10" width="8.33203125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.86328125" style="2" customWidth="1"/>
     <col min="12" max="12" width="6.33203125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="7.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.53125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.86328125" style="2" customWidth="1"/>
     <col min="15" max="15" width="7.33203125" style="2" customWidth="1"/>
-    <col min="16" max="17" width="5.5546875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="6.44140625" style="2" customWidth="1"/>
+    <col min="16" max="17" width="5.53125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="6.46484375" style="2" customWidth="1"/>
     <col min="19" max="19" width="7.33203125" style="1" customWidth="1"/>
     <col min="20" max="20" width="5.6640625" customWidth="1"/>
     <col min="21" max="21" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.45">
       <c r="E1" s="28" t="s">
         <v>60</v>
       </c>
@@ -35100,7 +35055,7 @@
       <c r="R1" s="31"/>
       <c r="S1" s="31"/>
     </row>
-    <row r="2" spans="1:21" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="42" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
         <v>62</v>
       </c>
@@ -35165,7 +35120,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -35235,7 +35190,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A4" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -35305,7 +35260,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A5" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -35375,7 +35330,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A6" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -35445,7 +35400,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A7" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -35515,7 +35470,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A8" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -35585,7 +35540,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A9" s="29">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -35655,7 +35610,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A10" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -35725,7 +35680,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A11" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -35795,7 +35750,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A12" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -35865,7 +35820,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A13" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -35935,7 +35890,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A14" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -36005,7 +35960,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A15" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -36075,7 +36030,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A16" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -36145,7 +36100,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A17" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -36215,7 +36170,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A18" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -36285,7 +36240,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A19" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -36355,7 +36310,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A20" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -36425,7 +36380,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A21" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -36495,7 +36450,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A22" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -36565,7 +36520,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A23" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -36635,7 +36590,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A24" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -36705,7 +36660,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A25" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -36775,7 +36730,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A26" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -36845,7 +36800,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A27" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -36915,7 +36870,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A28" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -36985,7 +36940,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A29" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -37055,7 +37010,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A30" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -37125,7 +37080,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A31" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -37195,7 +37150,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A32" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -37265,7 +37220,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A33" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
@@ -37335,7 +37290,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A34" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -37405,7 +37360,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A35" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -37475,7 +37430,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A36" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -37545,7 +37500,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A37" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
@@ -37615,7 +37570,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A38" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -37685,7 +37640,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A39" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -37755,7 +37710,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A40" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -37825,7 +37780,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A41" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>8</v>
@@ -37895,7 +37850,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A42" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -37965,7 +37920,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A43" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -38035,7 +37990,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A44" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>9</v>
@@ -38105,72 +38060,72 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A45" s="50">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A45" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>12</v>
       </c>
-      <c r="B45" s="43" t="str">
+      <c r="B45" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C45" s="51" t="str">
+      <c r="C45" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>diciembre</v>
       </c>
-      <c r="D45" s="52">
+      <c r="D45" s="21">
         <v>46012</v>
       </c>
-      <c r="E45" s="53" t="s">
+      <c r="E45" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="F45" s="54">
+      <c r="F45" s="23">
         <v>10966252</v>
       </c>
-      <c r="G45" s="54">
-        <v>5</v>
-      </c>
-      <c r="H45" s="54">
-        <v>5</v>
-      </c>
-      <c r="I45" s="54">
-        <v>5</v>
-      </c>
-      <c r="J45" s="54">
-        <v>5</v>
-      </c>
-      <c r="K45" s="54">
-        <v>4</v>
-      </c>
-      <c r="L45" s="54">
-        <v>3</v>
-      </c>
-      <c r="M45" s="54">
-        <v>5</v>
-      </c>
-      <c r="N45" s="54">
-        <v>5</v>
-      </c>
-      <c r="O45" s="54">
-        <v>4</v>
-      </c>
-      <c r="P45" s="54">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="54">
-        <v>3</v>
-      </c>
-      <c r="R45" s="54">
-        <v>3</v>
-      </c>
-      <c r="S45" s="54">
-        <v>5</v>
-      </c>
-      <c r="T45" s="55">
+      <c r="G45" s="23">
+        <v>5</v>
+      </c>
+      <c r="H45" s="23">
+        <v>5</v>
+      </c>
+      <c r="I45" s="23">
+        <v>5</v>
+      </c>
+      <c r="J45" s="23">
+        <v>5</v>
+      </c>
+      <c r="K45" s="23">
+        <v>4</v>
+      </c>
+      <c r="L45" s="23">
+        <v>3</v>
+      </c>
+      <c r="M45" s="23">
+        <v>5</v>
+      </c>
+      <c r="N45" s="23">
+        <v>5</v>
+      </c>
+      <c r="O45" s="23">
+        <v>4</v>
+      </c>
+      <c r="P45" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="23">
+        <v>3</v>
+      </c>
+      <c r="R45" s="23">
+        <v>3</v>
+      </c>
+      <c r="S45" s="23">
+        <v>5</v>
+      </c>
+      <c r="T45" s="24">
         <f>AVERAGE('NIVEL 3'!G45:S45)</f>
         <v>4.384615384615385</v>
       </c>
-      <c r="U45" s="56" t="str">
+      <c r="U45" s="32" t="str">
         <f>IF(T45=" "," ",IF(T45&gt;=4.9,"CAMBIA A EQUIPO"," "))</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -38192,15 +38147,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:D38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5546875" customWidth="1"/>
+    <col min="3" max="3" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
@@ -38214,7 +38169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="26">
         <v>2</v>
       </c>
@@ -38228,7 +38183,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="26">
         <v>2</v>
       </c>
@@ -38242,7 +38197,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="26">
         <v>2</v>
       </c>
@@ -38256,7 +38211,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="26">
         <v>2</v>
       </c>
@@ -38270,7 +38225,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="26">
         <v>2</v>
       </c>
@@ -38284,7 +38239,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="26">
         <v>2</v>
       </c>
@@ -38298,7 +38253,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="26">
         <v>2</v>
       </c>
@@ -38312,7 +38267,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="26">
         <v>2</v>
       </c>
@@ -38326,7 +38281,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="26">
         <v>2</v>
       </c>
@@ -38340,7 +38295,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="26">
         <v>2</v>
       </c>
@@ -38354,7 +38309,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="26">
         <v>2</v>
       </c>
@@ -38368,7 +38323,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="26">
         <v>2</v>
       </c>
@@ -38382,7 +38337,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="26">
         <v>2</v>
       </c>
@@ -38396,7 +38351,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="26">
         <v>3</v>
       </c>
@@ -38410,7 +38365,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="26">
         <v>3</v>
       </c>
@@ -38424,7 +38379,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="26">
         <v>3</v>
       </c>
@@ -38438,7 +38393,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="26">
         <v>3</v>
       </c>
@@ -38452,7 +38407,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="26">
         <v>3</v>
       </c>
@@ -38466,7 +38421,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="26">
         <v>3</v>
       </c>
@@ -38480,7 +38435,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="26">
         <v>3</v>
       </c>
@@ -38494,7 +38449,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="26">
         <v>3</v>
       </c>
@@ -38508,7 +38463,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="26">
         <v>3</v>
       </c>
@@ -38522,7 +38477,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="26">
         <v>3</v>
       </c>
@@ -38536,7 +38491,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="26">
         <v>3</v>
       </c>
@@ -38550,7 +38505,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="26">
         <v>3</v>
       </c>
@@ -38564,7 +38519,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="26">
         <v>3</v>
       </c>
@@ -38578,7 +38533,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="26">
         <v>4</v>
       </c>
@@ -38592,7 +38547,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="26">
         <v>4</v>
       </c>
@@ -38606,7 +38561,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="26">
         <v>4</v>
       </c>
@@ -38620,7 +38575,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="26">
         <v>4</v>
       </c>
@@ -38634,7 +38589,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="26">
         <v>4</v>
       </c>
@@ -38648,7 +38603,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="26">
         <v>4</v>
       </c>
@@ -38662,7 +38617,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="26">
         <v>4</v>
       </c>
@@ -38676,7 +38631,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="26">
         <v>4</v>
       </c>
@@ -38690,7 +38645,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="26">
         <v>4</v>
       </c>
@@ -38704,7 +38659,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="26">
         <v>4</v>
       </c>
